--- a/data collecting.xlsx
+++ b/data collecting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phure\เอกสาร\GitHub\c-sorting-algorithm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396C7ED8-9601-4F7C-8B29-0E83B8066C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12530616-B171-411C-8F00-605F5C2C271A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
   </bookViews>
   <sheets>
     <sheet name="Random" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="27">
   <si>
     <t>Random</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>best case</t>
+  </si>
+  <si>
+    <t>Run time (ms)</t>
   </si>
 </sst>
 </file>
@@ -207,9 +210,6 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -218,20 +218,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -392,7 +395,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -412,20 +417,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="C00000"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Random!$C$32:$H$32</c:f>
@@ -460,22 +451,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.36422000000000004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>9.67014</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>36.853090000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>878.21911</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4564.8074900000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>14980.787660000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -495,7 +486,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -505,30 +498,14 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFC000"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="FFC000"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Random!$C$32:$H$32</c:f>
@@ -563,22 +540,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.50644999999999996</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>12.320329999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>47.644359999999992</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1086.7299800000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>5201.5640699999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>18064.839150000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -598,7 +575,11 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -620,22 +601,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Random!$C$32:$H$32</c:f>
@@ -670,22 +635,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.0605600000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>22.185459999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>85.587050000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>2045.66525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>11143.295770000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>62288.776029999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -705,7 +670,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -725,20 +692,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="00B0F0"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Random!$C$32:$H$32</c:f>
@@ -773,22 +726,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>5.9029999999999992E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.39964</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.0003899999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>5.46807</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>10.792719999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>31.327440000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -808,7 +761,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -830,22 +785,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent5">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Random!$C$32:$H$32</c:f>
@@ -880,22 +819,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>3.6109999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.33656999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.60311999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>3.6405899999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>7.5287499999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>21.730319999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -908,7 +847,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -1024,7 +962,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="t" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -1041,13 +979,14 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="685575535"/>
-        <c:crosses val="autoZero"/>
+        <c:crossesAt val="1.0000000000000002E-3"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10000"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="685575535"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -1129,7 +1068,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:tickLblPos val="low"/>
         <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -1171,34 +1110,14 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:legendEntry>
-        <c:idx val="5"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="6"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="7"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="8"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="9"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.92667582110746793"/>
+          <c:x val="0.90713583323604996"/>
           <c:y val="0.27791545793617906"/>
-          <c:w val="6.1926002600738737E-2"/>
-          <c:h val="0.37006837961044342"/>
+          <c:w val="8.1466054336217716E-2"/>
+          <c:h val="0.42708592347009255"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -4998,8 +4917,8 @@
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
@@ -5432,30 +5351,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17C49B7-A8B9-48AD-ACD3-ABC28260F018}">
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <f>C32</f>
         <v>1000</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <f>D32</f>
         <v>5000</v>
       </c>
@@ -5464,250 +5383,450 @@
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="C4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
       <c r="N4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N5" s="5"/>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="T5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="U5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="V5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="N6" s="3" t="s">
+      <c r="C6" s="2">
+        <v>0.49220000000000003</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.3281</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.32769999999999999</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.32719999999999999</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.32729999999999998</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.32769999999999999</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.3569</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0.33650000000000002</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0.49059999999999998</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
+      <c r="O6" s="2">
+        <v>9.8430999999999997</v>
+      </c>
+      <c r="P6" s="2">
+        <v>9.5047999999999995</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>9.3214000000000006</v>
+      </c>
+      <c r="R6" s="2">
+        <v>10.443</v>
+      </c>
+      <c r="S6" s="2">
+        <v>9.7606000000000002</v>
+      </c>
+      <c r="T6" s="2">
+        <v>9.3657000000000004</v>
+      </c>
+      <c r="U6" s="2">
+        <v>9.4465000000000003</v>
+      </c>
+      <c r="V6" s="2">
+        <v>9.8112999999999992</v>
+      </c>
+      <c r="W6" s="2">
+        <v>9.6693999999999996</v>
+      </c>
+      <c r="X6" s="2">
+        <v>9.5356000000000005</v>
+      </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="N7" s="3" t="s">
+      <c r="C7" s="2">
+        <v>0.67190000000000005</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.47110000000000002</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.44550000000000001</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.46579999999999999</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.44769999999999999</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.47170000000000001</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.59719999999999995</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.44180000000000003</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.43940000000000001</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0.61240000000000006</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
+      <c r="O7" s="2">
+        <v>12.0886</v>
+      </c>
+      <c r="P7" s="2">
+        <v>12.699199999999999</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>12.6198</v>
+      </c>
+      <c r="R7" s="2">
+        <v>12.742699999999999</v>
+      </c>
+      <c r="S7" s="2">
+        <v>12.448600000000001</v>
+      </c>
+      <c r="T7" s="2">
+        <v>12.148999999999999</v>
+      </c>
+      <c r="U7" s="2">
+        <v>11.754899999999999</v>
+      </c>
+      <c r="V7" s="2">
+        <v>12.508599999999999</v>
+      </c>
+      <c r="W7" s="2">
+        <v>12.1633</v>
+      </c>
+      <c r="X7" s="2">
+        <v>12.028600000000001</v>
+      </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="N8" s="3" t="s">
+      <c r="C8" s="2">
+        <v>2.6061000000000001</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1.2116</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.84740000000000004</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.87450000000000006</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.83779999999999999</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.84450000000000003</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.86209999999999998</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.83120000000000005</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0.86050000000000004</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0.82989999999999997</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
+      <c r="O8" s="2">
+        <v>22.090199999999999</v>
+      </c>
+      <c r="P8" s="2">
+        <v>23.225899999999999</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>22.233599999999999</v>
+      </c>
+      <c r="R8" s="2">
+        <v>22.464099999999998</v>
+      </c>
+      <c r="S8" s="2">
+        <v>21.996700000000001</v>
+      </c>
+      <c r="T8" s="2">
+        <v>21.8385</v>
+      </c>
+      <c r="U8" s="2">
+        <v>22.031199999999998</v>
+      </c>
+      <c r="V8" s="2">
+        <v>22.5487</v>
+      </c>
+      <c r="W8" s="2">
+        <v>21.6465</v>
+      </c>
+      <c r="X8" s="2">
+        <v>21.779199999999999</v>
+      </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="N9" s="3" t="s">
+      <c r="C9" s="2">
+        <v>6.6199999999999995E-2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4.9700000000000001E-2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4.2299999999999997E-2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>6.5600000000000006E-2</v>
+      </c>
+      <c r="H9" s="2">
+        <v>8.72E-2</v>
+      </c>
+      <c r="I9" s="2">
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="J9" s="2">
+        <v>4.0099999999999997E-2</v>
+      </c>
+      <c r="K9" s="2">
+        <v>4.82E-2</v>
+      </c>
+      <c r="L9" s="2">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="O9" s="2">
+        <v>0.55549999999999999</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.39140000000000003</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0.36609999999999998</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0.60389999999999999</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0.3453</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0.34960000000000002</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0.34089999999999998</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0.3377</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="N10" s="3" t="s">
+      <c r="C10" s="2">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>6.08E-2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4.99E-2</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3.32E-2</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="L10" s="2">
+        <v>2.52E-2</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="O10" s="2">
+        <v>0.27289999999999998</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.25430000000000003</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.40039999999999998</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.30359999999999998</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0.23669999999999999</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.2382</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0.3997</v>
+      </c>
+      <c r="V10" s="2">
+        <v>0.50309999999999999</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0.35680000000000001</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <f>E32</f>
         <v>10000</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="1">
         <f>F32</f>
         <v>50000</v>
       </c>
@@ -5716,250 +5835,450 @@
       <c r="B13" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
       <c r="N13" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="O13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N14" s="5"/>
-      <c r="O14" s="4" t="s">
+      <c r="O14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="4" t="s">
+      <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="4" t="s">
+      <c r="S14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T14" s="4" t="s">
+      <c r="T14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U14" s="4" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="4" t="s">
+      <c r="V14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W14" s="4" t="s">
+      <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="4" t="s">
+      <c r="X14" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="N15" s="3" t="s">
+      <c r="C15" s="2">
+        <v>39.850200000000001</v>
+      </c>
+      <c r="D15" s="2">
+        <v>35.699399999999997</v>
+      </c>
+      <c r="E15" s="2">
+        <v>36.984299999999998</v>
+      </c>
+      <c r="F15" s="2">
+        <v>36.067700000000002</v>
+      </c>
+      <c r="G15" s="2">
+        <v>39.254399999999997</v>
+      </c>
+      <c r="H15" s="2">
+        <v>36.649000000000001</v>
+      </c>
+      <c r="I15" s="2">
+        <v>36.569699999999997</v>
+      </c>
+      <c r="J15" s="2">
+        <v>35.6113</v>
+      </c>
+      <c r="K15" s="2">
+        <v>36.170099999999998</v>
+      </c>
+      <c r="L15" s="2">
+        <v>35.674799999999998</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
+      <c r="O15" s="2">
+        <v>907.29769999999996</v>
+      </c>
+      <c r="P15" s="2">
+        <v>872.34969999999998</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>863.6902</v>
+      </c>
+      <c r="R15" s="2">
+        <v>886.30849999999998</v>
+      </c>
+      <c r="S15" s="2">
+        <v>862.26350000000002</v>
+      </c>
+      <c r="T15" s="2">
+        <v>886.16380000000004</v>
+      </c>
+      <c r="U15" s="2">
+        <v>895.82</v>
+      </c>
+      <c r="V15" s="2">
+        <v>862.97190000000001</v>
+      </c>
+      <c r="W15" s="2">
+        <v>875.82529999999997</v>
+      </c>
+      <c r="X15" s="2">
+        <v>869.50049999999999</v>
+      </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="N16" s="3" t="s">
+      <c r="C16" s="2">
+        <v>46.165799999999997</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46.381</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45.488900000000001</v>
+      </c>
+      <c r="F16" s="2">
+        <v>45.981999999999999</v>
+      </c>
+      <c r="G16" s="2">
+        <v>57.173400000000001</v>
+      </c>
+      <c r="H16" s="2">
+        <v>47.706299999999999</v>
+      </c>
+      <c r="I16" s="2">
+        <v>47.266500000000001</v>
+      </c>
+      <c r="J16" s="2">
+        <v>47.130099999999999</v>
+      </c>
+      <c r="K16" s="2">
+        <v>46.887999999999998</v>
+      </c>
+      <c r="L16" s="2">
+        <v>46.261600000000001</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
+      <c r="O16" s="2">
+        <v>1080.6143999999999</v>
+      </c>
+      <c r="P16" s="2">
+        <v>1090.5824</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>1086.7518</v>
+      </c>
+      <c r="R16" s="2">
+        <v>1095.5998</v>
+      </c>
+      <c r="S16" s="2">
+        <v>1080.2744</v>
+      </c>
+      <c r="T16" s="2">
+        <v>1088.3126</v>
+      </c>
+      <c r="U16" s="2">
+        <v>1082.2109</v>
+      </c>
+      <c r="V16" s="2">
+        <v>1082.1899000000001</v>
+      </c>
+      <c r="W16" s="2">
+        <v>1087.5120999999999</v>
+      </c>
+      <c r="X16" s="2">
+        <v>1093.2515000000001</v>
+      </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="N17" s="3" t="s">
+      <c r="C17" s="2">
+        <v>83.672300000000007</v>
+      </c>
+      <c r="D17" s="2">
+        <v>85.691999999999993</v>
+      </c>
+      <c r="E17" s="2">
+        <v>86.024100000000004</v>
+      </c>
+      <c r="F17" s="2">
+        <v>86.278599999999997</v>
+      </c>
+      <c r="G17" s="2">
+        <v>85.533799999999999</v>
+      </c>
+      <c r="H17" s="2">
+        <v>86.352099999999993</v>
+      </c>
+      <c r="I17" s="2">
+        <v>85.687399999999997</v>
+      </c>
+      <c r="J17" s="2">
+        <v>85.438500000000005</v>
+      </c>
+      <c r="K17" s="2">
+        <v>84.899299999999997</v>
+      </c>
+      <c r="L17" s="2">
+        <v>86.292400000000001</v>
+      </c>
+      <c r="N17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
+      <c r="O17" s="2">
+        <v>2037.4096999999999</v>
+      </c>
+      <c r="P17" s="2">
+        <v>2059.0681</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>2046.8549</v>
+      </c>
+      <c r="R17" s="2">
+        <v>2037.3724</v>
+      </c>
+      <c r="S17" s="2">
+        <v>2052.6233999999999</v>
+      </c>
+      <c r="T17" s="2">
+        <v>2033.9108000000001</v>
+      </c>
+      <c r="U17" s="2">
+        <v>2052.6875</v>
+      </c>
+      <c r="V17" s="2">
+        <v>2040.3588999999999</v>
+      </c>
+      <c r="W17" s="2">
+        <v>2054.3508000000002</v>
+      </c>
+      <c r="X17" s="2">
+        <v>2042.0160000000001</v>
+      </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="N18" s="3" t="s">
+      <c r="C18" s="2">
+        <v>1.1992</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1.1561999999999999</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.79249999999999998</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.79579999999999995</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.79169999999999996</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.8004</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1.2157</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1.6266</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0.82840000000000003</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0.7974</v>
+      </c>
+      <c r="N18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
+      <c r="O18" s="2">
+        <v>5.2521000000000004</v>
+      </c>
+      <c r="P18" s="2">
+        <v>6.6478999999999999</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>5.1619999999999999</v>
+      </c>
+      <c r="R18" s="2">
+        <v>5.4260999999999999</v>
+      </c>
+      <c r="S18" s="2">
+        <v>6.1036999999999999</v>
+      </c>
+      <c r="T18" s="2">
+        <v>5.1371000000000002</v>
+      </c>
+      <c r="U18" s="2">
+        <v>4.9196</v>
+      </c>
+      <c r="V18" s="2">
+        <v>5.3000999999999996</v>
+      </c>
+      <c r="W18" s="2">
+        <v>5.0316000000000001</v>
+      </c>
+      <c r="X18" s="2">
+        <v>5.7004999999999999</v>
+      </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="N19" s="3" t="s">
+      <c r="C19" s="2">
+        <v>0.82210000000000005</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.64529999999999998</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.54420000000000002</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.52449999999999997</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.58650000000000002</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0.54449999999999998</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.54730000000000001</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.54630000000000001</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.7097</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0.56079999999999997</v>
+      </c>
+      <c r="N19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
+      <c r="O19" s="2">
+        <v>3.7528999999999999</v>
+      </c>
+      <c r="P19" s="2">
+        <v>3.2654999999999998</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>3.2263000000000002</v>
+      </c>
+      <c r="R19" s="2">
+        <v>3.7812999999999999</v>
+      </c>
+      <c r="S19" s="2">
+        <v>3.9308999999999998</v>
+      </c>
+      <c r="T19" s="2">
+        <v>3.9136000000000002</v>
+      </c>
+      <c r="U19" s="2">
+        <v>3.6465999999999998</v>
+      </c>
+      <c r="V19" s="2">
+        <v>4.2107999999999999</v>
+      </c>
+      <c r="W19" s="2">
+        <v>3.1949999999999998</v>
+      </c>
+      <c r="X19" s="2">
+        <v>3.4830000000000001</v>
+      </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <f>G32</f>
         <v>100000</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="N21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="1">
         <f>H32</f>
         <v>200000</v>
       </c>
@@ -5968,237 +6287,437 @@
       <c r="B22" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
       <c r="N22" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O22" s="7" t="s">
+      <c r="O22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N23" s="5"/>
-      <c r="O23" s="4" t="s">
+      <c r="O23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="4" t="s">
+      <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R23" s="4" t="s">
+      <c r="R23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="4" t="s">
+      <c r="S23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T23" s="4" t="s">
+      <c r="T23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U23" s="4" t="s">
+      <c r="U23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V23" s="4" t="s">
+      <c r="V23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W23" s="4" t="s">
+      <c r="W23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X23" s="4" t="s">
+      <c r="X23" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="N24" s="3" t="s">
+      <c r="C24" s="2">
+        <v>3639.0625</v>
+      </c>
+      <c r="D24" s="2">
+        <v>4663.7277999999997</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4217.8086000000003</v>
+      </c>
+      <c r="F24" s="2">
+        <v>4529.3531999999996</v>
+      </c>
+      <c r="G24" s="2">
+        <v>5172.2043000000003</v>
+      </c>
+      <c r="H24" s="2">
+        <v>4682.2672000000002</v>
+      </c>
+      <c r="I24" s="2">
+        <v>3684.5401999999999</v>
+      </c>
+      <c r="J24" s="2">
+        <v>4793.0232999999998</v>
+      </c>
+      <c r="K24" s="2">
+        <v>5145.2339000000002</v>
+      </c>
+      <c r="L24" s="2">
+        <v>5120.8539000000001</v>
+      </c>
+      <c r="N24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
+      <c r="O24" s="2">
+        <v>14922.466700000001</v>
+      </c>
+      <c r="P24" s="2">
+        <v>14424.4951</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>14419.5146</v>
+      </c>
+      <c r="R24" s="2">
+        <v>14420.635399999999</v>
+      </c>
+      <c r="S24" s="2">
+        <v>14398.777599999999</v>
+      </c>
+      <c r="T24" s="2">
+        <v>14402.429099999999</v>
+      </c>
+      <c r="U24" s="2">
+        <v>15088.7973</v>
+      </c>
+      <c r="V24" s="2">
+        <v>15723.8837</v>
+      </c>
+      <c r="W24" s="2">
+        <v>17623.284500000002</v>
+      </c>
+      <c r="X24" s="2">
+        <v>14383.5926</v>
+      </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="N25" s="3" t="s">
+      <c r="C25" s="2">
+        <v>6112.6725999999999</v>
+      </c>
+      <c r="D25" s="2">
+        <v>4725.6668</v>
+      </c>
+      <c r="E25" s="2">
+        <v>7209.2083000000002</v>
+      </c>
+      <c r="F25" s="2">
+        <v>6174.0099</v>
+      </c>
+      <c r="G25" s="2">
+        <v>4591.0883999999996</v>
+      </c>
+      <c r="H25" s="2">
+        <v>5036.2704000000003</v>
+      </c>
+      <c r="I25" s="2">
+        <v>4551.6623</v>
+      </c>
+      <c r="J25" s="2">
+        <v>4553.7164000000002</v>
+      </c>
+      <c r="K25" s="2">
+        <v>4531.9417000000003</v>
+      </c>
+      <c r="L25" s="2">
+        <v>4529.4039000000002</v>
+      </c>
+      <c r="N25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="O25" s="2">
+        <v>18053.092799999999</v>
+      </c>
+      <c r="P25" s="2">
+        <v>18099.409500000002</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>18046.831999999999</v>
+      </c>
+      <c r="R25" s="2">
+        <v>18042.3773</v>
+      </c>
+      <c r="S25" s="2">
+        <v>18036.889200000001</v>
+      </c>
+      <c r="T25" s="2">
+        <v>18066.208600000002</v>
+      </c>
+      <c r="U25" s="2">
+        <v>18075.027300000002</v>
+      </c>
+      <c r="V25" s="2">
+        <v>18068.5854</v>
+      </c>
+      <c r="W25" s="2">
+        <v>18121.3017</v>
+      </c>
+      <c r="X25" s="2">
+        <v>18038.667700000002</v>
+      </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="N26" s="3" t="s">
+      <c r="C26" s="2">
+        <v>10801.258900000001</v>
+      </c>
+      <c r="D26" s="2">
+        <v>10787.6518</v>
+      </c>
+      <c r="E26" s="2">
+        <v>10788.3876</v>
+      </c>
+      <c r="F26" s="2">
+        <v>11740.090899999999</v>
+      </c>
+      <c r="G26" s="2">
+        <v>12131.1373</v>
+      </c>
+      <c r="H26" s="2">
+        <v>10784.3791</v>
+      </c>
+      <c r="I26" s="2">
+        <v>10790.551100000001</v>
+      </c>
+      <c r="J26" s="2">
+        <v>11987.6605</v>
+      </c>
+      <c r="K26" s="2">
+        <v>10823.2502</v>
+      </c>
+      <c r="L26" s="2">
+        <v>10798.5903</v>
+      </c>
+      <c r="N26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
+      <c r="O26" s="2">
+        <v>58828.880599999997</v>
+      </c>
+      <c r="P26" s="2">
+        <v>59469.7474</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>59408.783000000003</v>
+      </c>
+      <c r="R26" s="2">
+        <v>59343.2042</v>
+      </c>
+      <c r="S26" s="2">
+        <v>59458.036899999999</v>
+      </c>
+      <c r="T26" s="2">
+        <v>60005.881800000003</v>
+      </c>
+      <c r="U26" s="2">
+        <v>59590.5</v>
+      </c>
+      <c r="V26" s="2">
+        <v>59339.46</v>
+      </c>
+      <c r="W26" s="2">
+        <v>64528.608</v>
+      </c>
+      <c r="X26" s="2">
+        <v>82914.6584</v>
+      </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="N27" s="3" t="s">
+      <c r="C27" s="2">
+        <v>10.477399999999999</v>
+      </c>
+      <c r="D27" s="2">
+        <v>10.584</v>
+      </c>
+      <c r="E27" s="2">
+        <v>11.0541</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10.1211</v>
+      </c>
+      <c r="G27" s="2">
+        <v>11.2773</v>
+      </c>
+      <c r="H27" s="2">
+        <v>11.317</v>
+      </c>
+      <c r="I27" s="2">
+        <v>11.112</v>
+      </c>
+      <c r="J27" s="2">
+        <v>10.5113</v>
+      </c>
+      <c r="K27" s="2">
+        <v>11.3485</v>
+      </c>
+      <c r="L27" s="2">
+        <v>10.124499999999999</v>
+      </c>
+      <c r="N27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
+      <c r="O27" s="2">
+        <v>32.117600000000003</v>
+      </c>
+      <c r="P27" s="2">
+        <v>30.944299999999998</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>32.287700000000001</v>
+      </c>
+      <c r="R27" s="2">
+        <v>30.9467</v>
+      </c>
+      <c r="S27" s="2">
+        <v>31.452500000000001</v>
+      </c>
+      <c r="T27" s="2">
+        <v>31.1341</v>
+      </c>
+      <c r="U27" s="2">
+        <v>31.2576</v>
+      </c>
+      <c r="V27" s="2">
+        <v>30.600999999999999</v>
+      </c>
+      <c r="W27" s="2">
+        <v>31.155000000000001</v>
+      </c>
+      <c r="X27" s="2">
+        <v>31.3779</v>
+      </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="N28" s="3" t="s">
+      <c r="C28" s="2">
+        <v>7.1571999999999996</v>
+      </c>
+      <c r="D28" s="2">
+        <v>7.8764000000000003</v>
+      </c>
+      <c r="E28" s="2">
+        <v>7.5198</v>
+      </c>
+      <c r="F28" s="2">
+        <v>7.4926000000000004</v>
+      </c>
+      <c r="G28" s="2">
+        <v>7.5778999999999996</v>
+      </c>
+      <c r="H28" s="2">
+        <v>7.8731999999999998</v>
+      </c>
+      <c r="I28" s="2">
+        <v>7.4576000000000002</v>
+      </c>
+      <c r="J28" s="2">
+        <v>7.3963000000000001</v>
+      </c>
+      <c r="K28" s="2">
+        <v>7.3672000000000004</v>
+      </c>
+      <c r="L28" s="2">
+        <v>7.5693000000000001</v>
+      </c>
+      <c r="N28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
+      <c r="O28" s="2">
+        <v>20.759499999999999</v>
+      </c>
+      <c r="P28" s="2">
+        <v>21.5764</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>21.446100000000001</v>
+      </c>
+      <c r="R28" s="2">
+        <v>21.149899999999999</v>
+      </c>
+      <c r="S28" s="2">
+        <v>21.637899999999998</v>
+      </c>
+      <c r="T28" s="2">
+        <v>20.783300000000001</v>
+      </c>
+      <c r="U28" s="2">
+        <v>21.5518</v>
+      </c>
+      <c r="V28" s="2">
+        <v>21.621400000000001</v>
+      </c>
+      <c r="W28" s="2">
+        <v>21.145199999999999</v>
+      </c>
+      <c r="X28" s="2">
+        <v>25.631699999999999</v>
+      </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
@@ -6212,175 +6731,218 @@
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
+      <c r="J31" s="1">
+        <v>20.759499999999999</v>
+      </c>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
-      <c r="C32" s="3">
+      <c r="C32" s="2">
         <v>1000</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="2">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="2">
         <v>10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>50000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="2">
         <v>100000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="2">
         <v>200000</v>
       </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
+      <c r="J32" s="1">
+        <v>21.5764</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="3" t="str">
+      <c r="C33" s="2">
         <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
-        <v>undone</v>
-      </c>
-      <c r="D33" s="3" t="str">
+        <v>0.36422000000000004</v>
+      </c>
+      <c r="D33" s="2">
         <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
-        <v>undone</v>
-      </c>
-      <c r="E33" s="3" t="str">
+        <v>9.67014</v>
+      </c>
+      <c r="E33" s="2">
         <f>IF(COUNTBLANK(C15:L15)&gt;0,"undone",AVERAGE(C15:L15))</f>
-        <v>undone</v>
-      </c>
-      <c r="F33" s="3" t="str">
+        <v>36.853090000000002</v>
+      </c>
+      <c r="F33" s="2">
         <f>IF(COUNTBLANK(O15:X15)&gt;0,"undone",AVERAGE(O15:X15))</f>
-        <v>undone</v>
-      </c>
-      <c r="G33" s="3" t="str">
+        <v>878.21911</v>
+      </c>
+      <c r="G33" s="2">
         <f>IF(COUNTBLANK(C24:L24)&gt;0,"undone",AVERAGE(C24:L24))</f>
-        <v>undone</v>
-      </c>
-      <c r="H33" s="3" t="str">
+        <v>4564.8074900000001</v>
+      </c>
+      <c r="H33" s="2">
         <f>IF(COUNTBLANK(O24:X24)&gt;0,"undone",AVERAGE(O24:X24))</f>
-        <v>undone</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
+        <v>14980.787660000002</v>
+      </c>
+      <c r="J33" s="1">
+        <v>21.446100000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="3" t="str">
-        <f t="shared" ref="C34:C37" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
-        <v>undone</v>
-      </c>
-      <c r="D34" s="3" t="str">
-        <f t="shared" ref="D34:D37" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
-        <v>undone</v>
-      </c>
-      <c r="E34" s="3" t="str">
-        <f t="shared" ref="E34:E37" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
-        <v>undone</v>
-      </c>
-      <c r="F34" s="3" t="str">
-        <f t="shared" ref="F34:F37" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
-        <v>undone</v>
-      </c>
-      <c r="G34" s="3" t="str">
-        <f t="shared" ref="G34:G37" si="4">IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
-        <v>undone</v>
-      </c>
-      <c r="H34" s="3" t="str">
+      <c r="C34" s="2">
+        <f>IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
+        <v>0.50644999999999996</v>
+      </c>
+      <c r="D34" s="2">
+        <f>IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
+        <v>12.320329999999997</v>
+      </c>
+      <c r="E34" s="2">
+        <f>IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
+        <v>47.644359999999992</v>
+      </c>
+      <c r="F34" s="2">
+        <f>IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
+        <v>1086.7299800000001</v>
+      </c>
+      <c r="G34" s="2">
+        <f>IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
+        <v>5201.5640699999994</v>
+      </c>
+      <c r="H34" s="2">
         <f>IF(COUNTBLANK(O25:X25)&gt;0,"undone",AVERAGE(O25:X25))</f>
-        <v>undone</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
+        <v>18064.839150000003</v>
+      </c>
+      <c r="J34" s="1">
+        <v>21.149899999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D35" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E35" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F35" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G35" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H35" s="3" t="str">
-        <f t="shared" ref="H34:H37" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",AVERAGE(O26:X26))</f>
-        <v>undone</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
+      <c r="C35" s="2">
+        <f>IF(COUNTBLANK(C8:L8)&gt;0,"undone",AVERAGE(C8:L8))</f>
+        <v>1.0605600000000002</v>
+      </c>
+      <c r="D35" s="2">
+        <f>IF(COUNTBLANK(O8:X8)&gt;0,"undone",AVERAGE(O8:X8))</f>
+        <v>22.185459999999999</v>
+      </c>
+      <c r="E35" s="2">
+        <f>IF(COUNTBLANK(C17:L17)&gt;0,"undone",AVERAGE(C17:L17))</f>
+        <v>85.587050000000005</v>
+      </c>
+      <c r="F35" s="2">
+        <f>IF(COUNTBLANK(O17:X17)&gt;0,"undone",AVERAGE(O17:X17))</f>
+        <v>2045.66525</v>
+      </c>
+      <c r="G35" s="2">
+        <f>IF(COUNTBLANK(C26:L26)&gt;0,"undone",AVERAGE(C26:L26))</f>
+        <v>11143.295770000001</v>
+      </c>
+      <c r="H35" s="2">
+        <f>IF(COUNTBLANK(O26:X26)&gt;0,"undone",AVERAGE(O26:X26))</f>
+        <v>62288.776029999994</v>
+      </c>
+      <c r="J35" s="1">
+        <v>21.637899999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D36" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E36" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F36" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G36" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H36" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>undone</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
+      <c r="C36" s="2">
+        <f>IF(COUNTBLANK(C9:L9)&gt;0,"undone",AVERAGE(C9:L9))</f>
+        <v>5.9029999999999992E-2</v>
+      </c>
+      <c r="D36" s="2">
+        <f>IF(COUNTBLANK(O9:X9)&gt;0,"undone",AVERAGE(O9:X9))</f>
+        <v>0.39964</v>
+      </c>
+      <c r="E36" s="2">
+        <f>IF(COUNTBLANK(C18:L18)&gt;0,"undone",AVERAGE(C18:L18))</f>
+        <v>1.0003899999999999</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(COUNTBLANK(O18:X18)&gt;0,"undone",AVERAGE(O18:X18))</f>
+        <v>5.46807</v>
+      </c>
+      <c r="G36" s="2">
+        <f>IF(COUNTBLANK(C27:L27)&gt;0,"undone",AVERAGE(C27:L27))</f>
+        <v>10.792719999999999</v>
+      </c>
+      <c r="H36" s="2">
+        <f>IF(COUNTBLANK(O27:X27)&gt;0,"undone",AVERAGE(O27:X27))</f>
+        <v>31.327440000000003</v>
+      </c>
+      <c r="J36" s="1">
+        <v>20.783300000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D37" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E37" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F37" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G37" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H37" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>undone</v>
+      <c r="C37" s="2">
+        <f>IF(COUNTBLANK(C10:L10)&gt;0,"undone",AVERAGE(C10:L10))</f>
+        <v>3.6109999999999996E-2</v>
+      </c>
+      <c r="D37" s="2">
+        <f>IF(COUNTBLANK(O10:X10)&gt;0,"undone",AVERAGE(O10:X10))</f>
+        <v>0.33656999999999998</v>
+      </c>
+      <c r="E37" s="2">
+        <f>IF(COUNTBLANK(C19:L19)&gt;0,"undone",AVERAGE(C19:L19))</f>
+        <v>0.60311999999999999</v>
+      </c>
+      <c r="F37" s="2">
+        <f>IF(COUNTBLANK(O19:X19)&gt;0,"undone",AVERAGE(O19:X19))</f>
+        <v>3.6405899999999995</v>
+      </c>
+      <c r="G37" s="2">
+        <f>IF(COUNTBLANK(C28:L28)&gt;0,"undone",AVERAGE(C28:L28))</f>
+        <v>7.5287499999999996</v>
+      </c>
+      <c r="H37" s="2">
+        <f>IF(COUNTBLANK(O28:X28)&gt;0,"undone",AVERAGE(O28:X28))</f>
+        <v>21.730319999999999</v>
+      </c>
+      <c r="J37" s="1">
+        <v>21.5518</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J38" s="1">
+        <v>21.621400000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J39" s="1">
+        <v>21.145199999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J40" s="1">
+        <v>25.631699999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:X4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C31:H31"/>
     <mergeCell ref="N22:N23"/>
     <mergeCell ref="O22:X22"/>
     <mergeCell ref="B13:B14"/>
@@ -6389,13 +6951,6 @@
     <mergeCell ref="O13:X13"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="C22:L22"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:X4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6408,10 +6963,10 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="17" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N17" t="s">
@@ -6432,27 +6987,27 @@
   <dimension ref="A1:X37"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <f>C32</f>
         <v>1000</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <f>D32</f>
         <v>5000</v>
       </c>
@@ -6461,250 +7016,250 @@
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
       <c r="N4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N5" s="5"/>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="T5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="U5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="V5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="N6" s="3" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="N6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="N7" s="3" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="N8" s="3" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="N8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="N9" s="3" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="N9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="N10" s="3" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="N10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <f>E32</f>
         <v>10000</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="1">
         <f>F32</f>
         <v>50000</v>
       </c>
@@ -6713,250 +7268,250 @@
       <c r="B13" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
       <c r="N13" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="O13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N14" s="5"/>
-      <c r="O14" s="4" t="s">
+      <c r="O14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="4" t="s">
+      <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="4" t="s">
+      <c r="S14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T14" s="4" t="s">
+      <c r="T14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U14" s="4" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="4" t="s">
+      <c r="V14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W14" s="4" t="s">
+      <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="4" t="s">
+      <c r="X14" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="N15" s="3" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="N15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="N16" s="3" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="N16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="N17" s="3" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="N17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="N18" s="3" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="N18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="N19" s="3" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="N19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <f>G32</f>
         <v>100000</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="N21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="1">
         <f>H32</f>
         <v>200000</v>
       </c>
@@ -6965,237 +7520,237 @@
       <c r="B22" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
       <c r="N22" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O22" s="7" t="s">
+      <c r="O22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N23" s="5"/>
-      <c r="O23" s="4" t="s">
+      <c r="O23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="4" t="s">
+      <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R23" s="4" t="s">
+      <c r="R23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="4" t="s">
+      <c r="S23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T23" s="4" t="s">
+      <c r="T23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U23" s="4" t="s">
+      <c r="U23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V23" s="4" t="s">
+      <c r="V23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W23" s="4" t="s">
+      <c r="W23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X23" s="4" t="s">
+      <c r="X23" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="N24" s="3" t="s">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="N24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="N25" s="3" t="s">
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="N25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="N26" s="3" t="s">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="N26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="N27" s="3" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="N27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="N28" s="3" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="N28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
@@ -7212,187 +7767,187 @@
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
-      <c r="C32" s="3">
+      <c r="C32" s="2">
         <v>1000</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="2">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="2">
         <v>10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>50000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="2">
         <v>100000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="2">
         <v>200000</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="3" t="str">
+      <c r="C33" s="2" t="str">
         <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
         <v>undone</v>
       </c>
-      <c r="D33" s="3" t="str">
+      <c r="D33" s="2" t="str">
         <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
         <v>undone</v>
       </c>
-      <c r="E33" s="3" t="str">
+      <c r="E33" s="2" t="str">
         <f>IF(COUNTBLANK(C15:L15)&gt;0,"undone",AVERAGE(C15:L15))</f>
         <v>undone</v>
       </c>
-      <c r="F33" s="3" t="str">
+      <c r="F33" s="2" t="str">
         <f>IF(COUNTBLANK(O15:X15)&gt;0,"undone",AVERAGE(O15:X15))</f>
         <v>undone</v>
       </c>
-      <c r="G33" s="3" t="str">
+      <c r="G33" s="2" t="str">
         <f>IF(COUNTBLANK(C24:L24)&gt;0,"undone",AVERAGE(C24:L24))</f>
         <v>undone</v>
       </c>
-      <c r="H33" s="3" t="str">
+      <c r="H33" s="2" t="str">
         <f>IF(COUNTBLANK(O24:X24)&gt;0,"undone",AVERAGE(O24:X24))</f>
         <v>undone</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="3" t="str">
+      <c r="C34" s="2" t="str">
         <f t="shared" ref="C34:C37" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
         <v>undone</v>
       </c>
-      <c r="D34" s="3" t="str">
+      <c r="D34" s="2" t="str">
         <f t="shared" ref="D34:D37" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
         <v>undone</v>
       </c>
-      <c r="E34" s="3" t="str">
+      <c r="E34" s="2" t="str">
         <f t="shared" ref="E34:E37" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
         <v>undone</v>
       </c>
-      <c r="F34" s="3" t="str">
+      <c r="F34" s="2" t="str">
         <f t="shared" ref="F34:F37" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
         <v>undone</v>
       </c>
-      <c r="G34" s="3" t="str">
+      <c r="G34" s="2" t="str">
         <f t="shared" ref="G34:G37" si="4">IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
         <v>undone</v>
       </c>
-      <c r="H34" s="3" t="str">
+      <c r="H34" s="2" t="str">
         <f t="shared" ref="H34:H37" si="5">IF(COUNTBLANK(O25:X25)&gt;0,"undone",AVERAGE(O25:X25))</f>
         <v>undone</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="3" t="str">
+      <c r="C35" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D35" s="3" t="str">
+      <c r="D35" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E35" s="3" t="str">
+      <c r="E35" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F35" s="3" t="str">
+      <c r="F35" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G35" s="3" t="str">
+      <c r="G35" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H35" s="3" t="str">
+      <c r="H35" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="3" t="str">
+      <c r="C36" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D36" s="3" t="str">
+      <c r="D36" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E36" s="3" t="str">
+      <c r="E36" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F36" s="3" t="str">
+      <c r="F36" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G36" s="3" t="str">
+      <c r="G36" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H36" s="3" t="str">
+      <c r="H36" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="3" t="str">
+      <c r="C37" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D37" s="3" t="str">
+      <c r="D37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E37" s="3" t="str">
+      <c r="E37" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F37" s="3" t="str">
+      <c r="F37" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G37" s="3" t="str">
+      <c r="G37" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H37" s="3" t="str">
+      <c r="H37" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:X13"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:X4"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="N22:N23"/>
     <mergeCell ref="O22:X22"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="C31:H31"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:X4"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:X13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7404,10 +7959,10 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="17" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N17" t="s">
@@ -7428,27 +7983,27 @@
   <dimension ref="A1:X37"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <f>C32</f>
         <v>1000</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <f>D32</f>
         <v>5000</v>
       </c>
@@ -7457,250 +8012,250 @@
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
       <c r="N4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N5" s="5"/>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="T5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="U5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="V5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="N6" s="3" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="N6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="N7" s="3" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="N8" s="3" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="N8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="N9" s="3" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="N9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="N10" s="3" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="N10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <f>E32</f>
         <v>10000</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="1">
         <f>F32</f>
         <v>50000</v>
       </c>
@@ -7709,250 +8264,250 @@
       <c r="B13" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
       <c r="N13" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="O13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N14" s="5"/>
-      <c r="O14" s="4" t="s">
+      <c r="O14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="4" t="s">
+      <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="4" t="s">
+      <c r="S14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T14" s="4" t="s">
+      <c r="T14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U14" s="4" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="4" t="s">
+      <c r="V14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W14" s="4" t="s">
+      <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="4" t="s">
+      <c r="X14" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="N15" s="3" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="N15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="N16" s="3" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="N16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="N17" s="3" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="N17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="N18" s="3" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="N18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="N19" s="3" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="N19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <f>G32</f>
         <v>100000</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="N21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="1">
         <f>H32</f>
         <v>200000</v>
       </c>
@@ -7961,237 +8516,237 @@
       <c r="B22" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
       <c r="N22" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O22" s="7" t="s">
+      <c r="O22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N23" s="5"/>
-      <c r="O23" s="4" t="s">
+      <c r="O23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="4" t="s">
+      <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R23" s="4" t="s">
+      <c r="R23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="4" t="s">
+      <c r="S23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T23" s="4" t="s">
+      <c r="T23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U23" s="4" t="s">
+      <c r="U23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V23" s="4" t="s">
+      <c r="V23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W23" s="4" t="s">
+      <c r="W23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X23" s="4" t="s">
+      <c r="X23" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="N24" s="3" t="s">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="N24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="N25" s="3" t="s">
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="N25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="N26" s="3" t="s">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="N26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="N27" s="3" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="N27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="N28" s="3" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="N28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
@@ -8208,187 +8763,187 @@
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
-      <c r="C32" s="3">
+      <c r="C32" s="2">
         <v>1000</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="2">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="2">
         <v>10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>50000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="2">
         <v>100000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="2">
         <v>200000</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="3" t="str">
+      <c r="C33" s="2" t="str">
         <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
         <v>undone</v>
       </c>
-      <c r="D33" s="3" t="str">
+      <c r="D33" s="2" t="str">
         <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
         <v>undone</v>
       </c>
-      <c r="E33" s="3" t="str">
+      <c r="E33" s="2" t="str">
         <f>IF(COUNTBLANK(C15:L15)&gt;0,"undone",AVERAGE(C15:L15))</f>
         <v>undone</v>
       </c>
-      <c r="F33" s="3" t="str">
+      <c r="F33" s="2" t="str">
         <f>IF(COUNTBLANK(O15:X15)&gt;0,"undone",AVERAGE(O15:X15))</f>
         <v>undone</v>
       </c>
-      <c r="G33" s="3" t="str">
+      <c r="G33" s="2" t="str">
         <f>IF(COUNTBLANK(C24:L24)&gt;0,"undone",AVERAGE(C24:L24))</f>
         <v>undone</v>
       </c>
-      <c r="H33" s="3" t="str">
+      <c r="H33" s="2" t="str">
         <f>IF(COUNTBLANK(O24:X24)&gt;0,"undone",AVERAGE(O24:X24))</f>
         <v>undone</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="3" t="str">
+      <c r="C34" s="2" t="str">
         <f t="shared" ref="C34:C37" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
         <v>undone</v>
       </c>
-      <c r="D34" s="3" t="str">
+      <c r="D34" s="2" t="str">
         <f t="shared" ref="D34:D37" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
         <v>undone</v>
       </c>
-      <c r="E34" s="3" t="str">
+      <c r="E34" s="2" t="str">
         <f t="shared" ref="E34:E37" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
         <v>undone</v>
       </c>
-      <c r="F34" s="3" t="str">
+      <c r="F34" s="2" t="str">
         <f t="shared" ref="F34:F37" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
         <v>undone</v>
       </c>
-      <c r="G34" s="3" t="str">
+      <c r="G34" s="2" t="str">
         <f t="shared" ref="G34:G37" si="4">IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
         <v>undone</v>
       </c>
-      <c r="H34" s="3" t="str">
+      <c r="H34" s="2" t="str">
         <f t="shared" ref="H34:H37" si="5">IF(COUNTBLANK(O25:X25)&gt;0,"undone",AVERAGE(O25:X25))</f>
         <v>undone</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="3" t="str">
+      <c r="C35" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D35" s="3" t="str">
+      <c r="D35" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E35" s="3" t="str">
+      <c r="E35" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F35" s="3" t="str">
+      <c r="F35" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G35" s="3" t="str">
+      <c r="G35" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H35" s="3" t="str">
+      <c r="H35" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="3" t="str">
+      <c r="C36" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D36" s="3" t="str">
+      <c r="D36" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E36" s="3" t="str">
+      <c r="E36" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F36" s="3" t="str">
+      <c r="F36" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G36" s="3" t="str">
+      <c r="G36" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H36" s="3" t="str">
+      <c r="H36" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="3" t="str">
+      <c r="C37" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D37" s="3" t="str">
+      <c r="D37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E37" s="3" t="str">
+      <c r="E37" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F37" s="3" t="str">
+      <c r="F37" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G37" s="3" t="str">
+      <c r="G37" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H37" s="3" t="str">
+      <c r="H37" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:X13"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:X4"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="N22:N23"/>
     <mergeCell ref="O22:X22"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="C31:H31"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:X4"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:X13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8400,10 +8955,10 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="17" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N17" t="s">

--- a/data collecting.xlsx
+++ b/data collecting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phure\เอกสาร\GitHub\c-sorting-algorithm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396C7ED8-9601-4F7C-8B29-0E83B8066C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBA728C-533B-43E9-BEF6-4580BF48FD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
   </bookViews>
   <sheets>
     <sheet name="Random" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="26">
   <si>
     <t>Random</t>
   </si>
@@ -207,9 +207,6 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -218,20 +215,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -392,7 +392,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -412,26 +414,12 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="C00000"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Random!$C$32:$H$32</c:f>
+              <c:f>Random!$E$32:$H$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -443,12 +431,6 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -495,7 +477,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -515,26 +499,12 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="FFC000"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Random!$C$32:$H$32</c:f>
+              <c:f>Random!$E$32:$H$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -546,12 +516,6 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -598,7 +562,11 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -620,28 +588,12 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Random!$C$32:$H$32</c:f>
+              <c:f>Random!$E$32:$H$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -653,12 +605,6 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -705,7 +651,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -725,26 +673,12 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="00B0F0"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Random!$C$32:$H$32</c:f>
+              <c:f>Random!$E$32:$H$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -756,12 +690,6 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -808,7 +736,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -830,28 +760,12 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent5">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Random!$C$32:$H$32</c:f>
+              <c:f>Random!$E$32:$H$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -863,12 +777,6 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -908,7 +816,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -923,7 +830,7 @@
         <c:axId val="684990623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="200000"/>
+          <c:max val="50000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1041,14 +948,16 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="685575535"/>
-        <c:crosses val="autoZero"/>
+        <c:crossesAt val="1.0000000000000002E-3"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="10000"/>
+        <c:majorUnit val="5000"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="685575535"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
+          <c:min val="1.0000000000000002E-3"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1171,34 +1080,14 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:legendEntry>
-        <c:idx val="5"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="6"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="7"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="8"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="9"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.92667582110746793"/>
+          <c:x val="0.88868190013482362"/>
           <c:y val="0.27791545793617906"/>
-          <c:w val="6.1926002600738737E-2"/>
-          <c:h val="0.37006837961044342"/>
+          <c:w val="9.9919923573383126E-2"/>
+          <c:h val="0.40954206382096975"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1416,7 +1305,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1436,20 +1327,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="C00000"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sorted!$C$32:$H$32</c:f>
@@ -1457,22 +1334,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>5000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1507,7 +1384,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-90EE-4A70-8E47-7B1D33192D4D}"/>
+              <c16:uniqueId val="{00000000-8D0B-4458-9FBB-8745893D7C64}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1519,7 +1396,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1539,20 +1418,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="FFC000"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sorted!$C$32:$H$32</c:f>
@@ -1560,22 +1425,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>5000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1610,7 +1475,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-90EE-4A70-8E47-7B1D33192D4D}"/>
+              <c16:uniqueId val="{00000001-8D0B-4458-9FBB-8745893D7C64}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1622,7 +1487,11 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1644,22 +1513,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sorted!$C$32:$H$32</c:f>
@@ -1667,22 +1520,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>5000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1717,7 +1570,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-90EE-4A70-8E47-7B1D33192D4D}"/>
+              <c16:uniqueId val="{00000002-8D0B-4458-9FBB-8745893D7C64}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1729,7 +1582,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1749,20 +1604,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="00B0F0"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sorted!$C$32:$H$32</c:f>
@@ -1770,22 +1611,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>5000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1820,7 +1661,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-90EE-4A70-8E47-7B1D33192D4D}"/>
+              <c16:uniqueId val="{00000003-8D0B-4458-9FBB-8745893D7C64}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1832,7 +1673,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1854,22 +1697,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent5">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sorted!$C$32:$H$32</c:f>
@@ -1877,22 +1704,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>5000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1927,7 +1754,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-90EE-4A70-8E47-7B1D33192D4D}"/>
+              <c16:uniqueId val="{00000004-8D0B-4458-9FBB-8745893D7C64}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1946,7 +1773,7 @@
         <c:axId val="684990623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="200000"/>
+          <c:max val="50000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2064,14 +1891,16 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="685575535"/>
-        <c:crosses val="autoZero"/>
+        <c:crossesAt val="1.0000000000000002E-3"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="10000"/>
+        <c:majorUnit val="5000"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="685575535"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
+          <c:min val="1.0000000000000002E-3"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2194,34 +2023,14 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:legendEntry>
-        <c:idx val="5"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="6"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="7"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="8"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="9"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.92667582110746793"/>
+          <c:x val="0.88868190013482362"/>
           <c:y val="0.27791545793617906"/>
-          <c:w val="6.1926002600738737E-2"/>
-          <c:h val="0.37006837961044342"/>
+          <c:w val="9.9919923573383126E-2"/>
+          <c:h val="0.40954206382096975"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -2439,7 +2248,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -2459,20 +2270,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="C00000"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'Rev-Sorted'!$C$32:$H$32</c:f>
@@ -2480,22 +2277,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>5000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2530,7 +2327,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C99C-4306-B424-113516D89B70}"/>
+              <c16:uniqueId val="{00000000-15B6-42FF-BAC6-0CE76102BA0F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2542,7 +2339,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -2562,20 +2361,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="FFC000"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'Rev-Sorted'!$C$32:$H$32</c:f>
@@ -2583,22 +2368,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>5000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2633,7 +2418,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C99C-4306-B424-113516D89B70}"/>
+              <c16:uniqueId val="{00000001-15B6-42FF-BAC6-0CE76102BA0F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2645,7 +2430,11 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -2667,22 +2456,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'Rev-Sorted'!$C$32:$H$32</c:f>
@@ -2690,22 +2463,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>5000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2740,7 +2513,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-C99C-4306-B424-113516D89B70}"/>
+              <c16:uniqueId val="{00000002-15B6-42FF-BAC6-0CE76102BA0F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2752,7 +2525,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -2772,20 +2547,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="00B0F0"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'Rev-Sorted'!$C$32:$H$32</c:f>
@@ -2793,22 +2554,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>5000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2843,7 +2604,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-C99C-4306-B424-113516D89B70}"/>
+              <c16:uniqueId val="{00000003-15B6-42FF-BAC6-0CE76102BA0F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2855,7 +2616,9 @@
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -2877,22 +2640,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent5">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'Rev-Sorted'!$C$32:$H$32</c:f>
@@ -2900,22 +2647,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>5000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2950,7 +2697,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-C99C-4306-B424-113516D89B70}"/>
+              <c16:uniqueId val="{00000004-15B6-42FF-BAC6-0CE76102BA0F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2969,7 +2716,7 @@
         <c:axId val="684990623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="200000"/>
+          <c:max val="50000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -3087,14 +2834,16 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="685575535"/>
-        <c:crosses val="autoZero"/>
+        <c:crossesAt val="1.0000000000000002E-3"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="10000"/>
+        <c:majorUnit val="5000"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="685575535"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
+          <c:min val="1.0000000000000002E-3"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -3217,34 +2966,14 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:legendEntry>
-        <c:idx val="5"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="6"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="7"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="8"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="9"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.92667582110746793"/>
+          <c:x val="0.88868190013482362"/>
           <c:y val="0.27791545793617906"/>
-          <c:w val="6.1926002600738737E-2"/>
-          <c:h val="0.37006837961044342"/>
+          <c:w val="9.9919923573383126E-2"/>
+          <c:h val="0.40954206382096975"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -5033,23 +4762,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>449580</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:colOff>640080</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="แผนภูมิ 1">
+        <xdr:cNvPr id="4" name="แผนภูมิ 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03E19C42-B328-4757-9088-41DF7CAE46B7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71BE9449-7574-4E24-A50B-7E49FC921C51}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5076,23 +4805,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>449580</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:colOff>640080</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="แผนภูมิ 1">
+        <xdr:cNvPr id="3" name="แผนภูมิ 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2610D8DC-0A85-4711-9193-0EDB5DEC46E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE94E5DB-503D-4B90-9650-48F976006EDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5435,33 +5164,33 @@
   <dimension ref="A1:X37"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="8"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <f>C32</f>
-        <v>1000</v>
-      </c>
-      <c r="N3" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <f>D32</f>
-        <v>5000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -5476,7 +5205,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="7" t="s">
@@ -5493,227 +5222,227 @@
       <c r="X4" s="7"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="5"/>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="4" t="s">
+      <c r="N5" s="6"/>
+      <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="T5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="U5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="V5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="N6" s="3" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="N6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="N7" s="3" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="N8" s="3" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="N8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="N9" s="3" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="N9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="N10" s="3" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="N10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <f>E32</f>
-        <v>10000</v>
-      </c>
-      <c r="N12" s="9" t="s">
+        <v>1000</v>
+      </c>
+      <c r="N12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="1">
         <f>F32</f>
-        <v>50000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -5728,7 +5457,7 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
-      <c r="N13" s="5" t="s">
+      <c r="N13" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O13" s="7" t="s">
@@ -5745,227 +5474,227 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="5"/>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="4" t="s">
+      <c r="N14" s="6"/>
+      <c r="O14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="4" t="s">
+      <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="4" t="s">
+      <c r="S14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T14" s="4" t="s">
+      <c r="T14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U14" s="4" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="4" t="s">
+      <c r="V14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W14" s="4" t="s">
+      <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="4" t="s">
+      <c r="X14" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="N15" s="3" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="N15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="N16" s="3" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="N16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="N17" s="3" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="N17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="N18" s="3" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="N18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="N19" s="3" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="N19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <f>G32</f>
-        <v>100000</v>
-      </c>
-      <c r="N21" s="9" t="s">
+        <v>10000</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="1">
         <f>H32</f>
-        <v>200000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -5980,7 +5709,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
-      <c r="N22" s="5" t="s">
+      <c r="N22" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O22" s="7" t="s">
@@ -5997,390 +5726,397 @@
       <c r="X22" s="7"/>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B23" s="5"/>
-      <c r="C23" s="4" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="4" t="s">
+      <c r="N23" s="6"/>
+      <c r="O23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="4" t="s">
+      <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R23" s="4" t="s">
+      <c r="R23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="4" t="s">
+      <c r="S23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T23" s="4" t="s">
+      <c r="T23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U23" s="4" t="s">
+      <c r="U23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V23" s="4" t="s">
+      <c r="V23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W23" s="4" t="s">
+      <c r="W23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X23" s="4" t="s">
+      <c r="X23" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="N24" s="3" t="s">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="N24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="N25" s="3" t="s">
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="N25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="N26" s="3" t="s">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="N26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="N27" s="3" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="N27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="N28" s="3" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="N28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B32" s="5"/>
-      <c r="C32" s="3">
+      <c r="B32" s="6"/>
+      <c r="C32" s="1">
+        <v>100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>500</v>
+      </c>
+      <c r="E32" s="2">
         <v>1000</v>
       </c>
-      <c r="D32" s="3">
+      <c r="F32" s="2">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="2">
         <v>10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="2">
         <v>50000</v>
       </c>
-      <c r="G32" s="3">
-        <v>100000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>200000</v>
-      </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="3" t="str">
+      <c r="C33" s="2" t="str">
         <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
         <v>undone</v>
       </c>
-      <c r="D33" s="3" t="str">
+      <c r="D33" s="2" t="str">
         <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
         <v>undone</v>
       </c>
-      <c r="E33" s="3" t="str">
+      <c r="E33" s="2" t="str">
         <f>IF(COUNTBLANK(C15:L15)&gt;0,"undone",AVERAGE(C15:L15))</f>
         <v>undone</v>
       </c>
-      <c r="F33" s="3" t="str">
+      <c r="F33" s="2" t="str">
         <f>IF(COUNTBLANK(O15:X15)&gt;0,"undone",AVERAGE(O15:X15))</f>
         <v>undone</v>
       </c>
-      <c r="G33" s="3" t="str">
+      <c r="G33" s="2" t="str">
         <f>IF(COUNTBLANK(C24:L24)&gt;0,"undone",AVERAGE(C24:L24))</f>
         <v>undone</v>
       </c>
-      <c r="H33" s="3" t="str">
+      <c r="H33" s="2" t="str">
         <f>IF(COUNTBLANK(O24:X24)&gt;0,"undone",AVERAGE(O24:X24))</f>
         <v>undone</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="3" t="str">
+      <c r="C34" s="2" t="str">
         <f t="shared" ref="C34:C37" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
         <v>undone</v>
       </c>
-      <c r="D34" s="3" t="str">
+      <c r="D34" s="2" t="str">
         <f t="shared" ref="D34:D37" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
         <v>undone</v>
       </c>
-      <c r="E34" s="3" t="str">
+      <c r="E34" s="2" t="str">
         <f t="shared" ref="E34:E37" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
         <v>undone</v>
       </c>
-      <c r="F34" s="3" t="str">
+      <c r="F34" s="2" t="str">
         <f t="shared" ref="F34:F37" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
         <v>undone</v>
       </c>
-      <c r="G34" s="3" t="str">
+      <c r="G34" s="2" t="str">
         <f t="shared" ref="G34:G37" si="4">IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
         <v>undone</v>
       </c>
-      <c r="H34" s="3" t="str">
+      <c r="H34" s="2" t="str">
         <f>IF(COUNTBLANK(O25:X25)&gt;0,"undone",AVERAGE(O25:X25))</f>
         <v>undone</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="3" t="str">
+      <c r="C35" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D35" s="3" t="str">
+      <c r="D35" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E35" s="3" t="str">
+      <c r="E35" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F35" s="3" t="str">
+      <c r="F35" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G35" s="3" t="str">
+      <c r="G35" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H35" s="3" t="str">
-        <f t="shared" ref="H34:H37" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",AVERAGE(O26:X26))</f>
+      <c r="H35" s="2" t="str">
+        <f t="shared" ref="H35:H37" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",AVERAGE(O26:X26))</f>
         <v>undone</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="3" t="str">
+      <c r="C36" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D36" s="3" t="str">
+      <c r="D36" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E36" s="3" t="str">
+      <c r="E36" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F36" s="3" t="str">
+      <c r="F36" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G36" s="3" t="str">
+      <c r="G36" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H36" s="3" t="str">
+      <c r="H36" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="3" t="str">
+      <c r="C37" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D37" s="3" t="str">
+      <c r="D37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E37" s="3" t="str">
+      <c r="E37" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F37" s="3" t="str">
+      <c r="F37" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G37" s="3" t="str">
+      <c r="G37" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H37" s="3" t="str">
+      <c r="H37" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:X4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C31:H31"/>
     <mergeCell ref="N22:N23"/>
     <mergeCell ref="O22:X22"/>
     <mergeCell ref="B13:B14"/>
@@ -6389,13 +6125,6 @@
     <mergeCell ref="O13:X13"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="C22:L22"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:X4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6408,10 +6137,10 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="5"/>
     </row>
     <row r="17" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N17" t="s">
@@ -6432,33 +6161,33 @@
   <dimension ref="A1:X37"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="8"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <f>C32</f>
-        <v>1000</v>
-      </c>
-      <c r="N3" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <f>D32</f>
-        <v>5000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -6473,7 +6202,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="7" t="s">
@@ -6490,227 +6219,227 @@
       <c r="X4" s="7"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="5"/>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="4" t="s">
+      <c r="N5" s="6"/>
+      <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="T5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="U5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="V5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="N6" s="3" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="N6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="N7" s="3" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="N8" s="3" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="N8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="N9" s="3" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="N9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="N10" s="3" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="N10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <f>E32</f>
-        <v>10000</v>
-      </c>
-      <c r="N12" s="9" t="s">
+        <v>1000</v>
+      </c>
+      <c r="N12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="1">
         <f>F32</f>
-        <v>50000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -6725,7 +6454,7 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
-      <c r="N13" s="5" t="s">
+      <c r="N13" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O13" s="7" t="s">
@@ -6742,227 +6471,227 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="5"/>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="4" t="s">
+      <c r="N14" s="6"/>
+      <c r="O14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="4" t="s">
+      <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="4" t="s">
+      <c r="S14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T14" s="4" t="s">
+      <c r="T14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U14" s="4" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="4" t="s">
+      <c r="V14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W14" s="4" t="s">
+      <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="4" t="s">
+      <c r="X14" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="N15" s="3" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="N15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="N16" s="3" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="N16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="N17" s="3" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="N17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="N18" s="3" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="N18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="N19" s="3" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="N19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <f>G32</f>
-        <v>100000</v>
-      </c>
-      <c r="N21" s="9" t="s">
+        <v>10000</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="1">
         <f>H32</f>
-        <v>200000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -6977,7 +6706,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
-      <c r="N22" s="5" t="s">
+      <c r="N22" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O22" s="7" t="s">
@@ -6994,384 +6723,384 @@
       <c r="X22" s="7"/>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B23" s="5"/>
-      <c r="C23" s="4" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="4" t="s">
+      <c r="N23" s="6"/>
+      <c r="O23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="4" t="s">
+      <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R23" s="4" t="s">
+      <c r="R23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="4" t="s">
+      <c r="S23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T23" s="4" t="s">
+      <c r="T23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U23" s="4" t="s">
+      <c r="U23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V23" s="4" t="s">
+      <c r="V23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W23" s="4" t="s">
+      <c r="W23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X23" s="4" t="s">
+      <c r="X23" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="N24" s="3" t="s">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="N24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="N25" s="3" t="s">
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="N25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="N26" s="3" t="s">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="N26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="N27" s="3" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="N27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="N28" s="3" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="N28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B32" s="5"/>
-      <c r="C32" s="3">
+      <c r="B32" s="6"/>
+      <c r="C32" s="1">
+        <v>100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>500</v>
+      </c>
+      <c r="E32" s="2">
         <v>1000</v>
       </c>
-      <c r="D32" s="3">
+      <c r="F32" s="2">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="2">
         <v>10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="2">
         <v>50000</v>
       </c>
-      <c r="G32" s="3">
-        <v>100000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>200000</v>
-      </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="3" t="str">
+      <c r="C33" s="2" t="str">
         <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
         <v>undone</v>
       </c>
-      <c r="D33" s="3" t="str">
+      <c r="D33" s="2" t="str">
         <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
         <v>undone</v>
       </c>
-      <c r="E33" s="3" t="str">
+      <c r="E33" s="2" t="str">
         <f>IF(COUNTBLANK(C15:L15)&gt;0,"undone",AVERAGE(C15:L15))</f>
         <v>undone</v>
       </c>
-      <c r="F33" s="3" t="str">
+      <c r="F33" s="2" t="str">
         <f>IF(COUNTBLANK(O15:X15)&gt;0,"undone",AVERAGE(O15:X15))</f>
         <v>undone</v>
       </c>
-      <c r="G33" s="3" t="str">
+      <c r="G33" s="2" t="str">
         <f>IF(COUNTBLANK(C24:L24)&gt;0,"undone",AVERAGE(C24:L24))</f>
         <v>undone</v>
       </c>
-      <c r="H33" s="3" t="str">
+      <c r="H33" s="2" t="str">
         <f>IF(COUNTBLANK(O24:X24)&gt;0,"undone",AVERAGE(O24:X24))</f>
         <v>undone</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="3" t="str">
+      <c r="C34" s="2" t="str">
         <f t="shared" ref="C34:C37" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
         <v>undone</v>
       </c>
-      <c r="D34" s="3" t="str">
+      <c r="D34" s="2" t="str">
         <f t="shared" ref="D34:D37" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
         <v>undone</v>
       </c>
-      <c r="E34" s="3" t="str">
+      <c r="E34" s="2" t="str">
         <f t="shared" ref="E34:E37" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
         <v>undone</v>
       </c>
-      <c r="F34" s="3" t="str">
+      <c r="F34" s="2" t="str">
         <f t="shared" ref="F34:F37" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
         <v>undone</v>
       </c>
-      <c r="G34" s="3" t="str">
+      <c r="G34" s="2" t="str">
         <f t="shared" ref="G34:G37" si="4">IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
         <v>undone</v>
       </c>
-      <c r="H34" s="3" t="str">
+      <c r="H34" s="2" t="str">
         <f t="shared" ref="H34:H37" si="5">IF(COUNTBLANK(O25:X25)&gt;0,"undone",AVERAGE(O25:X25))</f>
         <v>undone</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="3" t="str">
+      <c r="C35" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D35" s="3" t="str">
+      <c r="D35" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E35" s="3" t="str">
+      <c r="E35" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F35" s="3" t="str">
+      <c r="F35" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G35" s="3" t="str">
+      <c r="G35" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H35" s="3" t="str">
+      <c r="H35" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="3" t="str">
+      <c r="C36" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D36" s="3" t="str">
+      <c r="D36" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E36" s="3" t="str">
+      <c r="E36" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F36" s="3" t="str">
+      <c r="F36" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G36" s="3" t="str">
+      <c r="G36" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H36" s="3" t="str">
+      <c r="H36" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="3" t="str">
+      <c r="C37" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D37" s="3" t="str">
+      <c r="D37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E37" s="3" t="str">
+      <c r="E37" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F37" s="3" t="str">
+      <c r="F37" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G37" s="3" t="str">
+      <c r="G37" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H37" s="3" t="str">
+      <c r="H37" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
@@ -7384,15 +7113,15 @@
     <mergeCell ref="O22:X22"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="C31:H31"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:X13"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="O4:X4"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:X13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7404,10 +7133,10 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="5"/>
     </row>
     <row r="17" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N17" t="s">
@@ -7428,33 +7157,33 @@
   <dimension ref="A1:X37"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="8"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <f>C32</f>
-        <v>1000</v>
-      </c>
-      <c r="N3" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <f>D32</f>
-        <v>5000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -7469,7 +7198,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="7" t="s">
@@ -7486,227 +7215,227 @@
       <c r="X4" s="7"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="5"/>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="4" t="s">
+      <c r="N5" s="6"/>
+      <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="T5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="U5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="V5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="N6" s="3" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="N6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="N7" s="3" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="N8" s="3" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="N8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="N9" s="3" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="N9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="N10" s="3" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="N10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <f>E32</f>
-        <v>10000</v>
-      </c>
-      <c r="N12" s="9" t="s">
+        <v>1000</v>
+      </c>
+      <c r="N12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="1">
         <f>F32</f>
-        <v>50000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -7721,7 +7450,7 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
-      <c r="N13" s="5" t="s">
+      <c r="N13" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O13" s="7" t="s">
@@ -7738,227 +7467,227 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="5"/>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="4" t="s">
+      <c r="N14" s="6"/>
+      <c r="O14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="4" t="s">
+      <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="4" t="s">
+      <c r="S14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T14" s="4" t="s">
+      <c r="T14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U14" s="4" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="4" t="s">
+      <c r="V14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W14" s="4" t="s">
+      <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="4" t="s">
+      <c r="X14" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="N15" s="3" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="N15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="N16" s="3" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="N16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="N17" s="3" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="N17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="N18" s="3" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="N18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="N19" s="3" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="N19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <f>G32</f>
-        <v>100000</v>
-      </c>
-      <c r="N21" s="9" t="s">
+        <v>10000</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="1">
         <f>H32</f>
-        <v>200000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -7973,7 +7702,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
-      <c r="N22" s="5" t="s">
+      <c r="N22" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O22" s="7" t="s">
@@ -7990,384 +7719,384 @@
       <c r="X22" s="7"/>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B23" s="5"/>
-      <c r="C23" s="4" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="4" t="s">
+      <c r="N23" s="6"/>
+      <c r="O23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="4" t="s">
+      <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R23" s="4" t="s">
+      <c r="R23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="4" t="s">
+      <c r="S23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T23" s="4" t="s">
+      <c r="T23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="U23" s="4" t="s">
+      <c r="U23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V23" s="4" t="s">
+      <c r="V23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W23" s="4" t="s">
+      <c r="W23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X23" s="4" t="s">
+      <c r="X23" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="N24" s="3" t="s">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="N24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="N25" s="3" t="s">
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="N25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="N26" s="3" t="s">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="N26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="N27" s="3" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="N27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="N28" s="3" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="N28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B32" s="5"/>
-      <c r="C32" s="3">
+      <c r="B32" s="6"/>
+      <c r="C32" s="1">
+        <v>100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>500</v>
+      </c>
+      <c r="E32" s="2">
         <v>1000</v>
       </c>
-      <c r="D32" s="3">
+      <c r="F32" s="2">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="2">
         <v>10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="2">
         <v>50000</v>
       </c>
-      <c r="G32" s="3">
-        <v>100000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>200000</v>
-      </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="3" t="str">
+      <c r="C33" s="2" t="str">
         <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
         <v>undone</v>
       </c>
-      <c r="D33" s="3" t="str">
+      <c r="D33" s="2" t="str">
         <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
         <v>undone</v>
       </c>
-      <c r="E33" s="3" t="str">
+      <c r="E33" s="2" t="str">
         <f>IF(COUNTBLANK(C15:L15)&gt;0,"undone",AVERAGE(C15:L15))</f>
         <v>undone</v>
       </c>
-      <c r="F33" s="3" t="str">
+      <c r="F33" s="2" t="str">
         <f>IF(COUNTBLANK(O15:X15)&gt;0,"undone",AVERAGE(O15:X15))</f>
         <v>undone</v>
       </c>
-      <c r="G33" s="3" t="str">
+      <c r="G33" s="2" t="str">
         <f>IF(COUNTBLANK(C24:L24)&gt;0,"undone",AVERAGE(C24:L24))</f>
         <v>undone</v>
       </c>
-      <c r="H33" s="3" t="str">
+      <c r="H33" s="2" t="str">
         <f>IF(COUNTBLANK(O24:X24)&gt;0,"undone",AVERAGE(O24:X24))</f>
         <v>undone</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="3" t="str">
+      <c r="C34" s="2" t="str">
         <f t="shared" ref="C34:C37" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
         <v>undone</v>
       </c>
-      <c r="D34" s="3" t="str">
+      <c r="D34" s="2" t="str">
         <f t="shared" ref="D34:D37" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
         <v>undone</v>
       </c>
-      <c r="E34" s="3" t="str">
+      <c r="E34" s="2" t="str">
         <f t="shared" ref="E34:E37" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
         <v>undone</v>
       </c>
-      <c r="F34" s="3" t="str">
+      <c r="F34" s="2" t="str">
         <f t="shared" ref="F34:F37" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
         <v>undone</v>
       </c>
-      <c r="G34" s="3" t="str">
+      <c r="G34" s="2" t="str">
         <f t="shared" ref="G34:G37" si="4">IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
         <v>undone</v>
       </c>
-      <c r="H34" s="3" t="str">
+      <c r="H34" s="2" t="str">
         <f t="shared" ref="H34:H37" si="5">IF(COUNTBLANK(O25:X25)&gt;0,"undone",AVERAGE(O25:X25))</f>
         <v>undone</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="3" t="str">
+      <c r="C35" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D35" s="3" t="str">
+      <c r="D35" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E35" s="3" t="str">
+      <c r="E35" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F35" s="3" t="str">
+      <c r="F35" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G35" s="3" t="str">
+      <c r="G35" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H35" s="3" t="str">
+      <c r="H35" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="3" t="str">
+      <c r="C36" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D36" s="3" t="str">
+      <c r="D36" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E36" s="3" t="str">
+      <c r="E36" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F36" s="3" t="str">
+      <c r="F36" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G36" s="3" t="str">
+      <c r="G36" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H36" s="3" t="str">
+      <c r="H36" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="3" t="str">
+      <c r="C37" s="2" t="str">
         <f t="shared" si="0"/>
         <v>undone</v>
       </c>
-      <c r="D37" s="3" t="str">
+      <c r="D37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>undone</v>
       </c>
-      <c r="E37" s="3" t="str">
+      <c r="E37" s="2" t="str">
         <f t="shared" si="2"/>
         <v>undone</v>
       </c>
-      <c r="F37" s="3" t="str">
+      <c r="F37" s="2" t="str">
         <f t="shared" si="3"/>
         <v>undone</v>
       </c>
-      <c r="G37" s="3" t="str">
+      <c r="G37" s="2" t="str">
         <f t="shared" si="4"/>
         <v>undone</v>
       </c>
-      <c r="H37" s="3" t="str">
+      <c r="H37" s="2" t="str">
         <f t="shared" si="5"/>
         <v>undone</v>
       </c>
@@ -8380,15 +8109,15 @@
     <mergeCell ref="O22:X22"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="C31:H31"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:X13"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="O4:X4"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:X13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8396,19 +8125,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED80655-96D9-4D34-BEF1-EA0FC028976F}">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="17" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N17" t="s">
-        <v>23</v>
-      </c>
+      <c r="B1" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data collecting.xlsx
+++ b/data collecting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phure\เอกสาร\GitHub\c-sorting-algorithm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBA728C-533B-43E9-BEF6-4580BF48FD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DFC4B1-1C9D-4B44-8406-5BD109FC5B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
   </bookViews>
   <sheets>
     <sheet name="Random" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="27">
   <si>
     <t>Random</t>
   </si>
@@ -123,6 +123,9 @@
   <si>
     <t>best case</t>
   </si>
+  <si>
+    <t>Run time (ms)</t>
+  </si>
 </sst>
 </file>
 
@@ -177,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -200,11 +203,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -233,6 +273,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -442,22 +488,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>3.4100000000000007E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>9.7070000000000017E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.36215000000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>9.0675799999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>35.300449999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>898.78161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -527,22 +573,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>5.1600000000000005E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.1351</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.4676499999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>11.12998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>45.611530000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1144.4044900000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -616,22 +662,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>9.5599999999999973E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.26630999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.0637199999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>23.42755</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>95.326180000000008</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>2423.1844000000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -701,22 +747,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.1400000000000005E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.9650000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>4.4389999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.34113000000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.78540999999999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>4.9083600000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -788,22 +834,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.7799999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.6480000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.5600000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.22132000000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.53208999999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3.3549199999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1361,22 +1407,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.6000000000000004E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>8.9999999999999998E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.82E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>8.4700000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.5960000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>9.3109999999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1452,22 +1498,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.7599999999999995E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.11173999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.44557000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>11.415189999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>45.156060000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1578.6948299999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1547,22 +1593,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>5.9700000000000005E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.14710999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.58564000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>14.953890000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>60.254049999999992</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1499.0670599999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1638,22 +1684,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2.9499999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.7470000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.7480000000000006E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.21754999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.50645000000000007</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>2.5919500000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1731,22 +1777,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>5.0699999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>8.7919999999999984E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.43381000000000008</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>9.5659700000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>40.406939999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1172.0279999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2304,22 +2350,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>9.9500000000000005E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.24713999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.99377999999999989</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>25.123840000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>100.66342</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>2530.2127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2395,22 +2441,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>7.4400000000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.16192999999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.68050999999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>17.546299999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>72.064859999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1814.8987199999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2490,22 +2536,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.7569999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.39970999999999995</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.72557</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>46.811249999999994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>181.55905999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>4382.7229299999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2581,22 +2627,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.0699999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.051E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5.4539999999999991E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.31284999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.65659000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3.8224299999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2674,22 +2720,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>6.0499999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.13638999999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.53875000000000006</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>13.51234</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>53.08849</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1304.45454</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5171,7 +5217,7 @@
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
+      <c r="B1" s="10"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -5194,35 +5240,35 @@
         <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+        <v>26</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="12"/>
       <c r="N4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="12"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="6"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -5253,7 +5299,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="6"/>
+      <c r="N5" s="13"/>
       <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
@@ -5289,141 +5335,341 @@
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="C6" s="2">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3.3E-3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3.3E-3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3.3E-3</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="I6" s="2">
+        <v>3.3E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>3.3E-3</v>
+      </c>
+      <c r="K6" s="2">
+        <v>3.3E-3</v>
+      </c>
+      <c r="L6" s="2">
+        <v>3.3E-3</v>
+      </c>
       <c r="N6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
+      <c r="O6" s="2">
+        <v>0.1014</v>
+      </c>
+      <c r="P6" s="2">
+        <v>9.69E-2</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>9.6600000000000005E-2</v>
+      </c>
+      <c r="R6" s="2">
+        <v>9.6500000000000002E-2</v>
+      </c>
+      <c r="S6" s="2">
+        <v>9.6600000000000005E-2</v>
+      </c>
+      <c r="T6" s="2">
+        <v>9.6600000000000005E-2</v>
+      </c>
+      <c r="U6" s="2">
+        <v>9.6500000000000002E-2</v>
+      </c>
+      <c r="V6" s="2">
+        <v>9.6600000000000005E-2</v>
+      </c>
+      <c r="W6" s="2">
+        <v>9.6500000000000002E-2</v>
+      </c>
+      <c r="X6" s="2">
+        <v>9.6500000000000002E-2</v>
+      </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="C7" s="2">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="I7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="K7" s="2">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="L7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
       <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
+      <c r="O7" s="2">
+        <v>0.12709999999999999</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.1229</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0.1191</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0.1173</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0.11650000000000001</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0.1216</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0.13730000000000001</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0.1903</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0.18290000000000001</v>
+      </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="C8" s="2">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="G8" s="2">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H8" s="2">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="K8" s="2">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="L8" s="2">
+        <v>8.9999999999999993E-3</v>
+      </c>
       <c r="N8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
+      <c r="O8" s="2">
+        <v>0.26740000000000003</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.25119999999999998</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0.2492</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.2419</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0.24690000000000001</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0.24790000000000001</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0.23849999999999999</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0.37040000000000001</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0.31069999999999998</v>
+      </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="C9" s="2">
+        <v>5.3E-3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1.2200000000000001E-2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="I9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
       <c r="N9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
+      <c r="O9" s="2">
+        <v>4.6399999999999997E-2</v>
+      </c>
+      <c r="P9" s="2">
+        <v>3.27E-2</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="R9" s="2">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="S9" s="2">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="T9" s="2">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="U9" s="2">
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="V9" s="2">
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="W9" s="2">
+        <v>2.7E-2</v>
+      </c>
+      <c r="X9" s="2">
+        <v>2.7E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="C10" s="2">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1.4E-3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1.4E-3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1.4E-3</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1.4E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.4E-3</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1.4E-3</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1.4E-3</v>
+      </c>
       <c r="N10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
+      <c r="O10" s="2">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="P10" s="2">
+        <v>1.83E-2</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>1.34E-2</v>
+      </c>
+      <c r="R10" s="2">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="S10" s="2">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="T10" s="2">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="U10" s="2">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="V10" s="2">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="W10" s="2">
+        <v>1.29E-2</v>
+      </c>
+      <c r="X10" s="2">
+        <v>1.2999999999999999E-2</v>
+      </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
@@ -5448,33 +5694,33 @@
       <c r="C13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="12"/>
       <c r="N13" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="12"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="3" t="s">
         <v>2</v>
       </c>
@@ -5505,7 +5751,7 @@
       <c r="L14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N14" s="6"/>
+      <c r="N14" s="13"/>
       <c r="O14" s="3" t="s">
         <v>2</v>
       </c>
@@ -5541,141 +5787,341 @@
       <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="C15" s="2">
+        <v>0.50419999999999998</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.3548</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.34189999999999998</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.34370000000000001</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.35170000000000001</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0.34210000000000002</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.34239999999999998</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.3538</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0.34350000000000003</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0.34339999999999998</v>
+      </c>
       <c r="N15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
+      <c r="O15" s="2">
+        <v>8.8356999999999992</v>
+      </c>
+      <c r="P15" s="2">
+        <v>9.8757999999999999</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>9.2029999999999994</v>
+      </c>
+      <c r="R15" s="2">
+        <v>8.8292999999999999</v>
+      </c>
+      <c r="S15" s="2">
+        <v>9.1554000000000002</v>
+      </c>
+      <c r="T15" s="2">
+        <v>8.8246000000000002</v>
+      </c>
+      <c r="U15" s="2">
+        <v>9.6296999999999997</v>
+      </c>
+      <c r="V15" s="2">
+        <v>8.8139000000000003</v>
+      </c>
+      <c r="W15" s="2">
+        <v>8.7524999999999995</v>
+      </c>
+      <c r="X15" s="2">
+        <v>8.7559000000000005</v>
+      </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+      <c r="C16" s="2">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.46939999999999998</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.47020000000000001</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.46350000000000002</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.46610000000000001</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.46179999999999999</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.47139999999999999</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.46389999999999998</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0.4632</v>
+      </c>
       <c r="N16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
+      <c r="O16" s="2">
+        <v>10.988300000000001</v>
+      </c>
+      <c r="P16" s="2">
+        <v>11.533099999999999</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>11.131600000000001</v>
+      </c>
+      <c r="R16" s="2">
+        <v>10.855</v>
+      </c>
+      <c r="S16" s="2">
+        <v>10.9977</v>
+      </c>
+      <c r="T16" s="2">
+        <v>11.121700000000001</v>
+      </c>
+      <c r="U16" s="2">
+        <v>10.807499999999999</v>
+      </c>
+      <c r="V16" s="2">
+        <v>11.277699999999999</v>
+      </c>
+      <c r="W16" s="2">
+        <v>11.011799999999999</v>
+      </c>
+      <c r="X16" s="2">
+        <v>11.5754</v>
+      </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
+      <c r="C17" s="2">
+        <v>0.9607</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.94669999999999999</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.93959999999999999</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.93630000000000002</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1.2179</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1.3096000000000001</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1.3906000000000001</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1.0583</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0.94</v>
+      </c>
       <c r="N17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
+      <c r="O17" s="2">
+        <v>22.4754</v>
+      </c>
+      <c r="P17" s="2">
+        <v>23.703399999999998</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>23.3719</v>
+      </c>
+      <c r="R17" s="2">
+        <v>22.591000000000001</v>
+      </c>
+      <c r="S17" s="2">
+        <v>25.265999999999998</v>
+      </c>
+      <c r="T17" s="2">
+        <v>25.139500000000002</v>
+      </c>
+      <c r="U17" s="2">
+        <v>22.900099999999998</v>
+      </c>
+      <c r="V17" s="2">
+        <v>22.982099999999999</v>
+      </c>
+      <c r="W17" s="2">
+        <v>22.679099999999998</v>
+      </c>
+      <c r="X17" s="2">
+        <v>23.167000000000002</v>
+      </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
+      <c r="C18" s="2">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>4.9200000000000001E-2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>4.2299999999999997E-2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="G18" s="2">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="H18" s="2">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="I18" s="2">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="J18" s="2">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="K18" s="2">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="L18" s="2">
+        <v>3.9800000000000002E-2</v>
+      </c>
       <c r="N18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
+      <c r="O18" s="2">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0.33460000000000001</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0.33139999999999997</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0.32250000000000001</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0.32040000000000002</v>
+      </c>
+      <c r="V18" s="2">
+        <v>0.32219999999999999</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0.31630000000000003</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0.31590000000000001</v>
+      </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
+      <c r="C19" s="2">
+        <v>4.5199999999999997E-2</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1.9E-2</v>
+      </c>
+      <c r="L19" s="2">
+        <v>3.5099999999999999E-2</v>
+      </c>
       <c r="N19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
+      <c r="O19" s="2">
+        <v>0.2485</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0.2414</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="R19" s="2">
+        <v>0.21640000000000001</v>
+      </c>
+      <c r="S19" s="2">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="T19" s="2">
+        <v>0.20610000000000001</v>
+      </c>
+      <c r="U19" s="2">
+        <v>0.1981</v>
+      </c>
+      <c r="V19" s="2">
+        <v>0.20150000000000001</v>
+      </c>
+      <c r="W19" s="2">
+        <v>0.2361</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0.2286</v>
+      </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
@@ -5700,33 +6146,33 @@
       <c r="C22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="12"/>
       <c r="N22" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="12"/>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="13"/>
       <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
@@ -5757,7 +6203,7 @@
       <c r="L23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N23" s="6"/>
+      <c r="N23" s="13"/>
       <c r="O23" s="3" t="s">
         <v>2</v>
       </c>
@@ -5793,141 +6239,341 @@
       <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
+      <c r="C24" s="2">
+        <v>34.321100000000001</v>
+      </c>
+      <c r="D24" s="2">
+        <v>35.676400000000001</v>
+      </c>
+      <c r="E24" s="2">
+        <v>35.314399999999999</v>
+      </c>
+      <c r="F24" s="2">
+        <v>37.550400000000003</v>
+      </c>
+      <c r="G24" s="2">
+        <v>35.549700000000001</v>
+      </c>
+      <c r="H24" s="2">
+        <v>36.2181</v>
+      </c>
+      <c r="I24" s="2">
+        <v>35.344999999999999</v>
+      </c>
+      <c r="J24" s="2">
+        <v>34.2029</v>
+      </c>
+      <c r="K24" s="2">
+        <v>34.665199999999999</v>
+      </c>
+      <c r="L24" s="2">
+        <v>34.161299999999997</v>
+      </c>
       <c r="N24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
+      <c r="O24" s="2">
+        <v>868.06060000000002</v>
+      </c>
+      <c r="P24" s="2">
+        <v>877.39440000000002</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>866.85130000000004</v>
+      </c>
+      <c r="R24" s="2">
+        <v>882.58219999999994</v>
+      </c>
+      <c r="S24" s="2">
+        <v>903.27279999999996</v>
+      </c>
+      <c r="T24" s="2">
+        <v>923.50300000000004</v>
+      </c>
+      <c r="U24" s="2">
+        <v>886.74720000000002</v>
+      </c>
+      <c r="V24" s="2">
+        <v>921.13440000000003</v>
+      </c>
+      <c r="W24" s="2">
+        <v>919.10699999999997</v>
+      </c>
+      <c r="X24" s="2">
+        <v>939.16319999999996</v>
+      </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="C25" s="2">
+        <v>43.8628</v>
+      </c>
+      <c r="D25" s="2">
+        <v>43.9925</v>
+      </c>
+      <c r="E25" s="2">
+        <v>46.468200000000003</v>
+      </c>
+      <c r="F25" s="2">
+        <v>47.744300000000003</v>
+      </c>
+      <c r="G25" s="2">
+        <v>46.180799999999998</v>
+      </c>
+      <c r="H25" s="2">
+        <v>45.310699999999997</v>
+      </c>
+      <c r="I25" s="2">
+        <v>45.280299999999997</v>
+      </c>
+      <c r="J25" s="2">
+        <v>44.079099999999997</v>
+      </c>
+      <c r="K25" s="2">
+        <v>47.499099999999999</v>
+      </c>
+      <c r="L25" s="2">
+        <v>45.697499999999998</v>
+      </c>
       <c r="N25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
+      <c r="O25" s="2">
+        <v>1173.087</v>
+      </c>
+      <c r="P25" s="2">
+        <v>1129.7619999999999</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>1197.8713</v>
+      </c>
+      <c r="R25" s="2">
+        <v>1137.0664999999999</v>
+      </c>
+      <c r="S25" s="2">
+        <v>1121.0473</v>
+      </c>
+      <c r="T25" s="2">
+        <v>1150.1841999999999</v>
+      </c>
+      <c r="U25" s="2">
+        <v>1138.5012999999999</v>
+      </c>
+      <c r="V25" s="2">
+        <v>1141.0028</v>
+      </c>
+      <c r="W25" s="2">
+        <v>1133.9609</v>
+      </c>
+      <c r="X25" s="2">
+        <v>1121.5616</v>
+      </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
+      <c r="C26" s="2">
+        <v>98.279799999999994</v>
+      </c>
+      <c r="D26" s="2">
+        <v>96.567999999999998</v>
+      </c>
+      <c r="E26" s="2">
+        <v>98.576700000000002</v>
+      </c>
+      <c r="F26" s="2">
+        <v>93.311199999999999</v>
+      </c>
+      <c r="G26" s="2">
+        <v>92.759500000000003</v>
+      </c>
+      <c r="H26" s="2">
+        <v>94.284300000000002</v>
+      </c>
+      <c r="I26" s="2">
+        <v>97.297399999999996</v>
+      </c>
+      <c r="J26" s="2">
+        <v>97.755700000000004</v>
+      </c>
+      <c r="K26" s="2">
+        <v>93.373900000000006</v>
+      </c>
+      <c r="L26" s="2">
+        <v>91.055300000000003</v>
+      </c>
       <c r="N26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
+      <c r="O26" s="2">
+        <v>2339.2865000000002</v>
+      </c>
+      <c r="P26" s="2">
+        <v>2576.0318000000002</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>2428.8901000000001</v>
+      </c>
+      <c r="R26" s="2">
+        <v>2369.9295000000002</v>
+      </c>
+      <c r="S26" s="2">
+        <v>2413.4684000000002</v>
+      </c>
+      <c r="T26" s="2">
+        <v>2435.8843999999999</v>
+      </c>
+      <c r="U26" s="2">
+        <v>2426.3197</v>
+      </c>
+      <c r="V26" s="2">
+        <v>2421.0010000000002</v>
+      </c>
+      <c r="W26" s="2">
+        <v>2434.6837</v>
+      </c>
+      <c r="X26" s="2">
+        <v>2386.3489</v>
+      </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
+      <c r="C27" s="2">
+        <v>0.82410000000000005</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0.78639999999999999</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.78049999999999997</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.82630000000000003</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.78720000000000001</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0.77410000000000001</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0.76459999999999995</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0.76719999999999999</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0.77359999999999995</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0.77010000000000001</v>
+      </c>
       <c r="N27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
+      <c r="O27" s="2">
+        <v>4.8323999999999998</v>
+      </c>
+      <c r="P27" s="2">
+        <v>4.9688999999999997</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>5.1543999999999999</v>
+      </c>
+      <c r="R27" s="2">
+        <v>4.7093999999999996</v>
+      </c>
+      <c r="S27" s="2">
+        <v>5.1172000000000004</v>
+      </c>
+      <c r="T27" s="2">
+        <v>4.7491000000000003</v>
+      </c>
+      <c r="U27" s="2">
+        <v>4.7873000000000001</v>
+      </c>
+      <c r="V27" s="2">
+        <v>5.0522</v>
+      </c>
+      <c r="W27" s="2">
+        <v>5.0076000000000001</v>
+      </c>
+      <c r="X27" s="2">
+        <v>4.7050999999999998</v>
+      </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
+      <c r="C28" s="2">
+        <v>0.54369999999999996</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.53120000000000001</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.53349999999999997</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.53269999999999995</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0.52680000000000005</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0.52969999999999995</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0.52659999999999996</v>
+      </c>
+      <c r="K28" s="2">
+        <v>0.52039999999999997</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0.52429999999999999</v>
+      </c>
       <c r="N28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
+      <c r="O28" s="2">
+        <v>3.2902</v>
+      </c>
+      <c r="P28" s="2">
+        <v>3.4653999999999998</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>3.3106</v>
+      </c>
+      <c r="R28" s="2">
+        <v>3.4045999999999998</v>
+      </c>
+      <c r="S28" s="2">
+        <v>3.2970000000000002</v>
+      </c>
+      <c r="T28" s="2">
+        <v>3.3713000000000002</v>
+      </c>
+      <c r="U28" s="2">
+        <v>3.3136999999999999</v>
+      </c>
+      <c r="V28" s="2">
+        <v>3.3351000000000002</v>
+      </c>
+      <c r="W28" s="2">
+        <v>3.3092999999999999</v>
+      </c>
+      <c r="X28" s="2">
+        <v>3.452</v>
+      </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
@@ -5936,18 +6582,18 @@
       <c r="C31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="12"/>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B32" s="6"/>
-      <c r="C32" s="1">
+      <c r="B32" s="13"/>
+      <c r="C32" s="2">
         <v>100</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="2">
         <v>500</v>
       </c>
       <c r="E32" s="2">
@@ -5967,145 +6613,145 @@
       <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="2" t="str">
+      <c r="C33" s="2">
         <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
-        <v>undone</v>
-      </c>
-      <c r="D33" s="2" t="str">
+        <v>3.4100000000000007E-3</v>
+      </c>
+      <c r="D33" s="2">
         <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
-        <v>undone</v>
-      </c>
-      <c r="E33" s="2" t="str">
+        <v>9.7070000000000017E-2</v>
+      </c>
+      <c r="E33" s="2">
         <f>IF(COUNTBLANK(C15:L15)&gt;0,"undone",AVERAGE(C15:L15))</f>
-        <v>undone</v>
-      </c>
-      <c r="F33" s="2" t="str">
+        <v>0.36215000000000003</v>
+      </c>
+      <c r="F33" s="2">
         <f>IF(COUNTBLANK(O15:X15)&gt;0,"undone",AVERAGE(O15:X15))</f>
-        <v>undone</v>
-      </c>
-      <c r="G33" s="2" t="str">
+        <v>9.0675799999999995</v>
+      </c>
+      <c r="G33" s="2">
         <f>IF(COUNTBLANK(C24:L24)&gt;0,"undone",AVERAGE(C24:L24))</f>
-        <v>undone</v>
-      </c>
-      <c r="H33" s="2" t="str">
+        <v>35.300449999999998</v>
+      </c>
+      <c r="H33" s="2">
         <f>IF(COUNTBLANK(O24:X24)&gt;0,"undone",AVERAGE(O24:X24))</f>
-        <v>undone</v>
+        <v>898.78161</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="2" t="str">
-        <f t="shared" ref="C34:C37" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
-        <v>undone</v>
-      </c>
-      <c r="D34" s="2" t="str">
-        <f t="shared" ref="D34:D37" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
-        <v>undone</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <f t="shared" ref="E34:E37" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
-        <v>undone</v>
-      </c>
-      <c r="F34" s="2" t="str">
-        <f t="shared" ref="F34:F37" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
-        <v>undone</v>
-      </c>
-      <c r="G34" s="2" t="str">
-        <f t="shared" ref="G34:G37" si="4">IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
-        <v>undone</v>
-      </c>
-      <c r="H34" s="2" t="str">
+      <c r="C34" s="2">
+        <f>IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
+        <v>5.1600000000000005E-3</v>
+      </c>
+      <c r="D34" s="2">
+        <f>IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
+        <v>0.1351</v>
+      </c>
+      <c r="E34" s="2">
+        <f>IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
+        <v>0.4676499999999999</v>
+      </c>
+      <c r="F34" s="2">
+        <f>IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
+        <v>11.12998</v>
+      </c>
+      <c r="G34" s="2">
+        <f>IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
+        <v>45.611530000000002</v>
+      </c>
+      <c r="H34" s="2">
         <f>IF(COUNTBLANK(O25:X25)&gt;0,"undone",AVERAGE(O25:X25))</f>
-        <v>undone</v>
+        <v>1144.4044900000001</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D35" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F35" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G35" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H35" s="2" t="str">
-        <f t="shared" ref="H35:H37" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",AVERAGE(O26:X26))</f>
-        <v>undone</v>
+      <c r="C35" s="2">
+        <f>IF(COUNTBLANK(C8:L8)&gt;0,"undone",AVERAGE(C8:L8))</f>
+        <v>9.5599999999999973E-3</v>
+      </c>
+      <c r="D35" s="2">
+        <f>IF(COUNTBLANK(O8:X8)&gt;0,"undone",AVERAGE(O8:X8))</f>
+        <v>0.26630999999999999</v>
+      </c>
+      <c r="E35" s="2">
+        <f>IF(COUNTBLANK(C17:L17)&gt;0,"undone",AVERAGE(C17:L17))</f>
+        <v>1.0637199999999998</v>
+      </c>
+      <c r="F35" s="2">
+        <f>IF(COUNTBLANK(O17:X17)&gt;0,"undone",AVERAGE(O17:X17))</f>
+        <v>23.42755</v>
+      </c>
+      <c r="G35" s="2">
+        <f>IF(COUNTBLANK(C26:L26)&gt;0,"undone",AVERAGE(C26:L26))</f>
+        <v>95.326180000000008</v>
+      </c>
+      <c r="H35" s="2">
+        <f>IF(COUNTBLANK(O26:X26)&gt;0,"undone",AVERAGE(O26:X26))</f>
+        <v>2423.1844000000006</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D36" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F36" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G36" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H36" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>undone</v>
+      <c r="C36" s="2">
+        <f>IF(COUNTBLANK(C9:L9)&gt;0,"undone",AVERAGE(C9:L9))</f>
+        <v>4.1400000000000005E-3</v>
+      </c>
+      <c r="D36" s="2">
+        <f>IF(COUNTBLANK(O9:X9)&gt;0,"undone",AVERAGE(O9:X9))</f>
+        <v>2.9650000000000003E-2</v>
+      </c>
+      <c r="E36" s="2">
+        <f>IF(COUNTBLANK(C18:L18)&gt;0,"undone",AVERAGE(C18:L18))</f>
+        <v>4.4389999999999999E-2</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(COUNTBLANK(O18:X18)&gt;0,"undone",AVERAGE(O18:X18))</f>
+        <v>0.34113000000000004</v>
+      </c>
+      <c r="G36" s="2">
+        <f>IF(COUNTBLANK(C27:L27)&gt;0,"undone",AVERAGE(C27:L27))</f>
+        <v>0.78540999999999994</v>
+      </c>
+      <c r="H36" s="2">
+        <f>IF(COUNTBLANK(O27:X27)&gt;0,"undone",AVERAGE(O27:X27))</f>
+        <v>4.9083600000000001</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D37" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F37" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G37" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H37" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>undone</v>
+      <c r="C37" s="2">
+        <f>IF(COUNTBLANK(C10:L10)&gt;0,"undone",AVERAGE(C10:L10))</f>
+        <v>1.7799999999999999E-3</v>
+      </c>
+      <c r="D37" s="2">
+        <f>IF(COUNTBLANK(O10:X10)&gt;0,"undone",AVERAGE(O10:X10))</f>
+        <v>1.6480000000000002E-2</v>
+      </c>
+      <c r="E37" s="2">
+        <f>IF(COUNTBLANK(C19:L19)&gt;0,"undone",AVERAGE(C19:L19))</f>
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="F37" s="2">
+        <f>IF(COUNTBLANK(O19:X19)&gt;0,"undone",AVERAGE(O19:X19))</f>
+        <v>0.22132000000000002</v>
+      </c>
+      <c r="G37" s="2">
+        <f>IF(COUNTBLANK(C28:L28)&gt;0,"undone",AVERAGE(C28:L28))</f>
+        <v>0.53208999999999995</v>
+      </c>
+      <c r="H37" s="2">
+        <f>IF(COUNTBLANK(O28:X28)&gt;0,"undone",AVERAGE(O28:X28))</f>
+        <v>3.3549199999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6168,7 +6814,7 @@
       <c r="A1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="8"/>
+      <c r="B1" s="10"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -6193,33 +6839,33 @@
       <c r="C4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="12"/>
       <c r="N4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="12"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="6"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -6250,7 +6896,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="6"/>
+      <c r="N5" s="13"/>
       <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
@@ -6286,141 +6932,341 @@
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="C6" s="2">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="L6" s="2">
+        <v>2.0000000000000001E-4</v>
+      </c>
       <c r="N6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
+      <c r="O6" s="2">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="P6" s="2">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="R6" s="2">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="S6" s="2">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="T6" s="2">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="U6" s="2">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="V6" s="2">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="W6" s="2">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="X6" s="2">
+        <v>8.9999999999999998E-4</v>
+      </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="C7" s="2">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="I7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="K7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="L7" s="2">
+        <v>4.5999999999999999E-3</v>
+      </c>
       <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
+      <c r="O7" s="2">
+        <v>0.1157</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.11119999999999999</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0.1114</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0.1114</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0.1113</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0.1114</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0.11119999999999999</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0.11119999999999999</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0.1113</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0.1113</v>
+      </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="C8" s="2">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="K8" s="2">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="L8" s="2">
+        <v>6.0000000000000001E-3</v>
+      </c>
       <c r="N8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
+      <c r="O8" s="2">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0.1462</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.14610000000000001</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0.1462</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0.15040000000000001</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.1462</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0.1462</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0.15090000000000001</v>
+      </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="C9" s="2">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="I9" s="2">
+        <v>2.8E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2.8E-3</v>
+      </c>
       <c r="N9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
+      <c r="O9" s="2">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="P9" s="2">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="R9" s="2">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="S9" s="2">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="T9" s="2">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="U9" s="2">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="V9" s="2">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="W9" s="2">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="X9" s="2">
+        <v>1.7299999999999999E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="C10" s="2">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4.3E-3</v>
+      </c>
+      <c r="I10" s="2">
+        <v>4.3E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="K10" s="2">
+        <v>4.3E-3</v>
+      </c>
+      <c r="L10" s="2">
+        <v>4.3E-3</v>
+      </c>
       <c r="N10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
+      <c r="O10" s="2">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="P10" s="2">
+        <v>8.7800000000000003E-2</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>8.7800000000000003E-2</v>
+      </c>
+      <c r="R10" s="2">
+        <v>8.7900000000000006E-2</v>
+      </c>
+      <c r="S10" s="2">
+        <v>8.7900000000000006E-2</v>
+      </c>
+      <c r="T10" s="2">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="U10" s="2">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="V10" s="2">
+        <v>8.7900000000000006E-2</v>
+      </c>
+      <c r="W10" s="2">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="X10" s="2">
+        <v>8.7900000000000006E-2</v>
+      </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
@@ -6445,33 +7291,33 @@
       <c r="C13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="12"/>
       <c r="N13" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="12"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="3" t="s">
         <v>2</v>
       </c>
@@ -6502,7 +7348,7 @@
       <c r="L14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N14" s="6"/>
+      <c r="N14" s="13"/>
       <c r="O14" s="3" t="s">
         <v>2</v>
       </c>
@@ -6538,141 +7384,341 @@
       <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="C15" s="2">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1.8E-3</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1.8E-3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1.9E-3</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1.8E-3</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1.9E-3</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1.8E-3</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1.8E-3</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1.8E-3</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1.8E-3</v>
+      </c>
       <c r="N15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
+      <c r="O15" s="2">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="P15" s="2">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="R15" s="2">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="S15" s="2">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="T15" s="2">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="U15" s="2">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="V15" s="2">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="W15" s="2">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="X15" s="2">
+        <v>8.3999999999999995E-3</v>
+      </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+      <c r="C16" s="2">
+        <v>0.4486</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.44409999999999999</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.4506</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.44390000000000002</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.44750000000000001</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.44379999999999997</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.44379999999999997</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.44350000000000001</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0.44369999999999998</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0.44619999999999999</v>
+      </c>
       <c r="N16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
+      <c r="O16" s="2">
+        <v>11.0426</v>
+      </c>
+      <c r="P16" s="2">
+        <v>11.614800000000001</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>11.426500000000001</v>
+      </c>
+      <c r="R16" s="2">
+        <v>12.161099999999999</v>
+      </c>
+      <c r="S16" s="2">
+        <v>11.054399999999999</v>
+      </c>
+      <c r="T16" s="2">
+        <v>11.632899999999999</v>
+      </c>
+      <c r="U16" s="2">
+        <v>11.4293</v>
+      </c>
+      <c r="V16" s="2">
+        <v>11.1236</v>
+      </c>
+      <c r="W16" s="2">
+        <v>11.191599999999999</v>
+      </c>
+      <c r="X16" s="2">
+        <v>11.475099999999999</v>
+      </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
+      <c r="C17" s="2">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.5847</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.58809999999999996</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.58479999999999999</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.58479999999999999</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.58679999999999999</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.58479999999999999</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.58450000000000002</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0.58809999999999996</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0.58479999999999999</v>
+      </c>
       <c r="N17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
+      <c r="O17" s="2">
+        <v>15.2623</v>
+      </c>
+      <c r="P17" s="2">
+        <v>14.686199999999999</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>14.870200000000001</v>
+      </c>
+      <c r="R17" s="2">
+        <v>15.0558</v>
+      </c>
+      <c r="S17" s="2">
+        <v>15.020899999999999</v>
+      </c>
+      <c r="T17" s="2">
+        <v>14.7026</v>
+      </c>
+      <c r="U17" s="2">
+        <v>15.3482</v>
+      </c>
+      <c r="V17" s="2">
+        <v>14.5159</v>
+      </c>
+      <c r="W17" s="2">
+        <v>15.292999999999999</v>
+      </c>
+      <c r="X17" s="2">
+        <v>14.783799999999999</v>
+      </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
+      <c r="C18" s="2">
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>3.7400000000000003E-2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="G18" s="2">
+        <v>3.7400000000000003E-2</v>
+      </c>
+      <c r="H18" s="2">
+        <v>3.7400000000000003E-2</v>
+      </c>
+      <c r="I18" s="2">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="J18" s="2">
+        <v>3.73E-2</v>
+      </c>
+      <c r="K18" s="2">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="L18" s="2">
+        <v>3.7600000000000001E-2</v>
+      </c>
       <c r="N18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
+      <c r="O18" s="2">
+        <v>0.222</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.21679999999999999</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0.21690000000000001</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0.2167</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0.21629999999999999</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0.21679999999999999</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0.21690000000000001</v>
+      </c>
+      <c r="V18" s="2">
+        <v>0.2198</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0.2167</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0.21659999999999999</v>
+      </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
+      <c r="C19" s="2">
+        <v>0.40770000000000001</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.60060000000000002</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.4597</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.41349999999999998</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.40920000000000001</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0.41420000000000001</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.41289999999999999</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.40789999999999998</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.40839999999999999</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0.40400000000000003</v>
+      </c>
       <c r="N19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
+      <c r="O19" s="2">
+        <v>9.8001000000000005</v>
+      </c>
+      <c r="P19" s="2">
+        <v>9.4856999999999996</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>9.8346999999999998</v>
+      </c>
+      <c r="R19" s="2">
+        <v>9.1980000000000004</v>
+      </c>
+      <c r="S19" s="2">
+        <v>9.7324000000000002</v>
+      </c>
+      <c r="T19" s="2">
+        <v>9.3353999999999999</v>
+      </c>
+      <c r="U19" s="2">
+        <v>9.6067999999999998</v>
+      </c>
+      <c r="V19" s="2">
+        <v>9.9581</v>
+      </c>
+      <c r="W19" s="2">
+        <v>9.2865000000000002</v>
+      </c>
+      <c r="X19" s="2">
+        <v>9.4220000000000006</v>
+      </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
@@ -6697,33 +7743,33 @@
       <c r="C22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="12"/>
       <c r="N22" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="12"/>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="13"/>
       <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
@@ -6754,7 +7800,7 @@
       <c r="L23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N23" s="6"/>
+      <c r="N23" s="13"/>
       <c r="O23" s="3" t="s">
         <v>2</v>
       </c>
@@ -6790,141 +7836,341 @@
       <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
+      <c r="C24" s="2">
+        <v>1.6E-2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1.6E-2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1.6E-2</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1.6E-2</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1.6E-2</v>
+      </c>
       <c r="N24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
+      <c r="O24" s="2">
+        <v>9.7799999999999998E-2</v>
+      </c>
+      <c r="P24" s="2">
+        <v>9.6299999999999997E-2</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>9.9299999999999999E-2</v>
+      </c>
+      <c r="R24" s="2">
+        <v>9.5399999999999999E-2</v>
+      </c>
+      <c r="S24" s="2">
+        <v>9.9099999999999994E-2</v>
+      </c>
+      <c r="T24" s="2">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="U24" s="2">
+        <v>8.8599999999999998E-2</v>
+      </c>
+      <c r="V24" s="2">
+        <v>8.8599999999999998E-2</v>
+      </c>
+      <c r="W24" s="2">
+        <v>8.8599999999999998E-2</v>
+      </c>
+      <c r="X24" s="2">
+        <v>8.8400000000000006E-2</v>
+      </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="C25" s="2">
+        <v>43.956299999999999</v>
+      </c>
+      <c r="D25" s="2">
+        <v>47.018099999999997</v>
+      </c>
+      <c r="E25" s="2">
+        <v>50.816600000000001</v>
+      </c>
+      <c r="F25" s="2">
+        <v>45.354100000000003</v>
+      </c>
+      <c r="G25" s="2">
+        <v>45.864199999999997</v>
+      </c>
+      <c r="H25" s="2">
+        <v>45.458300000000001</v>
+      </c>
+      <c r="I25" s="2">
+        <v>43.521299999999997</v>
+      </c>
+      <c r="J25" s="2">
+        <v>42.778700000000001</v>
+      </c>
+      <c r="K25" s="2">
+        <v>43.060299999999998</v>
+      </c>
+      <c r="L25" s="2">
+        <v>43.732700000000001</v>
+      </c>
       <c r="N25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
+      <c r="O25" s="2">
+        <v>1205.9837</v>
+      </c>
+      <c r="P25" s="2">
+        <v>1638.5706</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>1661.7444</v>
+      </c>
+      <c r="R25" s="2">
+        <v>1625.0369000000001</v>
+      </c>
+      <c r="S25" s="2">
+        <v>1622.0289</v>
+      </c>
+      <c r="T25" s="2">
+        <v>1659.8554999999999</v>
+      </c>
+      <c r="U25" s="2">
+        <v>1560.0806</v>
+      </c>
+      <c r="V25" s="2">
+        <v>1578.2026000000001</v>
+      </c>
+      <c r="W25" s="2">
+        <v>1615.7471</v>
+      </c>
+      <c r="X25" s="2">
+        <v>1619.6980000000001</v>
+      </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
+      <c r="C26" s="2">
+        <v>57.050600000000003</v>
+      </c>
+      <c r="D26" s="2">
+        <v>59.419800000000002</v>
+      </c>
+      <c r="E26" s="2">
+        <v>60.781999999999996</v>
+      </c>
+      <c r="F26" s="2">
+        <v>58.686199999999999</v>
+      </c>
+      <c r="G26" s="2">
+        <v>63.0807</v>
+      </c>
+      <c r="H26" s="2">
+        <v>60.058399999999999</v>
+      </c>
+      <c r="I26" s="2">
+        <v>60.618600000000001</v>
+      </c>
+      <c r="J26" s="2">
+        <v>62.023699999999998</v>
+      </c>
+      <c r="K26" s="2">
+        <v>61.230200000000004</v>
+      </c>
+      <c r="L26" s="2">
+        <v>59.590299999999999</v>
+      </c>
       <c r="N26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
+      <c r="O26" s="2">
+        <v>1528.5590999999999</v>
+      </c>
+      <c r="P26" s="2">
+        <v>1515.3344999999999</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>1518.1469999999999</v>
+      </c>
+      <c r="R26" s="2">
+        <v>1489.0852</v>
+      </c>
+      <c r="S26" s="2">
+        <v>1472.1224999999999</v>
+      </c>
+      <c r="T26" s="2">
+        <v>1468.0283999999999</v>
+      </c>
+      <c r="U26" s="2">
+        <v>1526.2985000000001</v>
+      </c>
+      <c r="V26" s="2">
+        <v>1511.4191000000001</v>
+      </c>
+      <c r="W26" s="2">
+        <v>1499.7338</v>
+      </c>
+      <c r="X26" s="2">
+        <v>1461.9425000000001</v>
+      </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
+      <c r="C27" s="2">
+        <v>0.47349999999999998</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0.46579999999999999</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.4642</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.48220000000000002</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.4698</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0.46529999999999999</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0.46589999999999998</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0.46460000000000001</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0.70720000000000005</v>
+      </c>
       <c r="N27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
+      <c r="O27" s="2">
+        <v>2.9761000000000002</v>
+      </c>
+      <c r="P27" s="2">
+        <v>2.5329999999999999</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>2.4996999999999998</v>
+      </c>
+      <c r="R27" s="2">
+        <v>2.5211999999999999</v>
+      </c>
+      <c r="S27" s="2">
+        <v>2.5223</v>
+      </c>
+      <c r="T27" s="2">
+        <v>2.5257000000000001</v>
+      </c>
+      <c r="U27" s="2">
+        <v>2.8889999999999998</v>
+      </c>
+      <c r="V27" s="2">
+        <v>2.4958</v>
+      </c>
+      <c r="W27" s="2">
+        <v>2.4750999999999999</v>
+      </c>
+      <c r="X27" s="2">
+        <v>2.4815999999999998</v>
+      </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
+      <c r="C28" s="2">
+        <v>40.399299999999997</v>
+      </c>
+      <c r="D28" s="2">
+        <v>40.592599999999997</v>
+      </c>
+      <c r="E28" s="2">
+        <v>39.578299999999999</v>
+      </c>
+      <c r="F28" s="2">
+        <v>40.654200000000003</v>
+      </c>
+      <c r="G28" s="2">
+        <v>40.483800000000002</v>
+      </c>
+      <c r="H28" s="2">
+        <v>40.684100000000001</v>
+      </c>
+      <c r="I28" s="2">
+        <v>40.582799999999999</v>
+      </c>
+      <c r="J28" s="2">
+        <v>40.0383</v>
+      </c>
+      <c r="K28" s="2">
+        <v>40.058900000000001</v>
+      </c>
+      <c r="L28" s="2">
+        <v>40.997100000000003</v>
+      </c>
       <c r="N28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
+      <c r="O28" s="2">
+        <v>964.99519999999995</v>
+      </c>
+      <c r="P28" s="2">
+        <v>972.25599999999997</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>1012.2445</v>
+      </c>
+      <c r="R28" s="2">
+        <v>991.51170000000002</v>
+      </c>
+      <c r="S28" s="2">
+        <v>996.05719999999997</v>
+      </c>
+      <c r="T28" s="2">
+        <v>1304.6711</v>
+      </c>
+      <c r="U28" s="2">
+        <v>1400.7298000000001</v>
+      </c>
+      <c r="V28" s="2">
+        <v>1314.1836000000001</v>
+      </c>
+      <c r="W28" s="2">
+        <v>1388.5877</v>
+      </c>
+      <c r="X28" s="2">
+        <v>1375.0432000000001</v>
+      </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
@@ -6933,18 +8179,18 @@
       <c r="C31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="12"/>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B32" s="6"/>
-      <c r="C32" s="1">
+      <c r="B32" s="13"/>
+      <c r="C32" s="2">
         <v>100</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="2">
         <v>500</v>
       </c>
       <c r="E32" s="2">
@@ -6964,155 +8210,149 @@
       <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="2" t="str">
+      <c r="C33" s="2">
         <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
-        <v>undone</v>
-      </c>
-      <c r="D33" s="2" t="str">
+        <v>1.6000000000000004E-4</v>
+      </c>
+      <c r="D33" s="2">
         <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
-        <v>undone</v>
-      </c>
-      <c r="E33" s="2" t="str">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="E33" s="2">
         <f>IF(COUNTBLANK(C15:L15)&gt;0,"undone",AVERAGE(C15:L15))</f>
-        <v>undone</v>
-      </c>
-      <c r="F33" s="2" t="str">
+        <v>1.82E-3</v>
+      </c>
+      <c r="F33" s="2">
         <f>IF(COUNTBLANK(O15:X15)&gt;0,"undone",AVERAGE(O15:X15))</f>
-        <v>undone</v>
-      </c>
-      <c r="G33" s="2" t="str">
+        <v>8.4700000000000001E-3</v>
+      </c>
+      <c r="G33" s="2">
         <f>IF(COUNTBLANK(C24:L24)&gt;0,"undone",AVERAGE(C24:L24))</f>
-        <v>undone</v>
-      </c>
-      <c r="H33" s="2" t="str">
+        <v>1.5960000000000002E-2</v>
+      </c>
+      <c r="H33" s="2">
         <f>IF(COUNTBLANK(O24:X24)&gt;0,"undone",AVERAGE(O24:X24))</f>
-        <v>undone</v>
+        <v>9.3109999999999998E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="2" t="str">
-        <f t="shared" ref="C34:C37" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
-        <v>undone</v>
-      </c>
-      <c r="D34" s="2" t="str">
-        <f t="shared" ref="D34:D37" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
-        <v>undone</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <f t="shared" ref="E34:E37" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
-        <v>undone</v>
-      </c>
-      <c r="F34" s="2" t="str">
-        <f t="shared" ref="F34:F37" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
-        <v>undone</v>
-      </c>
-      <c r="G34" s="2" t="str">
-        <f t="shared" ref="G34:G37" si="4">IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
-        <v>undone</v>
-      </c>
-      <c r="H34" s="2" t="str">
-        <f t="shared" ref="H34:H37" si="5">IF(COUNTBLANK(O25:X25)&gt;0,"undone",AVERAGE(O25:X25))</f>
-        <v>undone</v>
+      <c r="C34" s="2">
+        <f>IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
+        <v>4.7599999999999995E-3</v>
+      </c>
+      <c r="D34" s="2">
+        <f>IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
+        <v>0.11173999999999998</v>
+      </c>
+      <c r="E34" s="2">
+        <f>IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
+        <v>0.44557000000000002</v>
+      </c>
+      <c r="F34" s="2">
+        <f>IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
+        <v>11.415189999999999</v>
+      </c>
+      <c r="G34" s="2">
+        <f>IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
+        <v>45.156060000000004</v>
+      </c>
+      <c r="H34" s="2">
+        <f>IF(COUNTBLANK(O25:X25)&gt;0,"undone",AVERAGE(O25:X25))</f>
+        <v>1578.6948299999999</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D35" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F35" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G35" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H35" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>undone</v>
+      <c r="C35" s="2">
+        <f>IF(COUNTBLANK(C8:L8)&gt;0,"undone",AVERAGE(C8:L8))</f>
+        <v>5.9700000000000005E-3</v>
+      </c>
+      <c r="D35" s="2">
+        <f>IF(COUNTBLANK(O8:X8)&gt;0,"undone",AVERAGE(O8:X8))</f>
+        <v>0.14710999999999999</v>
+      </c>
+      <c r="E35" s="2">
+        <f>IF(COUNTBLANK(C17:L17)&gt;0,"undone",AVERAGE(C17:L17))</f>
+        <v>0.58564000000000005</v>
+      </c>
+      <c r="F35" s="2">
+        <f>IF(COUNTBLANK(O17:X17)&gt;0,"undone",AVERAGE(O17:X17))</f>
+        <v>14.953890000000001</v>
+      </c>
+      <c r="G35" s="2">
+        <f>IF(COUNTBLANK(C26:L26)&gt;0,"undone",AVERAGE(C26:L26))</f>
+        <v>60.254049999999992</v>
+      </c>
+      <c r="H35" s="2">
+        <f>IF(COUNTBLANK(O26:X26)&gt;0,"undone",AVERAGE(O26:X26))</f>
+        <v>1499.0670599999999</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D36" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F36" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G36" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H36" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>undone</v>
+      <c r="C36" s="2">
+        <f>IF(COUNTBLANK(C9:L9)&gt;0,"undone",AVERAGE(C9:L9))</f>
+        <v>2.9499999999999999E-3</v>
+      </c>
+      <c r="D36" s="2">
+        <f>IF(COUNTBLANK(O9:X9)&gt;0,"undone",AVERAGE(O9:X9))</f>
+        <v>1.7470000000000003E-2</v>
+      </c>
+      <c r="E36" s="2">
+        <f>IF(COUNTBLANK(C18:L18)&gt;0,"undone",AVERAGE(C18:L18))</f>
+        <v>3.7480000000000006E-2</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(COUNTBLANK(O18:X18)&gt;0,"undone",AVERAGE(O18:X18))</f>
+        <v>0.21754999999999999</v>
+      </c>
+      <c r="G36" s="2">
+        <f>IF(COUNTBLANK(C27:L27)&gt;0,"undone",AVERAGE(C27:L27))</f>
+        <v>0.50645000000000007</v>
+      </c>
+      <c r="H36" s="2">
+        <f>IF(COUNTBLANK(O27:X27)&gt;0,"undone",AVERAGE(O27:X27))</f>
+        <v>2.5919500000000002</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D37" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F37" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G37" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H37" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>undone</v>
+      <c r="C37" s="2">
+        <f>IF(COUNTBLANK(C10:L10)&gt;0,"undone",AVERAGE(C10:L10))</f>
+        <v>5.0699999999999999E-3</v>
+      </c>
+      <c r="D37" s="2">
+        <f>IF(COUNTBLANK(O10:X10)&gt;0,"undone",AVERAGE(O10:X10))</f>
+        <v>8.7919999999999984E-2</v>
+      </c>
+      <c r="E37" s="2">
+        <f>IF(COUNTBLANK(C19:L19)&gt;0,"undone",AVERAGE(C19:L19))</f>
+        <v>0.43381000000000008</v>
+      </c>
+      <c r="F37" s="2">
+        <f>IF(COUNTBLANK(O19:X19)&gt;0,"undone",AVERAGE(O19:X19))</f>
+        <v>9.5659700000000001</v>
+      </c>
+      <c r="G37" s="2">
+        <f>IF(COUNTBLANK(C28:L28)&gt;0,"undone",AVERAGE(C28:L28))</f>
+        <v>40.406939999999999</v>
+      </c>
+      <c r="H37" s="2">
+        <f>IF(COUNTBLANK(O28:X28)&gt;0,"undone",AVERAGE(O28:X28))</f>
+        <v>1172.0279999999998</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:L22"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="O22:X22"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:H31"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="N13:N14"/>
@@ -7122,6 +8362,12 @@
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="O4:X4"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="O22:X22"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:H31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7164,7 +8410,7 @@
       <c r="A1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="8"/>
+      <c r="B1" s="10"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -7189,33 +8435,33 @@
       <c r="C4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="12"/>
       <c r="N4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="12"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="6"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -7246,7 +8492,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="6"/>
+      <c r="N5" s="13"/>
       <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
@@ -7282,141 +8528,341 @@
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="C6" s="2">
+        <v>1.06E-2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="H6" s="2">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="I6" s="2">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="K6" s="2">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="L6" s="2">
+        <v>9.7999999999999997E-3</v>
+      </c>
       <c r="N6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
+      <c r="O6" s="2">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0.26069999999999999</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0.24429999999999999</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0.24410000000000001</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0.24440000000000001</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0.24410000000000001</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0.24429999999999999</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0.24390000000000001</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0.2492</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0.24429999999999999</v>
+      </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="C7" s="2">
+        <v>8.6E-3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>8.6E-3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="K7" s="2">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="L7" s="2">
+        <v>7.0000000000000001E-3</v>
+      </c>
       <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
+      <c r="O7" s="2">
+        <v>0.16250000000000001</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0.16209999999999999</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0.16189999999999999</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0.1618</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0.16189999999999999</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0.1618</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0.1618</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0.16170000000000001</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0.1618</v>
+      </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="C8" s="2">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1.77E-2</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1.77E-2</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1.77E-2</v>
+      </c>
       <c r="N8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
+      <c r="O8" s="2">
+        <v>0.42559999999999998</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.42149999999999999</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0.42149999999999999</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.42159999999999997</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0.45839999999999997</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0.55079999999999996</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.39269999999999999</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0.30170000000000002</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0.30170000000000002</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0.30159999999999998</v>
+      </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="C9" s="2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="F9" s="2">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="I9" s="2">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K9" s="2">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="L9" s="2">
+        <v>3.8999999999999998E-3</v>
+      </c>
       <c r="N9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
+      <c r="O9" s="2">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="P9" s="2">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="R9" s="2">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="S9" s="2">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="T9" s="2">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="U9" s="2">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="V9" s="2">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="W9" s="2">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="X9" s="2">
+        <v>2.3699999999999999E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="C10" s="2">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>6.3E-3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="I10" s="2">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="K10" s="2">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="L10" s="2">
+        <v>5.7000000000000002E-3</v>
+      </c>
       <c r="N10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
+      <c r="O10" s="2">
+        <v>0.14280000000000001</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.14760000000000001</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.1426</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.1318</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0.13189999999999999</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.1406</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0.13159999999999999</v>
+      </c>
+      <c r="V10" s="2">
+        <v>0.1318</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0.13159999999999999</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0.13159999999999999</v>
+      </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
@@ -7441,33 +8887,33 @@
       <c r="C13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="12"/>
       <c r="N13" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="12"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="3" t="s">
         <v>2</v>
       </c>
@@ -7498,7 +8944,7 @@
       <c r="L14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N14" s="6"/>
+      <c r="N14" s="13"/>
       <c r="O14" s="3" t="s">
         <v>2</v>
       </c>
@@ -7534,141 +8980,341 @@
       <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="C15" s="2">
+        <v>0.97050000000000003</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1.0367999999999999</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.999</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.97140000000000004</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0.99980000000000002</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.97070000000000001</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1.0327</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1.0008999999999999</v>
+      </c>
       <c r="N15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
+      <c r="O15" s="2">
+        <v>25.9312</v>
+      </c>
+      <c r="P15" s="2">
+        <v>27.631499999999999</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>24.940899999999999</v>
+      </c>
+      <c r="R15" s="2">
+        <v>24.842600000000001</v>
+      </c>
+      <c r="S15" s="2">
+        <v>24.635999999999999</v>
+      </c>
+      <c r="T15" s="2">
+        <v>24.614599999999999</v>
+      </c>
+      <c r="U15" s="2">
+        <v>25.124500000000001</v>
+      </c>
+      <c r="V15" s="2">
+        <v>24.5505</v>
+      </c>
+      <c r="W15" s="2">
+        <v>24.216000000000001</v>
+      </c>
+      <c r="X15" s="2">
+        <v>24.750599999999999</v>
+      </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+      <c r="C16" s="2">
+        <v>0.72529999999999994</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.72960000000000003</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.70369999999999999</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.47</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.52070000000000005</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.74609999999999999</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.72419999999999995</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0.73280000000000001</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0.72470000000000001</v>
+      </c>
       <c r="N16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
+      <c r="O16" s="2">
+        <v>17.1523</v>
+      </c>
+      <c r="P16" s="2">
+        <v>17.848299999999998</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>17.434699999999999</v>
+      </c>
+      <c r="R16" s="2">
+        <v>17.679400000000001</v>
+      </c>
+      <c r="S16" s="2">
+        <v>17.361599999999999</v>
+      </c>
+      <c r="T16" s="2">
+        <v>17.873999999999999</v>
+      </c>
+      <c r="U16" s="2">
+        <v>18.167200000000001</v>
+      </c>
+      <c r="V16" s="2">
+        <v>17.799199999999999</v>
+      </c>
+      <c r="W16" s="2">
+        <v>16.817</v>
+      </c>
+      <c r="X16" s="2">
+        <v>17.3293</v>
+      </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
+      <c r="C17" s="2">
+        <v>1.6888000000000001</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1.7133</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1.7928999999999999</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1.6888000000000001</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1.6978</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1.6827000000000001</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1.8147</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1.7455000000000001</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1.6912</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1.74</v>
+      </c>
       <c r="N17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
+      <c r="O17" s="2">
+        <v>43.648899999999998</v>
+      </c>
+      <c r="P17" s="2">
+        <v>52.196199999999997</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>50.922899999999998</v>
+      </c>
+      <c r="R17" s="2">
+        <v>53.752000000000002</v>
+      </c>
+      <c r="S17" s="2">
+        <v>47.679600000000001</v>
+      </c>
+      <c r="T17" s="2">
+        <v>43.726199999999999</v>
+      </c>
+      <c r="U17" s="2">
+        <v>44.172600000000003</v>
+      </c>
+      <c r="V17" s="2">
+        <v>43.718299999999999</v>
+      </c>
+      <c r="W17" s="2">
+        <v>44.755499999999998</v>
+      </c>
+      <c r="X17" s="2">
+        <v>43.540300000000002</v>
+      </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
+      <c r="C18" s="2">
+        <v>5.5899999999999998E-2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>5.4699999999999999E-2</v>
+      </c>
+      <c r="G18" s="2">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="H18" s="2">
+        <v>5.4699999999999999E-2</v>
+      </c>
+      <c r="I18" s="2">
+        <v>5.96E-2</v>
+      </c>
+      <c r="J18" s="2">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="K18" s="2">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="L18" s="2">
+        <v>5.1900000000000002E-2</v>
+      </c>
       <c r="N18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
+      <c r="O18" s="2">
+        <v>0.32529999999999998</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.30480000000000002</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0.31009999999999999</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0.3039</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0.30530000000000002</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0.30520000000000003</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0.30509999999999998</v>
+      </c>
+      <c r="V18" s="2">
+        <v>0.30470000000000003</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0.33260000000000001</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0.33150000000000002</v>
+      </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
+      <c r="C19" s="2">
+        <v>0.56530000000000002</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.58330000000000004</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.5585</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.55710000000000004</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.51219999999999999</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.51290000000000002</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.51639999999999997</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0.55879999999999996</v>
+      </c>
       <c r="N19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
+      <c r="O19" s="2">
+        <v>14.418699999999999</v>
+      </c>
+      <c r="P19" s="2">
+        <v>13.520099999999999</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>13.8674</v>
+      </c>
+      <c r="R19" s="2">
+        <v>13.321400000000001</v>
+      </c>
+      <c r="S19" s="2">
+        <v>13.1266</v>
+      </c>
+      <c r="T19" s="2">
+        <v>13.136699999999999</v>
+      </c>
+      <c r="U19" s="2">
+        <v>13.3796</v>
+      </c>
+      <c r="V19" s="2">
+        <v>13.4102</v>
+      </c>
+      <c r="W19" s="2">
+        <v>13.590400000000001</v>
+      </c>
+      <c r="X19" s="2">
+        <v>13.3523</v>
+      </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
@@ -7693,33 +9339,33 @@
       <c r="C22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="12"/>
       <c r="N22" s="6" t="s">
         <v>1</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="12"/>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="13"/>
       <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
@@ -7750,7 +9396,7 @@
       <c r="L23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N23" s="6"/>
+      <c r="N23" s="13"/>
       <c r="O23" s="3" t="s">
         <v>2</v>
       </c>
@@ -7786,141 +9432,341 @@
       <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
+      <c r="C24" s="2">
+        <v>103.0014</v>
+      </c>
+      <c r="D24" s="2">
+        <v>97.264099999999999</v>
+      </c>
+      <c r="E24" s="2">
+        <v>98.548199999999994</v>
+      </c>
+      <c r="F24" s="2">
+        <v>103.3318</v>
+      </c>
+      <c r="G24" s="2">
+        <v>100.3699</v>
+      </c>
+      <c r="H24" s="2">
+        <v>107.4867</v>
+      </c>
+      <c r="I24" s="2">
+        <v>101.21120000000001</v>
+      </c>
+      <c r="J24" s="2">
+        <v>98.551000000000002</v>
+      </c>
+      <c r="K24" s="2">
+        <v>98.846199999999996</v>
+      </c>
+      <c r="L24" s="2">
+        <v>98.023700000000005</v>
+      </c>
       <c r="N24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
+      <c r="O24" s="2">
+        <v>2510.3557000000001</v>
+      </c>
+      <c r="P24" s="2">
+        <v>2534.8559</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>2532.8533000000002</v>
+      </c>
+      <c r="R24" s="2">
+        <v>2548.2372</v>
+      </c>
+      <c r="S24" s="2">
+        <v>2499.2195999999999</v>
+      </c>
+      <c r="T24" s="2">
+        <v>2621.5641999999998</v>
+      </c>
+      <c r="U24" s="2">
+        <v>2527.2633999999998</v>
+      </c>
+      <c r="V24" s="2">
+        <v>2492.7882</v>
+      </c>
+      <c r="W24" s="2">
+        <v>2539.0194999999999</v>
+      </c>
+      <c r="X24" s="2">
+        <v>2495.9699999999998</v>
+      </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="C25" s="2">
+        <v>73.347800000000007</v>
+      </c>
+      <c r="D25" s="2">
+        <v>71.123400000000004</v>
+      </c>
+      <c r="E25" s="2">
+        <v>70.915099999999995</v>
+      </c>
+      <c r="F25" s="2">
+        <v>76.471800000000002</v>
+      </c>
+      <c r="G25" s="2">
+        <v>69.834299999999999</v>
+      </c>
+      <c r="H25" s="2">
+        <v>67.660399999999996</v>
+      </c>
+      <c r="I25" s="2">
+        <v>71.701599999999999</v>
+      </c>
+      <c r="J25" s="2">
+        <v>77.881600000000006</v>
+      </c>
+      <c r="K25" s="2">
+        <v>68.611400000000003</v>
+      </c>
+      <c r="L25" s="2">
+        <v>73.101200000000006</v>
+      </c>
       <c r="N25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
+      <c r="O25" s="2">
+        <v>1790.6885</v>
+      </c>
+      <c r="P25" s="2">
+        <v>1789.1306999999999</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>1810.4666999999999</v>
+      </c>
+      <c r="R25" s="2">
+        <v>1917.5634</v>
+      </c>
+      <c r="S25" s="2">
+        <v>1883.2183</v>
+      </c>
+      <c r="T25" s="2">
+        <v>1783.3923</v>
+      </c>
+      <c r="U25" s="2">
+        <v>1790.9532999999999</v>
+      </c>
+      <c r="V25" s="2">
+        <v>1788.106</v>
+      </c>
+      <c r="W25" s="2">
+        <v>1798.8915</v>
+      </c>
+      <c r="X25" s="2">
+        <v>1796.5764999999999</v>
+      </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
+      <c r="C26" s="2">
+        <v>173.47499999999999</v>
+      </c>
+      <c r="D26" s="2">
+        <v>178.95140000000001</v>
+      </c>
+      <c r="E26" s="2">
+        <v>171.9376</v>
+      </c>
+      <c r="F26" s="2">
+        <v>171.4178</v>
+      </c>
+      <c r="G26" s="2">
+        <v>181.54419999999999</v>
+      </c>
+      <c r="H26" s="2">
+        <v>179.70959999999999</v>
+      </c>
+      <c r="I26" s="2">
+        <v>205.8468</v>
+      </c>
+      <c r="J26" s="2">
+        <v>193.7859</v>
+      </c>
+      <c r="K26" s="2">
+        <v>175.297</v>
+      </c>
+      <c r="L26" s="2">
+        <v>183.62530000000001</v>
+      </c>
       <c r="N26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
+      <c r="O26" s="2">
+        <v>4471.6032999999998</v>
+      </c>
+      <c r="P26" s="2">
+        <v>4398.5838000000003</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>4252.6989000000003</v>
+      </c>
+      <c r="R26" s="2">
+        <v>4605.4750000000004</v>
+      </c>
+      <c r="S26" s="2">
+        <v>4160.6336000000001</v>
+      </c>
+      <c r="T26" s="2">
+        <v>4380.5757000000003</v>
+      </c>
+      <c r="U26" s="2">
+        <v>4295.415</v>
+      </c>
+      <c r="V26" s="2">
+        <v>4408.6949999999997</v>
+      </c>
+      <c r="W26" s="2">
+        <v>4494.3203000000003</v>
+      </c>
+      <c r="X26" s="2">
+        <v>4359.2286999999997</v>
+      </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
+      <c r="C27" s="2">
+        <v>0.64770000000000005</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.64429999999999998</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.64410000000000001</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.73370000000000002</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0.65259999999999996</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0.64539999999999997</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0.64429999999999998</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0.65869999999999995</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0.64410000000000001</v>
+      </c>
       <c r="N27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
+      <c r="O27" s="2">
+        <v>4.2145999999999999</v>
+      </c>
+      <c r="P27" s="2">
+        <v>4.4625000000000004</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>4.2648999999999999</v>
+      </c>
+      <c r="R27" s="2">
+        <v>3.7871000000000001</v>
+      </c>
+      <c r="S27" s="2">
+        <v>3.6907999999999999</v>
+      </c>
+      <c r="T27" s="2">
+        <v>3.6882000000000001</v>
+      </c>
+      <c r="U27" s="2">
+        <v>3.7121</v>
+      </c>
+      <c r="V27" s="2">
+        <v>3.3641000000000001</v>
+      </c>
+      <c r="W27" s="2">
+        <v>3.2909999999999999</v>
+      </c>
+      <c r="X27" s="2">
+        <v>3.7490000000000001</v>
+      </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
+      <c r="C28" s="2">
+        <v>51.192100000000003</v>
+      </c>
+      <c r="D28" s="2">
+        <v>53.964700000000001</v>
+      </c>
+      <c r="E28" s="2">
+        <v>54.935299999999998</v>
+      </c>
+      <c r="F28" s="2">
+        <v>55.374600000000001</v>
+      </c>
+      <c r="G28" s="2">
+        <v>53.714500000000001</v>
+      </c>
+      <c r="H28" s="2">
+        <v>56.671399999999998</v>
+      </c>
+      <c r="I28" s="2">
+        <v>51.577100000000002</v>
+      </c>
+      <c r="J28" s="2">
+        <v>51.2136</v>
+      </c>
+      <c r="K28" s="2">
+        <v>50.747100000000003</v>
+      </c>
+      <c r="L28" s="2">
+        <v>51.494500000000002</v>
+      </c>
       <c r="N28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
+      <c r="O28" s="2">
+        <v>1303.9401</v>
+      </c>
+      <c r="P28" s="2">
+        <v>1322.009</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>1295.6130000000001</v>
+      </c>
+      <c r="R28" s="2">
+        <v>1300.0952</v>
+      </c>
+      <c r="S28" s="2">
+        <v>1308.6188999999999</v>
+      </c>
+      <c r="T28" s="2">
+        <v>1359.2184999999999</v>
+      </c>
+      <c r="U28" s="2">
+        <v>1286.5686000000001</v>
+      </c>
+      <c r="V28" s="2">
+        <v>1277.6815999999999</v>
+      </c>
+      <c r="W28" s="2">
+        <v>1318.8362</v>
+      </c>
+      <c r="X28" s="2">
+        <v>1271.9643000000001</v>
+      </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
@@ -7929,18 +9775,18 @@
       <c r="C31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="12"/>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B32" s="6"/>
-      <c r="C32" s="1">
+      <c r="B32" s="13"/>
+      <c r="C32" s="2">
         <v>100</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="2">
         <v>500</v>
       </c>
       <c r="E32" s="2">
@@ -7960,155 +9806,149 @@
       <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="2" t="str">
+      <c r="C33" s="2">
         <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
-        <v>undone</v>
-      </c>
-      <c r="D33" s="2" t="str">
+        <v>9.9500000000000005E-3</v>
+      </c>
+      <c r="D33" s="2">
         <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
-        <v>undone</v>
-      </c>
-      <c r="E33" s="2" t="str">
+        <v>0.24713999999999997</v>
+      </c>
+      <c r="E33" s="2">
         <f>IF(COUNTBLANK(C15:L15)&gt;0,"undone",AVERAGE(C15:L15))</f>
-        <v>undone</v>
-      </c>
-      <c r="F33" s="2" t="str">
+        <v>0.99377999999999989</v>
+      </c>
+      <c r="F33" s="2">
         <f>IF(COUNTBLANK(O15:X15)&gt;0,"undone",AVERAGE(O15:X15))</f>
-        <v>undone</v>
-      </c>
-      <c r="G33" s="2" t="str">
+        <v>25.123840000000001</v>
+      </c>
+      <c r="G33" s="2">
         <f>IF(COUNTBLANK(C24:L24)&gt;0,"undone",AVERAGE(C24:L24))</f>
-        <v>undone</v>
-      </c>
-      <c r="H33" s="2" t="str">
+        <v>100.66342</v>
+      </c>
+      <c r="H33" s="2">
         <f>IF(COUNTBLANK(O24:X24)&gt;0,"undone",AVERAGE(O24:X24))</f>
-        <v>undone</v>
+        <v>2530.2127</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="2" t="str">
-        <f t="shared" ref="C34:C37" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
-        <v>undone</v>
-      </c>
-      <c r="D34" s="2" t="str">
-        <f t="shared" ref="D34:D37" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
-        <v>undone</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <f t="shared" ref="E34:E37" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
-        <v>undone</v>
-      </c>
-      <c r="F34" s="2" t="str">
-        <f t="shared" ref="F34:F37" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
-        <v>undone</v>
-      </c>
-      <c r="G34" s="2" t="str">
-        <f t="shared" ref="G34:G37" si="4">IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
-        <v>undone</v>
-      </c>
-      <c r="H34" s="2" t="str">
-        <f t="shared" ref="H34:H37" si="5">IF(COUNTBLANK(O25:X25)&gt;0,"undone",AVERAGE(O25:X25))</f>
-        <v>undone</v>
+      <c r="C34" s="2">
+        <f>IF(COUNTBLANK(C7:L7)&gt;0,"undone",AVERAGE(C7:L7))</f>
+        <v>7.4400000000000004E-3</v>
+      </c>
+      <c r="D34" s="2">
+        <f>IF(COUNTBLANK(O7:X7)&gt;0,"undone",AVERAGE(O7:X7))</f>
+        <v>0.16192999999999996</v>
+      </c>
+      <c r="E34" s="2">
+        <f>IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
+        <v>0.68050999999999995</v>
+      </c>
+      <c r="F34" s="2">
+        <f>IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
+        <v>17.546299999999995</v>
+      </c>
+      <c r="G34" s="2">
+        <f>IF(COUNTBLANK(C25:L25)&gt;0,"undone",AVERAGE(C25:L25))</f>
+        <v>72.064859999999996</v>
+      </c>
+      <c r="H34" s="2">
+        <f>IF(COUNTBLANK(O25:X25)&gt;0,"undone",AVERAGE(O25:X25))</f>
+        <v>1814.8987199999999</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D35" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F35" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G35" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H35" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>undone</v>
+      <c r="C35" s="2">
+        <f>IF(COUNTBLANK(C8:L8)&gt;0,"undone",AVERAGE(C8:L8))</f>
+        <v>1.7569999999999999E-2</v>
+      </c>
+      <c r="D35" s="2">
+        <f>IF(COUNTBLANK(O8:X8)&gt;0,"undone",AVERAGE(O8:X8))</f>
+        <v>0.39970999999999995</v>
+      </c>
+      <c r="E35" s="2">
+        <f>IF(COUNTBLANK(C17:L17)&gt;0,"undone",AVERAGE(C17:L17))</f>
+        <v>1.72557</v>
+      </c>
+      <c r="F35" s="2">
+        <f>IF(COUNTBLANK(O17:X17)&gt;0,"undone",AVERAGE(O17:X17))</f>
+        <v>46.811249999999994</v>
+      </c>
+      <c r="G35" s="2">
+        <f>IF(COUNTBLANK(C26:L26)&gt;0,"undone",AVERAGE(C26:L26))</f>
+        <v>181.55905999999999</v>
+      </c>
+      <c r="H35" s="2">
+        <f>IF(COUNTBLANK(O26:X26)&gt;0,"undone",AVERAGE(O26:X26))</f>
+        <v>4382.7229299999999</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D36" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F36" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G36" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H36" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>undone</v>
+      <c r="C36" s="2">
+        <f>IF(COUNTBLANK(C9:L9)&gt;0,"undone",AVERAGE(C9:L9))</f>
+        <v>4.0699999999999998E-3</v>
+      </c>
+      <c r="D36" s="2">
+        <f>IF(COUNTBLANK(O9:X9)&gt;0,"undone",AVERAGE(O9:X9))</f>
+        <v>2.051E-2</v>
+      </c>
+      <c r="E36" s="2">
+        <f>IF(COUNTBLANK(C18:L18)&gt;0,"undone",AVERAGE(C18:L18))</f>
+        <v>5.4539999999999991E-2</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(COUNTBLANK(O18:X18)&gt;0,"undone",AVERAGE(O18:X18))</f>
+        <v>0.31284999999999996</v>
+      </c>
+      <c r="G36" s="2">
+        <f>IF(COUNTBLANK(C27:L27)&gt;0,"undone",AVERAGE(C27:L27))</f>
+        <v>0.65659000000000001</v>
+      </c>
+      <c r="H36" s="2">
+        <f>IF(COUNTBLANK(O27:X27)&gt;0,"undone",AVERAGE(O27:X27))</f>
+        <v>3.8224299999999998</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>undone</v>
-      </c>
-      <c r="D37" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>undone</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>undone</v>
-      </c>
-      <c r="F37" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>undone</v>
-      </c>
-      <c r="G37" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>undone</v>
-      </c>
-      <c r="H37" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>undone</v>
+      <c r="C37" s="2">
+        <f>IF(COUNTBLANK(C10:L10)&gt;0,"undone",AVERAGE(C10:L10))</f>
+        <v>6.0499999999999998E-3</v>
+      </c>
+      <c r="D37" s="2">
+        <f>IF(COUNTBLANK(O10:X10)&gt;0,"undone",AVERAGE(O10:X10))</f>
+        <v>0.13638999999999996</v>
+      </c>
+      <c r="E37" s="2">
+        <f>IF(COUNTBLANK(C19:L19)&gt;0,"undone",AVERAGE(C19:L19))</f>
+        <v>0.53875000000000006</v>
+      </c>
+      <c r="F37" s="2">
+        <f>IF(COUNTBLANK(O19:X19)&gt;0,"undone",AVERAGE(O19:X19))</f>
+        <v>13.51234</v>
+      </c>
+      <c r="G37" s="2">
+        <f>IF(COUNTBLANK(C28:L28)&gt;0,"undone",AVERAGE(C28:L28))</f>
+        <v>53.08849</v>
+      </c>
+      <c r="H37" s="2">
+        <f>IF(COUNTBLANK(O28:X28)&gt;0,"undone",AVERAGE(O28:X28))</f>
+        <v>1304.45454</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:L22"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="O22:X22"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:H31"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="N13:N14"/>
@@ -8118,6 +9958,12 @@
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="O4:X4"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="O22:X22"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:H31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data collecting.xlsx
+++ b/data collecting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phure\เอกสาร\GitHub\c-sorting-algorithm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E229B1F-2017-49F2-8576-40324C508EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF10A220-80A1-4719-837A-8764BD1D6D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
   </bookViews>
   <sheets>
     <sheet name="Random" sheetId="1" r:id="rId1"/>
@@ -258,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -278,9 +278,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -299,13 +303,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -537,22 +540,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.4000000000000002E-3</c:v>
+                  <c:v>3.3250000000000007E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.6729999999999997E-2</c:v>
+                  <c:v>9.6124999999999988E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.34319</c:v>
+                  <c:v>0.34291250000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.9106600000000018</c:v>
+                  <c:v>8.8987499999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34.29101</c:v>
+                  <c:v>34.276687500000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>924.20444999999995</c:v>
+                  <c:v>918.55595000000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -628,22 +631,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>5.2100000000000002E-3</c:v>
+                  <c:v>5.0000000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.11685999999999999</c:v>
+                  <c:v>0.116075</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.47793000000000002</c:v>
+                  <c:v>0.47197499999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.00845</c:v>
+                  <c:v>10.990737499999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47.933389999999996</c:v>
+                  <c:v>46.921199999999992</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1546.0603700000001</c:v>
+                  <c:v>1564.8245625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -723,22 +726,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>8.9900000000000015E-3</c:v>
+                  <c:v>8.7375000000000005E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.22323999999999997</c:v>
+                  <c:v>0.22232499999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.86520999999999992</c:v>
+                  <c:v>0.86371249999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.974539999999998</c:v>
+                  <c:v>20.985674999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>89.085650000000001</c:v>
+                  <c:v>88.970937500000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3090.3531499999999</c:v>
+                  <c:v>3080.548875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -814,22 +817,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.2099999999999997E-3</c:v>
+                  <c:v>2.9624999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9649999999999997E-2</c:v>
+                  <c:v>1.85875E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.3359999999999996E-2</c:v>
+                  <c:v>4.0962499999999992E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.33721999999999996</c:v>
+                  <c:v>0.3334375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.88151000000000013</c:v>
+                  <c:v>0.85593750000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.7085000000000008</c:v>
+                  <c:v>6.6863124999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -907,22 +910,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.7599999999999998E-3</c:v>
+                  <c:v>1.5874999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.9300000000000013E-3</c:v>
+                  <c:v>8.9125000000000003E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.6549999999999997E-2</c:v>
+                  <c:v>2.5237499999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22603999999999996</c:v>
+                  <c:v>0.22592499999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.51679000000000008</c:v>
+                  <c:v>0.51642500000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.6064799999999995</c:v>
+                  <c:v>4.5932874999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -997,22 +1000,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.7600000000000003E-3</c:v>
+                  <c:v>3.4500000000000008E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9910000000000001E-2</c:v>
+                  <c:v>1.9224999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.3620000000000006E-2</c:v>
+                  <c:v>4.2412499999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30737999999999999</c:v>
+                  <c:v>0.30487500000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.67976999999999999</c:v>
+                  <c:v>0.67661250000000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.8393899999999999</c:v>
+                  <c:v>5.7241625000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1557,22 +1560,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.7999999999999998E-4</c:v>
+                  <c:v>2.875E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2399999999999998E-3</c:v>
+                  <c:v>1.2374999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.4799999999999996E-3</c:v>
+                  <c:v>2.4874999999999997E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2260000000000002E-2</c:v>
+                  <c:v>1.2262500000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.4469999999999999E-2</c:v>
+                  <c:v>2.4475E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.12282</c:v>
+                  <c:v>0.12228749999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1648,22 +1651,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.3800000000000003E-3</c:v>
+                  <c:v>7.2750000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.15373000000000001</c:v>
+                  <c:v>0.153225</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.64056000000000002</c:v>
+                  <c:v>0.63418750000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.431139999999999</c:v>
+                  <c:v>15.403874999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>61.678290000000004</c:v>
+                  <c:v>61.6993875</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1588.5216599999999</c:v>
+                  <c:v>1587.3118125000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1743,22 +1746,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.5699999999999986E-3</c:v>
+                  <c:v>7.5374999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.18410999999999997</c:v>
+                  <c:v>0.18411249999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75385000000000013</c:v>
+                  <c:v>0.75121250000000006</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18.468240000000002</c:v>
+                  <c:v>18.446875000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>76.96871999999999</c:v>
+                  <c:v>75.809237499999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1909.0088900000003</c:v>
+                  <c:v>1901.4957750000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1834,22 +1837,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.0300000000000006E-3</c:v>
+                  <c:v>3.9375000000000009E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3880000000000002E-2</c:v>
+                  <c:v>2.3862500000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.1610000000000003E-2</c:v>
+                  <c:v>5.15375E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30335000000000001</c:v>
+                  <c:v>0.30283749999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.64549999999999996</c:v>
+                  <c:v>0.64444999999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.6855800000000003</c:v>
+                  <c:v>3.6792499999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1927,22 +1930,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>6.2899999999999996E-3</c:v>
+                  <c:v>6.2249999999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14540000000000003</c:v>
+                  <c:v>0.1444125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.56005000000000005</c:v>
+                  <c:v>0.56381250000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.764590000000002</c:v>
+                  <c:v>13.799025</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55.286710000000006</c:v>
+                  <c:v>55.014850000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1396.0238599999998</c:v>
+                  <c:v>1390.3545124999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2017,22 +2020,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.7500000000000007E-3</c:v>
+                  <c:v>3.6750000000000003E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0990000000000002E-2</c:v>
+                  <c:v>2.0125000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.1000000000000008E-2</c:v>
+                  <c:v>4.4262499999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22716000000000003</c:v>
+                  <c:v>0.22641249999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.40522999999999998</c:v>
+                  <c:v>0.40345000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.9529099999999997</c:v>
+                  <c:v>2.9468124999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2556,22 +2559,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>9.9400000000000009E-3</c:v>
+                  <c:v>9.8625000000000015E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25718000000000002</c:v>
+                  <c:v>0.25591250000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98943999999999988</c:v>
+                  <c:v>0.98113750000000011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24.39499</c:v>
+                  <c:v>24.430362500000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100.12429999999999</c:v>
+                  <c:v>99.611262499999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2476.5824499999999</c:v>
+                  <c:v>2473.0774249999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2647,22 +2650,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.5899999999999995E-3</c:v>
+                  <c:v>7.5125000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.18755999999999998</c:v>
+                  <c:v>0.18476250000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.74761999999999995</c:v>
+                  <c:v>0.73175000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17.236690000000003</c:v>
+                  <c:v>17.197487500000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>69.557220000000001</c:v>
+                  <c:v>69.581837500000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1754.2494900000002</c:v>
+                  <c:v>1751.8876750000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2742,22 +2745,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.7080000000000001E-2</c:v>
+                  <c:v>1.6525000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.39037000000000005</c:v>
+                  <c:v>0.39001249999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.581</c:v>
+                  <c:v>1.5767875</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>39.528110000000005</c:v>
+                  <c:v>39.417412499999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>158.68270999999999</c:v>
+                  <c:v>157.20343750000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4058.2056299999995</c:v>
+                  <c:v>4051.6519750000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2833,22 +2836,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.0300000000000006E-3</c:v>
+                  <c:v>3.9249999999999997E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3870000000000002E-2</c:v>
+                  <c:v>2.38125E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.1280000000000006E-2</c:v>
+                  <c:v>5.1262500000000009E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30186999999999997</c:v>
+                  <c:v>0.30181249999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.66477000000000008</c:v>
+                  <c:v>0.66368749999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.7321400000000002</c:v>
+                  <c:v>3.7551500000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2926,22 +2929,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>5.9699999999999987E-3</c:v>
+                  <c:v>5.8499999999999993E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14348</c:v>
+                  <c:v>0.14306249999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.56440000000000001</c:v>
+                  <c:v>0.56122500000000008</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.838179999999999</c:v>
+                  <c:v>13.865499999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55.233159999999998</c:v>
+                  <c:v>55.1704875</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1385.84139</c:v>
+                  <c:v>1379.994475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3016,22 +3019,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.2099999999999993E-3</c:v>
+                  <c:v>4.0749999999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.1399999999999999E-2</c:v>
+                  <c:v>2.1049999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.3570000000000005E-2</c:v>
+                  <c:v>4.3212500000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.28176999999999996</c:v>
+                  <c:v>0.2749375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.52821000000000007</c:v>
+                  <c:v>0.51900000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.6694100000000001</c:v>
+                  <c:v>2.6659375000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5498,10 +5501,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -5520,39 +5523,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="12"/>
-      <c r="N4" s="8" t="s">
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="14"/>
+      <c r="N4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
-      <c r="X4" s="12"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="14"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="9"/>
+      <c r="B5" s="11"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -5583,7 +5586,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="9"/>
+      <c r="N5" s="11"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -5619,67 +5622,67 @@
       <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="7">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="7">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="7">
         <v>3.3E-3</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="7">
         <v>3.3E-3</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="7">
         <v>3.3E-3</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="7">
         <v>3.3E-3</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="7">
         <v>3.3E-3</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="7">
         <v>3.3E-3</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="7">
         <v>3.3E-3</v>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="7">
         <v>3.3E-3</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6" s="7">
         <v>9.6799999999999997E-2</v>
       </c>
-      <c r="P6" s="16">
+      <c r="P6" s="7">
         <v>9.6299999999999997E-2</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6" s="7">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="R6" s="16">
+      <c r="R6" s="7">
         <v>9.5799999999999996E-2</v>
       </c>
-      <c r="S6" s="16">
+      <c r="S6" s="7">
         <v>9.5899999999999999E-2</v>
       </c>
-      <c r="T6" s="16">
+      <c r="T6" s="7">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="U6" s="16">
+      <c r="U6" s="7">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="V6" s="16">
+      <c r="V6" s="7">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="W6" s="16">
+      <c r="W6" s="7">
         <v>0.10249999999999999</v>
       </c>
-      <c r="X6" s="16">
+      <c r="X6" s="7">
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
@@ -5687,67 +5690,67 @@
       <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="7">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="7">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="7">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="7">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="7">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="7">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="7">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="7">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="7">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="7">
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7" s="7">
         <v>0.12640000000000001</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7" s="7">
         <v>0.12189999999999999</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="7">
         <v>0.1179</v>
       </c>
-      <c r="R7" s="16">
+      <c r="R7" s="7">
         <v>0.1195</v>
       </c>
-      <c r="S7" s="16">
+      <c r="S7" s="7">
         <v>0.1143</v>
       </c>
-      <c r="T7" s="16">
+      <c r="T7" s="7">
         <v>0.1139</v>
       </c>
-      <c r="U7" s="16">
+      <c r="U7" s="7">
         <v>0.1137</v>
       </c>
-      <c r="V7" s="16">
+      <c r="V7" s="7">
         <v>0.1138</v>
       </c>
-      <c r="W7" s="16">
+      <c r="W7" s="7">
         <v>0.11360000000000001</v>
       </c>
-      <c r="X7" s="16">
+      <c r="X7" s="7">
         <v>0.11360000000000001</v>
       </c>
     </row>
@@ -5755,67 +5758,67 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="7">
         <v>1.17E-2</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="7">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="7">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="7">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="7">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="7">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="7">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="7">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="7">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="7">
         <v>8.3999999999999995E-3</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="16">
+      <c r="O8" s="7">
         <v>0.23680000000000001</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="7">
         <v>0.2329</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="7">
         <v>0.23019999999999999</v>
       </c>
-      <c r="R8" s="16">
+      <c r="R8" s="7">
         <v>0.22059999999999999</v>
       </c>
-      <c r="S8" s="16">
+      <c r="S8" s="7">
         <v>0.21940000000000001</v>
       </c>
-      <c r="T8" s="16">
+      <c r="T8" s="7">
         <v>0.21829999999999999</v>
       </c>
-      <c r="U8" s="16">
+      <c r="U8" s="7">
         <v>0.217</v>
       </c>
-      <c r="V8" s="16">
+      <c r="V8" s="7">
         <v>0.2223</v>
       </c>
-      <c r="W8" s="16">
+      <c r="W8" s="7">
         <v>0.2175</v>
       </c>
-      <c r="X8" s="16">
+      <c r="X8" s="7">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -5823,67 +5826,67 @@
       <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="7">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="7">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="7">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="7">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="7">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="7">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="7">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="7">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="7">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="7">
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O9" s="7">
         <v>2.9899999999999999E-2</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="7">
         <v>2.07E-2</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="7">
         <v>1.8200000000000001E-2</v>
       </c>
-      <c r="R9" s="16">
+      <c r="R9" s="7">
         <v>1.8200000000000001E-2</v>
       </c>
-      <c r="S9" s="16">
+      <c r="S9" s="7">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="T9" s="16">
+      <c r="T9" s="7">
         <v>1.7899999999999999E-2</v>
       </c>
-      <c r="U9" s="16">
+      <c r="U9" s="7">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="V9" s="16">
+      <c r="V9" s="7">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="W9" s="16">
+      <c r="W9" s="7">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="X9" s="16">
+      <c r="X9" s="7">
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
@@ -5891,67 +5894,67 @@
       <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="7">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="7">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="7">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="7">
         <v>1.4E-3</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="7">
         <v>1.4E-3</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="7">
         <v>1.4E-3</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="7">
         <v>1.4E-3</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="7">
         <v>1.4E-3</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="7">
         <v>1.5E-3</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="7">
         <v>1.4E-3</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="7">
         <v>1.95E-2</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="7">
         <v>1.0800000000000001E-2</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="7">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="7">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="S10" s="16">
+      <c r="S10" s="7">
         <v>8.6E-3</v>
       </c>
-      <c r="T10" s="16">
+      <c r="T10" s="7">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="U10" s="16">
+      <c r="U10" s="7">
         <v>8.6E-3</v>
       </c>
-      <c r="V10" s="16">
+      <c r="V10" s="7">
         <v>8.6E-3</v>
       </c>
-      <c r="W10" s="16">
+      <c r="W10" s="7">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="X10" s="16">
+      <c r="X10" s="7">
         <v>8.6999999999999994E-3</v>
       </c>
     </row>
@@ -5959,67 +5962,67 @@
       <c r="B11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="8">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="7">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="7">
         <v>3.3E-3</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="7">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="7">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="7">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="7">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="7">
         <v>3.3E-3</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="7">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="7">
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="8">
         <v>2.81E-2</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="7">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="7">
         <v>2.1899999999999999E-2</v>
       </c>
-      <c r="R11" s="16">
+      <c r="R11" s="7">
         <v>0.02</v>
       </c>
-      <c r="S11" s="16">
+      <c r="S11" s="7">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="T11" s="16">
+      <c r="T11" s="7">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="U11" s="16">
+      <c r="U11" s="7">
         <v>1.72E-2</v>
       </c>
-      <c r="V11" s="16">
+      <c r="V11" s="7">
         <v>1.9E-2</v>
       </c>
-      <c r="W11" s="16">
+      <c r="W11" s="7">
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="X11" s="16">
+      <c r="X11" s="7">
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
@@ -6040,39 +6043,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="12"/>
-      <c r="N14" s="8" t="s">
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="14"/>
+      <c r="N14" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="O14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="12"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="14"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -6103,7 +6106,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="9"/>
+      <c r="N15" s="11"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -6139,67 +6142,67 @@
       <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="7">
         <v>0.34260000000000002</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="7">
         <v>0.34179999999999999</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="7">
         <v>0.34150000000000003</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="7">
         <v>0.34139999999999998</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="7">
         <v>0.3453</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="7">
         <v>0.34150000000000003</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="7">
         <v>0.34139999999999998</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="7">
         <v>0.34720000000000001</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="7">
         <v>0.34320000000000001</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="7">
         <v>0.34599999999999997</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O16" s="7">
         <v>9.1956000000000007</v>
       </c>
-      <c r="P16" s="16">
+      <c r="P16" s="7">
         <v>8.8960000000000008</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="7">
         <v>8.8794000000000004</v>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="7">
         <v>8.8483999999999998</v>
       </c>
-      <c r="S16" s="16">
+      <c r="S16" s="7">
         <v>9.0548999999999999</v>
       </c>
-      <c r="T16" s="16">
+      <c r="T16" s="7">
         <v>9.0667000000000009</v>
       </c>
-      <c r="U16" s="16">
+      <c r="U16" s="7">
         <v>8.7662999999999993</v>
       </c>
-      <c r="V16" s="16">
+      <c r="V16" s="7">
         <v>8.7954000000000008</v>
       </c>
-      <c r="W16" s="16">
+      <c r="W16" s="7">
         <v>8.7210000000000001</v>
       </c>
-      <c r="X16" s="16">
+      <c r="X16" s="7">
         <v>8.8828999999999994</v>
       </c>
     </row>
@@ -6207,67 +6210,67 @@
       <c r="B17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="7">
         <v>0.47310000000000002</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="7">
         <v>0.46899999999999997</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="7">
         <v>0.46460000000000001</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="7">
         <v>0.5</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="7">
         <v>0.46539999999999998</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="7">
         <v>0.46089999999999998</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="7">
         <v>0.4607</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="7">
         <v>0.54279999999999995</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="7">
         <v>0.4768</v>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="7">
         <v>0.46600000000000003</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O17" s="16">
+      <c r="O17" s="7">
         <v>10.829000000000001</v>
       </c>
-      <c r="P17" s="16">
+      <c r="P17" s="7">
         <v>10.7707</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="Q17" s="7">
         <v>10.8287</v>
       </c>
-      <c r="R17" s="16">
+      <c r="R17" s="7">
         <v>10.837199999999999</v>
       </c>
-      <c r="S17" s="16">
+      <c r="S17" s="7">
         <v>10.815</v>
       </c>
-      <c r="T17" s="16">
+      <c r="T17" s="7">
         <v>11.3873</v>
       </c>
-      <c r="U17" s="16">
+      <c r="U17" s="7">
         <v>11.142799999999999</v>
       </c>
-      <c r="V17" s="16">
+      <c r="V17" s="7">
         <v>11.1646</v>
       </c>
-      <c r="W17" s="16">
+      <c r="W17" s="7">
         <v>11.3879</v>
       </c>
-      <c r="X17" s="16">
+      <c r="X17" s="7">
         <v>10.9213</v>
       </c>
     </row>
@@ -6275,67 +6278,67 @@
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="7">
         <v>0.88670000000000004</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="7">
         <v>0.87949999999999995</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="7">
         <v>0.87160000000000004</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="7">
         <v>0.8619</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="7">
         <v>0.85950000000000004</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="7">
         <v>0.86160000000000003</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="7">
         <v>0.85750000000000004</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="7">
         <v>0.85980000000000001</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="7">
         <v>0.85570000000000002</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="7">
         <v>0.85829999999999995</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O18" s="16">
+      <c r="O18" s="7">
         <v>20.911899999999999</v>
       </c>
-      <c r="P18" s="16">
+      <c r="P18" s="7">
         <v>21.035599999999999</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="Q18" s="7">
         <v>21.108899999999998</v>
       </c>
-      <c r="R18" s="16">
+      <c r="R18" s="7">
         <v>20.726600000000001</v>
       </c>
-      <c r="S18" s="16">
+      <c r="S18" s="7">
         <v>20.8309</v>
       </c>
-      <c r="T18" s="16">
+      <c r="T18" s="7">
         <v>21.097999999999999</v>
       </c>
-      <c r="U18" s="16">
+      <c r="U18" s="7">
         <v>21.315200000000001</v>
       </c>
-      <c r="V18" s="16">
+      <c r="V18" s="7">
         <v>21.2637</v>
       </c>
-      <c r="W18" s="16">
+      <c r="W18" s="7">
         <v>20.544799999999999</v>
       </c>
-      <c r="X18" s="16">
+      <c r="X18" s="7">
         <v>20.909800000000001</v>
       </c>
     </row>
@@ -6343,67 +6346,67 @@
       <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="7">
         <v>6.6199999999999995E-2</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="7">
         <v>4.7E-2</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="7">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="7">
         <v>4.0099999999999997E-2</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="7">
         <v>4.0099999999999997E-2</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="7">
         <v>3.9899999999999998E-2</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="7">
         <v>3.9699999999999999E-2</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="7">
         <v>3.9899999999999998E-2</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="7">
         <v>3.9800000000000002E-2</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="7">
         <v>3.9899999999999998E-2</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O19" s="16">
+      <c r="O19" s="7">
         <v>0.39389999999999997</v>
       </c>
-      <c r="P19" s="16">
+      <c r="P19" s="7">
         <v>0.35670000000000002</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="Q19" s="7">
         <v>0.34920000000000001</v>
       </c>
-      <c r="R19" s="16">
+      <c r="R19" s="7">
         <v>0.33929999999999999</v>
       </c>
-      <c r="S19" s="16">
+      <c r="S19" s="7">
         <v>0.33260000000000001</v>
       </c>
-      <c r="T19" s="16">
+      <c r="T19" s="7">
         <v>0.32940000000000003</v>
       </c>
-      <c r="U19" s="16">
+      <c r="U19" s="7">
         <v>0.3216</v>
       </c>
-      <c r="V19" s="16">
+      <c r="V19" s="7">
         <v>0.31890000000000002</v>
       </c>
-      <c r="W19" s="16">
+      <c r="W19" s="7">
         <v>0.31979999999999997</v>
       </c>
-      <c r="X19" s="16">
+      <c r="X19" s="7">
         <v>0.31080000000000002</v>
       </c>
     </row>
@@ -6411,67 +6414,67 @@
       <c r="B20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="7">
         <v>4.4699999999999997E-2</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="7">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="7">
         <v>2.23E-2</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="7">
         <v>1.95E-2</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="7">
         <v>3.49E-2</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="7">
         <v>0.03</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="7">
         <v>2.1700000000000001E-2</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="7">
         <v>1.95E-2</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="7">
         <v>1.95E-2</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="7">
         <v>1.89E-2</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O20" s="16">
+      <c r="O20" s="7">
         <v>0.25090000000000001</v>
       </c>
-      <c r="P20" s="16">
+      <c r="P20" s="7">
         <v>0.2427</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="Q20" s="7">
         <v>0.2344</v>
       </c>
-      <c r="R20" s="16">
+      <c r="R20" s="7">
         <v>0.2213</v>
       </c>
-      <c r="S20" s="16">
+      <c r="S20" s="7">
         <v>0.21249999999999999</v>
       </c>
-      <c r="T20" s="16">
+      <c r="T20" s="7">
         <v>0.2059</v>
       </c>
-      <c r="U20" s="16">
+      <c r="U20" s="7">
         <v>0.2021</v>
       </c>
-      <c r="V20" s="16">
+      <c r="V20" s="7">
         <v>0.21970000000000001</v>
       </c>
-      <c r="W20" s="16">
+      <c r="W20" s="7">
         <v>0.23880000000000001</v>
       </c>
-      <c r="X20" s="16">
+      <c r="X20" s="7">
         <v>0.2321</v>
       </c>
     </row>
@@ -6479,67 +6482,67 @@
       <c r="B21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="8">
         <v>6.08E-2</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="7">
         <v>5.0900000000000001E-2</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="7">
         <v>4.0599999999999997E-2</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="7">
         <v>4.6399999999999997E-2</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="7">
         <v>4.24E-2</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="7">
         <v>4.1799999999999997E-2</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="7">
         <v>4.2700000000000002E-2</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="7">
         <v>3.78E-2</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="7">
         <v>3.6700000000000003E-2</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="7">
         <v>3.61E-2</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="8">
         <v>0.34150000000000003</v>
       </c>
-      <c r="P21" s="16">
+      <c r="P21" s="7">
         <v>0.32079999999999997</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="Q21" s="7">
         <v>0.3145</v>
       </c>
-      <c r="R21" s="16">
+      <c r="R21" s="7">
         <v>0.31740000000000002</v>
       </c>
-      <c r="S21" s="16">
+      <c r="S21" s="7">
         <v>0.30299999999999999</v>
       </c>
-      <c r="T21" s="16">
+      <c r="T21" s="7">
         <v>0.29630000000000001</v>
       </c>
-      <c r="U21" s="16">
+      <c r="U21" s="7">
         <v>0.29330000000000001</v>
       </c>
-      <c r="V21" s="16">
+      <c r="V21" s="7">
         <v>0.2959</v>
       </c>
-      <c r="W21" s="16">
+      <c r="W21" s="7">
         <v>0.29520000000000002</v>
       </c>
-      <c r="X21" s="16">
+      <c r="X21" s="7">
         <v>0.2959</v>
       </c>
     </row>
@@ -6560,39 +6563,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="12"/>
-      <c r="N24" s="8" t="s">
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="14"/>
+      <c r="N24" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="10" t="s">
+      <c r="O24" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="12"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="14"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="9"/>
+      <c r="B25" s="11"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -6623,7 +6626,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="9"/>
+      <c r="N25" s="11"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -6659,67 +6662,67 @@
       <c r="B26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="7">
         <v>34.209400000000002</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="7">
         <v>34.849299999999999</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="7">
         <v>34.061100000000003</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="7">
         <v>34.154899999999998</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="7">
         <v>34.296300000000002</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="7">
         <v>34.161799999999999</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="7">
         <v>34.444899999999997</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="7">
         <v>34.367699999999999</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="7">
         <v>34.517400000000002</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="7">
         <v>33.847299999999997</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O26" s="7">
         <v>872.62760000000003</v>
       </c>
-      <c r="P26" s="16">
+      <c r="P26" s="7">
         <v>886.33439999999996</v>
       </c>
-      <c r="Q26" s="16">
+      <c r="Q26" s="7">
         <v>882.28300000000002</v>
       </c>
-      <c r="R26" s="16">
+      <c r="R26" s="7">
         <v>905.01099999999997</v>
       </c>
-      <c r="S26" s="16">
+      <c r="S26" s="7">
         <v>1020.9693</v>
       </c>
-      <c r="T26" s="16">
+      <c r="T26" s="7">
         <v>908.33280000000002</v>
       </c>
-      <c r="U26" s="16">
+      <c r="U26" s="7">
         <v>937.2405</v>
       </c>
-      <c r="V26" s="16">
+      <c r="V26" s="7">
         <v>908.33429999999998</v>
       </c>
-      <c r="W26" s="16">
+      <c r="W26" s="7">
         <v>930.68179999999995</v>
       </c>
-      <c r="X26" s="16">
+      <c r="X26" s="7">
         <v>990.22979999999995</v>
       </c>
     </row>
@@ -6727,67 +6730,67 @@
       <c r="B27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="7">
         <v>44.353400000000001</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="7">
         <v>43.189599999999999</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="7">
         <v>43.161999999999999</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="7">
         <v>43.813099999999999</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="7">
         <v>45.871400000000001</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="7">
         <v>46.393599999999999</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="7">
         <v>49.554499999999997</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="7">
         <v>52.761400000000002</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="7">
         <v>60.802300000000002</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="7">
         <v>49.432600000000001</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O27" s="16">
+      <c r="O27" s="7">
         <v>1470.896</v>
       </c>
-      <c r="P27" s="16">
+      <c r="P27" s="7">
         <v>1197.1107</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="Q27" s="7">
         <v>1528.1219000000001</v>
       </c>
-      <c r="R27" s="16">
+      <c r="R27" s="7">
         <v>1614.8674000000001</v>
       </c>
-      <c r="S27" s="16">
+      <c r="S27" s="7">
         <v>1612.5422000000001</v>
       </c>
-      <c r="T27" s="16">
+      <c r="T27" s="7">
         <v>1599.9371000000001</v>
       </c>
-      <c r="U27" s="16">
+      <c r="U27" s="7">
         <v>1744.8965000000001</v>
       </c>
-      <c r="V27" s="16">
+      <c r="V27" s="7">
         <v>1563.7733000000001</v>
       </c>
-      <c r="W27" s="16">
+      <c r="W27" s="7">
         <v>1550.4166</v>
       </c>
-      <c r="X27" s="16">
+      <c r="X27" s="7">
         <v>1578.0419999999999</v>
       </c>
     </row>
@@ -6795,67 +6798,67 @@
       <c r="B28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="7">
         <v>90.241299999999995</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="7">
         <v>94.488799999999998</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="7">
         <v>89.021600000000007</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="7">
         <v>88.33</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="7">
         <v>91.038700000000006</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="7">
         <v>88.762600000000006</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="7">
         <v>87.660899999999998</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="7">
         <v>89.802400000000006</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="7">
         <v>86.91</v>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="7">
         <v>84.600200000000001</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O28" s="16">
+      <c r="O28" s="7">
         <v>3065.0989</v>
       </c>
-      <c r="P28" s="16">
+      <c r="P28" s="7">
         <v>3034.4448000000002</v>
       </c>
-      <c r="Q28" s="16">
+      <c r="Q28" s="7">
         <v>3036.0689000000002</v>
       </c>
-      <c r="R28" s="16">
+      <c r="R28" s="7">
         <v>3224.6957000000002</v>
       </c>
-      <c r="S28" s="16">
+      <c r="S28" s="7">
         <v>3093.7710000000002</v>
       </c>
-      <c r="T28" s="16">
+      <c r="T28" s="7">
         <v>3058.2451999999998</v>
       </c>
-      <c r="U28" s="16">
+      <c r="U28" s="7">
         <v>3089.3368999999998</v>
       </c>
-      <c r="V28" s="16">
+      <c r="V28" s="7">
         <v>3082.3022999999998</v>
       </c>
-      <c r="W28" s="16">
+      <c r="W28" s="7">
         <v>3145.2235000000001</v>
       </c>
-      <c r="X28" s="16">
+      <c r="X28" s="7">
         <v>3074.3443000000002</v>
       </c>
     </row>
@@ -6863,67 +6866,67 @@
       <c r="B29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="7">
         <v>0.89849999999999997</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="7">
         <v>1.1771</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="7">
         <v>1.2047000000000001</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="7">
         <v>0.90910000000000002</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="7">
         <v>0.77880000000000005</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="7">
         <v>0.77939999999999998</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="7">
         <v>0.7722</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="7">
         <v>0.76759999999999995</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="7">
         <v>0.76480000000000004</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="7">
         <v>0.76290000000000002</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O29" s="16">
+      <c r="O29" s="7">
         <v>6.7157</v>
       </c>
-      <c r="P29" s="16">
+      <c r="P29" s="7">
         <v>7.2746000000000004</v>
       </c>
-      <c r="Q29" s="16">
+      <c r="Q29" s="7">
         <v>6.6779000000000002</v>
       </c>
-      <c r="R29" s="16">
+      <c r="R29" s="7">
         <v>6.7633000000000001</v>
       </c>
-      <c r="S29" s="16">
+      <c r="S29" s="7">
         <v>6.6882999999999999</v>
       </c>
-      <c r="T29" s="16">
+      <c r="T29" s="7">
         <v>6.6247999999999996</v>
       </c>
-      <c r="U29" s="16">
+      <c r="U29" s="7">
         <v>6.3198999999999996</v>
       </c>
-      <c r="V29" s="16">
+      <c r="V29" s="7">
         <v>6.6131000000000002</v>
       </c>
-      <c r="W29" s="16">
+      <c r="W29" s="7">
         <v>6.6803999999999997</v>
       </c>
-      <c r="X29" s="16">
+      <c r="X29" s="7">
         <v>6.7270000000000003</v>
       </c>
     </row>
@@ -6931,67 +6934,67 @@
       <c r="B30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="7">
         <v>0.52849999999999997</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="7">
         <v>0.52710000000000001</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="7">
         <v>0.51849999999999996</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="7">
         <v>0.51900000000000002</v>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="7">
         <v>0.51429999999999998</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="7">
         <v>0.51739999999999997</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="7">
         <v>0.51119999999999999</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="7">
         <v>0.51259999999999994</v>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="7">
         <v>0.50800000000000001</v>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="7">
         <v>0.51129999999999998</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O30" s="16">
+      <c r="O30" s="7">
         <v>4.6497999999999999</v>
       </c>
-      <c r="P30" s="16">
+      <c r="P30" s="7">
         <v>4.5945</v>
       </c>
-      <c r="Q30" s="16">
+      <c r="Q30" s="7">
         <v>4.5805999999999996</v>
       </c>
-      <c r="R30" s="16">
+      <c r="R30" s="7">
         <v>4.5838999999999999</v>
       </c>
-      <c r="S30" s="16">
+      <c r="S30" s="7">
         <v>4.7912999999999997</v>
       </c>
-      <c r="T30" s="16">
+      <c r="T30" s="7">
         <v>4.5858999999999996</v>
       </c>
-      <c r="U30" s="16">
+      <c r="U30" s="7">
         <v>4.5271999999999997</v>
       </c>
-      <c r="V30" s="16">
+      <c r="V30" s="7">
         <v>4.5297000000000001</v>
       </c>
-      <c r="W30" s="16">
+      <c r="W30" s="7">
         <v>4.6829999999999998</v>
       </c>
-      <c r="X30" s="16">
+      <c r="X30" s="7">
         <v>4.5388999999999999</v>
       </c>
     </row>
@@ -6999,85 +7002,85 @@
       <c r="B31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="8">
         <v>0.69540000000000002</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="7">
         <v>0.67749999999999999</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="7">
         <v>0.68089999999999995</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="7">
         <v>0.71740000000000004</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="7">
         <v>0.67849999999999999</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="7">
         <v>0.67030000000000001</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="7">
         <v>0.66859999999999997</v>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="7">
         <v>0.67330000000000001</v>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="7">
         <v>0.66739999999999999</v>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="7">
         <v>0.66839999999999999</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O31" s="17">
+      <c r="O31" s="8">
         <v>5.6353999999999997</v>
       </c>
-      <c r="P31" s="16">
+      <c r="P31" s="7">
         <v>5.3098000000000001</v>
       </c>
-      <c r="Q31" s="16">
+      <c r="Q31" s="7">
         <v>5.6139000000000001</v>
       </c>
-      <c r="R31" s="16">
+      <c r="R31" s="7">
         <v>5.6294000000000004</v>
       </c>
-      <c r="S31" s="16">
+      <c r="S31" s="7">
         <v>5.6874000000000002</v>
       </c>
-      <c r="T31" s="16">
+      <c r="T31" s="7">
         <v>5.6228999999999996</v>
       </c>
-      <c r="U31" s="16">
+      <c r="U31" s="7">
         <v>6.0076999999999998</v>
       </c>
-      <c r="V31" s="16">
+      <c r="V31" s="7">
         <v>7.2907999999999999</v>
       </c>
-      <c r="W31" s="16">
+      <c r="W31" s="7">
         <v>5.7356999999999996</v>
       </c>
-      <c r="X31" s="16">
+      <c r="X31" s="7">
         <v>5.8609</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="8" t="s">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="9"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="14"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="11"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -7097,178 +7100,182 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="16">
-        <f t="shared" ref="C36:C41" si="0">IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
-        <v>3.4000000000000002E-3</v>
-      </c>
-      <c r="D36" s="16">
-        <f t="shared" ref="D36:D41" si="1">IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
-        <v>9.6729999999999997E-2</v>
-      </c>
-      <c r="E36" s="16">
-        <f t="shared" ref="E36:E41" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
-        <v>0.34319</v>
-      </c>
-      <c r="F36" s="16">
-        <f t="shared" ref="F36:F41" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
-        <v>8.9106600000000018</v>
-      </c>
-      <c r="G36" s="16">
-        <f t="shared" ref="G36:G41" si="4">IF(COUNTBLANK(C26:L26)&gt;0,"undone",AVERAGE(C26:L26))</f>
-        <v>34.29101</v>
-      </c>
-      <c r="H36" s="16">
-        <f t="shared" ref="H36:H41" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",AVERAGE(O26:X26))</f>
-        <v>924.20444999999995</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C36" s="7">
+        <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",TRIMMEAN(C6:L6,2/COUNT(C6:L6)))</f>
+        <v>3.3250000000000007E-3</v>
+      </c>
+      <c r="D36" s="7">
+        <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
+        <v>9.6124999999999988E-2</v>
+      </c>
+      <c r="E36" s="7">
+        <f>IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
+        <v>0.34291250000000001</v>
+      </c>
+      <c r="F36" s="7">
+        <f>IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
+        <v>8.8987499999999997</v>
+      </c>
+      <c r="G36" s="7">
+        <f>IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
+        <v>34.276687500000001</v>
+      </c>
+      <c r="H36" s="7">
+        <f>IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
+        <v>918.55595000000005</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="16">
-        <f t="shared" si="0"/>
-        <v>5.2100000000000002E-3</v>
-      </c>
-      <c r="D37" s="16">
-        <f t="shared" si="1"/>
-        <v>0.11685999999999999</v>
-      </c>
-      <c r="E37" s="16">
-        <f t="shared" si="2"/>
-        <v>0.47793000000000002</v>
-      </c>
-      <c r="F37" s="16">
-        <f t="shared" si="3"/>
-        <v>11.00845</v>
-      </c>
-      <c r="G37" s="16">
-        <f t="shared" si="4"/>
-        <v>47.933389999999996</v>
-      </c>
-      <c r="H37" s="16">
-        <f t="shared" si="5"/>
-        <v>1546.0603700000001</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C37" s="7">
+        <f t="shared" ref="C37:C41" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",TRIMMEAN(C7:L7,2/COUNT(C7:L7)))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D37" s="7">
+        <f t="shared" ref="D37:D41" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",TRIMMEAN(O7:X7,2/COUNT(O7:X7)))</f>
+        <v>0.116075</v>
+      </c>
+      <c r="E37" s="7">
+        <f t="shared" ref="E37:E41" si="2">IF(COUNTBLANK(C17:L17)&gt;0,"undone",TRIMMEAN(C17:L17,2/COUNT(C17:L17)))</f>
+        <v>0.47197499999999998</v>
+      </c>
+      <c r="F37" s="7">
+        <f t="shared" ref="F37:F41" si="3">IF(COUNTBLANK(O17:X17)&gt;0,"undone",TRIMMEAN(O17:X17,2/COUNT(O17:X17)))</f>
+        <v>10.990737499999998</v>
+      </c>
+      <c r="G37" s="7">
+        <f t="shared" ref="G37:G41" si="4">IF(COUNTBLANK(C27:L27)&gt;0,"undone",TRIMMEAN(C27:L27,2/COUNT(C27:L27)))</f>
+        <v>46.921199999999992</v>
+      </c>
+      <c r="H37" s="7">
+        <f t="shared" ref="H37:H41" si="5">IF(COUNTBLANK(O27:X27)&gt;0,"undone",TRIMMEAN(O27:X27,2/COUNT(O27:X27)))</f>
+        <v>1564.8245625</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="7">
         <f t="shared" si="0"/>
-        <v>8.9900000000000015E-3</v>
-      </c>
-      <c r="D38" s="16">
+        <v>8.7375000000000005E-3</v>
+      </c>
+      <c r="D38" s="7">
         <f t="shared" si="1"/>
-        <v>0.22323999999999997</v>
-      </c>
-      <c r="E38" s="16">
+        <v>0.22232499999999999</v>
+      </c>
+      <c r="E38" s="7">
         <f t="shared" si="2"/>
-        <v>0.86520999999999992</v>
-      </c>
-      <c r="F38" s="16">
+        <v>0.86371249999999999</v>
+      </c>
+      <c r="F38" s="7">
         <f t="shared" si="3"/>
-        <v>20.974539999999998</v>
-      </c>
-      <c r="G38" s="16">
+        <v>20.985674999999997</v>
+      </c>
+      <c r="G38" s="7">
         <f t="shared" si="4"/>
-        <v>89.085650000000001</v>
-      </c>
-      <c r="H38" s="16">
+        <v>88.970937500000005</v>
+      </c>
+      <c r="H38" s="7">
         <f t="shared" si="5"/>
-        <v>3090.3531499999999</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+        <v>3080.548875</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="7">
         <f t="shared" si="0"/>
-        <v>3.2099999999999997E-3</v>
-      </c>
-      <c r="D39" s="16">
+        <v>2.9624999999999999E-3</v>
+      </c>
+      <c r="D39" s="7">
         <f t="shared" si="1"/>
-        <v>1.9649999999999997E-2</v>
-      </c>
-      <c r="E39" s="16">
+        <v>1.85875E-2</v>
+      </c>
+      <c r="E39" s="7">
         <f t="shared" si="2"/>
-        <v>4.3359999999999996E-2</v>
-      </c>
-      <c r="F39" s="16">
+        <v>4.0962499999999992E-2</v>
+      </c>
+      <c r="F39" s="7">
         <f t="shared" si="3"/>
-        <v>0.33721999999999996</v>
-      </c>
-      <c r="G39" s="16">
+        <v>0.3334375</v>
+      </c>
+      <c r="G39" s="7">
         <f t="shared" si="4"/>
-        <v>0.88151000000000013</v>
-      </c>
-      <c r="H39" s="16">
+        <v>0.85593750000000002</v>
+      </c>
+      <c r="H39" s="7">
         <f t="shared" si="5"/>
-        <v>6.7085000000000008</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+        <v>6.6863124999999997</v>
+      </c>
+      <c r="J39" s="19">
+        <f>MAX(C16:L16)</f>
+        <v>0.34720000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="7">
         <f t="shared" si="0"/>
-        <v>1.7599999999999998E-3</v>
-      </c>
-      <c r="D40" s="16">
+        <v>1.5874999999999999E-3</v>
+      </c>
+      <c r="D40" s="7">
         <f t="shared" si="1"/>
-        <v>9.9300000000000013E-3</v>
-      </c>
-      <c r="E40" s="16">
+        <v>8.9125000000000003E-3</v>
+      </c>
+      <c r="E40" s="7">
         <f t="shared" si="2"/>
-        <v>2.6549999999999997E-2</v>
-      </c>
-      <c r="F40" s="16">
+        <v>2.5237499999999996E-2</v>
+      </c>
+      <c r="F40" s="7">
         <f t="shared" si="3"/>
-        <v>0.22603999999999996</v>
-      </c>
-      <c r="G40" s="16">
+        <v>0.22592499999999999</v>
+      </c>
+      <c r="G40" s="7">
         <f t="shared" si="4"/>
-        <v>0.51679000000000008</v>
-      </c>
-      <c r="H40" s="16">
+        <v>0.51642500000000002</v>
+      </c>
+      <c r="H40" s="7">
         <f t="shared" si="5"/>
-        <v>4.6064799999999995</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+        <v>4.5932874999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="7">
         <f t="shared" si="0"/>
-        <v>3.7600000000000003E-3</v>
-      </c>
-      <c r="D41" s="16">
+        <v>3.4500000000000008E-3</v>
+      </c>
+      <c r="D41" s="7">
         <f t="shared" si="1"/>
-        <v>1.9910000000000001E-2</v>
-      </c>
-      <c r="E41" s="16">
+        <v>1.9224999999999999E-2</v>
+      </c>
+      <c r="E41" s="7">
         <f t="shared" si="2"/>
-        <v>4.3620000000000006E-2</v>
-      </c>
-      <c r="F41" s="16">
+        <v>4.2412499999999999E-2</v>
+      </c>
+      <c r="F41" s="7">
         <f t="shared" si="3"/>
-        <v>0.30737999999999999</v>
-      </c>
-      <c r="G41" s="16">
+        <v>0.30487500000000001</v>
+      </c>
+      <c r="G41" s="7">
         <f t="shared" si="4"/>
-        <v>0.67976999999999999</v>
-      </c>
-      <c r="H41" s="16">
+        <v>0.67661250000000006</v>
+      </c>
+      <c r="H41" s="7">
         <f t="shared" si="5"/>
-        <v>5.8393899999999999</v>
+        <v>5.7241625000000003</v>
       </c>
     </row>
   </sheetData>
@@ -7301,10 +7308,10 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="17" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N17" t="s">
@@ -7336,10 +7343,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -7358,39 +7365,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="12"/>
-      <c r="N4" s="8" t="s">
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="14"/>
+      <c r="N4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
-      <c r="X4" s="12"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="14"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="9"/>
+      <c r="B5" s="11"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -7421,7 +7428,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="9"/>
+      <c r="N5" s="11"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -7457,67 +7464,67 @@
       <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="7">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="7">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="7">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="7">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="7">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="7">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="7">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="7">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="7">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="7">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6" s="7">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="P6" s="16">
+      <c r="P6" s="7">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6" s="7">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="R6" s="16">
+      <c r="R6" s="7">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="S6" s="16">
+      <c r="S6" s="7">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="T6" s="16">
+      <c r="T6" s="7">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="U6" s="16">
+      <c r="U6" s="7">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="V6" s="16">
+      <c r="V6" s="7">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="W6" s="16">
+      <c r="W6" s="7">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="X6" s="16">
+      <c r="X6" s="7">
         <v>1.2999999999999999E-3</v>
       </c>
     </row>
@@ -7525,67 +7532,67 @@
       <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="7">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="7">
         <v>6.6E-3</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="7">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="7">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="7">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="7">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="7">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="7">
         <v>6.3E-3</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="7">
         <v>6.3E-3</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="7">
         <v>6.3E-3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7" s="7">
         <v>0.15329999999999999</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7" s="7">
         <v>0.15329999999999999</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="7">
         <v>0.1532</v>
       </c>
-      <c r="R7" s="16">
+      <c r="R7" s="7">
         <v>0.1532</v>
       </c>
-      <c r="S7" s="16">
+      <c r="S7" s="7">
         <v>0.1532</v>
       </c>
-      <c r="T7" s="16">
+      <c r="T7" s="7">
         <v>0.1532</v>
       </c>
-      <c r="U7" s="16">
+      <c r="U7" s="7">
         <v>0.1532</v>
       </c>
-      <c r="V7" s="16">
+      <c r="V7" s="7">
         <v>0.1583</v>
       </c>
-      <c r="W7" s="16">
+      <c r="W7" s="7">
         <v>0.1532</v>
       </c>
-      <c r="X7" s="16">
+      <c r="X7" s="7">
         <v>0.1532</v>
       </c>
     </row>
@@ -7593,67 +7600,67 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="7">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="7">
         <v>7.7999999999999996E-3</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="7">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="7">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="7">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="7">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="7">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="7">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="7">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="7">
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="16">
+      <c r="O8" s="7">
         <v>0.1842</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="7">
         <v>0.1842</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="7">
         <v>0.18410000000000001</v>
       </c>
-      <c r="R8" s="16">
+      <c r="R8" s="7">
         <v>0.184</v>
       </c>
-      <c r="S8" s="16">
+      <c r="S8" s="7">
         <v>0.18410000000000001</v>
       </c>
-      <c r="T8" s="16">
+      <c r="T8" s="7">
         <v>0.18410000000000001</v>
       </c>
-      <c r="U8" s="16">
+      <c r="U8" s="7">
         <v>0.18410000000000001</v>
       </c>
-      <c r="V8" s="16">
+      <c r="V8" s="7">
         <v>0.18410000000000001</v>
       </c>
-      <c r="W8" s="16">
+      <c r="W8" s="7">
         <v>0.1842</v>
       </c>
-      <c r="X8" s="16">
+      <c r="X8" s="7">
         <v>0.184</v>
       </c>
     </row>
@@ -7661,67 +7668,67 @@
       <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="7">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="7">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="7">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="7">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="7">
         <v>3.8E-3</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="7">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="7">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="7">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="7">
         <v>3.8E-3</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="7">
         <v>3.8999999999999998E-3</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O9" s="7">
         <v>2.4299999999999999E-2</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="7">
         <v>2.3900000000000001E-2</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="7">
         <v>2.3900000000000001E-2</v>
       </c>
-      <c r="R9" s="16">
+      <c r="R9" s="7">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="S9" s="16">
+      <c r="S9" s="7">
         <v>2.3599999999999999E-2</v>
       </c>
-      <c r="T9" s="16">
+      <c r="T9" s="7">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="U9" s="16">
+      <c r="U9" s="7">
         <v>2.3900000000000001E-2</v>
       </c>
-      <c r="V9" s="16">
+      <c r="V9" s="7">
         <v>2.3900000000000001E-2</v>
       </c>
-      <c r="W9" s="16">
+      <c r="W9" s="7">
         <v>2.3900000000000001E-2</v>
       </c>
-      <c r="X9" s="16">
+      <c r="X9" s="7">
         <v>2.3800000000000002E-2</v>
       </c>
     </row>
@@ -7729,67 +7736,67 @@
       <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="7">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="7">
         <v>6.7000000000000002E-3</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="7">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="7">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="7">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="7">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="7">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="7">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="7">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="7">
         <v>6.1000000000000004E-3</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="7">
         <v>0.14829999999999999</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="7">
         <v>0.156</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="7">
         <v>0.15010000000000001</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="7">
         <v>0.14269999999999999</v>
       </c>
-      <c r="S10" s="16">
+      <c r="S10" s="7">
         <v>0.14280000000000001</v>
       </c>
-      <c r="T10" s="16">
+      <c r="T10" s="7">
         <v>0.1429</v>
       </c>
-      <c r="U10" s="16">
+      <c r="U10" s="7">
         <v>0.1431</v>
       </c>
-      <c r="V10" s="16">
+      <c r="V10" s="7">
         <v>0.14269999999999999</v>
       </c>
-      <c r="W10" s="16">
+      <c r="W10" s="7">
         <v>0.14269999999999999</v>
       </c>
-      <c r="X10" s="16">
+      <c r="X10" s="7">
         <v>0.14269999999999999</v>
       </c>
     </row>
@@ -7797,67 +7804,67 @@
       <c r="B11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="8">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="7">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="7">
         <v>3.8E-3</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="7">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="7">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="7">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="7">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="7">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="7">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="7">
         <v>3.5000000000000001E-3</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="8">
         <v>2.2200000000000001E-2</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="7">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="7">
         <v>2.9600000000000001E-2</v>
       </c>
-      <c r="R11" s="16">
+      <c r="R11" s="7">
         <v>2.1100000000000001E-2</v>
       </c>
-      <c r="S11" s="16">
+      <c r="S11" s="7">
         <v>1.9699999999999999E-2</v>
       </c>
-      <c r="T11" s="16">
+      <c r="T11" s="7">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="U11" s="16">
+      <c r="U11" s="7">
         <v>1.9300000000000001E-2</v>
       </c>
-      <c r="V11" s="16">
+      <c r="V11" s="7">
         <v>1.95E-2</v>
       </c>
-      <c r="W11" s="16">
+      <c r="W11" s="7">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="X11" s="16">
+      <c r="X11" s="7">
         <v>1.9400000000000001E-2</v>
       </c>
     </row>
@@ -7878,39 +7885,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="12"/>
-      <c r="N14" s="8" t="s">
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="14"/>
+      <c r="N14" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="O14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="12"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="14"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -7941,7 +7948,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="9"/>
+      <c r="N15" s="11"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -7977,67 +7984,67 @@
       <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="7">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="7">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="7">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="7">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="7">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="7">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="7">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="7">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="7">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="7">
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O16" s="7">
         <v>1.23E-2</v>
       </c>
-      <c r="P16" s="16">
+      <c r="P16" s="7">
         <v>1.23E-2</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="7">
         <v>1.2200000000000001E-2</v>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="7">
         <v>1.23E-2</v>
       </c>
-      <c r="S16" s="16">
+      <c r="S16" s="7">
         <v>1.23E-2</v>
       </c>
-      <c r="T16" s="16">
+      <c r="T16" s="7">
         <v>1.2200000000000001E-2</v>
       </c>
-      <c r="U16" s="16">
+      <c r="U16" s="7">
         <v>1.23E-2</v>
       </c>
-      <c r="V16" s="16">
+      <c r="V16" s="7">
         <v>1.23E-2</v>
       </c>
-      <c r="W16" s="16">
+      <c r="W16" s="7">
         <v>1.2200000000000001E-2</v>
       </c>
-      <c r="X16" s="16">
+      <c r="X16" s="7">
         <v>1.2200000000000001E-2</v>
       </c>
     </row>
@@ -8045,67 +8052,67 @@
       <c r="B17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="7">
         <v>0.60799999999999998</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="7">
         <v>0.6079</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="7">
         <v>0.61329999999999996</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="7">
         <v>0.60880000000000001</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="7">
         <v>0.60899999999999999</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="7">
         <v>0.60899999999999999</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="7">
         <v>0.69530000000000003</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="7">
         <v>0.63239999999999996</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="7">
         <v>0.72419999999999995</v>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="7">
         <v>0.69769999999999999</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O17" s="16">
+      <c r="O17" s="7">
         <v>15.3589</v>
       </c>
-      <c r="P17" s="16">
+      <c r="P17" s="7">
         <v>15.2684</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="Q17" s="7">
         <v>15.609299999999999</v>
       </c>
-      <c r="R17" s="16">
+      <c r="R17" s="7">
         <v>15.8925</v>
       </c>
-      <c r="S17" s="16">
+      <c r="S17" s="7">
         <v>15.537599999999999</v>
       </c>
-      <c r="T17" s="16">
+      <c r="T17" s="7">
         <v>15.5802</v>
       </c>
-      <c r="U17" s="16">
+      <c r="U17" s="7">
         <v>15.3429</v>
       </c>
-      <c r="V17" s="16">
+      <c r="V17" s="7">
         <v>15.2437</v>
       </c>
-      <c r="W17" s="16">
+      <c r="W17" s="7">
         <v>15.187900000000001</v>
       </c>
-      <c r="X17" s="16">
+      <c r="X17" s="7">
         <v>15.29</v>
       </c>
     </row>
@@ -8113,67 +8120,67 @@
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="7">
         <v>0.75929999999999997</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="7">
         <v>0.74329999999999996</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="7">
         <v>0.78059999999999996</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="7">
         <v>0.77790000000000004</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="7">
         <v>0.79720000000000002</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="7">
         <v>0.74309999999999998</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="7">
         <v>0.73670000000000002</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="7">
         <v>0.73160000000000003</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="7">
         <v>0.7319</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="7">
         <v>0.7369</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O18" s="16">
+      <c r="O18" s="7">
         <v>19.000800000000002</v>
       </c>
-      <c r="P18" s="16">
+      <c r="P18" s="7">
         <v>18.380600000000001</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="Q18" s="7">
         <v>18.504999999999999</v>
       </c>
-      <c r="R18" s="16">
+      <c r="R18" s="7">
         <v>18.361999999999998</v>
       </c>
-      <c r="S18" s="16">
+      <c r="S18" s="7">
         <v>18.454899999999999</v>
       </c>
-      <c r="T18" s="16">
+      <c r="T18" s="7">
         <v>18.518999999999998</v>
       </c>
-      <c r="U18" s="16">
+      <c r="U18" s="7">
         <v>18.597799999999999</v>
       </c>
-      <c r="V18" s="16">
+      <c r="V18" s="7">
         <v>18.1066</v>
       </c>
-      <c r="W18" s="16">
+      <c r="W18" s="7">
         <v>18.316299999999998</v>
       </c>
-      <c r="X18" s="16">
+      <c r="X18" s="7">
         <v>18.439399999999999</v>
       </c>
     </row>
@@ -8181,67 +8188,67 @@
       <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="7">
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="7">
         <v>5.16E-2</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="7">
         <v>5.1299999999999998E-2</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="7">
         <v>5.1400000000000001E-2</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="7">
         <v>5.16E-2</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="7">
         <v>5.1499999999999997E-2</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="7">
         <v>5.1700000000000003E-2</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="7">
         <v>5.1499999999999997E-2</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="7">
         <v>5.1400000000000001E-2</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="7">
         <v>5.16E-2</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O19" s="16">
+      <c r="O19" s="7">
         <v>0.30370000000000003</v>
       </c>
-      <c r="P19" s="16">
+      <c r="P19" s="7">
         <v>0.30130000000000001</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="Q19" s="7">
         <v>0.3095</v>
       </c>
-      <c r="R19" s="16">
+      <c r="R19" s="7">
         <v>0.3019</v>
       </c>
-      <c r="S19" s="16">
+      <c r="S19" s="7">
         <v>0.30220000000000002</v>
       </c>
-      <c r="T19" s="16">
+      <c r="T19" s="7">
         <v>0.30259999999999998</v>
       </c>
-      <c r="U19" s="16">
+      <c r="U19" s="7">
         <v>0.30170000000000002</v>
       </c>
-      <c r="V19" s="16">
+      <c r="V19" s="7">
         <v>0.3014</v>
       </c>
-      <c r="W19" s="16">
+      <c r="W19" s="7">
         <v>0.30599999999999999</v>
       </c>
-      <c r="X19" s="16">
+      <c r="X19" s="7">
         <v>0.30320000000000003</v>
       </c>
     </row>
@@ -8249,67 +8256,67 @@
       <c r="B20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="7">
         <v>0.56340000000000001</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="7">
         <v>0.49430000000000002</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="7">
         <v>0.57110000000000005</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="7">
         <v>0.57809999999999995</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="7">
         <v>0.5585</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="7">
         <v>0.56359999999999999</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="7">
         <v>0.5585</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="7">
         <v>0.55869999999999997</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="7">
         <v>0.59570000000000001</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="7">
         <v>0.55859999999999999</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O20" s="16">
+      <c r="O20" s="7">
         <v>13.824</v>
       </c>
-      <c r="P20" s="16">
+      <c r="P20" s="7">
         <v>13.820499999999999</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="Q20" s="7">
         <v>13.5</v>
       </c>
-      <c r="R20" s="16">
+      <c r="R20" s="7">
         <v>13.808400000000001</v>
       </c>
-      <c r="S20" s="16">
+      <c r="S20" s="7">
         <v>13.8751</v>
       </c>
-      <c r="T20" s="16">
+      <c r="T20" s="7">
         <v>13.818899999999999</v>
       </c>
-      <c r="U20" s="16">
+      <c r="U20" s="7">
         <v>13.9016</v>
       </c>
-      <c r="V20" s="16">
+      <c r="V20" s="7">
         <v>13.2591</v>
       </c>
-      <c r="W20" s="16">
+      <c r="W20" s="7">
         <v>13.9946</v>
       </c>
-      <c r="X20" s="16">
+      <c r="X20" s="7">
         <v>13.8437</v>
       </c>
     </row>
@@ -8317,67 +8324,67 @@
       <c r="B21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="8">
         <v>4.7600000000000003E-2</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="7">
         <v>4.5199999999999997E-2</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="7">
         <v>0.31380000000000002</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="7">
         <v>4.3499999999999997E-2</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="7">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="7">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="7">
         <v>4.3900000000000002E-2</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="7">
         <v>4.3799999999999999E-2</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="7">
         <v>4.2900000000000001E-2</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="7">
         <v>4.2099999999999999E-2</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="8">
         <v>0.23980000000000001</v>
       </c>
-      <c r="P21" s="16">
+      <c r="P21" s="7">
         <v>0.2326</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="Q21" s="7">
         <v>0.2205</v>
       </c>
-      <c r="R21" s="16">
+      <c r="R21" s="7">
         <v>0.22520000000000001</v>
       </c>
-      <c r="S21" s="16">
+      <c r="S21" s="7">
         <v>0.23369999999999999</v>
       </c>
-      <c r="T21" s="16">
+      <c r="T21" s="7">
         <v>0.22309999999999999</v>
       </c>
-      <c r="U21" s="16">
+      <c r="U21" s="7">
         <v>0.22159999999999999</v>
       </c>
-      <c r="V21" s="16">
+      <c r="V21" s="7">
         <v>0.22209999999999999</v>
       </c>
-      <c r="W21" s="16">
+      <c r="W21" s="7">
         <v>0.22850000000000001</v>
       </c>
-      <c r="X21" s="16">
+      <c r="X21" s="7">
         <v>0.22450000000000001</v>
       </c>
     </row>
@@ -8398,39 +8405,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="12"/>
-      <c r="N24" s="8" t="s">
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="14"/>
+      <c r="N24" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="10" t="s">
+      <c r="O24" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="12"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="14"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="9"/>
+      <c r="B25" s="11"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -8461,7 +8468,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="9"/>
+      <c r="N25" s="11"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -8497,67 +8504,67 @@
       <c r="B26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="7">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="7">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="7">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="7">
         <v>2.4400000000000002E-2</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="7">
         <v>2.4400000000000002E-2</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="7">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="7">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="7">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="7">
         <v>2.4400000000000002E-2</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="7">
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O26" s="7">
         <v>0.12230000000000001</v>
       </c>
-      <c r="P26" s="16">
+      <c r="P26" s="7">
         <v>0.12230000000000001</v>
       </c>
-      <c r="Q26" s="16">
+      <c r="Q26" s="7">
         <v>0.12230000000000001</v>
       </c>
-      <c r="R26" s="16">
+      <c r="R26" s="7">
         <v>0.1222</v>
       </c>
-      <c r="S26" s="16">
+      <c r="S26" s="7">
         <v>0.12230000000000001</v>
       </c>
-      <c r="T26" s="16">
+      <c r="T26" s="7">
         <v>0.1222</v>
       </c>
-      <c r="U26" s="16">
+      <c r="U26" s="7">
         <v>0.12230000000000001</v>
       </c>
-      <c r="V26" s="16">
+      <c r="V26" s="7">
         <v>0.12770000000000001</v>
       </c>
-      <c r="W26" s="16">
+      <c r="W26" s="7">
         <v>0.12230000000000001</v>
       </c>
-      <c r="X26" s="16">
+      <c r="X26" s="7">
         <v>0.12230000000000001</v>
       </c>
     </row>
@@ -8565,67 +8572,67 @@
       <c r="B27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="7">
         <v>62.367600000000003</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="7">
         <v>61.901699999999998</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="7">
         <v>61.0244</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="7">
         <v>61.341900000000003</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="7">
         <v>62.475499999999997</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="7">
         <v>60.632399999999997</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="7">
         <v>61.600999999999999</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="7">
         <v>61.796999999999997</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="7">
         <v>61.085999999999999</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="7">
         <v>62.555399999999999</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O27" s="16">
+      <c r="O27" s="7">
         <v>1544.2574999999999</v>
       </c>
-      <c r="P27" s="16">
+      <c r="P27" s="7">
         <v>1557.4327000000001</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="Q27" s="7">
         <v>1568.2515000000001</v>
       </c>
-      <c r="R27" s="16">
+      <c r="R27" s="7">
         <v>1526.5696</v>
       </c>
-      <c r="S27" s="16">
+      <c r="S27" s="7">
         <v>1660.1524999999999</v>
       </c>
-      <c r="T27" s="16">
+      <c r="T27" s="7">
         <v>1614.6695999999999</v>
       </c>
-      <c r="U27" s="16">
+      <c r="U27" s="7">
         <v>1586.1161</v>
       </c>
-      <c r="V27" s="16">
+      <c r="V27" s="7">
         <v>1648.0002999999999</v>
       </c>
-      <c r="W27" s="16">
+      <c r="W27" s="7">
         <v>1579.9689000000001</v>
       </c>
-      <c r="X27" s="16">
+      <c r="X27" s="7">
         <v>1599.7979</v>
       </c>
     </row>
@@ -8633,67 +8640,67 @@
       <c r="B28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="7">
         <v>74.833799999999997</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="7">
         <v>76.621399999999994</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="7">
         <v>76.111699999999999</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="7">
         <v>73.632300000000001</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="7">
         <v>73.761700000000005</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="7">
         <v>73.587500000000006</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="7">
         <v>76.504099999999994</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="7">
         <v>81.421400000000006</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="7">
         <v>90.009</v>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="7">
         <v>73.204300000000003</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O28" s="16">
+      <c r="O28" s="7">
         <v>1912.9282000000001</v>
       </c>
-      <c r="P28" s="16">
+      <c r="P28" s="7">
         <v>1884.4626000000001</v>
       </c>
-      <c r="Q28" s="16">
+      <c r="Q28" s="7">
         <v>1904.6116999999999</v>
       </c>
-      <c r="R28" s="16">
+      <c r="R28" s="7">
         <v>2017.0499</v>
       </c>
-      <c r="S28" s="16">
+      <c r="S28" s="7">
         <v>1899.6895</v>
       </c>
-      <c r="T28" s="16">
+      <c r="T28" s="7">
         <v>1875.664</v>
       </c>
-      <c r="U28" s="16">
+      <c r="U28" s="7">
         <v>1980.425</v>
       </c>
-      <c r="V28" s="16">
+      <c r="V28" s="7">
         <v>1861.0727999999999</v>
       </c>
-      <c r="W28" s="16">
+      <c r="W28" s="7">
         <v>1872.2660000000001</v>
       </c>
-      <c r="X28" s="16">
+      <c r="X28" s="7">
         <v>1881.9192</v>
       </c>
     </row>
@@ -8701,67 +8708,67 @@
       <c r="B29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="7">
         <v>0.64270000000000005</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="7">
         <v>0.6401</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="7">
         <v>0.65539999999999998</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="7">
         <v>0.64</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="7">
         <v>0.65959999999999996</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="7">
         <v>0.64859999999999995</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="7">
         <v>0.63980000000000004</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="7">
         <v>0.64080000000000004</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="7">
         <v>0.64729999999999999</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="7">
         <v>0.64070000000000005</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O29" s="16">
+      <c r="O29" s="7">
         <v>3.6398000000000001</v>
       </c>
-      <c r="P29" s="16">
+      <c r="P29" s="7">
         <v>3.7240000000000002</v>
       </c>
-      <c r="Q29" s="16">
+      <c r="Q29" s="7">
         <v>3.6631</v>
       </c>
-      <c r="R29" s="16">
+      <c r="R29" s="7">
         <v>3.6871</v>
       </c>
-      <c r="S29" s="16">
+      <c r="S29" s="7">
         <v>3.6657000000000002</v>
       </c>
-      <c r="T29" s="16">
+      <c r="T29" s="7">
         <v>3.7033999999999998</v>
       </c>
-      <c r="U29" s="16">
+      <c r="U29" s="7">
         <v>3.6800999999999999</v>
       </c>
-      <c r="V29" s="16">
+      <c r="V29" s="7">
         <v>3.6440999999999999</v>
       </c>
-      <c r="W29" s="16">
+      <c r="W29" s="7">
         <v>3.6665000000000001</v>
       </c>
-      <c r="X29" s="16">
+      <c r="X29" s="7">
         <v>3.782</v>
       </c>
     </row>
@@ -8769,67 +8776,67 @@
       <c r="B30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="7">
         <v>54.234200000000001</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="7">
         <v>55.121499999999997</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="7">
         <v>54.447299999999998</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="7">
         <v>55.137500000000003</v>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="7">
         <v>58.606099999999998</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="7">
         <v>55.237900000000003</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="7">
         <v>54.664200000000001</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="7">
         <v>54.142200000000003</v>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="7">
         <v>54.662700000000001</v>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="7">
         <v>56.613500000000002</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O30" s="16">
+      <c r="O30" s="7">
         <v>1370.6029000000001</v>
       </c>
-      <c r="P30" s="16">
+      <c r="P30" s="7">
         <v>1386.6452999999999</v>
       </c>
-      <c r="Q30" s="16">
+      <c r="Q30" s="7">
         <v>1469.2831000000001</v>
       </c>
-      <c r="R30" s="16">
+      <c r="R30" s="7">
         <v>1389.9918</v>
       </c>
-      <c r="S30" s="16">
+      <c r="S30" s="7">
         <v>1388.2077999999999</v>
       </c>
-      <c r="T30" s="16">
+      <c r="T30" s="7">
         <v>1406.0782999999999</v>
       </c>
-      <c r="U30" s="16">
+      <c r="U30" s="7">
         <v>1403.9821999999999</v>
       </c>
-      <c r="V30" s="16">
+      <c r="V30" s="7">
         <v>1384.3742999999999</v>
       </c>
-      <c r="W30" s="16">
+      <c r="W30" s="7">
         <v>1392.9535000000001</v>
       </c>
-      <c r="X30" s="16">
+      <c r="X30" s="7">
         <v>1368.1194</v>
       </c>
     </row>
@@ -8837,85 +8844,85 @@
       <c r="B31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="8">
         <v>0.42549999999999999</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="7">
         <v>0.40849999999999997</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="7">
         <v>0.40429999999999999</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="7">
         <v>0.40250000000000002</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="7">
         <v>0.4</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="7">
         <v>0.4042</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="7">
         <v>0.40179999999999999</v>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="7">
         <v>0.3992</v>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="7">
         <v>0.39989999999999998</v>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="7">
         <v>0.40639999999999998</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O31" s="17">
+      <c r="O31" s="8">
         <v>2.9708000000000001</v>
       </c>
-      <c r="P31" s="16">
+      <c r="P31" s="7">
         <v>2.9462999999999999</v>
       </c>
-      <c r="Q31" s="16">
+      <c r="Q31" s="7">
         <v>2.8967999999999998</v>
       </c>
-      <c r="R31" s="16">
+      <c r="R31" s="7">
         <v>3.0565000000000002</v>
       </c>
-      <c r="S31" s="16">
+      <c r="S31" s="7">
         <v>2.9175</v>
       </c>
-      <c r="T31" s="16">
+      <c r="T31" s="7">
         <v>2.9504999999999999</v>
       </c>
-      <c r="U31" s="16">
+      <c r="U31" s="7">
         <v>2.9243999999999999</v>
       </c>
-      <c r="V31" s="16">
+      <c r="V31" s="7">
         <v>2.8656000000000001</v>
       </c>
-      <c r="W31" s="16">
+      <c r="W31" s="7">
         <v>3.089</v>
       </c>
-      <c r="X31" s="16">
+      <c r="X31" s="7">
         <v>2.9117000000000002</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="14"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="9"/>
+      <c r="B35" s="11"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -8939,178 +8946,183 @@
       <c r="B36" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="16">
-        <f t="shared" ref="C36:C41" si="0">IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
-        <v>2.7999999999999998E-4</v>
-      </c>
-      <c r="D36" s="16">
-        <f t="shared" ref="D36:D41" si="1">IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
-        <v>1.2399999999999998E-3</v>
-      </c>
-      <c r="E36" s="16">
-        <f t="shared" ref="E36:E41" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
-        <v>2.4799999999999996E-3</v>
-      </c>
-      <c r="F36" s="16">
-        <f t="shared" ref="F36:F41" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
-        <v>1.2260000000000002E-2</v>
-      </c>
-      <c r="G36" s="16">
-        <f t="shared" ref="G36:G41" si="4">IF(COUNTBLANK(C26:L26)&gt;0,"undone",AVERAGE(C26:L26))</f>
-        <v>2.4469999999999999E-2</v>
-      </c>
-      <c r="H36" s="16">
-        <f t="shared" ref="H36:H41" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",AVERAGE(O26:X26))</f>
-        <v>0.12282</v>
+      <c r="C36" s="7">
+        <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",TRIMMEAN(C6:L6,2/COUNT(C6:L6)))</f>
+        <v>2.875E-4</v>
+      </c>
+      <c r="D36" s="7">
+        <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
+        <v>1.2374999999999999E-3</v>
+      </c>
+      <c r="E36" s="7">
+        <f>IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
+        <v>2.4874999999999997E-3</v>
+      </c>
+      <c r="F36" s="7">
+        <f>IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
+        <v>1.2262500000000001E-2</v>
+      </c>
+      <c r="G36" s="7">
+        <f>IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
+        <v>2.4475E-2</v>
+      </c>
+      <c r="H36" s="7">
+        <f>IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
+        <v>0.12228749999999998</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="16">
-        <f t="shared" si="0"/>
-        <v>7.3800000000000003E-3</v>
-      </c>
-      <c r="D37" s="16">
-        <f t="shared" si="1"/>
-        <v>0.15373000000000001</v>
-      </c>
-      <c r="E37" s="16">
-        <f t="shared" si="2"/>
-        <v>0.64056000000000002</v>
-      </c>
-      <c r="F37" s="16">
-        <f t="shared" si="3"/>
-        <v>15.431139999999999</v>
-      </c>
-      <c r="G37" s="16">
-        <f t="shared" si="4"/>
-        <v>61.678290000000004</v>
-      </c>
-      <c r="H37" s="16">
-        <f t="shared" si="5"/>
-        <v>1588.5216599999999</v>
+      <c r="C37" s="7">
+        <f t="shared" ref="C37:C41" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",TRIMMEAN(C7:L7,2/COUNT(C7:L7)))</f>
+        <v>7.2750000000000002E-3</v>
+      </c>
+      <c r="D37" s="7">
+        <f t="shared" ref="D37:D41" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",TRIMMEAN(O7:X7,2/COUNT(O7:X7)))</f>
+        <v>0.153225</v>
+      </c>
+      <c r="E37" s="7">
+        <f t="shared" ref="E37:E41" si="2">IF(COUNTBLANK(C17:L17)&gt;0,"undone",TRIMMEAN(C17:L17,2/COUNT(C17:L17)))</f>
+        <v>0.63418750000000002</v>
+      </c>
+      <c r="F37" s="7">
+        <f t="shared" ref="F37:F41" si="3">IF(COUNTBLANK(O17:X17)&gt;0,"undone",TRIMMEAN(O17:X17,2/COUNT(O17:X17)))</f>
+        <v>15.403874999999999</v>
+      </c>
+      <c r="G37" s="7">
+        <f t="shared" ref="G37:G41" si="4">IF(COUNTBLANK(C27:L27)&gt;0,"undone",TRIMMEAN(C27:L27,2/COUNT(C27:L27)))</f>
+        <v>61.6993875</v>
+      </c>
+      <c r="H37" s="7">
+        <f t="shared" ref="H37:H41" si="5">IF(COUNTBLANK(O27:X27)&gt;0,"undone",TRIMMEAN(O27:X27,2/COUNT(O27:X27)))</f>
+        <v>1587.3118125000001</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="7">
         <f t="shared" si="0"/>
-        <v>7.5699999999999986E-3</v>
-      </c>
-      <c r="D38" s="16">
+        <v>7.5374999999999999E-3</v>
+      </c>
+      <c r="D38" s="7">
         <f t="shared" si="1"/>
-        <v>0.18410999999999997</v>
-      </c>
-      <c r="E38" s="16">
+        <v>0.18411249999999998</v>
+      </c>
+      <c r="E38" s="7">
         <f t="shared" si="2"/>
-        <v>0.75385000000000013</v>
-      </c>
-      <c r="F38" s="16">
+        <v>0.75121250000000006</v>
+      </c>
+      <c r="F38" s="7">
         <f t="shared" si="3"/>
-        <v>18.468240000000002</v>
-      </c>
-      <c r="G38" s="16">
+        <v>18.446875000000002</v>
+      </c>
+      <c r="G38" s="7">
         <f t="shared" si="4"/>
-        <v>76.96871999999999</v>
-      </c>
-      <c r="H38" s="16">
+        <v>75.809237499999995</v>
+      </c>
+      <c r="H38" s="7">
         <f t="shared" si="5"/>
-        <v>1909.0088900000003</v>
+        <v>1901.4957750000001</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="7">
         <f t="shared" si="0"/>
-        <v>4.0300000000000006E-3</v>
-      </c>
-      <c r="D39" s="16">
+        <v>3.9375000000000009E-3</v>
+      </c>
+      <c r="D39" s="7">
         <f t="shared" si="1"/>
-        <v>2.3880000000000002E-2</v>
-      </c>
-      <c r="E39" s="16">
+        <v>2.3862500000000002E-2</v>
+      </c>
+      <c r="E39" s="7">
         <f t="shared" si="2"/>
-        <v>5.1610000000000003E-2</v>
-      </c>
-      <c r="F39" s="16">
+        <v>5.15375E-2</v>
+      </c>
+      <c r="F39" s="7">
         <f t="shared" si="3"/>
-        <v>0.30335000000000001</v>
-      </c>
-      <c r="G39" s="16">
+        <v>0.30283749999999998</v>
+      </c>
+      <c r="G39" s="7">
         <f t="shared" si="4"/>
-        <v>0.64549999999999996</v>
-      </c>
-      <c r="H39" s="16">
+        <v>0.64444999999999997</v>
+      </c>
+      <c r="H39" s="7">
         <f t="shared" si="5"/>
-        <v>3.6855800000000003</v>
+        <v>3.6792499999999997</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="7">
         <f t="shared" si="0"/>
-        <v>6.2899999999999996E-3</v>
-      </c>
-      <c r="D40" s="16">
+        <v>6.2249999999999996E-3</v>
+      </c>
+      <c r="D40" s="7">
         <f t="shared" si="1"/>
-        <v>0.14540000000000003</v>
-      </c>
-      <c r="E40" s="16">
+        <v>0.1444125</v>
+      </c>
+      <c r="E40" s="7">
         <f t="shared" si="2"/>
-        <v>0.56005000000000005</v>
-      </c>
-      <c r="F40" s="16">
+        <v>0.56381250000000005</v>
+      </c>
+      <c r="F40" s="7">
         <f t="shared" si="3"/>
-        <v>13.764590000000002</v>
-      </c>
-      <c r="G40" s="16">
+        <v>13.799025</v>
+      </c>
+      <c r="G40" s="7">
         <f t="shared" si="4"/>
-        <v>55.286710000000006</v>
-      </c>
-      <c r="H40" s="16">
+        <v>55.014850000000003</v>
+      </c>
+      <c r="H40" s="7">
         <f t="shared" si="5"/>
-        <v>1396.0238599999998</v>
+        <v>1390.3545124999998</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="7">
         <f t="shared" si="0"/>
-        <v>3.7500000000000007E-3</v>
-      </c>
-      <c r="D41" s="16">
+        <v>3.6750000000000003E-3</v>
+      </c>
+      <c r="D41" s="7">
         <f t="shared" si="1"/>
-        <v>2.0990000000000002E-2</v>
-      </c>
-      <c r="E41" s="16">
+        <v>2.0125000000000001E-2</v>
+      </c>
+      <c r="E41" s="7">
         <f t="shared" si="2"/>
-        <v>7.1000000000000008E-2</v>
-      </c>
-      <c r="F41" s="16">
+        <v>4.4262499999999996E-2</v>
+      </c>
+      <c r="F41" s="7">
         <f t="shared" si="3"/>
-        <v>0.22716000000000003</v>
-      </c>
-      <c r="G41" s="16">
+        <v>0.22641249999999996</v>
+      </c>
+      <c r="G41" s="7">
         <f t="shared" si="4"/>
-        <v>0.40522999999999998</v>
-      </c>
-      <c r="H41" s="16">
+        <v>0.40345000000000003</v>
+      </c>
+      <c r="H41" s="7">
         <f t="shared" si="5"/>
-        <v>2.9529099999999997</v>
+        <v>2.9468124999999996</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -9121,11 +9133,6 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9138,454 +9145,454 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="18"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18"/>
-      <c r="S7" s="18"/>
-      <c r="T7" s="18"/>
-      <c r="U7" s="18"/>
-      <c r="V7" s="18"/>
-      <c r="W7" s="18"/>
-      <c r="X7" s="18"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="18"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18"/>
-      <c r="V8" s="18"/>
-      <c r="W8" s="18"/>
-      <c r="X8" s="18"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="18"/>
-      <c r="V9" s="18"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="18"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="18"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="18"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="18"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="18"/>
-      <c r="U11" s="18"/>
-      <c r="V11" s="18"/>
-      <c r="W11" s="18"/>
-      <c r="X11" s="18"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="18"/>
-      <c r="T16" s="18"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="18"/>
-      <c r="W16" s="18"/>
-      <c r="X16" s="18"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
     </row>
     <row r="17" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="18"/>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
-      <c r="V17" s="18"/>
-      <c r="W17" s="18"/>
-      <c r="X17" s="18"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
     </row>
     <row r="18" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="18"/>
-      <c r="R18" s="18"/>
-      <c r="S18" s="18"/>
-      <c r="T18" s="18"/>
-      <c r="U18" s="18"/>
-      <c r="V18" s="18"/>
-      <c r="W18" s="18"/>
-      <c r="X18" s="18"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
     </row>
     <row r="19" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="18"/>
-      <c r="W19" s="18"/>
-      <c r="X19" s="18"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
     </row>
     <row r="20" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="18"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
     </row>
     <row r="21" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="O21" s="18"/>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="18"/>
-      <c r="R21" s="18"/>
-      <c r="S21" s="18"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
     </row>
     <row r="26" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="18"/>
-      <c r="R26" s="18"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18"/>
-      <c r="U26" s="18"/>
-      <c r="V26" s="18"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
     </row>
     <row r="27" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="O27" s="18"/>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="18"/>
-      <c r="R27" s="18"/>
-      <c r="S27" s="18"/>
-      <c r="T27" s="18"/>
-      <c r="U27" s="18"/>
-      <c r="V27" s="18"/>
-      <c r="W27" s="18"/>
-      <c r="X27" s="18"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
     </row>
     <row r="28" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="O28" s="18"/>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="18"/>
-      <c r="R28" s="18"/>
-      <c r="S28" s="18"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="18"/>
-      <c r="V28" s="18"/>
-      <c r="W28" s="18"/>
-      <c r="X28" s="18"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="18"/>
-      <c r="V29" s="18"/>
-      <c r="W29" s="18"/>
-      <c r="X29" s="18"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
     </row>
     <row r="30" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="18"/>
-      <c r="V30" s="18"/>
-      <c r="W30" s="18"/>
-      <c r="X30" s="18"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="18"/>
-      <c r="V31" s="18"/>
-      <c r="W31" s="18"/>
-      <c r="X31" s="18"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
     </row>
     <row r="36" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
     </row>
     <row r="41" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9611,10 +9618,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -9633,39 +9640,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="12"/>
-      <c r="N4" s="8" t="s">
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="14"/>
+      <c r="N4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
-      <c r="X4" s="12"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="14"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="9"/>
+      <c r="B5" s="11"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -9696,7 +9703,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="9"/>
+      <c r="N5" s="11"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -9732,67 +9739,67 @@
       <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="7">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="7">
         <v>1.0200000000000001E-2</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="7">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="7">
         <v>9.7999999999999997E-3</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="7">
         <v>9.7999999999999997E-3</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="7">
         <v>9.7999999999999997E-3</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="7">
         <v>9.7999999999999997E-3</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="7">
         <v>9.7999999999999997E-3</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="7">
         <v>9.7999999999999997E-3</v>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="7">
         <v>9.7999999999999997E-3</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6" s="7">
         <v>0.25900000000000001</v>
       </c>
-      <c r="P6" s="16">
+      <c r="P6" s="7">
         <v>0.2727</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6" s="7">
         <v>0.27539999999999998</v>
       </c>
-      <c r="R6" s="16">
+      <c r="R6" s="7">
         <v>0.25779999999999997</v>
       </c>
-      <c r="S6" s="16">
+      <c r="S6" s="7">
         <v>0.24940000000000001</v>
       </c>
-      <c r="T6" s="16">
+      <c r="T6" s="7">
         <v>0.24929999999999999</v>
       </c>
-      <c r="U6" s="16">
+      <c r="U6" s="7">
         <v>0.25900000000000001</v>
       </c>
-      <c r="V6" s="16">
+      <c r="V6" s="7">
         <v>0.24909999999999999</v>
       </c>
-      <c r="W6" s="16">
+      <c r="W6" s="7">
         <v>0.2492</v>
       </c>
-      <c r="X6" s="16">
+      <c r="X6" s="7">
         <v>0.25090000000000001</v>
       </c>
     </row>
@@ -9800,67 +9807,67 @@
       <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="7">
         <v>8.6E-3</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="7">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="7">
         <v>7.4000000000000003E-3</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="7">
         <v>7.4000000000000003E-3</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="7">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="7">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="7">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="7">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="7">
         <v>7.1999999999999998E-3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7" s="7">
         <v>0.1842</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7" s="7">
         <v>0.1845</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="7">
         <v>0.18440000000000001</v>
       </c>
-      <c r="R7" s="16">
+      <c r="R7" s="7">
         <v>0.1842</v>
       </c>
-      <c r="S7" s="16">
+      <c r="S7" s="7">
         <v>0.18390000000000001</v>
       </c>
-      <c r="T7" s="16">
+      <c r="T7" s="7">
         <v>0.18820000000000001</v>
       </c>
-      <c r="U7" s="16">
+      <c r="U7" s="7">
         <v>0.1842</v>
       </c>
-      <c r="V7" s="16">
+      <c r="V7" s="7">
         <v>0.18440000000000001</v>
       </c>
-      <c r="W7" s="16">
+      <c r="W7" s="7">
         <v>0.21360000000000001</v>
       </c>
-      <c r="X7" s="16">
+      <c r="X7" s="7">
         <v>0.184</v>
       </c>
     </row>
@@ -9868,67 +9875,67 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="7">
         <v>1.6E-2</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="7">
         <v>2.2599999999999999E-2</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="7">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="7">
         <v>1.6500000000000001E-2</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="7">
         <v>1.6500000000000001E-2</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="7">
         <v>1.6500000000000001E-2</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="7">
         <v>1.66E-2</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="7">
         <v>1.6500000000000001E-2</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="7">
         <v>1.66E-2</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="7">
         <v>1.66E-2</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="16">
+      <c r="O8" s="7">
         <v>0.38940000000000002</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="7">
         <v>0.38950000000000001</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="7">
         <v>0.38950000000000001</v>
       </c>
-      <c r="R8" s="16">
+      <c r="R8" s="7">
         <v>0.3947</v>
       </c>
-      <c r="S8" s="16">
+      <c r="S8" s="7">
         <v>0.38990000000000002</v>
       </c>
-      <c r="T8" s="16">
+      <c r="T8" s="7">
         <v>0.39</v>
       </c>
-      <c r="U8" s="16">
+      <c r="U8" s="7">
         <v>0.38890000000000002</v>
       </c>
-      <c r="V8" s="16">
+      <c r="V8" s="7">
         <v>0.3891</v>
       </c>
-      <c r="W8" s="16">
+      <c r="W8" s="7">
         <v>0.39319999999999999</v>
       </c>
-      <c r="X8" s="16">
+      <c r="X8" s="7">
         <v>0.38950000000000001</v>
       </c>
     </row>
@@ -9936,67 +9943,67 @@
       <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="7">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="7">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="7">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="7">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="7">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="7">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="7">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="7">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="7">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="7">
         <v>3.8E-3</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O9" s="7">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="7">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="7">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="R9" s="16">
+      <c r="R9" s="7">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="S9" s="16">
+      <c r="S9" s="7">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="T9" s="16">
+      <c r="T9" s="7">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="U9" s="16">
+      <c r="U9" s="7">
         <v>2.3900000000000001E-2</v>
       </c>
-      <c r="V9" s="16">
+      <c r="V9" s="7">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="W9" s="16">
+      <c r="W9" s="7">
         <v>2.3900000000000001E-2</v>
       </c>
-      <c r="X9" s="16">
+      <c r="X9" s="7">
         <v>2.3800000000000002E-2</v>
       </c>
     </row>
@@ -10004,67 +10011,67 @@
       <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="7">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="7">
         <v>6.6E-3</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="7">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="7">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="7">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="7">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="7">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="7">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="7">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="7">
         <v>5.7000000000000002E-3</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="7">
         <v>0.14419999999999999</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="7">
         <v>0.14249999999999999</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="7">
         <v>0.14219999999999999</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="7">
         <v>0.1421</v>
       </c>
-      <c r="S10" s="16">
+      <c r="S10" s="7">
         <v>0.1421</v>
       </c>
-      <c r="T10" s="16">
+      <c r="T10" s="7">
         <v>0.14199999999999999</v>
       </c>
-      <c r="U10" s="16">
+      <c r="U10" s="7">
         <v>0.14729999999999999</v>
       </c>
-      <c r="V10" s="16">
+      <c r="V10" s="7">
         <v>0.14829999999999999</v>
       </c>
-      <c r="W10" s="16">
+      <c r="W10" s="7">
         <v>0.14199999999999999</v>
       </c>
-      <c r="X10" s="16">
+      <c r="X10" s="7">
         <v>0.1421</v>
       </c>
     </row>
@@ -10072,67 +10079,67 @@
       <c r="B11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="8">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="7">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="7">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="7">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="7">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="7">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="7">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="7">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="7">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="7">
         <v>5.4999999999999997E-3</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="8">
         <v>2.5600000000000001E-2</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="7">
         <v>2.23E-2</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="7">
         <v>2.1399999999999999E-2</v>
       </c>
-      <c r="R11" s="16">
+      <c r="R11" s="7">
         <v>2.1100000000000001E-2</v>
       </c>
-      <c r="S11" s="16">
+      <c r="S11" s="7">
         <v>2.0899999999999998E-2</v>
       </c>
-      <c r="T11" s="16">
+      <c r="T11" s="7">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="U11" s="16">
+      <c r="U11" s="7">
         <v>0.02</v>
       </c>
-      <c r="V11" s="16">
+      <c r="V11" s="7">
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="W11" s="16">
+      <c r="W11" s="7">
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="X11" s="16">
+      <c r="X11" s="7">
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
@@ -10153,39 +10160,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="12"/>
-      <c r="N14" s="8" t="s">
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="14"/>
+      <c r="N14" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="O14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="12"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="14"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -10216,7 +10223,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="9"/>
+      <c r="N15" s="11"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -10252,67 +10259,67 @@
       <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="7">
         <v>1.0750999999999999</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="7">
         <v>0.99370000000000003</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="7">
         <v>0.97160000000000002</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="7">
         <v>0.98199999999999998</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="7">
         <v>0.9718</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="7">
         <v>0.97619999999999996</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="7">
         <v>0.97540000000000004</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="7">
         <v>0.9829</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="7">
         <v>0.97019999999999995</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="7">
         <v>0.99550000000000005</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O16" s="7">
         <v>24.840299999999999</v>
       </c>
-      <c r="P16" s="16">
+      <c r="P16" s="7">
         <v>24.508500000000002</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="7">
         <v>24.6541</v>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="7">
         <v>24.295100000000001</v>
       </c>
-      <c r="S16" s="16">
+      <c r="S16" s="7">
         <v>24.7681</v>
       </c>
-      <c r="T16" s="16">
+      <c r="T16" s="7">
         <v>24.515899999999998</v>
       </c>
-      <c r="U16" s="16">
+      <c r="U16" s="7">
         <v>23.835899999999999</v>
       </c>
-      <c r="V16" s="16">
+      <c r="V16" s="7">
         <v>24.336400000000001</v>
       </c>
-      <c r="W16" s="16">
+      <c r="W16" s="7">
         <v>24.5289</v>
       </c>
-      <c r="X16" s="16">
+      <c r="X16" s="7">
         <v>23.666699999999999</v>
       </c>
     </row>
@@ -10320,67 +10327,67 @@
       <c r="B17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="7">
         <v>0.72299999999999998</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="7">
         <v>0.72360000000000002</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="7">
         <v>0.72740000000000005</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="7">
         <v>0.72340000000000004</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="7">
         <v>0.72340000000000004</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="7">
         <v>0.72629999999999995</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="7">
         <v>0.72270000000000001</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="7">
         <v>0.89949999999999997</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="7">
         <v>0.76639999999999997</v>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="7">
         <v>0.74050000000000005</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O17" s="16">
+      <c r="O17" s="7">
         <v>16.858899999999998</v>
       </c>
-      <c r="P17" s="16">
+      <c r="P17" s="7">
         <v>17.928100000000001</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="Q17" s="7">
         <v>17.011800000000001</v>
       </c>
-      <c r="R17" s="16">
+      <c r="R17" s="7">
         <v>17.098800000000001</v>
       </c>
-      <c r="S17" s="16">
+      <c r="S17" s="7">
         <v>17.081399999999999</v>
       </c>
-      <c r="T17" s="16">
+      <c r="T17" s="7">
         <v>17.333300000000001</v>
       </c>
-      <c r="U17" s="16">
+      <c r="U17" s="7">
         <v>17.135999999999999</v>
       </c>
-      <c r="V17" s="16">
+      <c r="V17" s="7">
         <v>17.391500000000001</v>
       </c>
-      <c r="W17" s="16">
+      <c r="W17" s="7">
         <v>17.0106</v>
       </c>
-      <c r="X17" s="16">
+      <c r="X17" s="7">
         <v>17.516500000000001</v>
       </c>
     </row>
@@ -10388,67 +10395,67 @@
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="7">
         <v>1.5733999999999999</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="7">
         <v>1.6429</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="7">
         <v>1.5697000000000001</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="7">
         <v>1.5553999999999999</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="7">
         <v>1.5952</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="7">
         <v>1.5569</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="7">
         <v>1.5528</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="7">
         <v>1.5565</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="7">
         <v>1.6240000000000001</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="7">
         <v>1.5831999999999999</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O18" s="16">
+      <c r="O18" s="7">
         <v>39.5075</v>
       </c>
-      <c r="P18" s="16">
+      <c r="P18" s="7">
         <v>39.857100000000003</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="Q18" s="7">
         <v>39.328400000000002</v>
       </c>
-      <c r="R18" s="16">
+      <c r="R18" s="7">
         <v>41.061</v>
       </c>
-      <c r="S18" s="16">
+      <c r="S18" s="7">
         <v>39.5852</v>
       </c>
-      <c r="T18" s="16">
+      <c r="T18" s="7">
         <v>39.423699999999997</v>
       </c>
-      <c r="U18" s="16">
+      <c r="U18" s="7">
         <v>38.983600000000003</v>
       </c>
-      <c r="V18" s="16">
+      <c r="V18" s="7">
         <v>38.880800000000001</v>
       </c>
-      <c r="W18" s="16">
+      <c r="W18" s="7">
         <v>39.415199999999999</v>
       </c>
-      <c r="X18" s="16">
+      <c r="X18" s="7">
         <v>39.238599999999998</v>
       </c>
     </row>
@@ -10456,67 +10463,67 @@
       <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="7">
         <v>5.16E-2</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="7">
         <v>5.1400000000000001E-2</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="7">
         <v>5.1299999999999998E-2</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="7">
         <v>5.1200000000000002E-2</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="7">
         <v>5.11E-2</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="7">
         <v>5.11E-2</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="7">
         <v>5.1499999999999997E-2</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="7">
         <v>5.1200000000000002E-2</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="7">
         <v>5.1200000000000002E-2</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="7">
         <v>5.1200000000000002E-2</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O19" s="16">
+      <c r="O19" s="7">
         <v>0.30109999999999998</v>
       </c>
-      <c r="P19" s="16">
+      <c r="P19" s="7">
         <v>0.29920000000000002</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="Q19" s="7">
         <v>0.2984</v>
       </c>
-      <c r="R19" s="16">
+      <c r="R19" s="7">
         <v>0.29849999999999999</v>
       </c>
-      <c r="S19" s="16">
+      <c r="S19" s="7">
         <v>0.30580000000000002</v>
       </c>
-      <c r="T19" s="16">
+      <c r="T19" s="7">
         <v>0.3029</v>
       </c>
-      <c r="U19" s="16">
+      <c r="U19" s="7">
         <v>0.30320000000000003</v>
       </c>
-      <c r="V19" s="16">
+      <c r="V19" s="7">
         <v>0.3034</v>
       </c>
-      <c r="W19" s="16">
+      <c r="W19" s="7">
         <v>0.30259999999999998</v>
       </c>
-      <c r="X19" s="16">
+      <c r="X19" s="7">
         <v>0.30359999999999998</v>
       </c>
     </row>
@@ -10524,67 +10531,67 @@
       <c r="B20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="7">
         <v>0.5645</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="7">
         <v>0.55740000000000001</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="7">
         <v>0.55689999999999995</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="7">
         <v>0.55730000000000002</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="7">
         <v>0.59730000000000005</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="7">
         <v>0.5575</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="7">
         <v>0.55720000000000003</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="7">
         <v>0.56169999999999998</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="7">
         <v>0.5575</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="7">
         <v>0.57669999999999999</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O20" s="16">
+      <c r="O20" s="7">
         <v>13.8203</v>
       </c>
-      <c r="P20" s="16">
+      <c r="P20" s="7">
         <v>13.972</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="Q20" s="7">
         <v>13.481999999999999</v>
       </c>
-      <c r="R20" s="16">
+      <c r="R20" s="7">
         <v>13.954800000000001</v>
       </c>
-      <c r="S20" s="16">
+      <c r="S20" s="7">
         <v>13.725099999999999</v>
       </c>
-      <c r="T20" s="16">
+      <c r="T20" s="7">
         <v>13.9758</v>
       </c>
-      <c r="U20" s="16">
+      <c r="U20" s="7">
         <v>13.8742</v>
       </c>
-      <c r="V20" s="16">
+      <c r="V20" s="7">
         <v>13.9161</v>
       </c>
-      <c r="W20" s="16">
+      <c r="W20" s="7">
         <v>13.9131</v>
       </c>
-      <c r="X20" s="16">
+      <c r="X20" s="7">
         <v>13.7484</v>
       </c>
     </row>
@@ -10592,67 +10599,67 @@
       <c r="B21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="8">
         <v>4.8099999999999997E-2</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="7">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="7">
         <v>4.4900000000000002E-2</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="7">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="7">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="7">
         <v>4.4499999999999998E-2</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="7">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="7">
         <v>4.2599999999999999E-2</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="7">
         <v>4.2200000000000001E-2</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="7">
         <v>4.19E-2</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="8">
         <v>0.26519999999999999</v>
       </c>
-      <c r="P21" s="16">
+      <c r="P21" s="7">
         <v>0.25779999999999997</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="Q21" s="7">
         <v>0.36549999999999999</v>
       </c>
-      <c r="R21" s="16">
+      <c r="R21" s="7">
         <v>0.33410000000000001</v>
       </c>
-      <c r="S21" s="16">
+      <c r="S21" s="7">
         <v>0.25269999999999998</v>
       </c>
-      <c r="T21" s="16">
+      <c r="T21" s="7">
         <v>0.2717</v>
       </c>
-      <c r="U21" s="16">
+      <c r="U21" s="7">
         <v>0.26079999999999998</v>
       </c>
-      <c r="V21" s="16">
+      <c r="V21" s="7">
         <v>0.27939999999999998</v>
       </c>
-      <c r="W21" s="16">
+      <c r="W21" s="7">
         <v>0.26889999999999997</v>
       </c>
-      <c r="X21" s="16">
+      <c r="X21" s="7">
         <v>0.2616</v>
       </c>
     </row>
@@ -10673,39 +10680,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="12"/>
-      <c r="N24" s="8" t="s">
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="14"/>
+      <c r="N24" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="10" t="s">
+      <c r="O24" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="12"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="14"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="9"/>
+      <c r="B25" s="11"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -10736,7 +10743,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="9"/>
+      <c r="N25" s="11"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -10772,67 +10779,67 @@
       <c r="B26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="7">
         <v>97.5488</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="7">
         <v>98.369799999999998</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="7">
         <v>99.552800000000005</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="7">
         <v>99.213399999999993</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="7">
         <v>98.655199999999994</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="7">
         <v>99.038399999999996</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="7">
         <v>97.869500000000002</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="7">
         <v>106.6422</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="7">
         <v>106.8325</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="7">
         <v>97.520399999999995</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O26" s="7">
         <v>2541.7563</v>
       </c>
-      <c r="P26" s="16">
+      <c r="P26" s="7">
         <v>2439.4488000000001</v>
       </c>
-      <c r="Q26" s="16">
+      <c r="Q26" s="7">
         <v>2473.8420999999998</v>
       </c>
-      <c r="R26" s="16">
+      <c r="R26" s="7">
         <v>2467.9744999999998</v>
       </c>
-      <c r="S26" s="16">
+      <c r="S26" s="7">
         <v>2440.3240000000001</v>
       </c>
-      <c r="T26" s="16">
+      <c r="T26" s="7">
         <v>2480.4919</v>
       </c>
-      <c r="U26" s="16">
+      <c r="U26" s="7">
         <v>2534.1064000000001</v>
       </c>
-      <c r="V26" s="16">
+      <c r="V26" s="7">
         <v>2492.3797</v>
       </c>
-      <c r="W26" s="16">
+      <c r="W26" s="7">
         <v>2451.6749</v>
       </c>
-      <c r="X26" s="16">
+      <c r="X26" s="7">
         <v>2443.8258999999998</v>
       </c>
     </row>
@@ -10840,67 +10847,67 @@
       <c r="B27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="7">
         <v>68.721800000000002</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="7">
         <v>70.764300000000006</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="7">
         <v>69.231700000000004</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="7">
         <v>69.771900000000002</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="7">
         <v>68.707700000000003</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="7">
         <v>70.793000000000006</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="7">
         <v>70.539599999999993</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="7">
         <v>69.965999999999994</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="7">
         <v>68.951700000000002</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="7">
         <v>68.124499999999998</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O27" s="16">
+      <c r="O27" s="7">
         <v>1706.2204999999999</v>
       </c>
-      <c r="P27" s="16">
+      <c r="P27" s="7">
         <v>1722.7882</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="Q27" s="7">
         <v>1716.2449999999999</v>
       </c>
-      <c r="R27" s="16">
+      <c r="R27" s="7">
         <v>1735.9366</v>
       </c>
-      <c r="S27" s="16">
+      <c r="S27" s="7">
         <v>1808.3788999999999</v>
       </c>
-      <c r="T27" s="16">
+      <c r="T27" s="7">
         <v>1739.9007999999999</v>
       </c>
-      <c r="U27" s="16">
+      <c r="U27" s="7">
         <v>1779.6002000000001</v>
       </c>
-      <c r="V27" s="16">
+      <c r="V27" s="7">
         <v>1821.173</v>
       </c>
-      <c r="W27" s="16">
+      <c r="W27" s="7">
         <v>1775.1714999999999</v>
       </c>
-      <c r="X27" s="16">
+      <c r="X27" s="7">
         <v>1737.0802000000001</v>
       </c>
     </row>
@@ -10908,67 +10915,67 @@
       <c r="B28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="7">
         <v>155.63669999999999</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="7">
         <v>158.48089999999999</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="7">
         <v>158.53970000000001</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="7">
         <v>156.80080000000001</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="7">
         <v>156.71109999999999</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="7">
         <v>156.67519999999999</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="7">
         <v>156.8115</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="7">
         <v>155.8948</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="7">
         <v>157.71350000000001</v>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="7">
         <v>173.56290000000001</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O28" s="16">
+      <c r="O28" s="7">
         <v>3981.8562999999999</v>
       </c>
-      <c r="P28" s="16">
+      <c r="P28" s="7">
         <v>4099.4161999999997</v>
       </c>
-      <c r="Q28" s="16">
+      <c r="Q28" s="7">
         <v>4157.1232</v>
       </c>
-      <c r="R28" s="16">
+      <c r="R28" s="7">
         <v>3990.9665</v>
       </c>
-      <c r="S28" s="16">
+      <c r="S28" s="7">
         <v>3977.2503999999999</v>
       </c>
-      <c r="T28" s="16">
+      <c r="T28" s="7">
         <v>4131.8361999999997</v>
       </c>
-      <c r="U28" s="16">
+      <c r="U28" s="7">
         <v>3977.6208999999999</v>
       </c>
-      <c r="V28" s="16">
+      <c r="V28" s="7">
         <v>4035.7348000000002</v>
       </c>
-      <c r="W28" s="16">
+      <c r="W28" s="7">
         <v>4038.6617000000001</v>
       </c>
-      <c r="X28" s="16">
+      <c r="X28" s="7">
         <v>4191.5901000000003</v>
       </c>
     </row>
@@ -10976,67 +10983,67 @@
       <c r="B29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="7">
         <v>0.69189999999999996</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="7">
         <v>0.64080000000000004</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="7">
         <v>0.6361</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="7">
         <v>0.64139999999999997</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="7">
         <v>0.66100000000000003</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="7">
         <v>0.63470000000000004</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="7">
         <v>0.70350000000000001</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="7">
         <v>0.67949999999999999</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="7">
         <v>0.6794</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="7">
         <v>0.6794</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O29" s="16">
+      <c r="O29" s="7">
         <v>3.7126999999999999</v>
       </c>
-      <c r="P29" s="16">
+      <c r="P29" s="7">
         <v>3.8384</v>
       </c>
-      <c r="Q29" s="16">
+      <c r="Q29" s="7">
         <v>3.323</v>
       </c>
-      <c r="R29" s="16">
+      <c r="R29" s="7">
         <v>3.7961999999999998</v>
       </c>
-      <c r="S29" s="16">
+      <c r="S29" s="7">
         <v>3.7214</v>
       </c>
-      <c r="T29" s="16">
+      <c r="T29" s="7">
         <v>3.6259000000000001</v>
       </c>
-      <c r="U29" s="16">
+      <c r="U29" s="7">
         <v>3.9177</v>
       </c>
-      <c r="V29" s="16">
+      <c r="V29" s="7">
         <v>3.6977000000000002</v>
       </c>
-      <c r="W29" s="16">
+      <c r="W29" s="7">
         <v>3.7311999999999999</v>
       </c>
-      <c r="X29" s="16">
+      <c r="X29" s="7">
         <v>3.9571999999999998</v>
       </c>
     </row>
@@ -11044,67 +11051,67 @@
       <c r="B30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="7">
         <v>55.2896</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="7">
         <v>55.613799999999998</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="7">
         <v>55.098100000000002</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="7">
         <v>56.133600000000001</v>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="7">
         <v>54.2136</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="7">
         <v>53.503</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="7">
         <v>54.895299999999999</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="7">
         <v>55.783099999999997</v>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="7">
         <v>54.336799999999997</v>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="7">
         <v>57.464700000000001</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O30" s="16">
+      <c r="O30" s="7">
         <v>1364.704</v>
       </c>
-      <c r="P30" s="16">
+      <c r="P30" s="7">
         <v>1377.2192</v>
       </c>
-      <c r="Q30" s="16">
+      <c r="Q30" s="7">
         <v>1443.9293</v>
       </c>
-      <c r="R30" s="16">
+      <c r="R30" s="7">
         <v>1437.0853999999999</v>
       </c>
-      <c r="S30" s="16">
+      <c r="S30" s="7">
         <v>1355.6685</v>
       </c>
-      <c r="T30" s="16">
+      <c r="T30" s="7">
         <v>1360.4951000000001</v>
       </c>
-      <c r="U30" s="16">
+      <c r="U30" s="7">
         <v>1347.2732000000001</v>
       </c>
-      <c r="V30" s="16">
+      <c r="V30" s="7">
         <v>1343.4028000000001</v>
       </c>
-      <c r="W30" s="16">
+      <c r="W30" s="7">
         <v>1475.0553</v>
       </c>
-      <c r="X30" s="16">
+      <c r="X30" s="7">
         <v>1353.5811000000001</v>
       </c>
     </row>
@@ -11112,85 +11119,85 @@
       <c r="B31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="8">
         <v>0.50380000000000003</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="7">
         <v>0.56520000000000004</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="7">
         <v>0.5272</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="7">
         <v>0.51649999999999996</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="7">
         <v>0.64090000000000003</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="7">
         <v>0.49530000000000002</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="7">
         <v>0.48920000000000002</v>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="7">
         <v>0.54569999999999996</v>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="7">
         <v>0.503</v>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="7">
         <v>0.49530000000000002</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O31" s="17">
+      <c r="O31" s="8">
         <v>2.6644000000000001</v>
       </c>
-      <c r="P31" s="16">
+      <c r="P31" s="7">
         <v>2.6221999999999999</v>
       </c>
-      <c r="Q31" s="16">
+      <c r="Q31" s="7">
         <v>2.6568999999999998</v>
       </c>
-      <c r="R31" s="16">
+      <c r="R31" s="7">
         <v>2.7187000000000001</v>
       </c>
-      <c r="S31" s="16">
+      <c r="S31" s="7">
         <v>2.7444000000000002</v>
       </c>
-      <c r="T31" s="16">
+      <c r="T31" s="7">
         <v>2.6414</v>
       </c>
-      <c r="U31" s="16">
+      <c r="U31" s="7">
         <v>2.6408999999999998</v>
       </c>
-      <c r="V31" s="16">
+      <c r="V31" s="7">
         <v>2.6421000000000001</v>
       </c>
-      <c r="W31" s="16">
+      <c r="W31" s="7">
         <v>2.6478999999999999</v>
       </c>
-      <c r="X31" s="16">
+      <c r="X31" s="7">
         <v>2.7151999999999998</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="14"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="9"/>
+      <c r="B35" s="11"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -11214,178 +11221,183 @@
       <c r="B36" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="16">
-        <f t="shared" ref="C36:C41" si="0">IF(COUNTBLANK(C6:L6)&gt;0,"undone",AVERAGE(C6:L6))</f>
-        <v>9.9400000000000009E-3</v>
-      </c>
-      <c r="D36" s="16">
-        <f t="shared" ref="D36:D41" si="1">IF(COUNTBLANK(O6:X6)&gt;0,"undone",AVERAGE(O6:X6))</f>
-        <v>0.25718000000000002</v>
-      </c>
-      <c r="E36" s="16">
-        <f t="shared" ref="E36:E41" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",AVERAGE(C16:L16))</f>
-        <v>0.98943999999999988</v>
-      </c>
-      <c r="F36" s="16">
-        <f t="shared" ref="F36:F41" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",AVERAGE(O16:X16))</f>
-        <v>24.39499</v>
-      </c>
-      <c r="G36" s="16">
-        <f t="shared" ref="G36:G41" si="4">IF(COUNTBLANK(C26:L26)&gt;0,"undone",AVERAGE(C26:L26))</f>
-        <v>100.12429999999999</v>
-      </c>
-      <c r="H36" s="16">
-        <f t="shared" ref="H36:H41" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",AVERAGE(O26:X26))</f>
-        <v>2476.5824499999999</v>
+      <c r="C36" s="7">
+        <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",TRIMMEAN(C6:L6,2/COUNT(C6:L6)))</f>
+        <v>9.8625000000000015E-3</v>
+      </c>
+      <c r="D36" s="7">
+        <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
+        <v>0.25591250000000004</v>
+      </c>
+      <c r="E36" s="7">
+        <f>IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
+        <v>0.98113750000000011</v>
+      </c>
+      <c r="F36" s="7">
+        <f>IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
+        <v>24.430362500000001</v>
+      </c>
+      <c r="G36" s="7">
+        <f>IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
+        <v>99.611262499999995</v>
+      </c>
+      <c r="H36" s="7">
+        <f>IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
+        <v>2473.0774249999999</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="16">
-        <f t="shared" si="0"/>
-        <v>7.5899999999999995E-3</v>
-      </c>
-      <c r="D37" s="16">
-        <f t="shared" si="1"/>
-        <v>0.18755999999999998</v>
-      </c>
-      <c r="E37" s="16">
-        <f t="shared" si="2"/>
-        <v>0.74761999999999995</v>
-      </c>
-      <c r="F37" s="16">
-        <f t="shared" si="3"/>
-        <v>17.236690000000003</v>
-      </c>
-      <c r="G37" s="16">
-        <f t="shared" si="4"/>
-        <v>69.557220000000001</v>
-      </c>
-      <c r="H37" s="16">
-        <f t="shared" si="5"/>
-        <v>1754.2494900000002</v>
+      <c r="C37" s="7">
+        <f t="shared" ref="C37:C41" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",TRIMMEAN(C7:L7,2/COUNT(C7:L7)))</f>
+        <v>7.5125000000000001E-3</v>
+      </c>
+      <c r="D37" s="7">
+        <f t="shared" ref="D37:D41" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",TRIMMEAN(O7:X7,2/COUNT(O7:X7)))</f>
+        <v>0.18476250000000002</v>
+      </c>
+      <c r="E37" s="7">
+        <f t="shared" ref="E37:E41" si="2">IF(COUNTBLANK(C17:L17)&gt;0,"undone",TRIMMEAN(C17:L17,2/COUNT(C17:L17)))</f>
+        <v>0.73175000000000001</v>
+      </c>
+      <c r="F37" s="7">
+        <f t="shared" ref="F37:F41" si="3">IF(COUNTBLANK(O17:X17)&gt;0,"undone",TRIMMEAN(O17:X17,2/COUNT(O17:X17)))</f>
+        <v>17.197487500000001</v>
+      </c>
+      <c r="G37" s="7">
+        <f t="shared" ref="G37:G41" si="4">IF(COUNTBLANK(C27:L27)&gt;0,"undone",TRIMMEAN(C27:L27,2/COUNT(C27:L27)))</f>
+        <v>69.581837500000006</v>
+      </c>
+      <c r="H37" s="7">
+        <f t="shared" ref="H37:H41" si="5">IF(COUNTBLANK(O27:X27)&gt;0,"undone",TRIMMEAN(O27:X27,2/COUNT(O27:X27)))</f>
+        <v>1751.8876750000002</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="7">
         <f t="shared" si="0"/>
-        <v>1.7080000000000001E-2</v>
-      </c>
-      <c r="D38" s="16">
+        <v>1.6525000000000001E-2</v>
+      </c>
+      <c r="D38" s="7">
         <f t="shared" si="1"/>
-        <v>0.39037000000000005</v>
-      </c>
-      <c r="E38" s="16">
+        <v>0.39001249999999998</v>
+      </c>
+      <c r="E38" s="7">
         <f t="shared" si="2"/>
-        <v>1.581</v>
-      </c>
-      <c r="F38" s="16">
+        <v>1.5767875</v>
+      </c>
+      <c r="F38" s="7">
         <f t="shared" si="3"/>
-        <v>39.528110000000005</v>
-      </c>
-      <c r="G38" s="16">
+        <v>39.417412499999998</v>
+      </c>
+      <c r="G38" s="7">
         <f t="shared" si="4"/>
-        <v>158.68270999999999</v>
-      </c>
-      <c r="H38" s="16">
+        <v>157.20343750000001</v>
+      </c>
+      <c r="H38" s="7">
         <f t="shared" si="5"/>
-        <v>4058.2056299999995</v>
+        <v>4051.6519750000002</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="7">
         <f t="shared" si="0"/>
-        <v>4.0300000000000006E-3</v>
-      </c>
-      <c r="D39" s="16">
+        <v>3.9249999999999997E-3</v>
+      </c>
+      <c r="D39" s="7">
         <f t="shared" si="1"/>
-        <v>2.3870000000000002E-2</v>
-      </c>
-      <c r="E39" s="16">
+        <v>2.38125E-2</v>
+      </c>
+      <c r="E39" s="7">
         <f t="shared" si="2"/>
-        <v>5.1280000000000006E-2</v>
-      </c>
-      <c r="F39" s="16">
+        <v>5.1262500000000009E-2</v>
+      </c>
+      <c r="F39" s="7">
         <f t="shared" si="3"/>
-        <v>0.30186999999999997</v>
-      </c>
-      <c r="G39" s="16">
+        <v>0.30181249999999998</v>
+      </c>
+      <c r="G39" s="7">
         <f t="shared" si="4"/>
-        <v>0.66477000000000008</v>
-      </c>
-      <c r="H39" s="16">
+        <v>0.66368749999999999</v>
+      </c>
+      <c r="H39" s="7">
         <f t="shared" si="5"/>
-        <v>3.7321400000000002</v>
+        <v>3.7551500000000004</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="7">
         <f t="shared" si="0"/>
-        <v>5.9699999999999987E-3</v>
-      </c>
-      <c r="D40" s="16">
+        <v>5.8499999999999993E-3</v>
+      </c>
+      <c r="D40" s="7">
         <f t="shared" si="1"/>
-        <v>0.14348</v>
-      </c>
-      <c r="E40" s="16">
+        <v>0.14306249999999998</v>
+      </c>
+      <c r="E40" s="7">
         <f t="shared" si="2"/>
-        <v>0.56440000000000001</v>
-      </c>
-      <c r="F40" s="16">
+        <v>0.56122500000000008</v>
+      </c>
+      <c r="F40" s="7">
         <f t="shared" si="3"/>
-        <v>13.838179999999999</v>
-      </c>
-      <c r="G40" s="16">
+        <v>13.865499999999999</v>
+      </c>
+      <c r="G40" s="7">
         <f t="shared" si="4"/>
-        <v>55.233159999999998</v>
-      </c>
-      <c r="H40" s="16">
+        <v>55.1704875</v>
+      </c>
+      <c r="H40" s="7">
         <f t="shared" si="5"/>
-        <v>1385.84139</v>
+        <v>1379.994475</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="7">
         <f t="shared" si="0"/>
-        <v>4.2099999999999993E-3</v>
-      </c>
-      <c r="D41" s="16">
+        <v>4.0749999999999996E-3</v>
+      </c>
+      <c r="D41" s="7">
         <f t="shared" si="1"/>
-        <v>2.1399999999999999E-2</v>
-      </c>
-      <c r="E41" s="16">
+        <v>2.1049999999999996E-2</v>
+      </c>
+      <c r="E41" s="7">
         <f t="shared" si="2"/>
-        <v>4.3570000000000005E-2</v>
-      </c>
-      <c r="F41" s="16">
+        <v>4.3212500000000001E-2</v>
+      </c>
+      <c r="F41" s="7">
         <f t="shared" si="3"/>
-        <v>0.28176999999999996</v>
-      </c>
-      <c r="G41" s="16">
+        <v>0.2749375</v>
+      </c>
+      <c r="G41" s="7">
         <f t="shared" si="4"/>
-        <v>0.52821000000000007</v>
-      </c>
-      <c r="H41" s="16">
+        <v>0.51900000000000002</v>
+      </c>
+      <c r="H41" s="7">
         <f t="shared" si="5"/>
-        <v>2.6694100000000001</v>
+        <v>2.6659375000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -11396,11 +11408,6 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11413,10 +11420,10 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data collecting.xlsx
+++ b/data collecting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phure\เอกสาร\GitHub\c-sorting-algorithm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30421DF-48C3-4ED6-BBD4-4DD53D136716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FA984D-3714-4C46-A920-846D65EE0359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
   </bookViews>
@@ -20,6 +20,9 @@
     <sheet name="Rev-Sorted" sheetId="3" r:id="rId5"/>
     <sheet name="rev_sorted_grpah " sheetId="13" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -121,37 +124,13 @@
     <t>เวลาเอารูปไปไม่ต้องเอาชื่อแผนภูมิไปนะ ไปตัดออก</t>
   </si>
   <si>
-    <r>
-      <t>O(N</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
     <t>O(N)</t>
   </si>
   <si>
     <t>O(NlogN)</t>
+  </si>
+  <si>
+    <t>O(N2)</t>
   </si>
 </sst>
 </file>
@@ -161,7 +140,7 @@
   <numFmts count="1">
     <numFmt numFmtId="187" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,14 +162,6 @@
       <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -226,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -297,11 +268,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -330,6 +327,9 @@
     <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -348,8 +348,29 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,22 +547,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.3250000000000007E-3</c:v>
+                  <c:v>3.2374999999999991E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.6124999999999988E-2</c:v>
+                  <c:v>9.2087499999999989E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.34291250000000001</c:v>
+                  <c:v>0.32903749999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.8987499999999997</c:v>
+                  <c:v>8.5749499999999994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34.276687500000001</c:v>
+                  <c:v>34.517949999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>918.55595000000005</c:v>
+                  <c:v>848.96680000000015</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -858,7 +879,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -1189,22 +1210,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.5374999999999999E-3</c:v>
+                  <c:v>5.1124999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.18411249999999998</c:v>
+                  <c:v>0.12496250000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75121250000000006</c:v>
+                  <c:v>0.49884999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18.446875000000002</c:v>
+                  <c:v>12.45715</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>75.809237499999995</c:v>
+                  <c:v>50.051387499999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1901.4957750000001</c:v>
+                  <c:v>1248.5817875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1521,7 +1542,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -1852,22 +1873,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.9375000000000009E-3</c:v>
+                  <c:v>2.6750000000000003E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3862500000000002E-2</c:v>
+                  <c:v>1.6037500000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.15375E-2</c:v>
+                  <c:v>3.6924999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30283749999999998</c:v>
+                  <c:v>0.20457499999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.64444999999999997</c:v>
+                  <c:v>0.43671249999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.6792499999999997</c:v>
+                  <c:v>2.4870749999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2184,7 +2205,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -2515,22 +2536,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>6.2249999999999996E-3</c:v>
+                  <c:v>4.3999999999999994E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1444125</c:v>
+                  <c:v>9.3350000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.56381250000000005</c:v>
+                  <c:v>0.38807499999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.799025</c:v>
+                  <c:v>9.5362000000000009</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55.014850000000003</c:v>
+                  <c:v>38.011587500000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1390.3545124999998</c:v>
+                  <c:v>945.68022500000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2847,7 +2868,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -3178,22 +3199,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.6750000000000003E-3</c:v>
+                  <c:v>2.5374999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0125000000000001E-2</c:v>
+                  <c:v>1.2412500000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.4262499999999996E-2</c:v>
+                  <c:v>2.9025000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22641249999999996</c:v>
+                  <c:v>0.15733749999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.40345000000000003</c:v>
+                  <c:v>0.37109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.9468124999999996</c:v>
+                  <c:v>2.7895749999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3510,7 +3531,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -3881,22 +3902,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.875E-4</c:v>
+                  <c:v>1.7500000000000003E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2374999999999999E-3</c:v>
+                  <c:v>8.0000000000000015E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.4874999999999997E-3</c:v>
+                  <c:v>1.6125000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2262500000000001E-2</c:v>
+                  <c:v>7.3875000000000017E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.4475E-2</c:v>
+                  <c:v>1.4450000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.12228749999999998</c:v>
+                  <c:v>8.2174999999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3972,22 +3993,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.2750000000000002E-3</c:v>
+                  <c:v>4.4124999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.153225</c:v>
+                  <c:v>0.10567500000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.63418750000000002</c:v>
+                  <c:v>0.42470000000000008</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.403874999999999</c:v>
+                  <c:v>10.738949999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>61.6993875</c:v>
+                  <c:v>42.800525</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1587.3118125000001</c:v>
+                  <c:v>1070.4900749999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4067,22 +4088,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.5374999999999999E-3</c:v>
+                  <c:v>5.1124999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.18411249999999998</c:v>
+                  <c:v>0.12496250000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75121250000000006</c:v>
+                  <c:v>0.49884999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18.446875000000002</c:v>
+                  <c:v>12.45715</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>75.809237499999995</c:v>
+                  <c:v>50.051387499999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1901.4957750000001</c:v>
+                  <c:v>1248.5817875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4158,22 +4179,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.9375000000000009E-3</c:v>
+                  <c:v>2.6750000000000003E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3862500000000002E-2</c:v>
+                  <c:v>1.6037500000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.15375E-2</c:v>
+                  <c:v>3.6924999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30283749999999998</c:v>
+                  <c:v>0.20457499999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.64444999999999997</c:v>
+                  <c:v>0.43671249999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.6792499999999997</c:v>
+                  <c:v>2.4870749999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4251,22 +4272,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>6.2249999999999996E-3</c:v>
+                  <c:v>4.3999999999999994E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1444125</c:v>
+                  <c:v>9.3350000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.56381250000000005</c:v>
+                  <c:v>0.38807499999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.799025</c:v>
+                  <c:v>9.5362000000000009</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55.014850000000003</c:v>
+                  <c:v>38.011587500000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1390.3545124999998</c:v>
+                  <c:v>945.68022500000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4341,22 +4362,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.6750000000000003E-3</c:v>
+                  <c:v>2.5374999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0125000000000001E-2</c:v>
+                  <c:v>1.2412500000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.4262499999999996E-2</c:v>
+                  <c:v>2.9025000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22641249999999996</c:v>
+                  <c:v>0.15733749999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.40345000000000003</c:v>
+                  <c:v>0.37109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.9468124999999996</c:v>
+                  <c:v>2.7895749999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4544,7 +4565,19 @@
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>(ms)</a:t>
+                  <a:t>(ms</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="th-TH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>, log scale</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>)</a:t>
                 </a:r>
                 <a:endParaRPr lang="th-TH" sz="1200">
                   <a:solidFill>
@@ -4848,22 +4881,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>9.8625000000000015E-3</c:v>
+                  <c:v>6.9874999999999989E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25591250000000004</c:v>
+                  <c:v>0.17252500000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98113750000000011</c:v>
+                  <c:v>0.68552499999999994</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24.430362500000001</c:v>
+                  <c:v>16.905687500000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>99.611262499999995</c:v>
+                  <c:v>67.898949999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2473.0774249999999</c:v>
+                  <c:v>1699.54865</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5180,7 +5213,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -5511,22 +5544,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.5125000000000001E-3</c:v>
+                  <c:v>5.1624999999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.18476250000000002</c:v>
+                  <c:v>0.12428749999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.73175000000000001</c:v>
+                  <c:v>0.47798750000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17.197487500000001</c:v>
+                  <c:v>11.9602</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>69.581837500000006</c:v>
+                  <c:v>48.382975000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1751.8876750000002</c:v>
+                  <c:v>1211.3593874999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5843,7 +5876,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -6174,22 +6207,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.6525000000000001E-2</c:v>
+                  <c:v>1.0874999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.39001249999999998</c:v>
+                  <c:v>0.25931249999999995</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5767875</c:v>
+                  <c:v>1.0002499999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>39.417412499999998</c:v>
+                  <c:v>25.497987499999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>157.20343750000001</c:v>
+                  <c:v>101.96351250000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4051.6519750000002</c:v>
+                  <c:v>2558.8650750000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6506,7 +6539,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -6837,22 +6870,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.9249999999999997E-3</c:v>
+                  <c:v>2.7250000000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.38125E-2</c:v>
+                  <c:v>1.685E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.1262500000000009E-2</c:v>
+                  <c:v>3.5125000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30181249999999998</c:v>
+                  <c:v>0.21203749999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.66368749999999999</c:v>
+                  <c:v>0.44373750000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.7551500000000004</c:v>
+                  <c:v>2.5085625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7169,7 +7202,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -7500,22 +7533,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>5.8499999999999993E-3</c:v>
+                  <c:v>4.0750000000000005E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14306249999999998</c:v>
+                  <c:v>0.10169999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.56122500000000008</c:v>
+                  <c:v>0.38579999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.865499999999999</c:v>
+                  <c:v>9.5796749999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55.1704875</c:v>
+                  <c:v>37.982999999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1379.994475</c:v>
+                  <c:v>941.21522500000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7832,7 +7865,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -8163,22 +8196,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>5.0000000000000001E-3</c:v>
+                  <c:v>4.725E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.116075</c:v>
+                  <c:v>0.11115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.47197499999999998</c:v>
+                  <c:v>0.45730000000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.990737499999998</c:v>
+                  <c:v>10.927024999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46.921199999999992</c:v>
+                  <c:v>45.488837500000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1564.8245625</c:v>
+                  <c:v>1075.8161375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8495,7 +8528,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -8818,22 +8851,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.0749999999999996E-3</c:v>
+                  <c:v>2.6749999999999994E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.1049999999999996E-2</c:v>
+                  <c:v>1.3599999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.3212500000000001E-2</c:v>
+                  <c:v>2.8712500000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2749375</c:v>
+                  <c:v>2.1148750000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.51900000000000002</c:v>
+                  <c:v>18.998987500000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.6659375000000001</c:v>
+                  <c:v>706.74744999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9150,7 +9183,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -9508,22 +9541,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>9.8625000000000015E-3</c:v>
+                  <c:v>6.9874999999999989E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25591250000000004</c:v>
+                  <c:v>0.17252500000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98113750000000011</c:v>
+                  <c:v>0.68552499999999994</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24.430362500000001</c:v>
+                  <c:v>16.905687500000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>99.611262499999995</c:v>
+                  <c:v>67.898949999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2473.0774249999999</c:v>
+                  <c:v>1699.54865</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9599,22 +9632,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.5125000000000001E-3</c:v>
+                  <c:v>5.1624999999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.18476250000000002</c:v>
+                  <c:v>0.12428749999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.73175000000000001</c:v>
+                  <c:v>0.47798750000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17.197487500000001</c:v>
+                  <c:v>11.9602</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>69.581837500000006</c:v>
+                  <c:v>48.382975000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1751.8876750000002</c:v>
+                  <c:v>1211.3593874999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9694,22 +9727,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.6525000000000001E-2</c:v>
+                  <c:v>1.0874999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.39001249999999998</c:v>
+                  <c:v>0.25931249999999995</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5767875</c:v>
+                  <c:v>1.0002499999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>39.417412499999998</c:v>
+                  <c:v>25.497987499999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>157.20343750000001</c:v>
+                  <c:v>101.96351250000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4051.6519750000002</c:v>
+                  <c:v>2558.8650750000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9785,22 +9818,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.9249999999999997E-3</c:v>
+                  <c:v>2.7250000000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.38125E-2</c:v>
+                  <c:v>1.685E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.1262500000000009E-2</c:v>
+                  <c:v>3.5125000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30181249999999998</c:v>
+                  <c:v>0.21203749999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.66368749999999999</c:v>
+                  <c:v>0.44373750000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.7551500000000004</c:v>
+                  <c:v>2.5085625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9878,22 +9911,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>5.8499999999999993E-3</c:v>
+                  <c:v>4.0750000000000005E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14306249999999998</c:v>
+                  <c:v>0.10169999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.56122500000000008</c:v>
+                  <c:v>0.38579999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.865499999999999</c:v>
+                  <c:v>9.5796749999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55.1704875</c:v>
+                  <c:v>37.982999999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1379.994475</c:v>
+                  <c:v>941.21522500000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9968,22 +10001,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.0749999999999996E-3</c:v>
+                  <c:v>2.6749999999999994E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.1049999999999996E-2</c:v>
+                  <c:v>1.3599999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.3212500000000001E-2</c:v>
+                  <c:v>2.8712500000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2749375</c:v>
+                  <c:v>2.1148750000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.51900000000000002</c:v>
+                  <c:v>18.998987500000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.6659375000000001</c:v>
+                  <c:v>706.74744999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10171,7 +10204,19 @@
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>(ms)</a:t>
+                  <a:t>(ms</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="th-TH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>, log scale</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>)</a:t>
                 </a:r>
                 <a:endParaRPr lang="th-TH" sz="1200">
                   <a:solidFill>
@@ -10475,22 +10520,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>8.7375000000000005E-3</c:v>
+                  <c:v>7.9500000000000005E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.22232499999999999</c:v>
+                  <c:v>0.20223750000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.86371249999999999</c:v>
+                  <c:v>0.8023125000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.985674999999997</c:v>
+                  <c:v>19.875374999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>88.970937500000005</c:v>
+                  <c:v>83.256074999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3080.548875</c:v>
+                  <c:v>1988.4961750000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10807,7 +10852,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -11138,22 +11183,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.9624999999999999E-3</c:v>
+                  <c:v>2.8250000000000003E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.85875E-2</c:v>
+                  <c:v>1.7975000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.0962499999999992E-2</c:v>
+                  <c:v>3.8687499999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3334375</c:v>
+                  <c:v>0.36593750000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.85593750000000002</c:v>
+                  <c:v>0.81251249999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.6863124999999997</c:v>
+                  <c:v>4.5662125000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11470,7 +11515,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -11801,22 +11846,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.5874999999999999E-3</c:v>
+                  <c:v>1.5999999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.9125000000000003E-3</c:v>
+                  <c:v>9.1750000000000009E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.5237499999999996E-2</c:v>
+                  <c:v>2.0137499999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22592499999999999</c:v>
+                  <c:v>0.21444999999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.51642500000000002</c:v>
+                  <c:v>0.54075000000000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.5932874999999997</c:v>
+                  <c:v>3.0949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12133,7 +12178,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -12464,22 +12509,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.4500000000000008E-3</c:v>
+                  <c:v>3.0625000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9224999999999999E-2</c:v>
+                  <c:v>1.7774999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.2412499999999999E-2</c:v>
+                  <c:v>3.9275000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30487500000000001</c:v>
+                  <c:v>0.29073749999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.67661250000000006</c:v>
+                  <c:v>0.69238750000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.7241625000000003</c:v>
+                  <c:v>3.8935500000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12796,7 +12841,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -13183,22 +13228,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.3250000000000007E-3</c:v>
+                  <c:v>3.2374999999999991E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.6124999999999988E-2</c:v>
+                  <c:v>9.2087499999999989E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.34291250000000001</c:v>
+                  <c:v>0.32903749999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.8987499999999997</c:v>
+                  <c:v>8.5749499999999994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34.276687500000001</c:v>
+                  <c:v>34.517949999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>918.55595000000005</c:v>
+                  <c:v>848.96680000000015</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13274,22 +13319,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>5.0000000000000001E-3</c:v>
+                  <c:v>4.725E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.116075</c:v>
+                  <c:v>0.11115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.47197499999999998</c:v>
+                  <c:v>0.45730000000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.990737499999998</c:v>
+                  <c:v>10.927024999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46.921199999999992</c:v>
+                  <c:v>45.488837500000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1564.8245625</c:v>
+                  <c:v>1075.8161375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13369,22 +13414,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>8.7375000000000005E-3</c:v>
+                  <c:v>7.9500000000000005E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.22232499999999999</c:v>
+                  <c:v>0.20223750000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.86371249999999999</c:v>
+                  <c:v>0.8023125000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.985674999999997</c:v>
+                  <c:v>19.875374999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>88.970937500000005</c:v>
+                  <c:v>83.256074999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3080.548875</c:v>
+                  <c:v>1988.4961750000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13460,22 +13505,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.9624999999999999E-3</c:v>
+                  <c:v>2.8250000000000003E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.85875E-2</c:v>
+                  <c:v>1.7975000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.0962499999999992E-2</c:v>
+                  <c:v>3.8687499999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3334375</c:v>
+                  <c:v>0.36593750000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.85593750000000002</c:v>
+                  <c:v>0.81251249999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.6863124999999997</c:v>
+                  <c:v>4.5662125000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13553,22 +13598,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.5874999999999999E-3</c:v>
+                  <c:v>1.5999999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.9125000000000003E-3</c:v>
+                  <c:v>9.1750000000000009E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.5237499999999996E-2</c:v>
+                  <c:v>2.0137499999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22592499999999999</c:v>
+                  <c:v>0.21444999999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.51642500000000002</c:v>
+                  <c:v>0.54075000000000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.5932874999999997</c:v>
+                  <c:v>3.0949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13643,22 +13688,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.4500000000000008E-3</c:v>
+                  <c:v>3.0625000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9224999999999999E-2</c:v>
+                  <c:v>1.7774999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.2412499999999999E-2</c:v>
+                  <c:v>3.9275000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30487500000000001</c:v>
+                  <c:v>0.29073749999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.67661250000000006</c:v>
+                  <c:v>0.69238750000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.7241625000000003</c:v>
+                  <c:v>3.8935500000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13854,7 +13899,19 @@
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>(ms)</a:t>
+                  <a:t>(ms</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="th-TH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>, log scale</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>)</a:t>
                 </a:r>
                 <a:endParaRPr lang="th-TH" sz="1200">
                   <a:solidFill>
@@ -14158,22 +14215,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.875E-4</c:v>
+                  <c:v>1.7500000000000003E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2374999999999999E-3</c:v>
+                  <c:v>8.0000000000000015E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.4874999999999997E-3</c:v>
+                  <c:v>1.6125000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2262500000000001E-2</c:v>
+                  <c:v>7.3875000000000017E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.4475E-2</c:v>
+                  <c:v>1.4450000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.12228749999999998</c:v>
+                  <c:v>8.2174999999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14490,7 +14547,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -14813,22 +14870,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.2750000000000002E-3</c:v>
+                  <c:v>4.4124999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.153225</c:v>
+                  <c:v>0.10567500000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.63418750000000002</c:v>
+                  <c:v>0.42470000000000008</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.403874999999999</c:v>
+                  <c:v>10.738949999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>61.6993875</c:v>
+                  <c:v>42.800525</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1587.3118125000001</c:v>
+                  <c:v>1070.4900749999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15145,7 +15202,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -27255,7 +27312,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9289143" cy="6068786"/>
+    <xdr:ext cx="9289143" cy="6059714"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="แผนภูมิ 1">
@@ -27521,7 +27578,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9289143" cy="6068786"/>
+    <xdr:ext cx="9285514" cy="6063343"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="แผนภูมิ 1">
@@ -27787,7 +27844,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9289143" cy="6068786"/>
+    <xdr:ext cx="9289143" cy="6059714"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="แผนภูมิ 1">
@@ -27814,6 +27871,54 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Random"/>
+      <sheetName val="random_grpah"/>
+      <sheetName val="Sorted"/>
+      <sheetName val="sorted_grpah "/>
+      <sheetName val="Rev-Sorted"/>
+      <sheetName val="rev_sorted_grpah "/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2">
+        <row r="35">
+          <cell r="C35">
+            <v>100</v>
+          </cell>
+          <cell r="D35">
+            <v>500</v>
+          </cell>
+          <cell r="E35">
+            <v>1000</v>
+          </cell>
+          <cell r="F35">
+            <v>5000</v>
+          </cell>
+          <cell r="G35">
+            <v>10000</v>
+          </cell>
+          <cell r="H35">
+            <v>50000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -28150,10 +28255,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="17"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -28172,39 +28277,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="14"/>
-      <c r="N4" s="10" t="s">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
+      <c r="N4" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="14"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="21"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="11"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -28235,7 +28340,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="11"/>
+      <c r="N5" s="23"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -28272,67 +28377,67 @@
         <v>16</v>
       </c>
       <c r="C6" s="7">
-        <v>4.1000000000000003E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="D6" s="7">
-        <v>3.5000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="E6" s="7">
         <v>3.3E-3</v>
       </c>
       <c r="F6" s="7">
-        <v>3.3E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="G6" s="7">
-        <v>3.3E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="H6" s="7">
-        <v>3.3E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="I6" s="7">
-        <v>3.3E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="J6" s="7">
-        <v>3.3E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="K6" s="7">
-        <v>3.3E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="L6" s="7">
-        <v>3.3E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O6" s="7">
-        <v>9.6799999999999997E-2</v>
+        <v>9.2700000000000005E-2</v>
       </c>
       <c r="P6" s="7">
-        <v>9.6299999999999997E-2</v>
+        <v>9.2600000000000002E-2</v>
       </c>
       <c r="Q6" s="7">
-        <v>9.6000000000000002E-2</v>
+        <v>9.2100000000000001E-2</v>
       </c>
       <c r="R6" s="7">
-        <v>9.5799999999999996E-2</v>
+        <v>9.2100000000000001E-2</v>
       </c>
       <c r="S6" s="7">
-        <v>9.5899999999999999E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="T6" s="7">
-        <v>9.6000000000000002E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="U6" s="7">
-        <v>9.6000000000000002E-2</v>
+        <v>9.1899999999999996E-2</v>
       </c>
       <c r="V6" s="7">
-        <v>9.6000000000000002E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="W6" s="7">
-        <v>0.10249999999999999</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="X6" s="7">
-        <v>9.6000000000000002E-2</v>
+        <v>9.1899999999999996E-2</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -28340,67 +28445,67 @@
         <v>17</v>
       </c>
       <c r="C7" s="7">
-        <v>7.4999999999999997E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="D7" s="7">
-        <v>7.1999999999999998E-3</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="E7" s="7">
-        <v>5.1000000000000004E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="F7" s="7">
-        <v>4.5999999999999999E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="G7" s="7">
-        <v>4.5999999999999999E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="H7" s="7">
-        <v>4.5999999999999999E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="I7" s="7">
-        <v>4.5999999999999999E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="J7" s="7">
-        <v>4.5999999999999999E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="K7" s="7">
-        <v>4.5999999999999999E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="L7" s="7">
-        <v>4.7000000000000002E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O7" s="7">
-        <v>0.12640000000000001</v>
+        <v>0.12089999999999999</v>
       </c>
       <c r="P7" s="7">
-        <v>0.12189999999999999</v>
+        <v>0.11650000000000001</v>
       </c>
       <c r="Q7" s="7">
-        <v>0.1179</v>
+        <v>0.1129</v>
       </c>
       <c r="R7" s="7">
-        <v>0.1195</v>
+        <v>0.11119999999999999</v>
       </c>
       <c r="S7" s="7">
-        <v>0.1143</v>
+        <v>0.1103</v>
       </c>
       <c r="T7" s="7">
-        <v>0.1139</v>
+        <v>0.10979999999999999</v>
       </c>
       <c r="U7" s="7">
-        <v>0.1137</v>
+        <v>0.1096</v>
       </c>
       <c r="V7" s="7">
-        <v>0.1138</v>
+        <v>0.1095</v>
       </c>
       <c r="W7" s="7">
-        <v>0.11360000000000001</v>
+        <v>0.1094</v>
       </c>
       <c r="X7" s="7">
-        <v>0.11360000000000001</v>
+        <v>0.1094</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -28408,67 +28513,67 @@
         <v>18</v>
       </c>
       <c r="C8" s="7">
-        <v>1.17E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="D8" s="7">
-        <v>1.0500000000000001E-2</v>
+        <v>9.2999999999999992E-3</v>
       </c>
       <c r="E8" s="7">
-        <v>8.9999999999999993E-3</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="F8" s="7">
-        <v>8.5000000000000006E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="G8" s="7">
-        <v>8.3000000000000001E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="H8" s="7">
-        <v>8.3000000000000001E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="I8" s="7">
-        <v>8.3999999999999995E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="J8" s="7">
-        <v>8.3999999999999995E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="K8" s="7">
-        <v>8.3999999999999995E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="L8" s="7">
-        <v>8.3999999999999995E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O8" s="7">
-        <v>0.23680000000000001</v>
+        <v>0.2261</v>
       </c>
       <c r="P8" s="7">
-        <v>0.2329</v>
+        <v>0.21310000000000001</v>
       </c>
       <c r="Q8" s="7">
-        <v>0.23019999999999999</v>
+        <v>0.20530000000000001</v>
       </c>
       <c r="R8" s="7">
-        <v>0.22059999999999999</v>
+        <v>0.20230000000000001</v>
       </c>
       <c r="S8" s="7">
-        <v>0.21940000000000001</v>
+        <v>0.2001</v>
       </c>
       <c r="T8" s="7">
-        <v>0.21829999999999999</v>
+        <v>0.1996</v>
       </c>
       <c r="U8" s="7">
-        <v>0.217</v>
+        <v>0.19969999999999999</v>
       </c>
       <c r="V8" s="7">
-        <v>0.2223</v>
+        <v>0.19889999999999999</v>
       </c>
       <c r="W8" s="7">
-        <v>0.2175</v>
+        <v>0.19869999999999999</v>
       </c>
       <c r="X8" s="7">
-        <v>0.21740000000000001</v>
+        <v>0.19889999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -28476,67 +28581,67 @@
         <v>19</v>
       </c>
       <c r="C9" s="7">
-        <v>5.4999999999999997E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="D9" s="7">
-        <v>3.3999999999999998E-3</v>
+        <v>3.3E-3</v>
       </c>
       <c r="E9" s="7">
-        <v>2.8999999999999998E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="F9" s="7">
-        <v>2.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G9" s="7">
-        <v>2.8999999999999998E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="H9" s="7">
-        <v>2.8999999999999998E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="I9" s="7">
-        <v>2.8999999999999998E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="J9" s="7">
-        <v>2.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="K9" s="7">
-        <v>2.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="L9" s="7">
-        <v>2.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O9" s="7">
-        <v>2.9899999999999999E-2</v>
+        <v>2.81E-2</v>
       </c>
       <c r="P9" s="7">
-        <v>2.07E-2</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="Q9" s="7">
-        <v>1.8200000000000001E-2</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="R9" s="7">
-        <v>1.8200000000000001E-2</v>
+        <v>2.18E-2</v>
       </c>
       <c r="S9" s="7">
-        <v>1.7999999999999999E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="T9" s="7">
-        <v>1.7899999999999999E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="U9" s="7">
-        <v>1.7999999999999999E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="V9" s="7">
-        <v>1.7999999999999999E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="W9" s="7">
-        <v>1.9599999999999999E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="X9" s="7">
-        <v>1.7999999999999999E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -28544,67 +28649,67 @@
         <v>20</v>
       </c>
       <c r="C10" s="7">
-        <v>3.5000000000000001E-3</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="D10" s="7">
-        <v>2.5999999999999999E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="E10" s="7">
-        <v>1.6000000000000001E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="F10" s="7">
-        <v>1.4E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="G10" s="7">
         <v>1.4E-3</v>
       </c>
       <c r="H10" s="7">
-        <v>1.4E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="I10" s="7">
-        <v>1.4E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="J10" s="7">
         <v>1.4E-3</v>
       </c>
       <c r="K10" s="7">
-        <v>1.5E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="L10" s="7">
-        <v>1.4E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O10" s="7">
-        <v>1.95E-2</v>
+        <v>1.9099999999999999E-2</v>
       </c>
       <c r="P10" s="7">
-        <v>1.0800000000000001E-2</v>
+        <v>1.35E-2</v>
       </c>
       <c r="Q10" s="7">
-        <v>8.8000000000000005E-3</v>
+        <v>1.04E-2</v>
       </c>
       <c r="R10" s="7">
-        <v>8.6999999999999994E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="S10" s="7">
-        <v>8.6E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="T10" s="7">
-        <v>8.5000000000000006E-3</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="U10" s="7">
-        <v>8.6E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="V10" s="7">
-        <v>8.6E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="W10" s="7">
-        <v>8.5000000000000006E-3</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="X10" s="7">
-        <v>8.6999999999999994E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -28612,31 +28717,31 @@
         <v>21</v>
       </c>
       <c r="C11" s="8">
-        <v>6.8999999999999999E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="D11" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="E11" s="7">
-        <v>3.3E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="F11" s="7">
-        <v>4.1000000000000003E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G11" s="7">
-        <v>3.3999999999999998E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="H11" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="I11" s="7">
-        <v>3.0999999999999999E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="J11" s="7">
-        <v>3.3E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="K11" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="L11" s="7">
         <v>3.2000000000000002E-3</v>
@@ -28645,34 +28750,34 @@
         <v>21</v>
       </c>
       <c r="O11" s="8">
-        <v>2.81E-2</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="P11" s="7">
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="Q11" s="7">
-        <v>2.1899999999999999E-2</v>
+        <v>1.7100000000000001E-2</v>
       </c>
       <c r="R11" s="7">
-        <v>0.02</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="S11" s="7">
-        <v>1.7299999999999999E-2</v>
+        <v>1.55E-2</v>
       </c>
       <c r="T11" s="7">
-        <v>1.7299999999999999E-2</v>
+        <v>1.8700000000000001E-2</v>
       </c>
       <c r="U11" s="7">
-        <v>1.72E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="V11" s="7">
-        <v>1.9E-2</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="W11" s="7">
-        <v>1.9800000000000002E-2</v>
+        <v>1.9699999999999999E-2</v>
       </c>
       <c r="X11" s="7">
-        <v>1.7500000000000002E-2</v>
+        <v>1.6400000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -28692,39 +28797,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="14"/>
-      <c r="N14" s="10" t="s">
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="21"/>
+      <c r="N14" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="O14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="14"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="21"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="11"/>
+      <c r="B15" s="23"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -28755,7 +28860,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="11"/>
+      <c r="N15" s="23"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -28792,67 +28897,67 @@
         <v>16</v>
       </c>
       <c r="C16" s="7">
-        <v>0.34260000000000002</v>
+        <v>0.3281</v>
       </c>
       <c r="D16" s="7">
-        <v>0.34179999999999999</v>
+        <v>0.32750000000000001</v>
       </c>
       <c r="E16" s="7">
-        <v>0.34150000000000003</v>
+        <v>0.32669999999999999</v>
       </c>
       <c r="F16" s="7">
-        <v>0.34139999999999998</v>
+        <v>0.32679999999999998</v>
       </c>
       <c r="G16" s="7">
-        <v>0.3453</v>
+        <v>0.33689999999999998</v>
       </c>
       <c r="H16" s="7">
-        <v>0.34150000000000003</v>
+        <v>0.3286</v>
       </c>
       <c r="I16" s="7">
-        <v>0.34139999999999998</v>
+        <v>0.32850000000000001</v>
       </c>
       <c r="J16" s="7">
-        <v>0.34720000000000001</v>
+        <v>0.32879999999999998</v>
       </c>
       <c r="K16" s="7">
-        <v>0.34320000000000001</v>
+        <v>0.33379999999999999</v>
       </c>
       <c r="L16" s="7">
-        <v>0.34599999999999997</v>
+        <v>0.33019999999999999</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O16" s="7">
-        <v>9.1956000000000007</v>
+        <v>8.9773999999999994</v>
       </c>
       <c r="P16" s="7">
-        <v>8.8960000000000008</v>
+        <v>8.3798999999999992</v>
       </c>
       <c r="Q16" s="7">
-        <v>8.8794000000000004</v>
+        <v>8.7765000000000004</v>
       </c>
       <c r="R16" s="7">
-        <v>8.8483999999999998</v>
+        <v>8.6914999999999996</v>
       </c>
       <c r="S16" s="7">
-        <v>9.0548999999999999</v>
+        <v>8.3993000000000002</v>
       </c>
       <c r="T16" s="7">
-        <v>9.0667000000000009</v>
+        <v>8.6715999999999998</v>
       </c>
       <c r="U16" s="7">
-        <v>8.7662999999999993</v>
+        <v>8.4224999999999994</v>
       </c>
       <c r="V16" s="7">
-        <v>8.7954000000000008</v>
+        <v>8.5189000000000004</v>
       </c>
       <c r="W16" s="7">
-        <v>8.7210000000000001</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="X16" s="7">
-        <v>8.8828999999999994</v>
+        <v>8.5892999999999997</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
@@ -28860,67 +28965,67 @@
         <v>17</v>
       </c>
       <c r="C17" s="7">
-        <v>0.47310000000000002</v>
+        <v>0.50509999999999999</v>
       </c>
       <c r="D17" s="7">
-        <v>0.46899999999999997</v>
+        <v>0.48630000000000001</v>
       </c>
       <c r="E17" s="7">
-        <v>0.46460000000000001</v>
+        <v>0.45279999999999998</v>
       </c>
       <c r="F17" s="7">
-        <v>0.5</v>
+        <v>0.4451</v>
       </c>
       <c r="G17" s="7">
-        <v>0.46539999999999998</v>
+        <v>0.44879999999999998</v>
       </c>
       <c r="H17" s="7">
-        <v>0.46089999999999998</v>
+        <v>0.44230000000000003</v>
       </c>
       <c r="I17" s="7">
-        <v>0.4607</v>
+        <v>0.44719999999999999</v>
       </c>
       <c r="J17" s="7">
-        <v>0.54279999999999995</v>
+        <v>0.44369999999999998</v>
       </c>
       <c r="K17" s="7">
-        <v>0.4768</v>
+        <v>0.44359999999999999</v>
       </c>
       <c r="L17" s="7">
-        <v>0.46600000000000003</v>
+        <v>0.4909</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O17" s="7">
-        <v>10.829000000000001</v>
+        <v>10.8446</v>
       </c>
       <c r="P17" s="7">
-        <v>10.7707</v>
+        <v>10.9262</v>
       </c>
       <c r="Q17" s="7">
-        <v>10.8287</v>
+        <v>10.9701</v>
       </c>
       <c r="R17" s="7">
-        <v>10.837199999999999</v>
+        <v>11.167899999999999</v>
       </c>
       <c r="S17" s="7">
-        <v>10.815</v>
+        <v>10.581</v>
       </c>
       <c r="T17" s="7">
-        <v>11.3873</v>
+        <v>10.9725</v>
       </c>
       <c r="U17" s="7">
-        <v>11.142799999999999</v>
+        <v>10.822800000000001</v>
       </c>
       <c r="V17" s="7">
-        <v>11.1646</v>
+        <v>10.866300000000001</v>
       </c>
       <c r="W17" s="7">
-        <v>11.3879</v>
+        <v>10.845800000000001</v>
       </c>
       <c r="X17" s="7">
-        <v>10.9213</v>
+        <v>11.6493</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
@@ -28928,67 +29033,67 @@
         <v>18</v>
       </c>
       <c r="C18" s="7">
-        <v>0.88670000000000004</v>
+        <v>0.81579999999999997</v>
       </c>
       <c r="D18" s="7">
-        <v>0.87949999999999995</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="E18" s="7">
-        <v>0.87160000000000004</v>
+        <v>0.80210000000000004</v>
       </c>
       <c r="F18" s="7">
-        <v>0.8619</v>
+        <v>0.7984</v>
       </c>
       <c r="G18" s="7">
-        <v>0.85950000000000004</v>
+        <v>0.80320000000000003</v>
       </c>
       <c r="H18" s="7">
-        <v>0.86160000000000003</v>
+        <v>0.80300000000000005</v>
       </c>
       <c r="I18" s="7">
-        <v>0.85750000000000004</v>
+        <v>0.80659999999999998</v>
       </c>
       <c r="J18" s="7">
-        <v>0.85980000000000001</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="K18" s="7">
-        <v>0.85570000000000002</v>
+        <v>0.79269999999999996</v>
       </c>
       <c r="L18" s="7">
-        <v>0.85829999999999995</v>
+        <v>0.7954</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O18" s="7">
-        <v>20.911899999999999</v>
+        <v>19.862400000000001</v>
       </c>
       <c r="P18" s="7">
-        <v>21.035599999999999</v>
+        <v>19.755299999999998</v>
       </c>
       <c r="Q18" s="7">
-        <v>21.108899999999998</v>
+        <v>19.978100000000001</v>
       </c>
       <c r="R18" s="7">
-        <v>20.726600000000001</v>
+        <v>19.949100000000001</v>
       </c>
       <c r="S18" s="7">
-        <v>20.8309</v>
+        <v>19.834800000000001</v>
       </c>
       <c r="T18" s="7">
-        <v>21.097999999999999</v>
+        <v>19.773099999999999</v>
       </c>
       <c r="U18" s="7">
-        <v>21.315200000000001</v>
+        <v>19.981400000000001</v>
       </c>
       <c r="V18" s="7">
-        <v>21.2637</v>
+        <v>20.439800000000002</v>
       </c>
       <c r="W18" s="7">
-        <v>20.544799999999999</v>
+        <v>19.6172</v>
       </c>
       <c r="X18" s="7">
-        <v>20.909800000000001</v>
+        <v>19.8688</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
@@ -28996,67 +29101,67 @@
         <v>19</v>
       </c>
       <c r="C19" s="7">
-        <v>6.6199999999999995E-2</v>
+        <v>6.1899999999999997E-2</v>
       </c>
       <c r="D19" s="7">
-        <v>4.7E-2</v>
+        <v>4.4600000000000001E-2</v>
       </c>
       <c r="E19" s="7">
-        <v>4.1000000000000002E-2</v>
+        <v>3.9100000000000003E-2</v>
       </c>
       <c r="F19" s="7">
-        <v>4.0099999999999997E-2</v>
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="G19" s="7">
-        <v>4.0099999999999997E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="H19" s="7">
-        <v>3.9899999999999998E-2</v>
+        <v>3.7600000000000001E-2</v>
       </c>
       <c r="I19" s="7">
-        <v>3.9699999999999999E-2</v>
+        <v>3.7600000000000001E-2</v>
       </c>
       <c r="J19" s="7">
-        <v>3.9899999999999998E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="K19" s="7">
-        <v>3.9800000000000002E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="L19" s="7">
-        <v>3.9899999999999998E-2</v>
+        <v>3.7400000000000003E-2</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O19" s="7">
-        <v>0.39389999999999997</v>
+        <v>0.39889999999999998</v>
       </c>
       <c r="P19" s="7">
-        <v>0.35670000000000002</v>
+        <v>0.48959999999999998</v>
       </c>
       <c r="Q19" s="7">
-        <v>0.34920000000000001</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="R19" s="7">
-        <v>0.33929999999999999</v>
+        <v>0.3679</v>
       </c>
       <c r="S19" s="7">
-        <v>0.33260000000000001</v>
+        <v>0.34699999999999998</v>
       </c>
       <c r="T19" s="7">
+        <v>0.34429999999999999</v>
+      </c>
+      <c r="U19" s="7">
+        <v>0.33129999999999998</v>
+      </c>
+      <c r="V19" s="7">
+        <v>0.32769999999999999</v>
+      </c>
+      <c r="W19" s="7">
         <v>0.32940000000000003</v>
       </c>
-      <c r="U19" s="7">
-        <v>0.3216</v>
-      </c>
-      <c r="V19" s="7">
-        <v>0.31890000000000002</v>
-      </c>
-      <c r="W19" s="7">
-        <v>0.31979999999999997</v>
-      </c>
       <c r="X19" s="7">
-        <v>0.31080000000000002</v>
+        <v>0.31380000000000002</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.25">
@@ -29064,67 +29169,67 @@
         <v>20</v>
       </c>
       <c r="C20" s="7">
-        <v>4.4699999999999997E-2</v>
+        <v>4.3299999999999998E-2</v>
       </c>
       <c r="D20" s="7">
-        <v>3.4500000000000003E-2</v>
+        <v>3.2500000000000001E-2</v>
       </c>
       <c r="E20" s="7">
-        <v>2.23E-2</v>
+        <v>2.06E-2</v>
       </c>
       <c r="F20" s="7">
-        <v>1.95E-2</v>
+        <v>1.84E-2</v>
       </c>
       <c r="G20" s="7">
-        <v>3.49E-2</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="H20" s="7">
-        <v>0.03</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="I20" s="7">
-        <v>2.1700000000000001E-2</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="J20" s="7">
-        <v>1.95E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="K20" s="7">
-        <v>1.95E-2</v>
+        <v>1.78E-2</v>
       </c>
       <c r="L20" s="7">
-        <v>1.89E-2</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O20" s="7">
-        <v>0.25090000000000001</v>
+        <v>0.24690000000000001</v>
       </c>
       <c r="P20" s="7">
-        <v>0.2427</v>
+        <v>0.2394</v>
       </c>
       <c r="Q20" s="7">
-        <v>0.2344</v>
+        <v>0.22950000000000001</v>
       </c>
       <c r="R20" s="7">
-        <v>0.2213</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="S20" s="7">
-        <v>0.21249999999999999</v>
+        <v>0.21920000000000001</v>
       </c>
       <c r="T20" s="7">
-        <v>0.2059</v>
+        <v>0.21010000000000001</v>
       </c>
       <c r="U20" s="7">
-        <v>0.2021</v>
+        <v>0.20449999999999999</v>
       </c>
       <c r="V20" s="7">
-        <v>0.21970000000000001</v>
+        <v>0.19570000000000001</v>
       </c>
       <c r="W20" s="7">
-        <v>0.23880000000000001</v>
+        <v>0.19120000000000001</v>
       </c>
       <c r="X20" s="7">
-        <v>0.2321</v>
+        <v>0.18759999999999999</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
@@ -29132,67 +29237,67 @@
         <v>21</v>
       </c>
       <c r="C21" s="8">
-        <v>6.08E-2</v>
+        <v>5.7799999999999997E-2</v>
       </c>
       <c r="D21" s="7">
-        <v>5.0900000000000001E-2</v>
+        <v>4.6300000000000001E-2</v>
       </c>
       <c r="E21" s="7">
-        <v>4.0599999999999997E-2</v>
+        <v>4.4900000000000002E-2</v>
       </c>
       <c r="F21" s="7">
-        <v>4.6399999999999997E-2</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="G21" s="7">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="H21" s="7">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="I21" s="7">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="J21" s="7">
         <v>4.24E-2</v>
       </c>
-      <c r="H21" s="7">
-        <v>4.1799999999999997E-2</v>
-      </c>
-      <c r="I21" s="7">
-        <v>4.2700000000000002E-2</v>
-      </c>
-      <c r="J21" s="7">
-        <v>3.78E-2</v>
-      </c>
       <c r="K21" s="7">
-        <v>3.6700000000000003E-2</v>
+        <v>3.8899999999999997E-2</v>
       </c>
       <c r="L21" s="7">
-        <v>3.61E-2</v>
+        <v>3.3599999999999998E-2</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O21" s="8">
-        <v>0.34150000000000003</v>
+        <v>0.32369999999999999</v>
       </c>
       <c r="P21" s="7">
-        <v>0.32079999999999997</v>
+        <v>0.3135</v>
       </c>
       <c r="Q21" s="7">
-        <v>0.3145</v>
+        <v>0.3049</v>
       </c>
       <c r="R21" s="7">
-        <v>0.31740000000000002</v>
+        <v>0.2984</v>
       </c>
       <c r="S21" s="7">
-        <v>0.30299999999999999</v>
+        <v>0.30049999999999999</v>
       </c>
       <c r="T21" s="7">
-        <v>0.29630000000000001</v>
+        <v>0.2853</v>
       </c>
       <c r="U21" s="7">
-        <v>0.29330000000000001</v>
+        <v>0.27879999999999999</v>
       </c>
       <c r="V21" s="7">
-        <v>0.2959</v>
+        <v>0.27310000000000001</v>
       </c>
       <c r="W21" s="7">
-        <v>0.29520000000000002</v>
+        <v>0.27139999999999997</v>
       </c>
       <c r="X21" s="7">
-        <v>0.2959</v>
+        <v>0.26669999999999999</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
@@ -29212,39 +29317,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="14"/>
-      <c r="N24" s="10" t="s">
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="21"/>
+      <c r="N24" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="12" t="s">
+      <c r="O24" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="13"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
-      <c r="U24" s="13"/>
-      <c r="V24" s="13"/>
-      <c r="W24" s="13"/>
-      <c r="X24" s="14"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="21"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="11"/>
+      <c r="B25" s="23"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -29275,7 +29380,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="11"/>
+      <c r="N25" s="23"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -29312,67 +29417,67 @@
         <v>16</v>
       </c>
       <c r="C26" s="7">
-        <v>34.209400000000002</v>
+        <v>36.0854</v>
       </c>
       <c r="D26" s="7">
-        <v>34.849299999999999</v>
+        <v>36.509799999999998</v>
       </c>
       <c r="E26" s="7">
-        <v>34.061100000000003</v>
+        <v>33.868099999999998</v>
       </c>
       <c r="F26" s="7">
-        <v>34.154899999999998</v>
+        <v>34.219299999999997</v>
       </c>
       <c r="G26" s="7">
-        <v>34.296300000000002</v>
+        <v>34.019300000000001</v>
       </c>
       <c r="H26" s="7">
-        <v>34.161799999999999</v>
+        <v>34.027700000000003</v>
       </c>
       <c r="I26" s="7">
-        <v>34.444899999999997</v>
+        <v>34.375999999999998</v>
       </c>
       <c r="J26" s="7">
-        <v>34.367699999999999</v>
+        <v>33.9512</v>
       </c>
       <c r="K26" s="7">
-        <v>34.517400000000002</v>
+        <v>33.910499999999999</v>
       </c>
       <c r="L26" s="7">
-        <v>33.847299999999997</v>
+        <v>35.554200000000002</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O26" s="7">
-        <v>872.62760000000003</v>
+        <v>868.13469999999995</v>
       </c>
       <c r="P26" s="7">
-        <v>886.33439999999996</v>
+        <v>849.78009999999995</v>
       </c>
       <c r="Q26" s="7">
-        <v>882.28300000000002</v>
+        <v>854.62429999999995</v>
       </c>
       <c r="R26" s="7">
-        <v>905.01099999999997</v>
+        <v>848.30889999999999</v>
       </c>
       <c r="S26" s="7">
-        <v>1020.9693</v>
+        <v>848.26819999999998</v>
       </c>
       <c r="T26" s="7">
-        <v>908.33280000000002</v>
+        <v>846.68939999999998</v>
       </c>
       <c r="U26" s="7">
-        <v>937.2405</v>
+        <v>846.56410000000005</v>
       </c>
       <c r="V26" s="7">
-        <v>908.33429999999998</v>
+        <v>848.04020000000003</v>
       </c>
       <c r="W26" s="7">
-        <v>930.68179999999995</v>
+        <v>849.45920000000001</v>
       </c>
       <c r="X26" s="7">
-        <v>990.22979999999995</v>
+        <v>846.13109999999995</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
@@ -29380,67 +29485,67 @@
         <v>17</v>
       </c>
       <c r="C27" s="7">
-        <v>44.353400000000001</v>
+        <v>46.733600000000003</v>
       </c>
       <c r="D27" s="7">
-        <v>43.189599999999999</v>
+        <v>47.954599999999999</v>
       </c>
       <c r="E27" s="7">
-        <v>43.161999999999999</v>
+        <v>45.374899999999997</v>
       </c>
       <c r="F27" s="7">
-        <v>43.813099999999999</v>
+        <v>44.984900000000003</v>
       </c>
       <c r="G27" s="7">
-        <v>45.871400000000001</v>
+        <v>47.805799999999998</v>
       </c>
       <c r="H27" s="7">
-        <v>46.393599999999999</v>
+        <v>45.228400000000001</v>
       </c>
       <c r="I27" s="7">
-        <v>49.554499999999997</v>
+        <v>44.974200000000003</v>
       </c>
       <c r="J27" s="7">
-        <v>52.761400000000002</v>
+        <v>44.585000000000001</v>
       </c>
       <c r="K27" s="7">
-        <v>60.802300000000002</v>
+        <v>44.2239</v>
       </c>
       <c r="L27" s="7">
-        <v>49.432600000000001</v>
+        <v>43.9114</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O27" s="7">
-        <v>1470.896</v>
+        <v>1071.5481</v>
       </c>
       <c r="P27" s="7">
-        <v>1197.1107</v>
+        <v>1090.5035</v>
       </c>
       <c r="Q27" s="7">
-        <v>1528.1219000000001</v>
+        <v>1152.9730999999999</v>
       </c>
       <c r="R27" s="7">
-        <v>1614.8674000000001</v>
+        <v>1079.67</v>
       </c>
       <c r="S27" s="7">
-        <v>1612.5422000000001</v>
+        <v>1071.8521000000001</v>
       </c>
       <c r="T27" s="7">
-        <v>1599.9371000000001</v>
+        <v>1076.0916999999999</v>
       </c>
       <c r="U27" s="7">
-        <v>1744.8965000000001</v>
+        <v>1070.2357</v>
       </c>
       <c r="V27" s="7">
-        <v>1563.7733000000001</v>
+        <v>1070.7905000000001</v>
       </c>
       <c r="W27" s="7">
-        <v>1550.4166</v>
+        <v>1074.7999</v>
       </c>
       <c r="X27" s="7">
-        <v>1578.0419999999999</v>
+        <v>1071.2733000000001</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
@@ -29448,67 +29553,67 @@
         <v>18</v>
       </c>
       <c r="C28" s="7">
-        <v>90.241299999999995</v>
+        <v>79.555599999999998</v>
       </c>
       <c r="D28" s="7">
-        <v>94.488799999999998</v>
+        <v>82.736500000000007</v>
       </c>
       <c r="E28" s="7">
-        <v>89.021600000000007</v>
+        <v>81.874399999999994</v>
       </c>
       <c r="F28" s="7">
-        <v>88.33</v>
+        <v>84.866299999999995</v>
       </c>
       <c r="G28" s="7">
-        <v>91.038700000000006</v>
+        <v>83.398899999999998</v>
       </c>
       <c r="H28" s="7">
-        <v>88.762600000000006</v>
+        <v>83.856399999999994</v>
       </c>
       <c r="I28" s="7">
-        <v>87.660899999999998</v>
+        <v>83.703199999999995</v>
       </c>
       <c r="J28" s="7">
-        <v>89.802400000000006</v>
+        <v>83.741500000000002</v>
       </c>
       <c r="K28" s="7">
-        <v>86.91</v>
+        <v>83.297600000000003</v>
       </c>
       <c r="L28" s="7">
-        <v>84.600200000000001</v>
+        <v>83.440100000000001</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O28" s="7">
-        <v>3065.0989</v>
+        <v>1992.8765000000001</v>
       </c>
       <c r="P28" s="7">
-        <v>3034.4448000000002</v>
+        <v>1989.4703</v>
       </c>
       <c r="Q28" s="7">
-        <v>3036.0689000000002</v>
+        <v>1993.2145</v>
       </c>
       <c r="R28" s="7">
-        <v>3224.6957000000002</v>
+        <v>1985.0156999999999</v>
       </c>
       <c r="S28" s="7">
-        <v>3093.7710000000002</v>
+        <v>2013.2155</v>
       </c>
       <c r="T28" s="7">
-        <v>3058.2451999999998</v>
+        <v>1981.0583999999999</v>
       </c>
       <c r="U28" s="7">
-        <v>3089.3368999999998</v>
+        <v>1991.2945</v>
       </c>
       <c r="V28" s="7">
-        <v>3082.3022999999998</v>
+        <v>1982.3389</v>
       </c>
       <c r="W28" s="7">
-        <v>3145.2235000000001</v>
+        <v>1990.1155000000001</v>
       </c>
       <c r="X28" s="7">
-        <v>3074.3443000000002</v>
+        <v>1983.6434999999999</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.25">
@@ -29516,67 +29621,67 @@
         <v>19</v>
       </c>
       <c r="C29" s="7">
-        <v>0.89849999999999997</v>
+        <v>0.87250000000000005</v>
       </c>
       <c r="D29" s="7">
-        <v>1.1771</v>
+        <v>0.80549999999999999</v>
       </c>
       <c r="E29" s="7">
-        <v>1.2047000000000001</v>
+        <v>0.80269999999999997</v>
       </c>
       <c r="F29" s="7">
-        <v>0.90910000000000002</v>
+        <v>0.79690000000000005</v>
       </c>
       <c r="G29" s="7">
-        <v>0.77880000000000005</v>
+        <v>0.80130000000000001</v>
       </c>
       <c r="H29" s="7">
-        <v>0.77939999999999998</v>
+        <v>0.79749999999999999</v>
       </c>
       <c r="I29" s="7">
-        <v>0.7722</v>
+        <v>0.84009999999999996</v>
       </c>
       <c r="J29" s="7">
-        <v>0.76759999999999995</v>
+        <v>0.81840000000000002</v>
       </c>
       <c r="K29" s="7">
-        <v>0.76480000000000004</v>
+        <v>0.81240000000000001</v>
       </c>
       <c r="L29" s="7">
-        <v>0.76290000000000002</v>
+        <v>0.82220000000000004</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O29" s="7">
-        <v>6.7157</v>
+        <v>4.6365999999999996</v>
       </c>
       <c r="P29" s="7">
-        <v>7.2746000000000004</v>
+        <v>4.5749000000000004</v>
       </c>
       <c r="Q29" s="7">
-        <v>6.6779000000000002</v>
+        <v>4.5422000000000002</v>
       </c>
       <c r="R29" s="7">
-        <v>6.7633000000000001</v>
+        <v>4.5556999999999999</v>
       </c>
       <c r="S29" s="7">
-        <v>6.6882999999999999</v>
+        <v>4.6478000000000002</v>
       </c>
       <c r="T29" s="7">
-        <v>6.6247999999999996</v>
+        <v>4.5381</v>
       </c>
       <c r="U29" s="7">
-        <v>6.3198999999999996</v>
+        <v>4.5664999999999996</v>
       </c>
       <c r="V29" s="7">
-        <v>6.6131000000000002</v>
+        <v>4.8815999999999997</v>
       </c>
       <c r="W29" s="7">
-        <v>6.6803999999999997</v>
+        <v>4.4542000000000002</v>
       </c>
       <c r="X29" s="7">
-        <v>6.7270000000000003</v>
+        <v>4.4679000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.25">
@@ -29584,67 +29689,67 @@
         <v>20</v>
       </c>
       <c r="C30" s="7">
-        <v>0.52849999999999997</v>
+        <v>0.5514</v>
       </c>
       <c r="D30" s="7">
-        <v>0.52710000000000001</v>
+        <v>0.54400000000000004</v>
       </c>
       <c r="E30" s="7">
-        <v>0.51849999999999996</v>
+        <v>0.54100000000000004</v>
       </c>
       <c r="F30" s="7">
-        <v>0.51900000000000002</v>
+        <v>0.53310000000000002</v>
       </c>
       <c r="G30" s="7">
-        <v>0.51429999999999998</v>
+        <v>0.53280000000000005</v>
       </c>
       <c r="H30" s="7">
-        <v>0.51739999999999997</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="I30" s="7">
-        <v>0.51119999999999999</v>
+        <v>0.54359999999999997</v>
       </c>
       <c r="J30" s="7">
-        <v>0.51259999999999994</v>
+        <v>0.53590000000000004</v>
       </c>
       <c r="K30" s="7">
-        <v>0.50800000000000001</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="L30" s="7">
-        <v>0.51129999999999998</v>
+        <v>0.53900000000000003</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O30" s="7">
-        <v>4.6497999999999999</v>
+        <v>3.0779000000000001</v>
       </c>
       <c r="P30" s="7">
-        <v>4.5945</v>
+        <v>3.5038</v>
       </c>
       <c r="Q30" s="7">
-        <v>4.5805999999999996</v>
+        <v>3.0491000000000001</v>
       </c>
       <c r="R30" s="7">
-        <v>4.5838999999999999</v>
+        <v>3.0448</v>
       </c>
       <c r="S30" s="7">
-        <v>4.7912999999999997</v>
+        <v>3.0613999999999999</v>
       </c>
       <c r="T30" s="7">
-        <v>4.5858999999999996</v>
+        <v>3.0707</v>
       </c>
       <c r="U30" s="7">
-        <v>4.5271999999999997</v>
+        <v>3.1352000000000002</v>
       </c>
       <c r="V30" s="7">
-        <v>4.5297000000000001</v>
+        <v>3.0949</v>
       </c>
       <c r="W30" s="7">
-        <v>4.6829999999999998</v>
+        <v>3.1633</v>
       </c>
       <c r="X30" s="7">
-        <v>4.5388999999999999</v>
+        <v>3.1067</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
@@ -29652,111 +29757,111 @@
         <v>21</v>
       </c>
       <c r="C31" s="8">
-        <v>0.69540000000000002</v>
+        <v>0.70840000000000003</v>
       </c>
       <c r="D31" s="7">
-        <v>0.67749999999999999</v>
+        <v>0.70630000000000004</v>
       </c>
       <c r="E31" s="7">
-        <v>0.68089999999999995</v>
+        <v>0.69440000000000002</v>
       </c>
       <c r="F31" s="7">
-        <v>0.71740000000000004</v>
+        <v>0.69259999999999999</v>
       </c>
       <c r="G31" s="7">
-        <v>0.67849999999999999</v>
+        <v>0.69130000000000003</v>
       </c>
       <c r="H31" s="7">
-        <v>0.67030000000000001</v>
+        <v>0.69830000000000003</v>
       </c>
       <c r="I31" s="7">
-        <v>0.66859999999999997</v>
+        <v>0.68640000000000001</v>
       </c>
       <c r="J31" s="7">
-        <v>0.67330000000000001</v>
+        <v>0.68559999999999999</v>
       </c>
       <c r="K31" s="7">
-        <v>0.66739999999999999</v>
+        <v>0.68230000000000002</v>
       </c>
       <c r="L31" s="7">
-        <v>0.66839999999999999</v>
+        <v>0.68420000000000003</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O31" s="8">
-        <v>5.6353999999999997</v>
+        <v>3.8971</v>
       </c>
       <c r="P31" s="7">
-        <v>5.3098000000000001</v>
+        <v>3.9605999999999999</v>
       </c>
       <c r="Q31" s="7">
-        <v>5.6139000000000001</v>
+        <v>3.9091999999999998</v>
       </c>
       <c r="R31" s="7">
-        <v>5.6294000000000004</v>
+        <v>3.9257</v>
       </c>
       <c r="S31" s="7">
-        <v>5.6874000000000002</v>
+        <v>3.9053</v>
       </c>
       <c r="T31" s="7">
-        <v>5.6228999999999996</v>
+        <v>4.2199</v>
       </c>
       <c r="U31" s="7">
-        <v>6.0076999999999998</v>
+        <v>3.7858000000000001</v>
       </c>
       <c r="V31" s="7">
-        <v>7.2907999999999999</v>
+        <v>3.8134000000000001</v>
       </c>
       <c r="W31" s="7">
-        <v>5.7356999999999996</v>
+        <v>3.8363999999999998</v>
       </c>
       <c r="X31" s="7">
-        <v>5.8609</v>
+        <v>3.9007000000000001</v>
       </c>
     </row>
-    <row r="34" spans="2:17" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="B34" s="10" t="s">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B34" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="14"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
       <c r="K34" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L34" s="1">
-        <f>Sorted!C35</f>
+        <f>[1]Sorted!C35</f>
         <v>100</v>
       </c>
       <c r="M34" s="1">
-        <f>Sorted!D35</f>
+        <f>[1]Sorted!D35</f>
         <v>500</v>
       </c>
       <c r="N34" s="1">
-        <f>Sorted!E35</f>
+        <f>[1]Sorted!E35</f>
         <v>1000</v>
       </c>
       <c r="O34" s="1">
-        <f>Sorted!F35</f>
+        <f>[1]Sorted!F35</f>
         <v>5000</v>
       </c>
       <c r="P34" s="1">
-        <f>Sorted!G35</f>
+        <f>[1]Sorted!G35</f>
         <v>10000</v>
       </c>
       <c r="Q34" s="1">
-        <f>Sorted!H35</f>
+        <f>[1]Sorted!H35</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="35" spans="2:17" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="B35" s="11"/>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B35" s="23"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -29776,30 +29881,30 @@
         <v>50000</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L35" s="1">
-        <f>Sorted!C35^2</f>
+        <f>[1]Sorted!C35^2</f>
         <v>10000</v>
       </c>
       <c r="M35" s="1">
-        <f>Sorted!D35^2</f>
+        <f>[1]Sorted!D35^2</f>
         <v>250000</v>
       </c>
       <c r="N35" s="1">
-        <f>Sorted!E35^2</f>
+        <f>[1]Sorted!E35^2</f>
         <v>1000000</v>
       </c>
       <c r="O35" s="1">
-        <f>Sorted!F35^2</f>
+        <f>[1]Sorted!F35^2</f>
         <v>25000000</v>
       </c>
       <c r="P35" s="1">
-        <f>Sorted!G35^2</f>
+        <f>[1]Sorted!G35^2</f>
         <v>100000000</v>
       </c>
       <c r="Q35" s="1">
-        <f>Sorted!H35^2</f>
+        <f>[1]Sorted!H35^2</f>
         <v>2500000000</v>
       </c>
     </row>
@@ -29808,54 +29913,54 @@
         <v>16</v>
       </c>
       <c r="C36" s="7">
-        <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",TRIMMEAN(C6:L6,2/COUNT(C6:L6)))</f>
-        <v>3.3250000000000007E-3</v>
+        <f t="shared" ref="C36:C41" si="0">IF(COUNTBLANK(C6:L6)&gt;0,"undone",TRIMMEAN(C6:L6,2/COUNT(C6:L6)))</f>
+        <v>3.2374999999999991E-3</v>
       </c>
       <c r="D36" s="7">
-        <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
-        <v>9.6124999999999988E-2</v>
+        <f t="shared" ref="D36:D41" si="1">IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
+        <v>9.2087499999999989E-2</v>
       </c>
       <c r="E36" s="7">
-        <f>IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
-        <v>0.34291250000000001</v>
+        <f t="shared" ref="E36:E41" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
+        <v>0.32903749999999998</v>
       </c>
       <c r="F36" s="7">
-        <f>IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
-        <v>8.8987499999999997</v>
+        <f t="shared" ref="F36:F41" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
+        <v>8.5749499999999994</v>
       </c>
       <c r="G36" s="7">
-        <f>IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
-        <v>34.276687500000001</v>
+        <f t="shared" ref="G36:G41" si="4">IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
+        <v>34.517949999999999</v>
       </c>
       <c r="H36" s="7">
-        <f>IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
-        <v>918.55595000000005</v>
+        <f t="shared" ref="H36:H41" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
+        <v>848.96680000000015</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L36" s="1">
-        <f>Sorted!C35*LOG(Sorted!C35)</f>
+        <f>[1]Sorted!C35*LOG([1]Sorted!C35)</f>
         <v>200</v>
       </c>
       <c r="M36" s="1">
-        <f>Sorted!D35*LOG(Sorted!D35)</f>
+        <f>[1]Sorted!D35*LOG([1]Sorted!D35)</f>
         <v>1349.4850021680095</v>
       </c>
       <c r="N36" s="1">
-        <f>Sorted!E35*LOG(Sorted!E35)</f>
+        <f>[1]Sorted!E35*LOG([1]Sorted!E35)</f>
         <v>3000</v>
       </c>
       <c r="O36" s="1">
-        <f>Sorted!F35*LOG(Sorted!F35)</f>
+        <f>[1]Sorted!F35*LOG([1]Sorted!F35)</f>
         <v>18494.850021680093</v>
       </c>
       <c r="P36" s="1">
-        <f>Sorted!G35*LOG(Sorted!G35)</f>
+        <f>[1]Sorted!G35*LOG([1]Sorted!G35)</f>
         <v>40000</v>
       </c>
       <c r="Q36" s="1">
-        <f>Sorted!H35*LOG(Sorted!H35)</f>
+        <f>[1]Sorted!H35*LOG([1]Sorted!H35)</f>
         <v>234948.50021680092</v>
       </c>
     </row>
@@ -29864,28 +29969,28 @@
         <v>17</v>
       </c>
       <c r="C37" s="7">
-        <f t="shared" ref="C37:C41" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",TRIMMEAN(C7:L7,2/COUNT(C7:L7)))</f>
-        <v>5.0000000000000001E-3</v>
+        <f t="shared" si="0"/>
+        <v>4.725E-3</v>
       </c>
       <c r="D37" s="7">
-        <f t="shared" ref="D37:D41" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",TRIMMEAN(O7:X7,2/COUNT(O7:X7)))</f>
-        <v>0.116075</v>
+        <f t="shared" si="1"/>
+        <v>0.11115</v>
       </c>
       <c r="E37" s="7">
-        <f t="shared" ref="E37:E41" si="2">IF(COUNTBLANK(C17:L17)&gt;0,"undone",TRIMMEAN(C17:L17,2/COUNT(C17:L17)))</f>
-        <v>0.47197499999999998</v>
+        <f t="shared" si="2"/>
+        <v>0.45730000000000004</v>
       </c>
       <c r="F37" s="7">
-        <f t="shared" ref="F37:F41" si="3">IF(COUNTBLANK(O17:X17)&gt;0,"undone",TRIMMEAN(O17:X17,2/COUNT(O17:X17)))</f>
-        <v>10.990737499999998</v>
+        <f t="shared" si="3"/>
+        <v>10.927024999999999</v>
       </c>
       <c r="G37" s="7">
-        <f t="shared" ref="G37:G41" si="4">IF(COUNTBLANK(C27:L27)&gt;0,"undone",TRIMMEAN(C27:L27,2/COUNT(C27:L27)))</f>
-        <v>46.921199999999992</v>
+        <f t="shared" si="4"/>
+        <v>45.488837500000002</v>
       </c>
       <c r="H37" s="7">
-        <f t="shared" ref="H37:H41" si="5">IF(COUNTBLANK(O27:X27)&gt;0,"undone",TRIMMEAN(O27:X27,2/COUNT(O27:X27)))</f>
-        <v>1564.8245625</v>
+        <f t="shared" si="5"/>
+        <v>1075.8161375</v>
       </c>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
@@ -29894,27 +29999,27 @@
       </c>
       <c r="C38" s="7">
         <f t="shared" si="0"/>
-        <v>8.7375000000000005E-3</v>
+        <v>7.9500000000000005E-3</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="1"/>
-        <v>0.22232499999999999</v>
+        <v>0.20223750000000001</v>
       </c>
       <c r="E38" s="7">
         <f t="shared" si="2"/>
-        <v>0.86371249999999999</v>
+        <v>0.8023125000000001</v>
       </c>
       <c r="F38" s="7">
         <f t="shared" si="3"/>
-        <v>20.985674999999997</v>
+        <v>19.875374999999998</v>
       </c>
       <c r="G38" s="7">
         <f t="shared" si="4"/>
-        <v>88.970937500000005</v>
+        <v>83.256074999999996</v>
       </c>
       <c r="H38" s="7">
-        <f>IF(COUNTBLANK(O28:X28)&gt;0,"undone",TRIMMEAN(O28:X28,2/COUNT(O28:X28)))</f>
-        <v>3080.548875</v>
+        <f t="shared" si="5"/>
+        <v>1988.4961750000002</v>
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
@@ -29923,27 +30028,27 @@
       </c>
       <c r="C39" s="7">
         <f t="shared" si="0"/>
-        <v>2.9624999999999999E-3</v>
+        <v>2.8250000000000003E-3</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="1"/>
-        <v>1.85875E-2</v>
+        <v>1.7975000000000001E-2</v>
       </c>
       <c r="E39" s="7">
         <f t="shared" si="2"/>
-        <v>4.0962499999999992E-2</v>
+        <v>3.8687499999999993E-2</v>
       </c>
       <c r="F39" s="7">
         <f t="shared" si="3"/>
-        <v>0.3334375</v>
+        <v>0.36593750000000003</v>
       </c>
       <c r="G39" s="7">
         <f t="shared" si="4"/>
-        <v>0.85593750000000002</v>
+        <v>0.81251249999999997</v>
       </c>
       <c r="H39" s="7">
         <f t="shared" si="5"/>
-        <v>6.6863124999999997</v>
+        <v>4.5662125000000007</v>
       </c>
       <c r="J39" s="9"/>
     </row>
@@ -29953,27 +30058,27 @@
       </c>
       <c r="C40" s="7">
         <f t="shared" si="0"/>
-        <v>1.5874999999999999E-3</v>
+        <v>1.5999999999999999E-3</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="1"/>
-        <v>8.9125000000000003E-3</v>
+        <v>9.1750000000000009E-3</v>
       </c>
       <c r="E40" s="7">
         <f t="shared" si="2"/>
-        <v>2.5237499999999996E-2</v>
+        <v>2.0137499999999999E-2</v>
       </c>
       <c r="F40" s="7">
         <f t="shared" si="3"/>
-        <v>0.22592499999999999</v>
+        <v>0.21444999999999997</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="4"/>
-        <v>0.51642500000000002</v>
+        <v>0.54075000000000006</v>
       </c>
       <c r="H40" s="7">
         <f t="shared" si="5"/>
-        <v>4.5932874999999997</v>
+        <v>3.0949</v>
       </c>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
@@ -29982,34 +30087,34 @@
       </c>
       <c r="C41" s="7">
         <f t="shared" si="0"/>
-        <v>3.4500000000000008E-3</v>
+        <v>3.0625000000000001E-3</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="1"/>
-        <v>1.9224999999999999E-2</v>
+        <v>1.7774999999999999E-2</v>
       </c>
       <c r="E41" s="7">
         <f t="shared" si="2"/>
-        <v>4.2412499999999999E-2</v>
+        <v>3.9275000000000004E-2</v>
       </c>
       <c r="F41" s="7">
         <f t="shared" si="3"/>
-        <v>0.30487500000000001</v>
+        <v>0.29073749999999998</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="4"/>
-        <v>0.67661250000000006</v>
+        <v>0.69238750000000004</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="5"/>
-        <v>5.7241625000000003</v>
+        <v>3.8935500000000003</v>
       </c>
     </row>
     <row r="44" spans="2:17" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="10" t="s">
         <v>24</v>
       </c>
     </row>
@@ -30054,10 +30159,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="17"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -30076,39 +30181,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="14"/>
-      <c r="N4" s="10" t="s">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
+      <c r="N4" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="14"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="21"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="11"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -30139,7 +30244,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="11"/>
+      <c r="N5" s="23"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -30176,67 +30281,67 @@
         <v>16</v>
       </c>
       <c r="C6" s="7">
-        <v>2.9999999999999997E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="D6" s="7">
-        <v>2.9999999999999997E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="E6" s="7">
-        <v>2.9999999999999997E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="F6" s="7">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G6" s="7">
-        <v>2.9999999999999997E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="H6" s="7">
-        <v>2.9999999999999997E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="I6" s="7">
-        <v>2.9999999999999997E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="J6" s="7">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="K6" s="7">
-        <v>2.9999999999999997E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="L6" s="7">
-        <v>2.9999999999999997E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O6" s="7">
-        <v>1.1999999999999999E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="P6" s="7">
-        <v>1.2999999999999999E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q6" s="7">
-        <v>1.1999999999999999E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="R6" s="7">
-        <v>1.1999999999999999E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="S6" s="7">
-        <v>1.2999999999999999E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="T6" s="7">
-        <v>1.2999999999999999E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="U6" s="7">
-        <v>1.1999999999999999E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="V6" s="7">
-        <v>1.1999999999999999E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="W6" s="7">
-        <v>1.1999999999999999E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="X6" s="7">
-        <v>1.2999999999999999E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -30244,67 +30349,67 @@
         <v>17</v>
       </c>
       <c r="C7" s="7">
-        <v>6.7999999999999996E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="D7" s="7">
-        <v>6.6E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="E7" s="7">
-        <v>6.4000000000000003E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="F7" s="7">
-        <v>9.2999999999999992E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="G7" s="7">
-        <v>8.8999999999999999E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="H7" s="7">
-        <v>8.5000000000000006E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="I7" s="7">
-        <v>8.3999999999999995E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="J7" s="7">
-        <v>6.3E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="K7" s="7">
-        <v>6.3E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="L7" s="7">
-        <v>6.3E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O7" s="7">
-        <v>0.15329999999999999</v>
+        <v>0.11260000000000001</v>
       </c>
       <c r="P7" s="7">
-        <v>0.15329999999999999</v>
+        <v>0.1056</v>
       </c>
       <c r="Q7" s="7">
-        <v>0.1532</v>
+        <v>0.1057</v>
       </c>
       <c r="R7" s="7">
-        <v>0.1532</v>
+        <v>0.1056</v>
       </c>
       <c r="S7" s="7">
-        <v>0.1532</v>
+        <v>0.1057</v>
       </c>
       <c r="T7" s="7">
-        <v>0.1532</v>
+        <v>0.1057</v>
       </c>
       <c r="U7" s="7">
-        <v>0.1532</v>
+        <v>0.1057</v>
       </c>
       <c r="V7" s="7">
-        <v>0.1583</v>
+        <v>0.1056</v>
       </c>
       <c r="W7" s="7">
-        <v>0.1532</v>
+        <v>0.1057</v>
       </c>
       <c r="X7" s="7">
-        <v>0.1532</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -30312,67 +30417,67 @@
         <v>18</v>
       </c>
       <c r="C8" s="7">
-        <v>7.9000000000000008E-3</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="D8" s="7">
-        <v>7.7999999999999996E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="E8" s="7">
-        <v>7.4999999999999997E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="F8" s="7">
-        <v>7.4999999999999997E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="G8" s="7">
-        <v>7.4999999999999997E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="H8" s="7">
-        <v>7.4999999999999997E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="I8" s="7">
-        <v>7.4999999999999997E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="J8" s="7">
-        <v>7.4999999999999997E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="K8" s="7">
-        <v>7.4999999999999997E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="L8" s="7">
-        <v>7.4999999999999997E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O8" s="7">
-        <v>0.1842</v>
+        <v>0.1242</v>
       </c>
       <c r="P8" s="7">
-        <v>0.1842</v>
+        <v>0.1242</v>
       </c>
       <c r="Q8" s="7">
-        <v>0.18410000000000001</v>
+        <v>0.1242</v>
       </c>
       <c r="R8" s="7">
-        <v>0.184</v>
+        <v>0.1242</v>
       </c>
       <c r="S8" s="7">
-        <v>0.18410000000000001</v>
+        <v>0.1283</v>
       </c>
       <c r="T8" s="7">
-        <v>0.18410000000000001</v>
+        <v>0.1249</v>
       </c>
       <c r="U8" s="7">
-        <v>0.18410000000000001</v>
+        <v>0.12479999999999999</v>
       </c>
       <c r="V8" s="7">
-        <v>0.18410000000000001</v>
+        <v>0.12770000000000001</v>
       </c>
       <c r="W8" s="7">
-        <v>0.1842</v>
+        <v>0.1249</v>
       </c>
       <c r="X8" s="7">
-        <v>0.184</v>
+        <v>0.12479999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -30380,67 +30485,67 @@
         <v>19</v>
       </c>
       <c r="C9" s="7">
-        <v>5.0000000000000001E-3</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="D9" s="7">
-        <v>4.0000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="E9" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="F9" s="7">
-        <v>4.0000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G9" s="7">
-        <v>3.8E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="H9" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="I9" s="7">
-        <v>4.1000000000000003E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="J9" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="K9" s="7">
-        <v>3.8E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="L9" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O9" s="7">
-        <v>2.4299999999999999E-2</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="P9" s="7">
-        <v>2.3900000000000001E-2</v>
+        <v>1.61E-2</v>
       </c>
       <c r="Q9" s="7">
-        <v>2.3900000000000001E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="R9" s="7">
-        <v>2.3800000000000002E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="S9" s="7">
-        <v>2.3599999999999999E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="T9" s="7">
-        <v>2.3800000000000002E-2</v>
+        <v>1.61E-2</v>
       </c>
       <c r="U9" s="7">
-        <v>2.3900000000000001E-2</v>
+        <v>1.5900000000000001E-2</v>
       </c>
       <c r="V9" s="7">
-        <v>2.3900000000000001E-2</v>
+        <v>1.61E-2</v>
       </c>
       <c r="W9" s="7">
-        <v>2.3900000000000001E-2</v>
+        <v>1.5900000000000001E-2</v>
       </c>
       <c r="X9" s="7">
-        <v>2.3800000000000002E-2</v>
+        <v>1.61E-2</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -30448,67 +30553,67 @@
         <v>20</v>
       </c>
       <c r="C10" s="7">
-        <v>7.0000000000000001E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="D10" s="7">
-        <v>6.7000000000000002E-3</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="E10" s="7">
-        <v>6.1999999999999998E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="F10" s="7">
-        <v>6.1999999999999998E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="G10" s="7">
-        <v>6.1999999999999998E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="H10" s="7">
-        <v>6.1000000000000004E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="I10" s="7">
-        <v>6.1000000000000004E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="J10" s="7">
-        <v>6.1999999999999998E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="K10" s="7">
-        <v>6.1000000000000004E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="L10" s="7">
-        <v>6.1000000000000004E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O10" s="7">
-        <v>0.14829999999999999</v>
+        <v>9.9199999999999997E-2</v>
       </c>
       <c r="P10" s="7">
-        <v>0.156</v>
+        <v>9.9099999999999994E-2</v>
       </c>
       <c r="Q10" s="7">
-        <v>0.15010000000000001</v>
+        <v>9.9299999999999999E-2</v>
       </c>
       <c r="R10" s="7">
-        <v>0.14269999999999999</v>
+        <v>9.9400000000000002E-2</v>
       </c>
       <c r="S10" s="7">
-        <v>0.14280000000000001</v>
+        <v>9.9199999999999997E-2</v>
       </c>
       <c r="T10" s="7">
-        <v>0.1429</v>
+        <v>0.1113</v>
       </c>
       <c r="U10" s="7">
-        <v>0.1431</v>
+        <v>8.3599999999999994E-2</v>
       </c>
       <c r="V10" s="7">
-        <v>0.14269999999999999</v>
+        <v>8.3400000000000002E-2</v>
       </c>
       <c r="W10" s="7">
-        <v>0.14269999999999999</v>
+        <v>8.3199999999999996E-2</v>
       </c>
       <c r="X10" s="7">
-        <v>0.14269999999999999</v>
+        <v>8.3599999999999994E-2</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -30516,67 +30621,67 @@
         <v>21</v>
       </c>
       <c r="C11" s="8">
-        <v>4.5999999999999999E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="D11" s="7">
-        <v>3.7000000000000002E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E11" s="7">
-        <v>3.8E-3</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="F11" s="7">
-        <v>3.7000000000000002E-3</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="G11" s="7">
-        <v>3.5999999999999999E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="H11" s="7">
-        <v>3.7000000000000002E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="I11" s="7">
-        <v>3.5999999999999999E-3</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="J11" s="7">
-        <v>3.5999999999999999E-3</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="K11" s="7">
-        <v>3.7000000000000002E-3</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="L11" s="7">
-        <v>3.5000000000000001E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O11" s="8">
-        <v>2.2200000000000001E-2</v>
+        <v>1.34E-2</v>
       </c>
       <c r="P11" s="7">
-        <v>2.0299999999999999E-2</v>
+        <v>1.34E-2</v>
       </c>
       <c r="Q11" s="7">
-        <v>2.9600000000000001E-2</v>
+        <v>1.24E-2</v>
       </c>
       <c r="R11" s="7">
-        <v>2.1100000000000001E-2</v>
+        <v>1.2200000000000001E-2</v>
       </c>
       <c r="S11" s="7">
-        <v>1.9699999999999999E-2</v>
+        <v>1.2200000000000001E-2</v>
       </c>
       <c r="T11" s="7">
-        <v>1.9400000000000001E-2</v>
+        <v>1.23E-2</v>
       </c>
       <c r="U11" s="7">
-        <v>1.9300000000000001E-2</v>
+        <v>1.23E-2</v>
       </c>
       <c r="V11" s="7">
-        <v>1.95E-2</v>
+        <v>1.21E-2</v>
       </c>
       <c r="W11" s="7">
-        <v>1.9400000000000001E-2</v>
+        <v>1.23E-2</v>
       </c>
       <c r="X11" s="7">
-        <v>1.9400000000000001E-2</v>
+        <v>1.2200000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -30596,39 +30701,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="14"/>
-      <c r="N14" s="10" t="s">
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="21"/>
+      <c r="N14" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="O14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="14"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="21"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="11"/>
+      <c r="B15" s="23"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -30659,7 +30764,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="11"/>
+      <c r="N15" s="23"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -30696,67 +30801,67 @@
         <v>16</v>
       </c>
       <c r="C16" s="7">
-        <v>2.5000000000000001E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="D16" s="7">
-        <v>2.3999999999999998E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="E16" s="7">
-        <v>2.3999999999999998E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="F16" s="7">
-        <v>2.5000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="G16" s="7">
-        <v>2.5000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="H16" s="7">
-        <v>2.5000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="I16" s="7">
-        <v>2.5000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="J16" s="7">
-        <v>2.5000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="K16" s="7">
-        <v>2.5000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="L16" s="7">
-        <v>2.5000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O16" s="7">
-        <v>1.23E-2</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="P16" s="7">
-        <v>1.23E-2</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="Q16" s="7">
-        <v>1.2200000000000001E-2</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="R16" s="7">
-        <v>1.23E-2</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="S16" s="7">
-        <v>1.23E-2</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="T16" s="7">
-        <v>1.2200000000000001E-2</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="U16" s="7">
-        <v>1.23E-2</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="V16" s="7">
-        <v>1.23E-2</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="W16" s="7">
-        <v>1.2200000000000001E-2</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="X16" s="7">
-        <v>1.2200000000000001E-2</v>
+        <v>7.4000000000000003E-3</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
@@ -30764,67 +30869,67 @@
         <v>17</v>
       </c>
       <c r="C17" s="7">
-        <v>0.60799999999999998</v>
+        <v>0.43509999999999999</v>
       </c>
       <c r="D17" s="7">
-        <v>0.6079</v>
+        <v>0.42149999999999999</v>
       </c>
       <c r="E17" s="7">
-        <v>0.61329999999999996</v>
+        <v>0.42149999999999999</v>
       </c>
       <c r="F17" s="7">
-        <v>0.60880000000000001</v>
+        <v>0.4214</v>
       </c>
       <c r="G17" s="7">
-        <v>0.60899999999999999</v>
+        <v>0.42430000000000001</v>
       </c>
       <c r="H17" s="7">
-        <v>0.60899999999999999</v>
+        <v>0.42220000000000002</v>
       </c>
       <c r="I17" s="7">
-        <v>0.69530000000000003</v>
+        <v>0.42730000000000001</v>
       </c>
       <c r="J17" s="7">
-        <v>0.63239999999999996</v>
+        <v>0.42449999999999999</v>
       </c>
       <c r="K17" s="7">
-        <v>0.72419999999999995</v>
+        <v>0.42749999999999999</v>
       </c>
       <c r="L17" s="7">
-        <v>0.69769999999999999</v>
+        <v>0.42880000000000001</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O17" s="7">
-        <v>15.3589</v>
+        <v>10.6355</v>
       </c>
       <c r="P17" s="7">
-        <v>15.2684</v>
+        <v>12.818099999999999</v>
       </c>
       <c r="Q17" s="7">
-        <v>15.609299999999999</v>
+        <v>10.764799999999999</v>
       </c>
       <c r="R17" s="7">
-        <v>15.8925</v>
+        <v>10.975899999999999</v>
       </c>
       <c r="S17" s="7">
-        <v>15.537599999999999</v>
+        <v>10.452</v>
       </c>
       <c r="T17" s="7">
-        <v>15.5802</v>
+        <v>10.635199999999999</v>
       </c>
       <c r="U17" s="7">
-        <v>15.3429</v>
+        <v>10.6526</v>
       </c>
       <c r="V17" s="7">
-        <v>15.2437</v>
+        <v>10.620699999999999</v>
       </c>
       <c r="W17" s="7">
-        <v>15.187900000000001</v>
+        <v>10.8705</v>
       </c>
       <c r="X17" s="7">
-        <v>15.29</v>
+        <v>10.756399999999999</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
@@ -30832,67 +30937,67 @@
         <v>18</v>
       </c>
       <c r="C18" s="7">
-        <v>0.75929999999999997</v>
+        <v>0.50090000000000001</v>
       </c>
       <c r="D18" s="7">
-        <v>0.74329999999999996</v>
+        <v>0.50090000000000001</v>
       </c>
       <c r="E18" s="7">
-        <v>0.78059999999999996</v>
+        <v>0.501</v>
       </c>
       <c r="F18" s="7">
-        <v>0.77790000000000004</v>
+        <v>0.50380000000000003</v>
       </c>
       <c r="G18" s="7">
-        <v>0.79720000000000002</v>
+        <v>0.50170000000000003</v>
       </c>
       <c r="H18" s="7">
-        <v>0.74309999999999998</v>
+        <v>0.49590000000000001</v>
       </c>
       <c r="I18" s="7">
-        <v>0.73670000000000002</v>
+        <v>0.49590000000000001</v>
       </c>
       <c r="J18" s="7">
-        <v>0.73160000000000003</v>
+        <v>0.49869999999999998</v>
       </c>
       <c r="K18" s="7">
-        <v>0.7319</v>
+        <v>0.49580000000000002</v>
       </c>
       <c r="L18" s="7">
-        <v>0.7369</v>
+        <v>0.49569999999999997</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O18" s="7">
-        <v>19.000800000000002</v>
+        <v>12.281499999999999</v>
       </c>
       <c r="P18" s="7">
-        <v>18.380600000000001</v>
+        <v>12.3811</v>
       </c>
       <c r="Q18" s="7">
-        <v>18.504999999999999</v>
+        <v>12.477499999999999</v>
       </c>
       <c r="R18" s="7">
-        <v>18.361999999999998</v>
+        <v>12.4749</v>
       </c>
       <c r="S18" s="7">
-        <v>18.454899999999999</v>
+        <v>12.6495</v>
       </c>
       <c r="T18" s="7">
-        <v>18.518999999999998</v>
+        <v>12.4552</v>
       </c>
       <c r="U18" s="7">
-        <v>18.597799999999999</v>
+        <v>12.4793</v>
       </c>
       <c r="V18" s="7">
-        <v>18.1066</v>
+        <v>12.6523</v>
       </c>
       <c r="W18" s="7">
-        <v>18.316299999999998</v>
+        <v>12.405900000000001</v>
       </c>
       <c r="X18" s="7">
-        <v>18.439399999999999</v>
+        <v>12.3338</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
@@ -30900,67 +31005,67 @@
         <v>19</v>
       </c>
       <c r="C19" s="7">
-        <v>5.2499999999999998E-2</v>
+        <v>3.4700000000000002E-2</v>
       </c>
       <c r="D19" s="7">
-        <v>5.16E-2</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="E19" s="7">
-        <v>5.1299999999999998E-2</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="F19" s="7">
-        <v>5.1400000000000001E-2</v>
+        <v>3.44E-2</v>
       </c>
       <c r="G19" s="7">
-        <v>5.16E-2</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="H19" s="7">
-        <v>5.1499999999999997E-2</v>
+        <v>3.4700000000000002E-2</v>
       </c>
       <c r="I19" s="7">
-        <v>5.1700000000000003E-2</v>
+        <v>4.7699999999999999E-2</v>
       </c>
       <c r="J19" s="7">
-        <v>5.1499999999999997E-2</v>
+        <v>4.8500000000000001E-2</v>
       </c>
       <c r="K19" s="7">
-        <v>5.1400000000000001E-2</v>
+        <v>4.0300000000000002E-2</v>
       </c>
       <c r="L19" s="7">
-        <v>5.16E-2</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O19" s="7">
-        <v>0.30370000000000003</v>
+        <v>0.20760000000000001</v>
       </c>
       <c r="P19" s="7">
-        <v>0.30130000000000001</v>
+        <v>0.20949999999999999</v>
       </c>
       <c r="Q19" s="7">
-        <v>0.3095</v>
+        <v>0.2041</v>
       </c>
       <c r="R19" s="7">
-        <v>0.3019</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="S19" s="7">
-        <v>0.30220000000000002</v>
+        <v>0.20430000000000001</v>
       </c>
       <c r="T19" s="7">
-        <v>0.30259999999999998</v>
+        <v>0.2041</v>
       </c>
       <c r="U19" s="7">
-        <v>0.30170000000000002</v>
+        <v>0.2041</v>
       </c>
       <c r="V19" s="7">
-        <v>0.3014</v>
+        <v>0.2044</v>
       </c>
       <c r="W19" s="7">
-        <v>0.30599999999999999</v>
+        <v>0.20380000000000001</v>
       </c>
       <c r="X19" s="7">
-        <v>0.30320000000000003</v>
+        <v>0.20399999999999999</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.25">
@@ -30968,67 +31073,67 @@
         <v>20</v>
       </c>
       <c r="C20" s="7">
-        <v>0.56340000000000001</v>
+        <v>0.38779999999999998</v>
       </c>
       <c r="D20" s="7">
-        <v>0.49430000000000002</v>
+        <v>0.3911</v>
       </c>
       <c r="E20" s="7">
-        <v>0.57110000000000005</v>
+        <v>0.38790000000000002</v>
       </c>
       <c r="F20" s="7">
-        <v>0.57809999999999995</v>
+        <v>0.3876</v>
       </c>
       <c r="G20" s="7">
-        <v>0.5585</v>
+        <v>0.39029999999999998</v>
       </c>
       <c r="H20" s="7">
-        <v>0.56359999999999999</v>
+        <v>0.38679999999999998</v>
       </c>
       <c r="I20" s="7">
-        <v>0.5585</v>
+        <v>0.3871</v>
       </c>
       <c r="J20" s="7">
-        <v>0.55869999999999997</v>
+        <v>0.38719999999999999</v>
       </c>
       <c r="K20" s="7">
-        <v>0.59570000000000001</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="L20" s="7">
-        <v>0.55859999999999999</v>
+        <v>0.38969999999999999</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O20" s="7">
-        <v>13.824</v>
+        <v>9.5584000000000007</v>
       </c>
       <c r="P20" s="7">
-        <v>13.820499999999999</v>
+        <v>9.5318000000000005</v>
       </c>
       <c r="Q20" s="7">
-        <v>13.5</v>
+        <v>9.4718999999999998</v>
       </c>
       <c r="R20" s="7">
-        <v>13.808400000000001</v>
+        <v>9.5315999999999992</v>
       </c>
       <c r="S20" s="7">
-        <v>13.8751</v>
+        <v>9.5273000000000003</v>
       </c>
       <c r="T20" s="7">
-        <v>13.818899999999999</v>
+        <v>9.5197000000000003</v>
       </c>
       <c r="U20" s="7">
-        <v>13.9016</v>
+        <v>9.5466999999999995</v>
       </c>
       <c r="V20" s="7">
-        <v>13.2591</v>
+        <v>9.5459999999999994</v>
       </c>
       <c r="W20" s="7">
-        <v>13.9946</v>
+        <v>9.5281000000000002</v>
       </c>
       <c r="X20" s="7">
-        <v>13.8437</v>
+        <v>9.766</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
@@ -31036,67 +31141,67 @@
         <v>21</v>
       </c>
       <c r="C21" s="8">
-        <v>4.7600000000000003E-2</v>
+        <v>3.15E-2</v>
       </c>
       <c r="D21" s="7">
-        <v>4.5199999999999997E-2</v>
+        <v>2.9700000000000001E-2</v>
       </c>
       <c r="E21" s="7">
-        <v>0.31380000000000002</v>
+        <v>3.0499999999999999E-2</v>
       </c>
       <c r="F21" s="7">
-        <v>4.3499999999999997E-2</v>
+        <v>2.9499999999999998E-2</v>
       </c>
       <c r="G21" s="7">
-        <v>4.3999999999999997E-2</v>
+        <v>2.86E-2</v>
       </c>
       <c r="H21" s="7">
-        <v>4.3200000000000002E-2</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="I21" s="7">
-        <v>4.3900000000000002E-2</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="J21" s="7">
-        <v>4.3799999999999999E-2</v>
+        <v>2.8299999999999999E-2</v>
       </c>
       <c r="K21" s="7">
-        <v>4.2900000000000001E-2</v>
+        <v>2.8400000000000002E-2</v>
       </c>
       <c r="L21" s="7">
-        <v>4.2099999999999999E-2</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O21" s="8">
-        <v>0.23980000000000001</v>
+        <v>0.1681</v>
       </c>
       <c r="P21" s="7">
-        <v>0.2326</v>
+        <v>0.15740000000000001</v>
       </c>
       <c r="Q21" s="7">
-        <v>0.2205</v>
+        <v>0.1573</v>
       </c>
       <c r="R21" s="7">
-        <v>0.22520000000000001</v>
+        <v>0.15759999999999999</v>
       </c>
       <c r="S21" s="7">
-        <v>0.23369999999999999</v>
+        <v>0.1585</v>
       </c>
       <c r="T21" s="7">
-        <v>0.22309999999999999</v>
+        <v>0.15859999999999999</v>
       </c>
       <c r="U21" s="7">
-        <v>0.22159999999999999</v>
+        <v>0.1575</v>
       </c>
       <c r="V21" s="7">
-        <v>0.22209999999999999</v>
+        <v>0.15559999999999999</v>
       </c>
       <c r="W21" s="7">
-        <v>0.22850000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="X21" s="7">
-        <v>0.22450000000000001</v>
+        <v>0.15579999999999999</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
@@ -31116,39 +31221,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="14"/>
-      <c r="N24" s="10" t="s">
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="21"/>
+      <c r="N24" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="12" t="s">
+      <c r="O24" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="13"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
-      <c r="U24" s="13"/>
-      <c r="V24" s="13"/>
-      <c r="W24" s="13"/>
-      <c r="X24" s="14"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="21"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="11"/>
+      <c r="B25" s="23"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -31179,7 +31284,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="11"/>
+      <c r="N25" s="23"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -31216,67 +31321,67 @@
         <v>16</v>
       </c>
       <c r="C26" s="7">
-        <v>2.4500000000000001E-2</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="D26" s="7">
-        <v>2.4500000000000001E-2</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="E26" s="7">
-        <v>2.4500000000000001E-2</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="F26" s="7">
-        <v>2.4400000000000002E-2</v>
+        <v>1.44E-2</v>
       </c>
       <c r="G26" s="7">
-        <v>2.4400000000000002E-2</v>
+        <v>1.44E-2</v>
       </c>
       <c r="H26" s="7">
-        <v>2.4500000000000001E-2</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="I26" s="7">
-        <v>2.4500000000000001E-2</v>
+        <v>1.44E-2</v>
       </c>
       <c r="J26" s="7">
-        <v>2.4500000000000001E-2</v>
+        <v>1.44E-2</v>
       </c>
       <c r="K26" s="7">
-        <v>2.4400000000000002E-2</v>
+        <v>1.44E-2</v>
       </c>
       <c r="L26" s="7">
-        <v>2.4500000000000001E-2</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O26" s="7">
-        <v>0.12230000000000001</v>
+        <v>7.5300000000000006E-2</v>
       </c>
       <c r="P26" s="7">
-        <v>0.12230000000000001</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="Q26" s="7">
-        <v>0.12230000000000001</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="R26" s="7">
-        <v>0.1222</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="S26" s="7">
-        <v>0.12230000000000001</v>
+        <v>8.1900000000000001E-2</v>
       </c>
       <c r="T26" s="7">
-        <v>0.1222</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="U26" s="7">
-        <v>0.12230000000000001</v>
+        <v>8.1900000000000001E-2</v>
       </c>
       <c r="V26" s="7">
-        <v>0.12770000000000001</v>
+        <v>8.7300000000000003E-2</v>
       </c>
       <c r="W26" s="7">
-        <v>0.12230000000000001</v>
+        <v>8.3599999999999994E-2</v>
       </c>
       <c r="X26" s="7">
-        <v>0.12230000000000001</v>
+        <v>8.2000000000000003E-2</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
@@ -31284,67 +31389,67 @@
         <v>17</v>
       </c>
       <c r="C27" s="7">
-        <v>62.367600000000003</v>
+        <v>42.495199999999997</v>
       </c>
       <c r="D27" s="7">
-        <v>61.901699999999998</v>
+        <v>42.446399999999997</v>
       </c>
       <c r="E27" s="7">
-        <v>61.0244</v>
+        <v>43.199399999999997</v>
       </c>
       <c r="F27" s="7">
-        <v>61.341900000000003</v>
+        <v>43.211100000000002</v>
       </c>
       <c r="G27" s="7">
-        <v>62.475499999999997</v>
+        <v>42.449199999999998</v>
       </c>
       <c r="H27" s="7">
-        <v>60.632399999999997</v>
+        <v>42.714500000000001</v>
       </c>
       <c r="I27" s="7">
-        <v>61.600999999999999</v>
+        <v>42.832799999999999</v>
       </c>
       <c r="J27" s="7">
-        <v>61.796999999999997</v>
+        <v>43.162599999999998</v>
       </c>
       <c r="K27" s="7">
-        <v>61.085999999999999</v>
+        <v>42.555399999999999</v>
       </c>
       <c r="L27" s="7">
-        <v>62.555399999999999</v>
+        <v>42.995100000000001</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O27" s="7">
-        <v>1544.2574999999999</v>
+        <v>1067.8127999999999</v>
       </c>
       <c r="P27" s="7">
-        <v>1557.4327000000001</v>
+        <v>1068.742</v>
       </c>
       <c r="Q27" s="7">
-        <v>1568.2515000000001</v>
+        <v>1068.3106</v>
       </c>
       <c r="R27" s="7">
-        <v>1526.5696</v>
+        <v>1073.9188999999999</v>
       </c>
       <c r="S27" s="7">
-        <v>1660.1524999999999</v>
+        <v>1069.395</v>
       </c>
       <c r="T27" s="7">
-        <v>1614.6695999999999</v>
+        <v>1070.9504999999999</v>
       </c>
       <c r="U27" s="7">
-        <v>1586.1161</v>
+        <v>1069.8886</v>
       </c>
       <c r="V27" s="7">
-        <v>1648.0002999999999</v>
+        <v>1077.56</v>
       </c>
       <c r="W27" s="7">
-        <v>1579.9689000000001</v>
+        <v>1072.7401</v>
       </c>
       <c r="X27" s="7">
-        <v>1599.7979</v>
+        <v>1069.9748999999999</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
@@ -31352,67 +31457,67 @@
         <v>18</v>
       </c>
       <c r="C28" s="7">
-        <v>74.833799999999997</v>
+        <v>50.0229</v>
       </c>
       <c r="D28" s="7">
-        <v>76.621399999999994</v>
+        <v>49.666800000000002</v>
       </c>
       <c r="E28" s="7">
-        <v>76.111699999999999</v>
+        <v>49.838700000000003</v>
       </c>
       <c r="F28" s="7">
-        <v>73.632300000000001</v>
+        <v>49.8506</v>
       </c>
       <c r="G28" s="7">
-        <v>73.761700000000005</v>
+        <v>50.689700000000002</v>
       </c>
       <c r="H28" s="7">
-        <v>73.587500000000006</v>
+        <v>50.465499999999999</v>
       </c>
       <c r="I28" s="7">
-        <v>76.504099999999994</v>
+        <v>51.234900000000003</v>
       </c>
       <c r="J28" s="7">
-        <v>81.421400000000006</v>
+        <v>49.853900000000003</v>
       </c>
       <c r="K28" s="7">
-        <v>90.009</v>
+        <v>49.991900000000001</v>
       </c>
       <c r="L28" s="7">
-        <v>73.204300000000003</v>
+        <v>49.697899999999997</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O28" s="7">
-        <v>1912.9282000000001</v>
+        <v>1249.0036</v>
       </c>
       <c r="P28" s="7">
-        <v>1884.4626000000001</v>
+        <v>1257.0833</v>
       </c>
       <c r="Q28" s="7">
-        <v>1904.6116999999999</v>
+        <v>1251.0545</v>
       </c>
       <c r="R28" s="7">
-        <v>2017.0499</v>
+        <v>1246.2598</v>
       </c>
       <c r="S28" s="7">
-        <v>1899.6895</v>
+        <v>1252.7464</v>
       </c>
       <c r="T28" s="7">
-        <v>1875.664</v>
+        <v>1246.9866</v>
       </c>
       <c r="U28" s="7">
-        <v>1980.425</v>
+        <v>1246.7275999999999</v>
       </c>
       <c r="V28" s="7">
-        <v>1861.0727999999999</v>
+        <v>1248.1189999999999</v>
       </c>
       <c r="W28" s="7">
-        <v>1872.2660000000001</v>
+        <v>1247.336</v>
       </c>
       <c r="X28" s="7">
-        <v>1881.9192</v>
+        <v>1246.6805999999999</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.25">
@@ -31420,67 +31525,67 @@
         <v>19</v>
       </c>
       <c r="C29" s="7">
-        <v>0.64270000000000005</v>
+        <v>0.4415</v>
       </c>
       <c r="D29" s="7">
-        <v>0.6401</v>
+        <v>0.44119999999999998</v>
       </c>
       <c r="E29" s="7">
-        <v>0.65539999999999998</v>
+        <v>0.44030000000000002</v>
       </c>
       <c r="F29" s="7">
-        <v>0.64</v>
+        <v>0.43559999999999999</v>
       </c>
       <c r="G29" s="7">
-        <v>0.65959999999999996</v>
+        <v>0.43880000000000002</v>
       </c>
       <c r="H29" s="7">
-        <v>0.64859999999999995</v>
+        <v>0.43369999999999997</v>
       </c>
       <c r="I29" s="7">
-        <v>0.63980000000000004</v>
+        <v>0.43680000000000002</v>
       </c>
       <c r="J29" s="7">
-        <v>0.64080000000000004</v>
+        <v>0.43280000000000002</v>
       </c>
       <c r="K29" s="7">
-        <v>0.64729999999999999</v>
+        <v>0.43369999999999997</v>
       </c>
       <c r="L29" s="7">
-        <v>0.64070000000000005</v>
+        <v>0.43359999999999999</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O29" s="7">
-        <v>3.6398000000000001</v>
+        <v>2.5145</v>
       </c>
       <c r="P29" s="7">
-        <v>3.7240000000000002</v>
+        <v>2.4899</v>
       </c>
       <c r="Q29" s="7">
-        <v>3.6631</v>
+        <v>2.4817999999999998</v>
       </c>
       <c r="R29" s="7">
-        <v>3.6871</v>
+        <v>2.5047999999999999</v>
       </c>
       <c r="S29" s="7">
-        <v>3.6657000000000002</v>
+        <v>2.4796999999999998</v>
       </c>
       <c r="T29" s="7">
-        <v>3.7033999999999998</v>
+        <v>2.5041000000000002</v>
       </c>
       <c r="U29" s="7">
-        <v>3.6800999999999999</v>
+        <v>2.4923999999999999</v>
       </c>
       <c r="V29" s="7">
-        <v>3.6440999999999999</v>
+        <v>2.9016000000000002</v>
       </c>
       <c r="W29" s="7">
-        <v>3.6665000000000001</v>
+        <v>2.4239000000000002</v>
       </c>
       <c r="X29" s="7">
-        <v>3.782</v>
+        <v>2.4293999999999998</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.25">
@@ -31488,67 +31593,67 @@
         <v>20</v>
       </c>
       <c r="C30" s="7">
-        <v>54.234200000000001</v>
+        <v>37.9071</v>
       </c>
       <c r="D30" s="7">
-        <v>55.121499999999997</v>
+        <v>37.999299999999998</v>
       </c>
       <c r="E30" s="7">
-        <v>54.447299999999998</v>
+        <v>37.873399999999997</v>
       </c>
       <c r="F30" s="7">
-        <v>55.137500000000003</v>
+        <v>38.021299999999997</v>
       </c>
       <c r="G30" s="7">
-        <v>58.606099999999998</v>
+        <v>38.034500000000001</v>
       </c>
       <c r="H30" s="7">
-        <v>55.237900000000003</v>
+        <v>37.784300000000002</v>
       </c>
       <c r="I30" s="7">
-        <v>54.664200000000001</v>
+        <v>38.297800000000002</v>
       </c>
       <c r="J30" s="7">
-        <v>54.142200000000003</v>
+        <v>38.147300000000001</v>
       </c>
       <c r="K30" s="7">
-        <v>54.662700000000001</v>
+        <v>38.0456</v>
       </c>
       <c r="L30" s="7">
-        <v>56.613500000000002</v>
+        <v>38.0642</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O30" s="7">
-        <v>1370.6029000000001</v>
+        <v>946.50329999999997</v>
       </c>
       <c r="P30" s="7">
-        <v>1386.6452999999999</v>
+        <v>945.11410000000001</v>
       </c>
       <c r="Q30" s="7">
-        <v>1469.2831000000001</v>
+        <v>948.30470000000003</v>
       </c>
       <c r="R30" s="7">
-        <v>1389.9918</v>
+        <v>944.83420000000001</v>
       </c>
       <c r="S30" s="7">
-        <v>1388.2077999999999</v>
+        <v>944.54679999999996</v>
       </c>
       <c r="T30" s="7">
-        <v>1406.0782999999999</v>
+        <v>944.74469999999997</v>
       </c>
       <c r="U30" s="7">
-        <v>1403.9821999999999</v>
+        <v>947.21109999999999</v>
       </c>
       <c r="V30" s="7">
-        <v>1384.3742999999999</v>
+        <v>945.00059999999996</v>
       </c>
       <c r="W30" s="7">
-        <v>1392.9535000000001</v>
+        <v>946.19650000000001</v>
       </c>
       <c r="X30" s="7">
-        <v>1368.1194</v>
+        <v>945.83730000000003</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
@@ -31556,111 +31661,111 @@
         <v>21</v>
       </c>
       <c r="C31" s="8">
-        <v>0.42549999999999999</v>
+        <v>0.38479999999999998</v>
       </c>
       <c r="D31" s="7">
-        <v>0.40849999999999997</v>
+        <v>0.36549999999999999</v>
       </c>
       <c r="E31" s="7">
-        <v>0.40429999999999999</v>
+        <v>0.36670000000000003</v>
       </c>
       <c r="F31" s="7">
-        <v>0.40250000000000002</v>
+        <v>0.37419999999999998</v>
       </c>
       <c r="G31" s="7">
-        <v>0.4</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H31" s="7">
-        <v>0.4042</v>
+        <v>0.38080000000000003</v>
       </c>
       <c r="I31" s="7">
-        <v>0.40179999999999999</v>
+        <v>0.36230000000000001</v>
       </c>
       <c r="J31" s="7">
-        <v>0.3992</v>
+        <v>0.3594</v>
       </c>
       <c r="K31" s="7">
-        <v>0.39989999999999998</v>
+        <v>0.37490000000000001</v>
       </c>
       <c r="L31" s="7">
-        <v>0.40639999999999998</v>
+        <v>0.37719999999999998</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O31" s="8">
-        <v>2.9708000000000001</v>
+        <v>2.6922000000000001</v>
       </c>
       <c r="P31" s="7">
-        <v>2.9462999999999999</v>
+        <v>2.7564000000000002</v>
       </c>
       <c r="Q31" s="7">
-        <v>2.8967999999999998</v>
+        <v>2.7909999999999999</v>
       </c>
       <c r="R31" s="7">
-        <v>3.0565000000000002</v>
+        <v>2.7925</v>
       </c>
       <c r="S31" s="7">
-        <v>2.9175</v>
+        <v>2.7885</v>
       </c>
       <c r="T31" s="7">
-        <v>2.9504999999999999</v>
+        <v>2.8820999999999999</v>
       </c>
       <c r="U31" s="7">
-        <v>2.9243999999999999</v>
+        <v>2.8068</v>
       </c>
       <c r="V31" s="7">
-        <v>2.8656000000000001</v>
+        <v>2.7907999999999999</v>
       </c>
       <c r="W31" s="7">
-        <v>3.089</v>
+        <v>2.8008999999999999</v>
       </c>
       <c r="X31" s="7">
-        <v>2.9117000000000002</v>
+        <v>2.7896999999999998</v>
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="14"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
       <c r="K34" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L34" s="1">
-        <f>Sorted!C35</f>
+        <f>[1]Sorted!C35</f>
         <v>100</v>
       </c>
       <c r="M34" s="1">
-        <f>Sorted!D35</f>
+        <f>[1]Sorted!D35</f>
         <v>500</v>
       </c>
       <c r="N34" s="1">
-        <f>Sorted!E35</f>
+        <f>[1]Sorted!E35</f>
         <v>1000</v>
       </c>
       <c r="O34" s="1">
-        <f>Sorted!F35</f>
+        <f>[1]Sorted!F35</f>
         <v>5000</v>
       </c>
       <c r="P34" s="1">
-        <f>Sorted!G35</f>
+        <f>[1]Sorted!G35</f>
         <v>10000</v>
       </c>
       <c r="Q34" s="1">
-        <f>Sorted!H35</f>
+        <f>[1]Sorted!H35</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="35" spans="2:17" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="B35" s="11"/>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B35" s="23"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -31680,30 +31785,30 @@
         <v>50000</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L35" s="1">
-        <f>Sorted!C35^2</f>
+        <f>[1]Sorted!C35^2</f>
         <v>10000</v>
       </c>
       <c r="M35" s="1">
-        <f>Sorted!D35^2</f>
+        <f>[1]Sorted!D35^2</f>
         <v>250000</v>
       </c>
       <c r="N35" s="1">
-        <f>Sorted!E35^2</f>
+        <f>[1]Sorted!E35^2</f>
         <v>1000000</v>
       </c>
       <c r="O35" s="1">
-        <f>Sorted!F35^2</f>
+        <f>[1]Sorted!F35^2</f>
         <v>25000000</v>
       </c>
       <c r="P35" s="1">
-        <f>Sorted!G35^2</f>
+        <f>[1]Sorted!G35^2</f>
         <v>100000000</v>
       </c>
       <c r="Q35" s="1">
-        <f>Sorted!H35^2</f>
+        <f>[1]Sorted!H35^2</f>
         <v>2500000000</v>
       </c>
     </row>
@@ -31712,54 +31817,54 @@
         <v>16</v>
       </c>
       <c r="C36" s="7">
-        <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",TRIMMEAN(C6:L6,2/COUNT(C6:L6)))</f>
-        <v>2.875E-4</v>
+        <f t="shared" ref="C36:C41" si="0">IF(COUNTBLANK(C6:L6)&gt;0,"undone",TRIMMEAN(C6:L6,2/COUNT(C6:L6)))</f>
+        <v>1.7500000000000003E-4</v>
       </c>
       <c r="D36" s="7">
-        <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
-        <v>1.2374999999999999E-3</v>
+        <f t="shared" ref="D36:D41" si="1">IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
+        <v>8.0000000000000015E-4</v>
       </c>
       <c r="E36" s="7">
-        <f>IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
-        <v>2.4874999999999997E-3</v>
+        <f t="shared" ref="E36:E41" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
+        <v>1.6125000000000002E-3</v>
       </c>
       <c r="F36" s="7">
-        <f>IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
-        <v>1.2262500000000001E-2</v>
+        <f t="shared" ref="F36:F41" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
+        <v>7.3875000000000017E-3</v>
       </c>
       <c r="G36" s="7">
-        <f>IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
-        <v>2.4475E-2</v>
+        <f t="shared" ref="G36:G41" si="4">IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
+        <v>1.4450000000000003E-2</v>
       </c>
       <c r="H36" s="7">
-        <f>IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
-        <v>0.12228749999999998</v>
+        <f t="shared" ref="H36:H41" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
+        <v>8.2174999999999998E-2</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L36" s="1">
-        <f>Sorted!C35*LOG(Sorted!C35)</f>
+        <f>[1]Sorted!C35*LOG([1]Sorted!C35)</f>
         <v>200</v>
       </c>
       <c r="M36" s="1">
-        <f>Sorted!D35*LOG(Sorted!D35)</f>
+        <f>[1]Sorted!D35*LOG([1]Sorted!D35)</f>
         <v>1349.4850021680095</v>
       </c>
       <c r="N36" s="1">
-        <f>Sorted!E35*LOG(Sorted!E35)</f>
+        <f>[1]Sorted!E35*LOG([1]Sorted!E35)</f>
         <v>3000</v>
       </c>
       <c r="O36" s="1">
-        <f>Sorted!F35*LOG(Sorted!F35)</f>
+        <f>[1]Sorted!F35*LOG([1]Sorted!F35)</f>
         <v>18494.850021680093</v>
       </c>
       <c r="P36" s="1">
-        <f>Sorted!G35*LOG(Sorted!G35)</f>
+        <f>[1]Sorted!G35*LOG([1]Sorted!G35)</f>
         <v>40000</v>
       </c>
       <c r="Q36" s="1">
-        <f>Sorted!H35*LOG(Sorted!H35)</f>
+        <f>[1]Sorted!H35*LOG([1]Sorted!H35)</f>
         <v>234948.50021680092</v>
       </c>
     </row>
@@ -31768,28 +31873,28 @@
         <v>17</v>
       </c>
       <c r="C37" s="7">
-        <f t="shared" ref="C37:C41" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",TRIMMEAN(C7:L7,2/COUNT(C7:L7)))</f>
-        <v>7.2750000000000002E-3</v>
+        <f t="shared" si="0"/>
+        <v>4.4124999999999998E-3</v>
       </c>
       <c r="D37" s="7">
-        <f t="shared" ref="D37:D41" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",TRIMMEAN(O7:X7,2/COUNT(O7:X7)))</f>
-        <v>0.153225</v>
+        <f t="shared" si="1"/>
+        <v>0.10567500000000001</v>
       </c>
       <c r="E37" s="7">
-        <f t="shared" ref="E37:E41" si="2">IF(COUNTBLANK(C17:L17)&gt;0,"undone",TRIMMEAN(C17:L17,2/COUNT(C17:L17)))</f>
-        <v>0.63418750000000002</v>
+        <f t="shared" si="2"/>
+        <v>0.42470000000000008</v>
       </c>
       <c r="F37" s="7">
-        <f t="shared" ref="F37:F41" si="3">IF(COUNTBLANK(O17:X17)&gt;0,"undone",TRIMMEAN(O17:X17,2/COUNT(O17:X17)))</f>
-        <v>15.403874999999999</v>
+        <f t="shared" si="3"/>
+        <v>10.738949999999997</v>
       </c>
       <c r="G37" s="7">
-        <f t="shared" ref="G37:G41" si="4">IF(COUNTBLANK(C27:L27)&gt;0,"undone",TRIMMEAN(C27:L27,2/COUNT(C27:L27)))</f>
-        <v>61.6993875</v>
+        <f t="shared" si="4"/>
+        <v>42.800525</v>
       </c>
       <c r="H37" s="7">
-        <f t="shared" ref="H37:H41" si="5">IF(COUNTBLANK(O27:X27)&gt;0,"undone",TRIMMEAN(O27:X27,2/COUNT(O27:X27)))</f>
-        <v>1587.3118125000001</v>
+        <f t="shared" si="5"/>
+        <v>1070.4900749999999</v>
       </c>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
@@ -31798,27 +31903,27 @@
       </c>
       <c r="C38" s="7">
         <f t="shared" si="0"/>
-        <v>7.5374999999999999E-3</v>
+        <v>5.1124999999999999E-3</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="1"/>
-        <v>0.18411249999999998</v>
+        <v>0.12496250000000002</v>
       </c>
       <c r="E38" s="7">
         <f t="shared" si="2"/>
-        <v>0.75121250000000006</v>
+        <v>0.49884999999999996</v>
       </c>
       <c r="F38" s="7">
         <f t="shared" si="3"/>
-        <v>18.446875000000002</v>
+        <v>12.45715</v>
       </c>
       <c r="G38" s="7">
         <f t="shared" si="4"/>
-        <v>75.809237499999995</v>
+        <v>50.051387499999997</v>
       </c>
       <c r="H38" s="7">
         <f t="shared" si="5"/>
-        <v>1901.4957750000001</v>
+        <v>1248.5817875</v>
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
@@ -31827,27 +31932,27 @@
       </c>
       <c r="C39" s="7">
         <f t="shared" si="0"/>
-        <v>3.9375000000000009E-3</v>
+        <v>2.6750000000000003E-3</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="1"/>
-        <v>2.3862500000000002E-2</v>
+        <v>1.6037500000000003E-2</v>
       </c>
       <c r="E39" s="7">
         <f t="shared" si="2"/>
-        <v>5.15375E-2</v>
+        <v>3.6924999999999999E-2</v>
       </c>
       <c r="F39" s="7">
         <f t="shared" si="3"/>
-        <v>0.30283749999999998</v>
+        <v>0.20457499999999998</v>
       </c>
       <c r="G39" s="7">
         <f t="shared" si="4"/>
-        <v>0.64444999999999997</v>
+        <v>0.43671249999999995</v>
       </c>
       <c r="H39" s="7">
         <f t="shared" si="5"/>
-        <v>3.6792499999999997</v>
+        <v>2.4870749999999999</v>
       </c>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
@@ -31856,27 +31961,27 @@
       </c>
       <c r="C40" s="7">
         <f t="shared" si="0"/>
-        <v>6.2249999999999996E-3</v>
+        <v>4.3999999999999994E-3</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="1"/>
-        <v>0.1444125</v>
+        <v>9.3350000000000002E-2</v>
       </c>
       <c r="E40" s="7">
         <f t="shared" si="2"/>
-        <v>0.56381250000000005</v>
+        <v>0.38807499999999995</v>
       </c>
       <c r="F40" s="7">
         <f t="shared" si="3"/>
-        <v>13.799025</v>
+        <v>9.5362000000000009</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="4"/>
-        <v>55.014850000000003</v>
+        <v>38.011587500000005</v>
       </c>
       <c r="H40" s="7">
         <f t="shared" si="5"/>
-        <v>1390.3545124999998</v>
+        <v>945.68022500000006</v>
       </c>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
@@ -31885,39 +31990,44 @@
       </c>
       <c r="C41" s="7">
         <f t="shared" si="0"/>
-        <v>3.6750000000000003E-3</v>
+        <v>2.5374999999999998E-3</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="1"/>
-        <v>2.0125000000000001E-2</v>
+        <v>1.2412500000000003E-2</v>
       </c>
       <c r="E41" s="7">
         <f t="shared" si="2"/>
-        <v>4.4262499999999996E-2</v>
+        <v>2.9025000000000002E-2</v>
       </c>
       <c r="F41" s="7">
         <f t="shared" si="3"/>
-        <v>0.22641249999999996</v>
+        <v>0.15733749999999996</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="4"/>
-        <v>0.40345000000000003</v>
+        <v>0.37109999999999999</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="5"/>
-        <v>2.9468124999999996</v>
+        <v>2.7895749999999997</v>
       </c>
     </row>
     <row r="44" spans="2:17" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="10" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -31928,11 +32038,6 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -31946,19 +32051,19 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="1"/>
-    <col min="2" max="2" width="20.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="12" width="9.69921875" style="1" customWidth="1"/>
     <col min="13" max="13" width="8.796875" style="1"/>
-    <col min="14" max="14" width="20.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="24" width="9.69921875" style="1" customWidth="1"/>
     <col min="25" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="17"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -31977,39 +32082,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="14"/>
-      <c r="N4" s="10" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="15"/>
+      <c r="N4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="15"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="11"/>
+      <c r="B5" s="12"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -32040,7 +32145,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="11"/>
+      <c r="N5" s="12"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -32077,67 +32182,67 @@
         <v>16</v>
       </c>
       <c r="C6" s="7">
-        <v>1.0699999999999999E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="D6" s="7">
-        <v>1.0200000000000001E-2</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="E6" s="7">
-        <v>9.9000000000000008E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="F6" s="7">
-        <v>9.7999999999999997E-3</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="G6" s="7">
-        <v>9.7999999999999997E-3</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="H6" s="7">
-        <v>9.7999999999999997E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I6" s="7">
-        <v>9.7999999999999997E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="J6" s="7">
-        <v>9.7999999999999997E-3</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="K6" s="7">
-        <v>9.7999999999999997E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="L6" s="7">
-        <v>9.7999999999999997E-3</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O6" s="7">
-        <v>0.25900000000000001</v>
+        <v>0.17480000000000001</v>
       </c>
       <c r="P6" s="7">
-        <v>0.2727</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="Q6" s="7">
-        <v>0.27539999999999998</v>
+        <v>0.17130000000000001</v>
       </c>
       <c r="R6" s="7">
-        <v>0.25779999999999997</v>
+        <v>0.17130000000000001</v>
       </c>
       <c r="S6" s="7">
-        <v>0.24940000000000001</v>
+        <v>0.1714</v>
       </c>
       <c r="T6" s="7">
-        <v>0.24929999999999999</v>
+        <v>0.17130000000000001</v>
       </c>
       <c r="U6" s="7">
-        <v>0.25900000000000001</v>
+        <v>0.1714</v>
       </c>
       <c r="V6" s="7">
-        <v>0.24909999999999999</v>
+        <v>0.1769</v>
       </c>
       <c r="W6" s="7">
-        <v>0.2492</v>
+        <v>0.17150000000000001</v>
       </c>
       <c r="X6" s="7">
-        <v>0.25090000000000001</v>
+        <v>0.1716</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -32145,67 +32250,67 @@
         <v>17</v>
       </c>
       <c r="C7" s="7">
-        <v>8.6E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D7" s="7">
-        <v>8.5000000000000006E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="E7" s="7">
-        <v>8.0000000000000002E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="F7" s="7">
-        <v>7.4000000000000003E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="G7" s="7">
-        <v>7.4000000000000003E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="H7" s="7">
-        <v>7.1999999999999998E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="I7" s="7">
-        <v>7.1999999999999998E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="J7" s="7">
-        <v>7.1999999999999998E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="K7" s="7">
-        <v>7.1999999999999998E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="L7" s="7">
-        <v>7.1999999999999998E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O7" s="7">
-        <v>0.1842</v>
+        <v>0.13009999999999999</v>
       </c>
       <c r="P7" s="7">
-        <v>0.1845</v>
+        <v>0.13009999999999999</v>
       </c>
       <c r="Q7" s="7">
-        <v>0.18440000000000001</v>
+        <v>0.1343</v>
       </c>
       <c r="R7" s="7">
-        <v>0.1842</v>
+        <v>0.12920000000000001</v>
       </c>
       <c r="S7" s="7">
-        <v>0.18390000000000001</v>
+        <v>0.17019999999999999</v>
       </c>
       <c r="T7" s="7">
-        <v>0.18820000000000001</v>
+        <v>0.13020000000000001</v>
       </c>
       <c r="U7" s="7">
-        <v>0.1842</v>
+        <v>0.1138</v>
       </c>
       <c r="V7" s="7">
-        <v>0.18440000000000001</v>
+        <v>0.1133</v>
       </c>
       <c r="W7" s="7">
-        <v>0.21360000000000001</v>
+        <v>0.1132</v>
       </c>
       <c r="X7" s="7">
-        <v>0.184</v>
+        <v>0.1133</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -32213,67 +32318,67 @@
         <v>18</v>
       </c>
       <c r="C8" s="7">
-        <v>1.6E-2</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="D8" s="7">
-        <v>2.2599999999999999E-2</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="E8" s="7">
-        <v>1.6400000000000001E-2</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="F8" s="7">
-        <v>1.6500000000000001E-2</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="G8" s="7">
-        <v>1.6500000000000001E-2</v>
+        <v>1.09E-2</v>
       </c>
       <c r="H8" s="7">
-        <v>1.6500000000000001E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="I8" s="7">
-        <v>1.66E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="J8" s="7">
-        <v>1.6500000000000001E-2</v>
+        <v>1.09E-2</v>
       </c>
       <c r="K8" s="7">
-        <v>1.66E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="L8" s="7">
-        <v>1.66E-2</v>
+        <v>1.09E-2</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O8" s="7">
-        <v>0.38940000000000002</v>
+        <v>0.25890000000000002</v>
       </c>
       <c r="P8" s="7">
-        <v>0.38950000000000001</v>
+        <v>0.2656</v>
       </c>
       <c r="Q8" s="7">
-        <v>0.38950000000000001</v>
+        <v>0.25829999999999997</v>
       </c>
       <c r="R8" s="7">
-        <v>0.3947</v>
+        <v>0.25369999999999998</v>
       </c>
       <c r="S8" s="7">
-        <v>0.38990000000000002</v>
+        <v>0.25729999999999997</v>
       </c>
       <c r="T8" s="7">
-        <v>0.39</v>
+        <v>0.27939999999999998</v>
       </c>
       <c r="U8" s="7">
-        <v>0.38890000000000002</v>
+        <v>0.25519999999999998</v>
       </c>
       <c r="V8" s="7">
-        <v>0.3891</v>
+        <v>0.25509999999999999</v>
       </c>
       <c r="W8" s="7">
-        <v>0.39319999999999999</v>
+        <v>0.2646</v>
       </c>
       <c r="X8" s="7">
-        <v>0.38950000000000001</v>
+        <v>0.25950000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -32281,67 +32386,67 @@
         <v>19</v>
       </c>
       <c r="C9" s="7">
-        <v>5.1000000000000004E-3</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="D9" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="E9" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="F9" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G9" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="H9" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="I9" s="7">
-        <v>4.0000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="J9" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="K9" s="7">
-        <v>4.0000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="L9" s="7">
-        <v>3.8E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O9" s="7">
-        <v>2.4500000000000001E-2</v>
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="P9" s="7">
-        <v>2.3800000000000002E-2</v>
+        <v>1.67E-2</v>
       </c>
       <c r="Q9" s="7">
-        <v>2.3699999999999999E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="R9" s="7">
-        <v>2.3699999999999999E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="S9" s="7">
-        <v>2.3800000000000002E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="T9" s="7">
-        <v>2.3800000000000002E-2</v>
+        <v>1.67E-2</v>
       </c>
       <c r="U9" s="7">
-        <v>2.3900000000000001E-2</v>
+        <v>1.67E-2</v>
       </c>
       <c r="V9" s="7">
-        <v>2.3800000000000002E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="W9" s="7">
-        <v>2.3900000000000001E-2</v>
+        <v>6.6600000000000006E-2</v>
       </c>
       <c r="X9" s="7">
-        <v>2.3800000000000002E-2</v>
+        <v>1.67E-2</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -32349,67 +32454,67 @@
         <v>20</v>
       </c>
       <c r="C10" s="7">
-        <v>7.1999999999999998E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="D10" s="7">
-        <v>6.6E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="E10" s="7">
-        <v>5.7999999999999996E-3</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="F10" s="7">
-        <v>5.7000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="G10" s="7">
-        <v>5.7999999999999996E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="H10" s="7">
-        <v>5.7000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="I10" s="7">
-        <v>5.7000000000000002E-3</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="J10" s="7">
-        <v>5.7999999999999996E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="K10" s="7">
-        <v>5.7000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="L10" s="7">
-        <v>5.7000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O10" s="7">
-        <v>0.14419999999999999</v>
+        <v>0.1017</v>
       </c>
       <c r="P10" s="7">
-        <v>0.14249999999999999</v>
+        <v>0.1019</v>
       </c>
       <c r="Q10" s="7">
-        <v>0.14219999999999999</v>
+        <v>0.1011</v>
       </c>
       <c r="R10" s="7">
-        <v>0.1421</v>
+        <v>0.1012</v>
       </c>
       <c r="S10" s="7">
-        <v>0.1421</v>
+        <v>0.10390000000000001</v>
       </c>
       <c r="T10" s="7">
-        <v>0.14199999999999999</v>
+        <v>0.1013</v>
       </c>
       <c r="U10" s="7">
-        <v>0.14729999999999999</v>
+        <v>0.1012</v>
       </c>
       <c r="V10" s="7">
-        <v>0.14829999999999999</v>
+        <v>0.1012</v>
       </c>
       <c r="W10" s="7">
-        <v>0.14199999999999999</v>
+        <v>0.1012</v>
       </c>
       <c r="X10" s="7">
-        <v>0.1421</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -32417,67 +32522,67 @@
         <v>21</v>
       </c>
       <c r="C11" s="8">
-        <v>4.4999999999999997E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="D11" s="7">
-        <v>3.5000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E11" s="7">
-        <v>4.1999999999999997E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="F11" s="7">
-        <v>3.7000000000000002E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="G11" s="7">
-        <v>3.3999999999999998E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="H11" s="7">
-        <v>3.5999999999999999E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="I11" s="7">
-        <v>3.3999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="J11" s="7">
-        <v>4.1999999999999997E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="K11" s="7">
-        <v>6.1000000000000004E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="L11" s="7">
-        <v>5.4999999999999997E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O11" s="8">
-        <v>2.5600000000000001E-2</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="P11" s="7">
-        <v>2.23E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="Q11" s="7">
-        <v>2.1399999999999999E-2</v>
+        <v>1.49E-2</v>
       </c>
       <c r="R11" s="7">
-        <v>2.1100000000000001E-2</v>
+        <v>1.3899999999999999E-2</v>
       </c>
       <c r="S11" s="7">
-        <v>2.0899999999999998E-2</v>
+        <v>1.3299999999999999E-2</v>
       </c>
       <c r="T11" s="7">
-        <v>2.0500000000000001E-2</v>
+        <v>1.29E-2</v>
       </c>
       <c r="U11" s="7">
-        <v>0.02</v>
+        <v>1.32E-2</v>
       </c>
       <c r="V11" s="7">
-        <v>2.0400000000000001E-2</v>
+        <v>1.29E-2</v>
       </c>
       <c r="W11" s="7">
-        <v>2.0799999999999999E-2</v>
+        <v>1.29E-2</v>
       </c>
       <c r="X11" s="7">
-        <v>2.1000000000000001E-2</v>
+        <v>1.3100000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -32497,39 +32602,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="14"/>
-      <c r="N14" s="10" t="s">
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="15"/>
+      <c r="N14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="O14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="15"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="11"/>
+      <c r="B15" s="12"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -32560,7 +32665,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="11"/>
+      <c r="N15" s="12"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -32597,67 +32702,67 @@
         <v>16</v>
       </c>
       <c r="C16" s="7">
-        <v>1.0750999999999999</v>
+        <v>0.68989999999999996</v>
       </c>
       <c r="D16" s="7">
-        <v>0.99370000000000003</v>
+        <v>0.68389999999999995</v>
       </c>
       <c r="E16" s="7">
-        <v>0.97160000000000002</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="F16" s="7">
-        <v>0.98199999999999998</v>
+        <v>0.6845</v>
       </c>
       <c r="G16" s="7">
-        <v>0.9718</v>
+        <v>0.68820000000000003</v>
       </c>
       <c r="H16" s="7">
-        <v>0.97619999999999996</v>
+        <v>0.68110000000000004</v>
       </c>
       <c r="I16" s="7">
-        <v>0.97540000000000004</v>
+        <v>0.69020000000000004</v>
       </c>
       <c r="J16" s="7">
-        <v>0.9829</v>
+        <v>0.68640000000000001</v>
       </c>
       <c r="K16" s="7">
-        <v>0.97019999999999995</v>
+        <v>0.68100000000000005</v>
       </c>
       <c r="L16" s="7">
-        <v>0.99550000000000005</v>
+        <v>0.68920000000000003</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O16" s="7">
-        <v>24.840299999999999</v>
+        <v>16.920300000000001</v>
       </c>
       <c r="P16" s="7">
-        <v>24.508500000000002</v>
+        <v>17.025300000000001</v>
       </c>
       <c r="Q16" s="7">
-        <v>24.6541</v>
+        <v>16.694500000000001</v>
       </c>
       <c r="R16" s="7">
-        <v>24.295100000000001</v>
+        <v>17.04</v>
       </c>
       <c r="S16" s="7">
-        <v>24.7681</v>
+        <v>16.639399999999998</v>
       </c>
       <c r="T16" s="7">
-        <v>24.515899999999998</v>
+        <v>16.909400000000002</v>
       </c>
       <c r="U16" s="7">
-        <v>23.835899999999999</v>
+        <v>16.9025</v>
       </c>
       <c r="V16" s="7">
-        <v>24.336400000000001</v>
+        <v>17.027799999999999</v>
       </c>
       <c r="W16" s="7">
-        <v>24.5289</v>
+        <v>16.7257</v>
       </c>
       <c r="X16" s="7">
-        <v>23.666699999999999</v>
+        <v>17.191099999999999</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
@@ -32665,67 +32770,67 @@
         <v>17</v>
       </c>
       <c r="C17" s="7">
-        <v>0.72299999999999998</v>
+        <v>0.51280000000000003</v>
       </c>
       <c r="D17" s="7">
-        <v>0.72360000000000002</v>
+        <v>0.44080000000000003</v>
       </c>
       <c r="E17" s="7">
-        <v>0.72740000000000005</v>
+        <v>0.45329999999999998</v>
       </c>
       <c r="F17" s="7">
-        <v>0.72340000000000004</v>
+        <v>0.50149999999999995</v>
       </c>
       <c r="G17" s="7">
-        <v>0.72340000000000004</v>
+        <v>0.50480000000000003</v>
       </c>
       <c r="H17" s="7">
-        <v>0.72629999999999995</v>
+        <v>0.44629999999999997</v>
       </c>
       <c r="I17" s="7">
-        <v>0.72270000000000001</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="J17" s="7">
-        <v>0.89949999999999997</v>
+        <v>0.44579999999999997</v>
       </c>
       <c r="K17" s="7">
-        <v>0.76639999999999997</v>
+        <v>0.44740000000000002</v>
       </c>
       <c r="L17" s="7">
-        <v>0.74050000000000005</v>
+        <v>0.68979999999999997</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O17" s="7">
-        <v>16.858899999999998</v>
+        <v>11.850199999999999</v>
       </c>
       <c r="P17" s="7">
-        <v>17.928100000000001</v>
+        <v>12.0915</v>
       </c>
       <c r="Q17" s="7">
-        <v>17.011800000000001</v>
+        <v>12.497400000000001</v>
       </c>
       <c r="R17" s="7">
-        <v>17.098800000000001</v>
+        <v>12.0062</v>
       </c>
       <c r="S17" s="7">
-        <v>17.081399999999999</v>
+        <v>11.7148</v>
       </c>
       <c r="T17" s="7">
-        <v>17.333300000000001</v>
+        <v>11.9001</v>
       </c>
       <c r="U17" s="7">
-        <v>17.135999999999999</v>
+        <v>11.708299999999999</v>
       </c>
       <c r="V17" s="7">
-        <v>17.391500000000001</v>
+        <v>11.889099999999999</v>
       </c>
       <c r="W17" s="7">
-        <v>17.0106</v>
+        <v>11.9368</v>
       </c>
       <c r="X17" s="7">
-        <v>17.516500000000001</v>
+        <v>12.292899999999999</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
@@ -32733,67 +32838,67 @@
         <v>18</v>
       </c>
       <c r="C18" s="7">
-        <v>1.5733999999999999</v>
+        <v>1.2501</v>
       </c>
       <c r="D18" s="7">
-        <v>1.6429</v>
+        <v>1.0087999999999999</v>
       </c>
       <c r="E18" s="7">
-        <v>1.5697000000000001</v>
+        <v>0.9899</v>
       </c>
       <c r="F18" s="7">
-        <v>1.5553999999999999</v>
+        <v>0.98770000000000002</v>
       </c>
       <c r="G18" s="7">
-        <v>1.5952</v>
+        <v>0.98450000000000004</v>
       </c>
       <c r="H18" s="7">
-        <v>1.5569</v>
+        <v>1.0074000000000001</v>
       </c>
       <c r="I18" s="7">
-        <v>1.5528</v>
+        <v>1.0205</v>
       </c>
       <c r="J18" s="7">
-        <v>1.5565</v>
+        <v>0.99329999999999996</v>
       </c>
       <c r="K18" s="7">
-        <v>1.6240000000000001</v>
+        <v>0.998</v>
       </c>
       <c r="L18" s="7">
-        <v>1.5831999999999999</v>
+        <v>0.99639999999999995</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O18" s="7">
-        <v>39.5075</v>
+        <v>25.4651</v>
       </c>
       <c r="P18" s="7">
-        <v>39.857100000000003</v>
+        <v>25.5458</v>
       </c>
       <c r="Q18" s="7">
-        <v>39.328400000000002</v>
+        <v>25.408899999999999</v>
       </c>
       <c r="R18" s="7">
-        <v>41.061</v>
+        <v>25.216699999999999</v>
       </c>
       <c r="S18" s="7">
-        <v>39.5852</v>
+        <v>25.8779</v>
       </c>
       <c r="T18" s="7">
-        <v>39.423699999999997</v>
+        <v>25.418399999999998</v>
       </c>
       <c r="U18" s="7">
-        <v>38.983600000000003</v>
+        <v>25.435600000000001</v>
       </c>
       <c r="V18" s="7">
-        <v>38.880800000000001</v>
+        <v>25.497800000000002</v>
       </c>
       <c r="W18" s="7">
-        <v>39.415199999999999</v>
+        <v>25.334399999999999</v>
       </c>
       <c r="X18" s="7">
-        <v>39.238599999999998</v>
+        <v>25.971399999999999</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
@@ -32801,67 +32906,67 @@
         <v>19</v>
       </c>
       <c r="C19" s="7">
-        <v>5.16E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="D19" s="7">
-        <v>5.1400000000000001E-2</v>
+        <v>3.5099999999999999E-2</v>
       </c>
       <c r="E19" s="7">
-        <v>5.1299999999999998E-2</v>
+        <v>3.5200000000000002E-2</v>
       </c>
       <c r="F19" s="7">
-        <v>5.1200000000000002E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G19" s="7">
-        <v>5.11E-2</v>
+        <v>3.5200000000000002E-2</v>
       </c>
       <c r="H19" s="7">
-        <v>5.11E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="I19" s="7">
-        <v>5.1499999999999997E-2</v>
+        <v>3.5099999999999999E-2</v>
       </c>
       <c r="J19" s="7">
-        <v>5.1200000000000002E-2</v>
+        <v>3.5200000000000002E-2</v>
       </c>
       <c r="K19" s="7">
-        <v>5.1200000000000002E-2</v>
+        <v>3.5099999999999999E-2</v>
       </c>
       <c r="L19" s="7">
-        <v>5.1200000000000002E-2</v>
+        <v>3.5099999999999999E-2</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O19" s="7">
-        <v>0.30109999999999998</v>
+        <v>0.214</v>
       </c>
       <c r="P19" s="7">
-        <v>0.29920000000000002</v>
+        <v>0.2112</v>
       </c>
       <c r="Q19" s="7">
-        <v>0.2984</v>
+        <v>0.21329999999999999</v>
       </c>
       <c r="R19" s="7">
-        <v>0.29849999999999999</v>
+        <v>0.21160000000000001</v>
       </c>
       <c r="S19" s="7">
-        <v>0.30580000000000002</v>
+        <v>0.21540000000000001</v>
       </c>
       <c r="T19" s="7">
-        <v>0.3029</v>
+        <v>0.21029999999999999</v>
       </c>
       <c r="U19" s="7">
-        <v>0.30320000000000003</v>
+        <v>0.2102</v>
       </c>
       <c r="V19" s="7">
-        <v>0.3034</v>
+        <v>0.22789999999999999</v>
       </c>
       <c r="W19" s="7">
-        <v>0.30259999999999998</v>
+        <v>0.2102</v>
       </c>
       <c r="X19" s="7">
-        <v>0.30359999999999998</v>
+        <v>0.21029999999999999</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.25">
@@ -32869,67 +32974,67 @@
         <v>20</v>
       </c>
       <c r="C20" s="7">
-        <v>0.5645</v>
+        <v>0.38969999999999999</v>
       </c>
       <c r="D20" s="7">
-        <v>0.55740000000000001</v>
+        <v>0.38840000000000002</v>
       </c>
       <c r="E20" s="7">
-        <v>0.55689999999999995</v>
+        <v>0.38450000000000001</v>
       </c>
       <c r="F20" s="7">
-        <v>0.55730000000000002</v>
+        <v>0.3876</v>
       </c>
       <c r="G20" s="7">
-        <v>0.59730000000000005</v>
+        <v>0.38369999999999999</v>
       </c>
       <c r="H20" s="7">
-        <v>0.5575</v>
+        <v>0.38540000000000002</v>
       </c>
       <c r="I20" s="7">
-        <v>0.55720000000000003</v>
+        <v>0.38390000000000002</v>
       </c>
       <c r="J20" s="7">
-        <v>0.56169999999999998</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="K20" s="7">
-        <v>0.5575</v>
+        <v>0.38379999999999997</v>
       </c>
       <c r="L20" s="7">
-        <v>0.57669999999999999</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O20" s="7">
-        <v>13.8203</v>
+        <v>9.5238999999999994</v>
       </c>
       <c r="P20" s="7">
-        <v>13.972</v>
+        <v>9.5929000000000002</v>
       </c>
       <c r="Q20" s="7">
-        <v>13.481999999999999</v>
+        <v>9.6265000000000001</v>
       </c>
       <c r="R20" s="7">
-        <v>13.954800000000001</v>
+        <v>9.5663</v>
       </c>
       <c r="S20" s="7">
-        <v>13.725099999999999</v>
+        <v>9.6060999999999996</v>
       </c>
       <c r="T20" s="7">
-        <v>13.9758</v>
+        <v>9.9222000000000001</v>
       </c>
       <c r="U20" s="7">
-        <v>13.8742</v>
+        <v>9.5063999999999993</v>
       </c>
       <c r="V20" s="7">
-        <v>13.9161</v>
+        <v>9.7729999999999997</v>
       </c>
       <c r="W20" s="7">
-        <v>13.9131</v>
+        <v>9.3637999999999995</v>
       </c>
       <c r="X20" s="7">
-        <v>13.7484</v>
+        <v>9.4422999999999995</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
@@ -32937,67 +33042,67 @@
         <v>21</v>
       </c>
       <c r="C21" s="8">
-        <v>4.8099999999999997E-2</v>
+        <v>3.2399999999999998E-2</v>
       </c>
       <c r="D21" s="7">
-        <v>4.2999999999999997E-2</v>
+        <v>2.8899999999999999E-2</v>
       </c>
       <c r="E21" s="7">
-        <v>4.4900000000000002E-2</v>
+        <v>2.7400000000000001E-2</v>
       </c>
       <c r="F21" s="7">
-        <v>4.2500000000000003E-2</v>
+        <v>3.1800000000000002E-2</v>
       </c>
       <c r="G21" s="7">
-        <v>4.2000000000000003E-2</v>
+        <v>2.9600000000000001E-2</v>
       </c>
       <c r="H21" s="7">
-        <v>4.4499999999999998E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="I21" s="7">
-        <v>4.3999999999999997E-2</v>
+        <v>2.7799999999999998E-2</v>
       </c>
       <c r="J21" s="7">
-        <v>4.2599999999999999E-2</v>
+        <v>2.76E-2</v>
       </c>
       <c r="K21" s="7">
-        <v>4.2200000000000001E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="L21" s="7">
-        <v>4.19E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O21" s="8">
-        <v>0.26519999999999999</v>
+        <v>2.1086999999999998</v>
       </c>
       <c r="P21" s="7">
-        <v>0.25779999999999997</v>
+        <v>2.2776000000000001</v>
       </c>
       <c r="Q21" s="7">
-        <v>0.36549999999999999</v>
+        <v>2.1141999999999999</v>
       </c>
       <c r="R21" s="7">
-        <v>0.33410000000000001</v>
+        <v>2.1067</v>
       </c>
       <c r="S21" s="7">
-        <v>0.25269999999999998</v>
+        <v>2.0512999999999999</v>
       </c>
       <c r="T21" s="7">
-        <v>0.2717</v>
+        <v>2.0969000000000002</v>
       </c>
       <c r="U21" s="7">
-        <v>0.26079999999999998</v>
+        <v>2.1240000000000001</v>
       </c>
       <c r="V21" s="7">
-        <v>0.27939999999999998</v>
+        <v>2.1334</v>
       </c>
       <c r="W21" s="7">
-        <v>0.26889999999999997</v>
+        <v>2.1204999999999998</v>
       </c>
       <c r="X21" s="7">
-        <v>0.2616</v>
+        <v>2.1145999999999998</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
@@ -33017,39 +33122,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="14"/>
-      <c r="N24" s="10" t="s">
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="15"/>
+      <c r="N24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="12" t="s">
+      <c r="O24" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="13"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
-      <c r="U24" s="13"/>
-      <c r="V24" s="13"/>
-      <c r="W24" s="13"/>
-      <c r="X24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="15"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="11"/>
+      <c r="B25" s="12"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -33080,7 +33185,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="11"/>
+      <c r="N25" s="12"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -33117,67 +33222,67 @@
         <v>16</v>
       </c>
       <c r="C26" s="7">
-        <v>97.5488</v>
+        <v>67.531700000000001</v>
       </c>
       <c r="D26" s="7">
-        <v>98.369799999999998</v>
+        <v>68.365600000000001</v>
       </c>
       <c r="E26" s="7">
-        <v>99.552800000000005</v>
+        <v>68.717500000000001</v>
       </c>
       <c r="F26" s="7">
-        <v>99.213399999999993</v>
+        <v>68.486199999999997</v>
       </c>
       <c r="G26" s="7">
-        <v>98.655199999999994</v>
+        <v>67.471100000000007</v>
       </c>
       <c r="H26" s="7">
-        <v>99.038399999999996</v>
+        <v>67.694800000000001</v>
       </c>
       <c r="I26" s="7">
-        <v>97.869500000000002</v>
+        <v>68.088999999999999</v>
       </c>
       <c r="J26" s="7">
-        <v>106.6422</v>
+        <v>67.8489</v>
       </c>
       <c r="K26" s="7">
-        <v>106.8325</v>
+        <v>67.704300000000003</v>
       </c>
       <c r="L26" s="7">
-        <v>97.520399999999995</v>
+        <v>67.257900000000006</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O26" s="7">
-        <v>2541.7563</v>
+        <v>1704.355</v>
       </c>
       <c r="P26" s="7">
-        <v>2439.4488000000001</v>
+        <v>1706.5268000000001</v>
       </c>
       <c r="Q26" s="7">
-        <v>2473.8420999999998</v>
+        <v>1697.0744</v>
       </c>
       <c r="R26" s="7">
-        <v>2467.9744999999998</v>
+        <v>1696.6005</v>
       </c>
       <c r="S26" s="7">
-        <v>2440.3240000000001</v>
+        <v>1698.7782999999999</v>
       </c>
       <c r="T26" s="7">
-        <v>2480.4919</v>
+        <v>1697.3117999999999</v>
       </c>
       <c r="U26" s="7">
-        <v>2534.1064000000001</v>
+        <v>1705.2108000000001</v>
       </c>
       <c r="V26" s="7">
-        <v>2492.3797</v>
+        <v>1694.2313999999999</v>
       </c>
       <c r="W26" s="7">
-        <v>2451.6749</v>
+        <v>1702.827</v>
       </c>
       <c r="X26" s="7">
-        <v>2443.8258999999998</v>
+        <v>1692.5108</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
@@ -33185,67 +33290,67 @@
         <v>17</v>
       </c>
       <c r="C27" s="7">
-        <v>68.721800000000002</v>
+        <v>46.318600000000004</v>
       </c>
       <c r="D27" s="7">
-        <v>70.764300000000006</v>
+        <v>49.363599999999998</v>
       </c>
       <c r="E27" s="7">
-        <v>69.231700000000004</v>
+        <v>49.122199999999999</v>
       </c>
       <c r="F27" s="7">
-        <v>69.771900000000002</v>
+        <v>48.263599999999997</v>
       </c>
       <c r="G27" s="7">
-        <v>68.707700000000003</v>
+        <v>46.6447</v>
       </c>
       <c r="H27" s="7">
-        <v>70.793000000000006</v>
+        <v>47.982199999999999</v>
       </c>
       <c r="I27" s="7">
-        <v>70.539599999999993</v>
+        <v>49.3</v>
       </c>
       <c r="J27" s="7">
-        <v>69.965999999999994</v>
+        <v>48.601500000000001</v>
       </c>
       <c r="K27" s="7">
-        <v>68.951700000000002</v>
+        <v>48.712000000000003</v>
       </c>
       <c r="L27" s="7">
-        <v>68.124499999999998</v>
+        <v>48.437600000000003</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O27" s="7">
-        <v>1706.2204999999999</v>
+        <v>1212.8842</v>
       </c>
       <c r="P27" s="7">
-        <v>1722.7882</v>
+        <v>1220.2150999999999</v>
       </c>
       <c r="Q27" s="7">
-        <v>1716.2449999999999</v>
+        <v>1207.1577</v>
       </c>
       <c r="R27" s="7">
-        <v>1735.9366</v>
+        <v>1206.5849000000001</v>
       </c>
       <c r="S27" s="7">
-        <v>1808.3788999999999</v>
+        <v>1205.1511</v>
       </c>
       <c r="T27" s="7">
-        <v>1739.9007999999999</v>
+        <v>1210.357</v>
       </c>
       <c r="U27" s="7">
-        <v>1779.6002000000001</v>
+        <v>1216.5509</v>
       </c>
       <c r="V27" s="7">
-        <v>1821.173</v>
+        <v>1214.7883999999999</v>
       </c>
       <c r="W27" s="7">
-        <v>1775.1714999999999</v>
+        <v>1211.2609</v>
       </c>
       <c r="X27" s="7">
-        <v>1737.0802000000001</v>
+        <v>1211.2910999999999</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
@@ -33253,67 +33358,67 @@
         <v>18</v>
       </c>
       <c r="C28" s="7">
-        <v>155.63669999999999</v>
+        <v>101.9512</v>
       </c>
       <c r="D28" s="7">
-        <v>158.48089999999999</v>
+        <v>101.96720000000001</v>
       </c>
       <c r="E28" s="7">
-        <v>158.53970000000001</v>
+        <v>102.4148</v>
       </c>
       <c r="F28" s="7">
-        <v>156.80080000000001</v>
+        <v>102.0264</v>
       </c>
       <c r="G28" s="7">
-        <v>156.71109999999999</v>
+        <v>101.7398</v>
       </c>
       <c r="H28" s="7">
-        <v>156.67519999999999</v>
+        <v>102.89409999999999</v>
       </c>
       <c r="I28" s="7">
-        <v>156.8115</v>
+        <v>101.6403</v>
       </c>
       <c r="J28" s="7">
-        <v>155.8948</v>
+        <v>101.6966</v>
       </c>
       <c r="K28" s="7">
-        <v>157.71350000000001</v>
+        <v>102.2206</v>
       </c>
       <c r="L28" s="7">
-        <v>173.56290000000001</v>
+        <v>101.6915</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O28" s="7">
-        <v>3981.8562999999999</v>
+        <v>2568.9774000000002</v>
       </c>
       <c r="P28" s="7">
-        <v>4099.4161999999997</v>
+        <v>2557.8825000000002</v>
       </c>
       <c r="Q28" s="7">
-        <v>4157.1232</v>
+        <v>2558.6363999999999</v>
       </c>
       <c r="R28" s="7">
-        <v>3990.9665</v>
+        <v>2552.7147</v>
       </c>
       <c r="S28" s="7">
-        <v>3977.2503999999999</v>
+        <v>2563.7993999999999</v>
       </c>
       <c r="T28" s="7">
-        <v>4131.8361999999997</v>
+        <v>2558.0715</v>
       </c>
       <c r="U28" s="7">
-        <v>3977.6208999999999</v>
+        <v>2558.2168000000001</v>
       </c>
       <c r="V28" s="7">
-        <v>4035.7348000000002</v>
+        <v>2562.7926000000002</v>
       </c>
       <c r="W28" s="7">
-        <v>4038.6617000000001</v>
+        <v>2557.5095000000001</v>
       </c>
       <c r="X28" s="7">
-        <v>4191.5901000000003</v>
+        <v>2554.0119</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.25">
@@ -33321,67 +33426,67 @@
         <v>19</v>
       </c>
       <c r="C29" s="7">
-        <v>0.69189999999999996</v>
+        <v>0.4456</v>
       </c>
       <c r="D29" s="7">
-        <v>0.64080000000000004</v>
+        <v>0.44919999999999999</v>
       </c>
       <c r="E29" s="7">
-        <v>0.6361</v>
+        <v>0.43980000000000002</v>
       </c>
       <c r="F29" s="7">
-        <v>0.64139999999999997</v>
+        <v>0.47370000000000001</v>
       </c>
       <c r="G29" s="7">
-        <v>0.66100000000000003</v>
+        <v>0.43969999999999998</v>
       </c>
       <c r="H29" s="7">
-        <v>0.63470000000000004</v>
+        <v>0.44790000000000002</v>
       </c>
       <c r="I29" s="7">
-        <v>0.70350000000000001</v>
+        <v>0.44019999999999998</v>
       </c>
       <c r="J29" s="7">
-        <v>0.67949999999999999</v>
+        <v>0.44450000000000001</v>
       </c>
       <c r="K29" s="7">
-        <v>0.6794</v>
+        <v>0.43969999999999998</v>
       </c>
       <c r="L29" s="7">
-        <v>0.6794</v>
+        <v>0.443</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O29" s="7">
-        <v>3.7126999999999999</v>
+        <v>2.6747999999999998</v>
       </c>
       <c r="P29" s="7">
-        <v>3.8384</v>
+        <v>2.5108999999999999</v>
       </c>
       <c r="Q29" s="7">
-        <v>3.323</v>
+        <v>2.4885000000000002</v>
       </c>
       <c r="R29" s="7">
-        <v>3.7961999999999998</v>
+        <v>2.4946000000000002</v>
       </c>
       <c r="S29" s="7">
-        <v>3.7214</v>
+        <v>2.4944000000000002</v>
       </c>
       <c r="T29" s="7">
-        <v>3.6259000000000001</v>
+        <v>2.5190000000000001</v>
       </c>
       <c r="U29" s="7">
-        <v>3.9177</v>
+        <v>2.5017</v>
       </c>
       <c r="V29" s="7">
-        <v>3.6977000000000002</v>
+        <v>2.5183</v>
       </c>
       <c r="W29" s="7">
-        <v>3.7311999999999999</v>
+        <v>2.5156999999999998</v>
       </c>
       <c r="X29" s="7">
-        <v>3.9571999999999998</v>
+        <v>2.5139</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.25">
@@ -33389,67 +33494,67 @@
         <v>20</v>
       </c>
       <c r="C30" s="7">
-        <v>55.2896</v>
+        <v>37.799500000000002</v>
       </c>
       <c r="D30" s="7">
-        <v>55.613799999999998</v>
+        <v>38.145299999999999</v>
       </c>
       <c r="E30" s="7">
-        <v>55.098100000000002</v>
+        <v>37.7181</v>
       </c>
       <c r="F30" s="7">
-        <v>56.133600000000001</v>
+        <v>38.5563</v>
       </c>
       <c r="G30" s="7">
-        <v>54.2136</v>
+        <v>37.9253</v>
       </c>
       <c r="H30" s="7">
-        <v>53.503</v>
+        <v>37.891500000000001</v>
       </c>
       <c r="I30" s="7">
-        <v>54.895299999999999</v>
+        <v>38.280500000000004</v>
       </c>
       <c r="J30" s="7">
-        <v>55.783099999999997</v>
+        <v>37.790300000000002</v>
       </c>
       <c r="K30" s="7">
-        <v>54.336799999999997</v>
+        <v>37.927599999999998</v>
       </c>
       <c r="L30" s="7">
-        <v>57.464700000000001</v>
+        <v>38.103999999999999</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O30" s="7">
-        <v>1364.704</v>
+        <v>943.43960000000004</v>
       </c>
       <c r="P30" s="7">
-        <v>1377.2192</v>
+        <v>939.11509999999998</v>
       </c>
       <c r="Q30" s="7">
-        <v>1443.9293</v>
+        <v>942.70849999999996</v>
       </c>
       <c r="R30" s="7">
-        <v>1437.0853999999999</v>
+        <v>938.6848</v>
       </c>
       <c r="S30" s="7">
-        <v>1355.6685</v>
+        <v>939.2251</v>
       </c>
       <c r="T30" s="7">
-        <v>1360.4951000000001</v>
+        <v>940.30679999999995</v>
       </c>
       <c r="U30" s="7">
-        <v>1347.2732000000001</v>
+        <v>941.39530000000002</v>
       </c>
       <c r="V30" s="7">
-        <v>1343.4028000000001</v>
+        <v>943.50930000000005</v>
       </c>
       <c r="W30" s="7">
-        <v>1475.0553</v>
+        <v>947.02620000000002</v>
       </c>
       <c r="X30" s="7">
-        <v>1353.5811000000001</v>
+        <v>940.02210000000002</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
@@ -33457,111 +33562,111 @@
         <v>21</v>
       </c>
       <c r="C31" s="8">
-        <v>0.50380000000000003</v>
+        <v>18.523099999999999</v>
       </c>
       <c r="D31" s="7">
-        <v>0.56520000000000004</v>
+        <v>18.729099999999999</v>
       </c>
       <c r="E31" s="7">
-        <v>0.5272</v>
+        <v>19.262899999999998</v>
       </c>
       <c r="F31" s="7">
-        <v>0.51649999999999996</v>
+        <v>19.386299999999999</v>
       </c>
       <c r="G31" s="7">
-        <v>0.64090000000000003</v>
+        <v>19.2669</v>
       </c>
       <c r="H31" s="7">
-        <v>0.49530000000000002</v>
+        <v>18.703700000000001</v>
       </c>
       <c r="I31" s="7">
-        <v>0.48920000000000002</v>
+        <v>18.654499999999999</v>
       </c>
       <c r="J31" s="7">
-        <v>0.54569999999999996</v>
+        <v>18.894100000000002</v>
       </c>
       <c r="K31" s="7">
-        <v>0.503</v>
+        <v>19.3001</v>
       </c>
       <c r="L31" s="7">
-        <v>0.49530000000000002</v>
+        <v>19.180599999999998</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O31" s="8">
-        <v>2.6644000000000001</v>
+        <v>714.22910000000002</v>
       </c>
       <c r="P31" s="7">
-        <v>2.6221999999999999</v>
+        <v>714.57740000000001</v>
       </c>
       <c r="Q31" s="7">
-        <v>2.6568999999999998</v>
+        <v>670.0172</v>
       </c>
       <c r="R31" s="7">
-        <v>2.7187000000000001</v>
+        <v>722.71590000000003</v>
       </c>
       <c r="S31" s="7">
-        <v>2.7444000000000002</v>
+        <v>715.40890000000002</v>
       </c>
       <c r="T31" s="7">
-        <v>2.6414</v>
+        <v>662.06359999999995</v>
       </c>
       <c r="U31" s="7">
-        <v>2.6408999999999998</v>
+        <v>697.14430000000004</v>
       </c>
       <c r="V31" s="7">
-        <v>2.6421000000000001</v>
+        <v>714.52409999999998</v>
       </c>
       <c r="W31" s="7">
-        <v>2.6478999999999999</v>
+        <v>713.06240000000003</v>
       </c>
       <c r="X31" s="7">
-        <v>2.7151999999999998</v>
+        <v>715.01620000000003</v>
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="15"/>
       <c r="K34" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L34" s="1">
-        <f>Sorted!C35</f>
+        <f>[1]Sorted!C35</f>
         <v>100</v>
       </c>
       <c r="M34" s="1">
-        <f>Sorted!D35</f>
+        <f>[1]Sorted!D35</f>
         <v>500</v>
       </c>
       <c r="N34" s="1">
-        <f>Sorted!E35</f>
+        <f>[1]Sorted!E35</f>
         <v>1000</v>
       </c>
       <c r="O34" s="1">
-        <f>Sorted!F35</f>
+        <f>[1]Sorted!F35</f>
         <v>5000</v>
       </c>
       <c r="P34" s="1">
-        <f>Sorted!G35</f>
+        <f>[1]Sorted!G35</f>
         <v>10000</v>
       </c>
       <c r="Q34" s="1">
-        <f>Sorted!H35</f>
+        <f>[1]Sorted!H35</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="35" spans="2:17" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="B35" s="11"/>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B35" s="12"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -33581,30 +33686,30 @@
         <v>50000</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L35" s="1">
-        <f>Sorted!C35^2</f>
+        <f>[1]Sorted!C35^2</f>
         <v>10000</v>
       </c>
       <c r="M35" s="1">
-        <f>Sorted!D35^2</f>
+        <f>[1]Sorted!D35^2</f>
         <v>250000</v>
       </c>
       <c r="N35" s="1">
-        <f>Sorted!E35^2</f>
+        <f>[1]Sorted!E35^2</f>
         <v>1000000</v>
       </c>
       <c r="O35" s="1">
-        <f>Sorted!F35^2</f>
+        <f>[1]Sorted!F35^2</f>
         <v>25000000</v>
       </c>
       <c r="P35" s="1">
-        <f>Sorted!G35^2</f>
+        <f>[1]Sorted!G35^2</f>
         <v>100000000</v>
       </c>
       <c r="Q35" s="1">
-        <f>Sorted!H35^2</f>
+        <f>[1]Sorted!H35^2</f>
         <v>2500000000</v>
       </c>
     </row>
@@ -33613,54 +33718,54 @@
         <v>16</v>
       </c>
       <c r="C36" s="7">
-        <f>IF(COUNTBLANK(C6:L6)&gt;0,"undone",TRIMMEAN(C6:L6,2/COUNT(C6:L6)))</f>
-        <v>9.8625000000000015E-3</v>
+        <f t="shared" ref="C36:C41" si="0">IF(COUNTBLANK(C6:L6)&gt;0,"undone",TRIMMEAN(C6:L6,2/COUNT(C6:L6)))</f>
+        <v>6.9874999999999989E-3</v>
       </c>
       <c r="D36" s="7">
-        <f>IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
-        <v>0.25591250000000004</v>
+        <f t="shared" ref="D36:D41" si="1">IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
+        <v>0.17252500000000001</v>
       </c>
       <c r="E36" s="7">
-        <f>IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
-        <v>0.98113750000000011</v>
+        <f t="shared" ref="E36:E41" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
+        <v>0.68552499999999994</v>
       </c>
       <c r="F36" s="7">
-        <f>IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
-        <v>24.430362500000001</v>
+        <f t="shared" ref="F36:F41" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
+        <v>16.905687500000003</v>
       </c>
       <c r="G36" s="7">
-        <f>IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
-        <v>99.611262499999995</v>
+        <f t="shared" ref="G36:G41" si="4">IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
+        <v>67.898949999999999</v>
       </c>
       <c r="H36" s="7">
-        <f>IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
-        <v>2473.0774249999999</v>
+        <f t="shared" ref="H36:H41" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
+        <v>1699.54865</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L36" s="1">
-        <f>Sorted!C35*LOG(Sorted!C35)</f>
+        <f>[1]Sorted!C35*LOG([1]Sorted!C35)</f>
         <v>200</v>
       </c>
       <c r="M36" s="1">
-        <f>Sorted!D35*LOG(Sorted!D35)</f>
+        <f>[1]Sorted!D35*LOG([1]Sorted!D35)</f>
         <v>1349.4850021680095</v>
       </c>
       <c r="N36" s="1">
-        <f>Sorted!E35*LOG(Sorted!E35)</f>
+        <f>[1]Sorted!E35*LOG([1]Sorted!E35)</f>
         <v>3000</v>
       </c>
       <c r="O36" s="1">
-        <f>Sorted!F35*LOG(Sorted!F35)</f>
+        <f>[1]Sorted!F35*LOG([1]Sorted!F35)</f>
         <v>18494.850021680093</v>
       </c>
       <c r="P36" s="1">
-        <f>Sorted!G35*LOG(Sorted!G35)</f>
+        <f>[1]Sorted!G35*LOG([1]Sorted!G35)</f>
         <v>40000</v>
       </c>
       <c r="Q36" s="1">
-        <f>Sorted!H35*LOG(Sorted!H35)</f>
+        <f>[1]Sorted!H35*LOG([1]Sorted!H35)</f>
         <v>234948.50021680092</v>
       </c>
     </row>
@@ -33669,28 +33774,28 @@
         <v>17</v>
       </c>
       <c r="C37" s="7">
-        <f t="shared" ref="C37:C41" si="0">IF(COUNTBLANK(C7:L7)&gt;0,"undone",TRIMMEAN(C7:L7,2/COUNT(C7:L7)))</f>
-        <v>7.5125000000000001E-3</v>
+        <f t="shared" si="0"/>
+        <v>5.1624999999999996E-3</v>
       </c>
       <c r="D37" s="7">
-        <f t="shared" ref="D37:D41" si="1">IF(COUNTBLANK(O7:X7)&gt;0,"undone",TRIMMEAN(O7:X7,2/COUNT(O7:X7)))</f>
-        <v>0.18476250000000002</v>
+        <f t="shared" si="1"/>
+        <v>0.12428749999999998</v>
       </c>
       <c r="E37" s="7">
-        <f t="shared" ref="E37:E41" si="2">IF(COUNTBLANK(C17:L17)&gt;0,"undone",TRIMMEAN(C17:L17,2/COUNT(C17:L17)))</f>
-        <v>0.73175000000000001</v>
+        <f t="shared" si="2"/>
+        <v>0.47798750000000001</v>
       </c>
       <c r="F37" s="7">
-        <f t="shared" ref="F37:F41" si="3">IF(COUNTBLANK(O17:X17)&gt;0,"undone",TRIMMEAN(O17:X17,2/COUNT(O17:X17)))</f>
-        <v>17.197487500000001</v>
+        <f t="shared" si="3"/>
+        <v>11.9602</v>
       </c>
       <c r="G37" s="7">
-        <f t="shared" ref="G37:G41" si="4">IF(COUNTBLANK(C27:L27)&gt;0,"undone",TRIMMEAN(C27:L27,2/COUNT(C27:L27)))</f>
-        <v>69.581837500000006</v>
+        <f t="shared" si="4"/>
+        <v>48.382975000000002</v>
       </c>
       <c r="H37" s="7">
-        <f t="shared" ref="H37:H41" si="5">IF(COUNTBLANK(O27:X27)&gt;0,"undone",TRIMMEAN(O27:X27,2/COUNT(O27:X27)))</f>
-        <v>1751.8876750000002</v>
+        <f t="shared" si="5"/>
+        <v>1211.3593874999999</v>
       </c>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
@@ -33699,27 +33804,27 @@
       </c>
       <c r="C38" s="7">
         <f t="shared" si="0"/>
-        <v>1.6525000000000001E-2</v>
+        <v>1.0874999999999999E-2</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="1"/>
-        <v>0.39001249999999998</v>
+        <v>0.25931249999999995</v>
       </c>
       <c r="E38" s="7">
         <f t="shared" si="2"/>
-        <v>1.5767875</v>
+        <v>1.0002499999999999</v>
       </c>
       <c r="F38" s="7">
         <f t="shared" si="3"/>
-        <v>39.417412499999998</v>
+        <v>25.497987499999997</v>
       </c>
       <c r="G38" s="7">
         <f t="shared" si="4"/>
-        <v>157.20343750000001</v>
+        <v>101.96351250000001</v>
       </c>
       <c r="H38" s="7">
         <f t="shared" si="5"/>
-        <v>4051.6519750000002</v>
+        <v>2558.8650750000002</v>
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
@@ -33728,27 +33833,27 @@
       </c>
       <c r="C39" s="7">
         <f t="shared" si="0"/>
-        <v>3.9249999999999997E-3</v>
+        <v>2.7250000000000004E-3</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="1"/>
-        <v>2.38125E-2</v>
+        <v>1.685E-2</v>
       </c>
       <c r="E39" s="7">
         <f t="shared" si="2"/>
-        <v>5.1262500000000009E-2</v>
+        <v>3.5125000000000003E-2</v>
       </c>
       <c r="F39" s="7">
         <f t="shared" si="3"/>
-        <v>0.30181249999999998</v>
+        <v>0.21203749999999999</v>
       </c>
       <c r="G39" s="7">
         <f t="shared" si="4"/>
-        <v>0.66368749999999999</v>
+        <v>0.44373750000000001</v>
       </c>
       <c r="H39" s="7">
         <f t="shared" si="5"/>
-        <v>3.7551500000000004</v>
+        <v>2.5085625</v>
       </c>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
@@ -33757,27 +33862,27 @@
       </c>
       <c r="C40" s="7">
         <f t="shared" si="0"/>
-        <v>5.8499999999999993E-3</v>
+        <v>4.0750000000000005E-3</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="1"/>
-        <v>0.14306249999999998</v>
+        <v>0.10169999999999998</v>
       </c>
       <c r="E40" s="7">
         <f t="shared" si="2"/>
-        <v>0.56122500000000008</v>
+        <v>0.38579999999999998</v>
       </c>
       <c r="F40" s="7">
         <f t="shared" si="3"/>
-        <v>13.865499999999999</v>
+        <v>9.5796749999999999</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="4"/>
-        <v>55.1704875</v>
+        <v>37.982999999999997</v>
       </c>
       <c r="H40" s="7">
         <f t="shared" si="5"/>
-        <v>1379.994475</v>
+        <v>941.21522500000003</v>
       </c>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
@@ -33786,39 +33891,44 @@
       </c>
       <c r="C41" s="7">
         <f t="shared" si="0"/>
-        <v>4.0749999999999996E-3</v>
+        <v>2.6749999999999994E-3</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="1"/>
-        <v>2.1049999999999996E-2</v>
+        <v>1.3599999999999999E-2</v>
       </c>
       <c r="E41" s="7">
         <f t="shared" si="2"/>
-        <v>4.3212500000000001E-2</v>
+        <v>2.8712500000000002E-2</v>
       </c>
       <c r="F41" s="7">
         <f t="shared" si="3"/>
-        <v>0.2749375</v>
+        <v>2.1148750000000001</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="4"/>
-        <v>0.51900000000000002</v>
+        <v>18.998987500000002</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="5"/>
-        <v>2.6659375000000001</v>
+        <v>706.74744999999996</v>
       </c>
     </row>
     <row r="44" spans="2:17" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="10" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -33829,11 +33939,6 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data collecting.xlsx
+++ b/data collecting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phure\เอกสาร\GitHub\c-sorting-algorithm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FA984D-3714-4C46-A920-846D65EE0359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BD2835-3152-4496-8075-BE1779657C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
   </bookViews>
@@ -197,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -268,37 +268,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -330,46 +304,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,22 +497,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.2374999999999991E-3</c:v>
+                  <c:v>4.8124999999999991E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.2087499999999989E-2</c:v>
+                  <c:v>0.13966250000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.32903749999999998</c:v>
+                  <c:v>0.38126250000000006</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.5749499999999994</c:v>
+                  <c:v>9.1625374999999991</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34.517949999999999</c:v>
+                  <c:v>36.635325000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>848.96680000000015</c:v>
+                  <c:v>868.77935000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1210,22 +1160,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>5.1124999999999999E-3</c:v>
+                  <c:v>5.1624999999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12496250000000002</c:v>
+                  <c:v>0.12739999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.49884999999999996</c:v>
+                  <c:v>0.49443750000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.45715</c:v>
+                  <c:v>12.511575000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>50.051387499999997</c:v>
+                  <c:v>50.242349999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1248.5817875</c:v>
+                  <c:v>1260.3892000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1873,22 +1823,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.6750000000000003E-3</c:v>
+                  <c:v>2.6500000000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6037500000000003E-2</c:v>
+                  <c:v>1.6387499999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.6924999999999999E-2</c:v>
+                  <c:v>3.4399999999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.20457499999999998</c:v>
+                  <c:v>0.20878750000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.43671249999999995</c:v>
+                  <c:v>0.43558749999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.4870749999999999</c:v>
+                  <c:v>2.4973625000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2536,22 +2486,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.3999999999999994E-3</c:v>
+                  <c:v>4.4750000000000007E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.3350000000000002E-2</c:v>
+                  <c:v>0.1011625</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.38807499999999995</c:v>
+                  <c:v>0.38603750000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.5362000000000009</c:v>
+                  <c:v>9.6170749999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38.011587500000005</c:v>
+                  <c:v>38.135925</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>945.68022500000006</c:v>
+                  <c:v>949.47337500000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3199,22 +3149,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.5374999999999998E-3</c:v>
+                  <c:v>3.0249999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2412500000000003E-2</c:v>
+                  <c:v>2.3074999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9025000000000002E-2</c:v>
+                  <c:v>3.3175000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.15733749999999996</c:v>
+                  <c:v>0.17295000000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.37109999999999999</c:v>
+                  <c:v>0.33651249999999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.7895749999999997</c:v>
+                  <c:v>2.0946875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3905,19 +3855,19 @@
                   <c:v>1.7500000000000003E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.0000000000000015E-4</c:v>
+                  <c:v>8.25E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.6125000000000002E-3</c:v>
+                  <c:v>1.9E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.3875000000000017E-3</c:v>
+                  <c:v>7.3750000000000013E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4450000000000003E-2</c:v>
+                  <c:v>1.4599999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.2174999999999998E-2</c:v>
+                  <c:v>7.5200000000000003E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3993,22 +3943,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.4124999999999998E-3</c:v>
+                  <c:v>4.4875000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.10567500000000001</c:v>
+                  <c:v>0.10781249999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.42470000000000008</c:v>
+                  <c:v>0.41909999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.738949999999997</c:v>
+                  <c:v>10.769450000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>42.800525</c:v>
+                  <c:v>42.853400000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1070.4900749999999</c:v>
+                  <c:v>1075.4819874999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4088,22 +4038,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>5.1124999999999999E-3</c:v>
+                  <c:v>5.1624999999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12496250000000002</c:v>
+                  <c:v>0.12739999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.49884999999999996</c:v>
+                  <c:v>0.49443750000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.45715</c:v>
+                  <c:v>12.511575000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>50.051387499999997</c:v>
+                  <c:v>50.242349999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1248.5817875</c:v>
+                  <c:v>1260.3892000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4179,22 +4129,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.6750000000000003E-3</c:v>
+                  <c:v>2.6500000000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6037500000000003E-2</c:v>
+                  <c:v>1.6387499999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.6924999999999999E-2</c:v>
+                  <c:v>3.4399999999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.20457499999999998</c:v>
+                  <c:v>0.20878750000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.43671249999999995</c:v>
+                  <c:v>0.43558749999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.4870749999999999</c:v>
+                  <c:v>2.4973625000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4272,22 +4222,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.3999999999999994E-3</c:v>
+                  <c:v>4.4750000000000007E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.3350000000000002E-2</c:v>
+                  <c:v>0.1011625</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.38807499999999995</c:v>
+                  <c:v>0.38603750000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.5362000000000009</c:v>
+                  <c:v>9.6170749999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38.011587500000005</c:v>
+                  <c:v>38.135925</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>945.68022500000006</c:v>
+                  <c:v>949.47337500000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4362,22 +4312,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.5374999999999998E-3</c:v>
+                  <c:v>3.0249999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2412500000000003E-2</c:v>
+                  <c:v>2.3074999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9025000000000002E-2</c:v>
+                  <c:v>3.3175000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.15733749999999996</c:v>
+                  <c:v>0.17295000000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.37109999999999999</c:v>
+                  <c:v>0.33651249999999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.7895749999999997</c:v>
+                  <c:v>2.0946875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4881,22 +4831,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>6.9874999999999989E-3</c:v>
+                  <c:v>7.0875000000000009E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.17252500000000001</c:v>
+                  <c:v>0.17197499999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.68552499999999994</c:v>
+                  <c:v>0.68328750000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16.905687500000003</c:v>
+                  <c:v>16.931525000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>67.898949999999999</c:v>
+                  <c:v>67.847662499999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1699.54865</c:v>
+                  <c:v>1702.9779874999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5547,19 +5497,19 @@
                   <c:v>5.1624999999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12428749999999998</c:v>
+                  <c:v>0.12125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.47798750000000001</c:v>
+                  <c:v>0.50707499999999994</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.9602</c:v>
+                  <c:v>12.1383375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>48.382975000000002</c:v>
+                  <c:v>48.517387499999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1211.3593874999999</c:v>
+                  <c:v>1213.9240124999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6207,22 +6157,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.0874999999999999E-2</c:v>
+                  <c:v>1.1375E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25931249999999995</c:v>
+                  <c:v>0.26517499999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0002499999999999</c:v>
+                  <c:v>1.0350250000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25.497987499999997</c:v>
+                  <c:v>25.831062500000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>101.96351250000001</c:v>
+                  <c:v>102.25823750000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2558.8650750000002</c:v>
+                  <c:v>2566.876675</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6870,22 +6820,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.7250000000000004E-3</c:v>
+                  <c:v>2.7875E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.685E-2</c:v>
+                  <c:v>1.6812499999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.5125000000000003E-2</c:v>
+                  <c:v>4.1299999999999989E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21203749999999999</c:v>
+                  <c:v>0.20830000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.44373750000000001</c:v>
+                  <c:v>0.45038750000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.5085625</c:v>
+                  <c:v>2.54515</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7533,22 +7483,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.0750000000000005E-3</c:v>
+                  <c:v>4.1749999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.10169999999999998</c:v>
+                  <c:v>9.3112500000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.38579999999999998</c:v>
+                  <c:v>0.37921249999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.5796749999999999</c:v>
+                  <c:v>9.6247250000000015</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>37.982999999999997</c:v>
+                  <c:v>37.946875000000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>941.21522500000003</c:v>
+                  <c:v>942.89426249999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8196,22 +8146,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.725E-3</c:v>
+                  <c:v>7.4500000000000009E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.11115</c:v>
+                  <c:v>0.1338625</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.45730000000000004</c:v>
+                  <c:v>0.67284999999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.927024999999999</c:v>
+                  <c:v>11.793262499999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>45.488837500000002</c:v>
+                  <c:v>46.627675000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1075.8161375</c:v>
+                  <c:v>1080.7087624999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8851,22 +8801,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.6749999999999994E-3</c:v>
+                  <c:v>2.7125000000000005E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3599999999999999E-2</c:v>
+                  <c:v>1.5162500000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.8712500000000002E-2</c:v>
+                  <c:v>3.0974999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.1148750000000001</c:v>
+                  <c:v>0.15201250000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18.998987500000002</c:v>
+                  <c:v>0.36193750000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>706.74744999999996</c:v>
+                  <c:v>1.9822499999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9541,22 +9491,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>6.9874999999999989E-3</c:v>
+                  <c:v>7.0875000000000009E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.17252500000000001</c:v>
+                  <c:v>0.17197499999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.68552499999999994</c:v>
+                  <c:v>0.68328750000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16.905687500000003</c:v>
+                  <c:v>16.931525000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>67.898949999999999</c:v>
+                  <c:v>67.847662499999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1699.54865</c:v>
+                  <c:v>1702.9779874999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9635,19 +9585,19 @@
                   <c:v>5.1624999999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12428749999999998</c:v>
+                  <c:v>0.12125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.47798750000000001</c:v>
+                  <c:v>0.50707499999999994</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.9602</c:v>
+                  <c:v>12.1383375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>48.382975000000002</c:v>
+                  <c:v>48.517387499999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1211.3593874999999</c:v>
+                  <c:v>1213.9240124999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9727,22 +9677,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.0874999999999999E-2</c:v>
+                  <c:v>1.1375E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25931249999999995</c:v>
+                  <c:v>0.26517499999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0002499999999999</c:v>
+                  <c:v>1.0350250000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25.497987499999997</c:v>
+                  <c:v>25.831062500000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>101.96351250000001</c:v>
+                  <c:v>102.25823750000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2558.8650750000002</c:v>
+                  <c:v>2566.876675</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9818,22 +9768,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.7250000000000004E-3</c:v>
+                  <c:v>2.7875E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.685E-2</c:v>
+                  <c:v>1.6812499999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.5125000000000003E-2</c:v>
+                  <c:v>4.1299999999999989E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21203749999999999</c:v>
+                  <c:v>0.20830000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.44373750000000001</c:v>
+                  <c:v>0.45038750000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.5085625</c:v>
+                  <c:v>2.54515</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9911,22 +9861,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.0750000000000005E-3</c:v>
+                  <c:v>4.1749999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.10169999999999998</c:v>
+                  <c:v>9.3112500000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.38579999999999998</c:v>
+                  <c:v>0.37921249999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.5796749999999999</c:v>
+                  <c:v>9.6247250000000015</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>37.982999999999997</c:v>
+                  <c:v>37.946875000000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>941.21522500000003</c:v>
+                  <c:v>942.89426249999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10001,22 +9951,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.6749999999999994E-3</c:v>
+                  <c:v>2.7125000000000005E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3599999999999999E-2</c:v>
+                  <c:v>1.5162500000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.8712500000000002E-2</c:v>
+                  <c:v>3.0974999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.1148750000000001</c:v>
+                  <c:v>0.15201250000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18.998987500000002</c:v>
+                  <c:v>0.36193750000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>706.74744999999996</c:v>
+                  <c:v>1.9822499999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10520,22 +10470,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.9500000000000005E-3</c:v>
+                  <c:v>1.2637499999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.20223750000000001</c:v>
+                  <c:v>0.22673750000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.8023125000000001</c:v>
+                  <c:v>0.97297500000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.875374999999998</c:v>
+                  <c:v>21.582700000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>83.256074999999996</c:v>
+                  <c:v>85.040899999999993</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1988.4961750000002</c:v>
+                  <c:v>2000.0543750000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11183,22 +11133,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.8250000000000003E-3</c:v>
+                  <c:v>4.4374999999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7975000000000001E-2</c:v>
+                  <c:v>2.1587499999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.8687499999999993E-2</c:v>
+                  <c:v>4.1737500000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.36593750000000003</c:v>
+                  <c:v>0.35088750000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.81251249999999997</c:v>
+                  <c:v>0.79519999999999991</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.5662125000000007</c:v>
+                  <c:v>4.5945875000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11846,22 +11796,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.5999999999999999E-3</c:v>
+                  <c:v>2.3625E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.1750000000000009E-3</c:v>
+                  <c:v>1.2125E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.0137499999999999E-2</c:v>
+                  <c:v>2.2712500000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21444999999999997</c:v>
+                  <c:v>0.273725</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.54075000000000006</c:v>
+                  <c:v>0.53790000000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.0949</c:v>
+                  <c:v>3.147125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12509,22 +12459,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.0625000000000001E-3</c:v>
+                  <c:v>4.5374999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7774999999999999E-2</c:v>
+                  <c:v>2.4125000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.9275000000000004E-2</c:v>
+                  <c:v>4.4487499999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.29073749999999998</c:v>
+                  <c:v>0.31668750000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.69238750000000004</c:v>
+                  <c:v>0.69691249999999993</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.8935500000000003</c:v>
+                  <c:v>3.8180250000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13228,22 +13178,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.2374999999999991E-3</c:v>
+                  <c:v>4.8124999999999991E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.2087499999999989E-2</c:v>
+                  <c:v>0.13966250000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.32903749999999998</c:v>
+                  <c:v>0.38126250000000006</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.5749499999999994</c:v>
+                  <c:v>9.1625374999999991</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34.517949999999999</c:v>
+                  <c:v>36.635325000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>848.96680000000015</c:v>
+                  <c:v>868.77935000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13319,22 +13269,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.725E-3</c:v>
+                  <c:v>7.4500000000000009E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.11115</c:v>
+                  <c:v>0.1338625</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.45730000000000004</c:v>
+                  <c:v>0.67284999999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.927024999999999</c:v>
+                  <c:v>11.793262499999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>45.488837500000002</c:v>
+                  <c:v>46.627675000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1075.8161375</c:v>
+                  <c:v>1080.7087624999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13414,22 +13364,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.9500000000000005E-3</c:v>
+                  <c:v>1.2637499999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.20223750000000001</c:v>
+                  <c:v>0.22673750000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.8023125000000001</c:v>
+                  <c:v>0.97297500000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.875374999999998</c:v>
+                  <c:v>21.582700000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>83.256074999999996</c:v>
+                  <c:v>85.040899999999993</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1988.4961750000002</c:v>
+                  <c:v>2000.0543750000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13505,22 +13455,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.8250000000000003E-3</c:v>
+                  <c:v>4.4374999999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7975000000000001E-2</c:v>
+                  <c:v>2.1587499999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.8687499999999993E-2</c:v>
+                  <c:v>4.1737500000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.36593750000000003</c:v>
+                  <c:v>0.35088750000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.81251249999999997</c:v>
+                  <c:v>0.79519999999999991</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.5662125000000007</c:v>
+                  <c:v>4.5945875000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13598,22 +13548,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.5999999999999999E-3</c:v>
+                  <c:v>2.3625E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.1750000000000009E-3</c:v>
+                  <c:v>1.2125E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.0137499999999999E-2</c:v>
+                  <c:v>2.2712500000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21444999999999997</c:v>
+                  <c:v>0.273725</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.54075000000000006</c:v>
+                  <c:v>0.53790000000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.0949</c:v>
+                  <c:v>3.147125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13688,22 +13638,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.0625000000000001E-3</c:v>
+                  <c:v>4.5374999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7774999999999999E-2</c:v>
+                  <c:v>2.4125000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.9275000000000004E-2</c:v>
+                  <c:v>4.4487499999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.29073749999999998</c:v>
+                  <c:v>0.31668750000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.69238750000000004</c:v>
+                  <c:v>0.69691249999999993</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.8935500000000003</c:v>
+                  <c:v>3.8180250000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14218,19 +14168,19 @@
                   <c:v>1.7500000000000003E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.0000000000000015E-4</c:v>
+                  <c:v>8.25E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.6125000000000002E-3</c:v>
+                  <c:v>1.9E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.3875000000000017E-3</c:v>
+                  <c:v>7.3750000000000013E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4450000000000003E-2</c:v>
+                  <c:v>1.4599999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.2174999999999998E-2</c:v>
+                  <c:v>7.5200000000000003E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14870,22 +14820,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.4124999999999998E-3</c:v>
+                  <c:v>4.4875000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.10567500000000001</c:v>
+                  <c:v>0.10781249999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.42470000000000008</c:v>
+                  <c:v>0.41909999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.738949999999997</c:v>
+                  <c:v>10.769450000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>42.800525</c:v>
+                  <c:v>42.853400000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1070.4900749999999</c:v>
+                  <c:v>1075.4819874999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -27876,10 +27826,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Random"/>
       <sheetName val="random_grpah"/>
@@ -27891,7 +27837,7 @@
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2">
+      <sheetData sheetId="2" refreshError="1">
         <row r="35">
           <cell r="C35">
             <v>100</v>
@@ -28255,10 +28201,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="12"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -28277,39 +28223,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="21"/>
-      <c r="N4" s="22" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="17"/>
+      <c r="N4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="19" t="s">
+      <c r="O4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20"/>
-      <c r="X4" s="21"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="17"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="23"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -28340,7 +28286,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="23"/>
+      <c r="N5" s="14"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -28377,67 +28323,67 @@
         <v>16</v>
       </c>
       <c r="C6" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="D6" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="E6" s="7">
-        <v>3.3E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="F6" s="7">
-        <v>3.0999999999999999E-3</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="G6" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="H6" s="7">
-        <v>3.0999999999999999E-3</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="I6" s="7">
-        <v>3.0999999999999999E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="J6" s="7">
-        <v>3.0999999999999999E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="K6" s="7">
-        <v>3.0999999999999999E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="L6" s="7">
-        <v>3.0999999999999999E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O6" s="7">
-        <v>9.2700000000000005E-2</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="P6" s="7">
-        <v>9.2600000000000002E-2</v>
+        <v>0.1386</v>
       </c>
       <c r="Q6" s="7">
-        <v>9.2100000000000001E-2</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="R6" s="7">
-        <v>9.2100000000000001E-2</v>
+        <v>0.1641</v>
       </c>
       <c r="S6" s="7">
-        <v>9.1999999999999998E-2</v>
+        <v>0.1401</v>
       </c>
       <c r="T6" s="7">
-        <v>9.1999999999999998E-2</v>
+        <v>0.1396</v>
       </c>
       <c r="U6" s="7">
-        <v>9.1899999999999996E-2</v>
+        <v>0.1439</v>
       </c>
       <c r="V6" s="7">
-        <v>9.1999999999999998E-2</v>
+        <v>0.13850000000000001</v>
       </c>
       <c r="W6" s="7">
-        <v>9.1999999999999998E-2</v>
+        <v>0.13880000000000001</v>
       </c>
       <c r="X6" s="7">
-        <v>9.1899999999999996E-2</v>
+        <v>0.13880000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -28445,67 +28391,67 @@
         <v>17</v>
       </c>
       <c r="C7" s="7">
-        <v>7.1000000000000004E-3</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="D7" s="7">
-        <v>6.4999999999999997E-3</v>
+        <v>0.01</v>
       </c>
       <c r="E7" s="7">
-        <v>4.7999999999999996E-3</v>
+        <v>7.6E-3</v>
       </c>
       <c r="F7" s="7">
-        <v>4.4000000000000003E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="G7" s="7">
-        <v>4.4000000000000003E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H7" s="7">
-        <v>4.4000000000000003E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I7" s="7">
-        <v>4.4999999999999997E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="J7" s="7">
-        <v>4.4000000000000003E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="K7" s="7">
-        <v>4.4000000000000003E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="L7" s="7">
-        <v>4.4000000000000003E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O7" s="7">
-        <v>0.12089999999999999</v>
+        <v>0.19370000000000001</v>
       </c>
       <c r="P7" s="7">
-        <v>0.11650000000000001</v>
+        <v>0.18729999999999999</v>
       </c>
       <c r="Q7" s="7">
-        <v>0.1129</v>
+        <v>0.15390000000000001</v>
       </c>
       <c r="R7" s="7">
-        <v>0.11119999999999999</v>
+        <v>0.1217</v>
       </c>
       <c r="S7" s="7">
-        <v>0.1103</v>
+        <v>0.1207</v>
       </c>
       <c r="T7" s="7">
-        <v>0.10979999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="U7" s="7">
-        <v>0.1096</v>
+        <v>0.1198</v>
       </c>
       <c r="V7" s="7">
-        <v>0.1095</v>
+        <v>0.1197</v>
       </c>
       <c r="W7" s="7">
-        <v>0.1094</v>
+        <v>0.1195</v>
       </c>
       <c r="X7" s="7">
-        <v>0.1094</v>
+        <v>0.1278</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -28513,67 +28459,67 @@
         <v>18</v>
       </c>
       <c r="C8" s="7">
-        <v>1.0999999999999999E-2</v>
+        <v>1.6400000000000001E-2</v>
       </c>
       <c r="D8" s="7">
-        <v>9.2999999999999992E-3</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="E8" s="7">
-        <v>7.9000000000000008E-3</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="F8" s="7">
-        <v>7.7999999999999996E-3</v>
+        <v>1.23E-2</v>
       </c>
       <c r="G8" s="7">
-        <v>7.7000000000000002E-3</v>
+        <v>1.23E-2</v>
       </c>
       <c r="H8" s="7">
-        <v>7.7999999999999996E-3</v>
+        <v>1.23E-2</v>
       </c>
       <c r="I8" s="7">
-        <v>7.7000000000000002E-3</v>
+        <v>1.23E-2</v>
       </c>
       <c r="J8" s="7">
-        <v>7.7000000000000002E-3</v>
+        <v>1.24E-2</v>
       </c>
       <c r="K8" s="7">
-        <v>7.7000000000000002E-3</v>
+        <v>1.24E-2</v>
       </c>
       <c r="L8" s="7">
-        <v>7.7000000000000002E-3</v>
+        <v>1.24E-2</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O8" s="7">
-        <v>0.2261</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="P8" s="7">
-        <v>0.21310000000000001</v>
+        <v>0.2316</v>
       </c>
       <c r="Q8" s="7">
-        <v>0.20530000000000001</v>
+        <v>0.2235</v>
       </c>
       <c r="R8" s="7">
-        <v>0.20230000000000001</v>
+        <v>0.2198</v>
       </c>
       <c r="S8" s="7">
-        <v>0.2001</v>
+        <v>0.218</v>
       </c>
       <c r="T8" s="7">
-        <v>0.1996</v>
+        <v>0.22170000000000001</v>
       </c>
       <c r="U8" s="7">
-        <v>0.19969999999999999</v>
+        <v>0.21740000000000001</v>
       </c>
       <c r="V8" s="7">
-        <v>0.19889999999999999</v>
+        <v>0.2172</v>
       </c>
       <c r="W8" s="7">
-        <v>0.19869999999999999</v>
+        <v>0.24510000000000001</v>
       </c>
       <c r="X8" s="7">
-        <v>0.19889999999999999</v>
+        <v>0.23680000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -28581,67 +28527,67 @@
         <v>19</v>
       </c>
       <c r="C9" s="7">
-        <v>5.1000000000000004E-3</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="D9" s="7">
-        <v>3.3E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E9" s="7">
-        <v>2.8E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="F9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="G9" s="7">
-        <v>2.8E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="H9" s="7">
-        <v>2.8E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="I9" s="7">
-        <v>2.8E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="J9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="K9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="L9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O9" s="7">
-        <v>2.81E-2</v>
+        <v>3.15E-2</v>
       </c>
       <c r="P9" s="7">
-        <v>1.9800000000000002E-2</v>
+        <v>2.1700000000000001E-2</v>
       </c>
       <c r="Q9" s="7">
-        <v>1.7399999999999999E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="R9" s="7">
-        <v>2.18E-2</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="S9" s="7">
-        <v>1.6899999999999998E-2</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="T9" s="7">
-        <v>1.7000000000000001E-2</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="U9" s="7">
-        <v>1.6899999999999998E-2</v>
+        <v>2.6499999999999999E-2</v>
       </c>
       <c r="V9" s="7">
-        <v>1.6899999999999998E-2</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="W9" s="7">
-        <v>1.7000000000000001E-2</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="X9" s="7">
-        <v>1.7000000000000001E-2</v>
+        <v>2.2800000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -28649,67 +28595,67 @@
         <v>20</v>
       </c>
       <c r="C10" s="7">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="D10" s="7">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="D10" s="7">
-        <v>3.0999999999999999E-3</v>
-      </c>
       <c r="E10" s="7">
-        <v>1.6999999999999999E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="F10" s="7">
-        <v>1.2999999999999999E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="G10" s="7">
-        <v>1.4E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="H10" s="7">
-        <v>1.2999999999999999E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="I10" s="7">
-        <v>1.2999999999999999E-3</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="J10" s="7">
-        <v>1.4E-3</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="K10" s="7">
-        <v>1.2999999999999999E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="L10" s="7">
-        <v>1.1999999999999999E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O10" s="7">
-        <v>1.9099999999999999E-2</v>
+        <v>2.6599999999999999E-2</v>
       </c>
       <c r="P10" s="7">
-        <v>1.35E-2</v>
+        <v>1.84E-2</v>
       </c>
       <c r="Q10" s="7">
-        <v>1.04E-2</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="R10" s="7">
-        <v>8.3000000000000001E-3</v>
+        <v>1.11E-2</v>
       </c>
       <c r="S10" s="7">
-        <v>8.0000000000000002E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="T10" s="7">
-        <v>8.2000000000000007E-3</v>
+        <v>1.12E-2</v>
       </c>
       <c r="U10" s="7">
-        <v>8.3000000000000001E-3</v>
+        <v>1.11E-2</v>
       </c>
       <c r="V10" s="7">
-        <v>8.3000000000000001E-3</v>
+        <v>1.11E-2</v>
       </c>
       <c r="W10" s="7">
-        <v>8.0999999999999996E-3</v>
+        <v>1.11E-2</v>
       </c>
       <c r="X10" s="7">
-        <v>8.3000000000000001E-3</v>
+        <v>1.11E-2</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -28717,67 +28663,67 @@
         <v>21</v>
       </c>
       <c r="C11" s="8">
-        <v>4.7999999999999996E-3</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="D11" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="E11" s="7">
-        <v>2.8E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="F11" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G11" s="7">
-        <v>3.0999999999999999E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="H11" s="7">
-        <v>3.7000000000000002E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="I11" s="7">
-        <v>3.0000000000000001E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="J11" s="7">
-        <v>2.8E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="K11" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="L11" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O11" s="8">
-        <v>2.6700000000000002E-2</v>
+        <v>3.78E-2</v>
       </c>
       <c r="P11" s="7">
-        <v>2.1000000000000001E-2</v>
+        <v>2.81E-2</v>
       </c>
       <c r="Q11" s="7">
-        <v>1.7100000000000001E-2</v>
+        <v>2.86E-2</v>
       </c>
       <c r="R11" s="7">
-        <v>1.5599999999999999E-2</v>
+        <v>2.4799999999999999E-2</v>
       </c>
       <c r="S11" s="7">
-        <v>1.55E-2</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="T11" s="7">
-        <v>1.8700000000000001E-2</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="U11" s="7">
-        <v>1.7999999999999999E-2</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="V11" s="7">
-        <v>1.5699999999999999E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="W11" s="7">
-        <v>1.9699999999999999E-2</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="X11" s="7">
-        <v>1.6400000000000001E-2</v>
+        <v>2.2499999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -28797,39 +28743,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="21"/>
-      <c r="N14" s="22" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="17"/>
+      <c r="N14" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="19" t="s">
+      <c r="O14" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="20"/>
-      <c r="U14" s="20"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="20"/>
-      <c r="X14" s="21"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="17"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="23"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -28860,7 +28806,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="23"/>
+      <c r="N15" s="14"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -28897,67 +28843,67 @@
         <v>16</v>
       </c>
       <c r="C16" s="7">
-        <v>0.3281</v>
+        <v>0.44409999999999999</v>
       </c>
       <c r="D16" s="7">
-        <v>0.32750000000000001</v>
+        <v>0.40960000000000002</v>
       </c>
       <c r="E16" s="7">
-        <v>0.32669999999999999</v>
+        <v>0.35360000000000003</v>
       </c>
       <c r="F16" s="7">
-        <v>0.32679999999999998</v>
+        <v>0.35349999999999998</v>
       </c>
       <c r="G16" s="7">
-        <v>0.33689999999999998</v>
+        <v>0.3533</v>
       </c>
       <c r="H16" s="7">
-        <v>0.3286</v>
+        <v>0.3533</v>
       </c>
       <c r="I16" s="7">
-        <v>0.32850000000000001</v>
+        <v>0.35349999999999998</v>
       </c>
       <c r="J16" s="7">
-        <v>0.32879999999999998</v>
+        <v>0.35949999999999999</v>
       </c>
       <c r="K16" s="7">
-        <v>0.33379999999999999</v>
+        <v>0.43059999999999998</v>
       </c>
       <c r="L16" s="7">
-        <v>0.33019999999999999</v>
+        <v>0.4365</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O16" s="7">
-        <v>8.9773999999999994</v>
+        <v>8.9814000000000007</v>
       </c>
       <c r="P16" s="7">
-        <v>8.3798999999999992</v>
+        <v>9.1234999999999999</v>
       </c>
       <c r="Q16" s="7">
-        <v>8.7765000000000004</v>
+        <v>8.8721999999999994</v>
       </c>
       <c r="R16" s="7">
-        <v>8.6914999999999996</v>
+        <v>9.1684000000000001</v>
       </c>
       <c r="S16" s="7">
-        <v>8.3993000000000002</v>
+        <v>9.2380999999999993</v>
       </c>
       <c r="T16" s="7">
-        <v>8.6715999999999998</v>
+        <v>10.230399999999999</v>
       </c>
       <c r="U16" s="7">
-        <v>8.4224999999999994</v>
+        <v>8.9791000000000007</v>
       </c>
       <c r="V16" s="7">
-        <v>8.5189000000000004</v>
+        <v>9.6593999999999998</v>
       </c>
       <c r="W16" s="7">
-        <v>8.5299999999999994</v>
+        <v>9.1508000000000003</v>
       </c>
       <c r="X16" s="7">
-        <v>8.5892999999999997</v>
+        <v>8.9995999999999992</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
@@ -28965,67 +28911,67 @@
         <v>17</v>
       </c>
       <c r="C17" s="7">
-        <v>0.50509999999999999</v>
+        <v>0.68459999999999999</v>
       </c>
       <c r="D17" s="7">
-        <v>0.48630000000000001</v>
+        <v>0.66569999999999996</v>
       </c>
       <c r="E17" s="7">
-        <v>0.45279999999999998</v>
+        <v>0.66379999999999995</v>
       </c>
       <c r="F17" s="7">
-        <v>0.4451</v>
+        <v>0.67290000000000005</v>
       </c>
       <c r="G17" s="7">
-        <v>0.44879999999999998</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="H17" s="7">
-        <v>0.44230000000000003</v>
+        <v>0.66910000000000003</v>
       </c>
       <c r="I17" s="7">
-        <v>0.44719999999999999</v>
+        <v>0.68110000000000004</v>
       </c>
       <c r="J17" s="7">
-        <v>0.44369999999999998</v>
+        <v>0.67479999999999996</v>
       </c>
       <c r="K17" s="7">
-        <v>0.44359999999999999</v>
+        <v>0.66979999999999995</v>
       </c>
       <c r="L17" s="7">
-        <v>0.4909</v>
+        <v>0.6784</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O17" s="7">
-        <v>10.8446</v>
+        <v>12.6663</v>
       </c>
       <c r="P17" s="7">
-        <v>10.9262</v>
+        <v>11.7286</v>
       </c>
       <c r="Q17" s="7">
-        <v>10.9701</v>
+        <v>11.5091</v>
       </c>
       <c r="R17" s="7">
-        <v>11.167899999999999</v>
+        <v>11.269500000000001</v>
       </c>
       <c r="S17" s="7">
-        <v>10.581</v>
+        <v>12.573700000000001</v>
       </c>
       <c r="T17" s="7">
-        <v>10.9725</v>
+        <v>11.5558</v>
       </c>
       <c r="U17" s="7">
-        <v>10.822800000000001</v>
+        <v>11.430099999999999</v>
       </c>
       <c r="V17" s="7">
-        <v>10.866300000000001</v>
+        <v>11.525600000000001</v>
       </c>
       <c r="W17" s="7">
-        <v>10.845800000000001</v>
+        <v>11.3569</v>
       </c>
       <c r="X17" s="7">
-        <v>11.6493</v>
+        <v>15.586399999999999</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
@@ -29033,67 +28979,67 @@
         <v>18</v>
       </c>
       <c r="C18" s="7">
-        <v>0.81579999999999997</v>
+        <v>1.1940999999999999</v>
       </c>
       <c r="D18" s="7">
-        <v>0.82269999999999999</v>
+        <v>1.1867000000000001</v>
       </c>
       <c r="E18" s="7">
-        <v>0.80210000000000004</v>
+        <v>1.0601</v>
       </c>
       <c r="F18" s="7">
-        <v>0.7984</v>
+        <v>0.85519999999999996</v>
       </c>
       <c r="G18" s="7">
-        <v>0.80320000000000003</v>
+        <v>0.85740000000000005</v>
       </c>
       <c r="H18" s="7">
-        <v>0.80300000000000005</v>
+        <v>0.85219999999999996</v>
       </c>
       <c r="I18" s="7">
-        <v>0.80659999999999998</v>
+        <v>0.84930000000000005</v>
       </c>
       <c r="J18" s="7">
-        <v>0.79400000000000004</v>
+        <v>0.85370000000000001</v>
       </c>
       <c r="K18" s="7">
-        <v>0.79269999999999996</v>
+        <v>0.9244</v>
       </c>
       <c r="L18" s="7">
-        <v>0.7954</v>
+        <v>2.173</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O18" s="7">
-        <v>19.862400000000001</v>
+        <v>21.7987</v>
       </c>
       <c r="P18" s="7">
-        <v>19.755299999999998</v>
+        <v>20.936</v>
       </c>
       <c r="Q18" s="7">
-        <v>19.978100000000001</v>
+        <v>21.080300000000001</v>
       </c>
       <c r="R18" s="7">
-        <v>19.949100000000001</v>
+        <v>22.374099999999999</v>
       </c>
       <c r="S18" s="7">
-        <v>19.834800000000001</v>
+        <v>22.233599999999999</v>
       </c>
       <c r="T18" s="7">
-        <v>19.773099999999999</v>
+        <v>21.0002</v>
       </c>
       <c r="U18" s="7">
-        <v>19.981400000000001</v>
+        <v>22.298300000000001</v>
       </c>
       <c r="V18" s="7">
-        <v>20.439800000000002</v>
+        <v>20.711200000000002</v>
       </c>
       <c r="W18" s="7">
-        <v>19.6172</v>
+        <v>22.537199999999999</v>
       </c>
       <c r="X18" s="7">
-        <v>19.8688</v>
+        <v>20.9404</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
@@ -29101,67 +29047,67 @@
         <v>19</v>
       </c>
       <c r="C19" s="7">
-        <v>6.1899999999999997E-2</v>
+        <v>6.6600000000000006E-2</v>
       </c>
       <c r="D19" s="7">
-        <v>4.4600000000000001E-2</v>
+        <v>4.9299999999999997E-2</v>
       </c>
       <c r="E19" s="7">
-        <v>3.9100000000000003E-2</v>
+        <v>4.19E-2</v>
       </c>
       <c r="F19" s="7">
-        <v>3.8100000000000002E-2</v>
+        <v>4.1799999999999997E-2</v>
       </c>
       <c r="G19" s="7">
-        <v>3.7499999999999999E-2</v>
+        <v>4.0099999999999997E-2</v>
       </c>
       <c r="H19" s="7">
-        <v>3.7600000000000001E-2</v>
+        <v>3.9800000000000002E-2</v>
       </c>
       <c r="I19" s="7">
-        <v>3.7600000000000001E-2</v>
+        <v>3.9800000000000002E-2</v>
       </c>
       <c r="J19" s="7">
-        <v>3.7499999999999999E-2</v>
+        <v>4.07E-2</v>
       </c>
       <c r="K19" s="7">
-        <v>3.7499999999999999E-2</v>
+        <v>4.0500000000000001E-2</v>
       </c>
       <c r="L19" s="7">
-        <v>3.7400000000000003E-2</v>
+        <v>3.9600000000000003E-2</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O19" s="7">
-        <v>0.39889999999999998</v>
+        <v>0.40589999999999998</v>
       </c>
       <c r="P19" s="7">
-        <v>0.48959999999999998</v>
+        <v>0.36809999999999998</v>
       </c>
       <c r="Q19" s="7">
-        <v>0.48099999999999998</v>
+        <v>0.35949999999999999</v>
       </c>
       <c r="R19" s="7">
-        <v>0.3679</v>
+        <v>0.35070000000000001</v>
       </c>
       <c r="S19" s="7">
-        <v>0.34699999999999998</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="T19" s="7">
-        <v>0.34429999999999999</v>
+        <v>0.34839999999999999</v>
       </c>
       <c r="U19" s="7">
-        <v>0.33129999999999998</v>
+        <v>0.33760000000000001</v>
       </c>
       <c r="V19" s="7">
-        <v>0.32769999999999999</v>
+        <v>0.34310000000000002</v>
       </c>
       <c r="W19" s="7">
-        <v>0.32940000000000003</v>
+        <v>0.33429999999999999</v>
       </c>
       <c r="X19" s="7">
-        <v>0.31380000000000002</v>
+        <v>0.35470000000000002</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.25">
@@ -29169,67 +29115,67 @@
         <v>20</v>
       </c>
       <c r="C20" s="7">
-        <v>4.3299999999999998E-2</v>
+        <v>4.5699999999999998E-2</v>
       </c>
       <c r="D20" s="7">
-        <v>3.2500000000000001E-2</v>
+        <v>4.02E-2</v>
       </c>
       <c r="E20" s="7">
-        <v>2.06E-2</v>
+        <v>2.4500000000000001E-2</v>
       </c>
       <c r="F20" s="7">
-        <v>1.84E-2</v>
+        <v>2.0400000000000001E-2</v>
       </c>
       <c r="G20" s="7">
-        <v>1.7899999999999999E-2</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="H20" s="7">
-        <v>1.7899999999999999E-2</v>
+        <v>1.9400000000000001E-2</v>
       </c>
       <c r="I20" s="7">
-        <v>1.7899999999999999E-2</v>
+        <v>1.9199999999999998E-2</v>
       </c>
       <c r="J20" s="7">
-        <v>1.7999999999999999E-2</v>
+        <v>1.9099999999999999E-2</v>
       </c>
       <c r="K20" s="7">
-        <v>1.78E-2</v>
+        <v>1.9099999999999999E-2</v>
       </c>
       <c r="L20" s="7">
-        <v>1.7899999999999999E-2</v>
+        <v>1.9099999999999999E-2</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O20" s="7">
-        <v>0.24690000000000001</v>
+        <v>0.33950000000000002</v>
       </c>
       <c r="P20" s="7">
-        <v>0.2394</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="Q20" s="7">
-        <v>0.22950000000000001</v>
+        <v>0.31740000000000002</v>
       </c>
       <c r="R20" s="7">
-        <v>0.22600000000000001</v>
+        <v>0.28910000000000002</v>
       </c>
       <c r="S20" s="7">
-        <v>0.21920000000000001</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="T20" s="7">
-        <v>0.21010000000000001</v>
+        <v>0.2162</v>
       </c>
       <c r="U20" s="7">
-        <v>0.20449999999999999</v>
+        <v>0.23269999999999999</v>
       </c>
       <c r="V20" s="7">
-        <v>0.19570000000000001</v>
+        <v>0.25619999999999998</v>
       </c>
       <c r="W20" s="7">
-        <v>0.19120000000000001</v>
+        <v>0.254</v>
       </c>
       <c r="X20" s="7">
-        <v>0.18759999999999999</v>
+        <v>0.2354</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
@@ -29237,67 +29183,67 @@
         <v>21</v>
       </c>
       <c r="C21" s="8">
-        <v>5.7799999999999997E-2</v>
+        <v>6.3299999999999995E-2</v>
       </c>
       <c r="D21" s="7">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="E21" s="7">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="F21" s="7">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="G21" s="7">
+        <v>4.1700000000000001E-2</v>
+      </c>
+      <c r="H21" s="7">
+        <v>3.95E-2</v>
+      </c>
+      <c r="I21" s="7">
         <v>4.6300000000000001E-2</v>
       </c>
-      <c r="E21" s="7">
-        <v>4.4900000000000002E-2</v>
-      </c>
-      <c r="F21" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="G21" s="7">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="H21" s="7">
-        <v>3.3099999999999997E-2</v>
-      </c>
-      <c r="I21" s="7">
-        <v>3.2800000000000003E-2</v>
-      </c>
       <c r="J21" s="7">
-        <v>4.24E-2</v>
+        <v>4.5100000000000001E-2</v>
       </c>
       <c r="K21" s="7">
-        <v>3.8899999999999997E-2</v>
+        <v>3.9199999999999999E-2</v>
       </c>
       <c r="L21" s="7">
-        <v>3.3599999999999998E-2</v>
+        <v>3.6900000000000002E-2</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O21" s="8">
-        <v>0.32369999999999999</v>
+        <v>0.3513</v>
       </c>
       <c r="P21" s="7">
-        <v>0.3135</v>
+        <v>0.33789999999999998</v>
       </c>
       <c r="Q21" s="7">
-        <v>0.3049</v>
+        <v>0.32669999999999999</v>
       </c>
       <c r="R21" s="7">
-        <v>0.2984</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="S21" s="7">
-        <v>0.30049999999999999</v>
+        <v>0.3226</v>
       </c>
       <c r="T21" s="7">
-        <v>0.2853</v>
+        <v>0.30230000000000001</v>
       </c>
       <c r="U21" s="7">
-        <v>0.27879999999999999</v>
+        <v>0.30580000000000002</v>
       </c>
       <c r="V21" s="7">
-        <v>0.27310000000000001</v>
+        <v>0.31359999999999999</v>
       </c>
       <c r="W21" s="7">
-        <v>0.27139999999999997</v>
+        <v>0.30120000000000002</v>
       </c>
       <c r="X21" s="7">
-        <v>0.26669999999999999</v>
+        <v>0.29320000000000002</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
@@ -29317,39 +29263,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="21"/>
-      <c r="N24" s="22" t="s">
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="17"/>
+      <c r="N24" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="19" t="s">
+      <c r="O24" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20"/>
-      <c r="X24" s="21"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="17"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="23"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -29380,7 +29326,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="23"/>
+      <c r="N25" s="14"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -29417,67 +29363,67 @@
         <v>16</v>
       </c>
       <c r="C26" s="7">
-        <v>36.0854</v>
+        <v>35.675800000000002</v>
       </c>
       <c r="D26" s="7">
-        <v>36.509799999999998</v>
+        <v>36.712400000000002</v>
       </c>
       <c r="E26" s="7">
-        <v>33.868099999999998</v>
+        <v>36.871499999999997</v>
       </c>
       <c r="F26" s="7">
-        <v>34.219299999999997</v>
+        <v>35.432099999999998</v>
       </c>
       <c r="G26" s="7">
-        <v>34.019300000000001</v>
+        <v>37.930300000000003</v>
       </c>
       <c r="H26" s="7">
-        <v>34.027700000000003</v>
+        <v>37.258099999999999</v>
       </c>
       <c r="I26" s="7">
-        <v>34.375999999999998</v>
+        <v>35.497599999999998</v>
       </c>
       <c r="J26" s="7">
-        <v>33.9512</v>
+        <v>37.010800000000003</v>
       </c>
       <c r="K26" s="7">
-        <v>33.910499999999999</v>
+        <v>37.037599999999998</v>
       </c>
       <c r="L26" s="7">
-        <v>35.554200000000002</v>
+        <v>37.018799999999999</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O26" s="7">
-        <v>868.13469999999995</v>
+        <v>909.13030000000003</v>
       </c>
       <c r="P26" s="7">
-        <v>849.78009999999995</v>
+        <v>909.67070000000001</v>
       </c>
       <c r="Q26" s="7">
-        <v>854.62429999999995</v>
+        <v>899.23199999999997</v>
       </c>
       <c r="R26" s="7">
-        <v>848.30889999999999</v>
+        <v>866.82849999999996</v>
       </c>
       <c r="S26" s="7">
-        <v>848.26819999999998</v>
+        <v>857.54229999999995</v>
       </c>
       <c r="T26" s="7">
-        <v>846.68939999999998</v>
+        <v>850.62350000000004</v>
       </c>
       <c r="U26" s="7">
-        <v>846.56410000000005</v>
+        <v>857.10140000000001</v>
       </c>
       <c r="V26" s="7">
-        <v>848.04020000000003</v>
+        <v>858.88520000000005</v>
       </c>
       <c r="W26" s="7">
-        <v>849.45920000000001</v>
+        <v>850.27059999999994</v>
       </c>
       <c r="X26" s="7">
-        <v>846.13109999999995</v>
+        <v>850.89160000000004</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
@@ -29485,67 +29431,67 @@
         <v>17</v>
       </c>
       <c r="C27" s="7">
-        <v>46.733600000000003</v>
+        <v>48.039099999999998</v>
       </c>
       <c r="D27" s="7">
-        <v>47.954599999999999</v>
+        <v>49.254300000000001</v>
       </c>
       <c r="E27" s="7">
-        <v>45.374899999999997</v>
+        <v>46.451799999999999</v>
       </c>
       <c r="F27" s="7">
-        <v>44.984900000000003</v>
+        <v>46.698099999999997</v>
       </c>
       <c r="G27" s="7">
-        <v>47.805799999999998</v>
+        <v>45.626399999999997</v>
       </c>
       <c r="H27" s="7">
-        <v>45.228400000000001</v>
+        <v>45.720300000000002</v>
       </c>
       <c r="I27" s="7">
-        <v>44.974200000000003</v>
+        <v>46.790999999999997</v>
       </c>
       <c r="J27" s="7">
-        <v>44.585000000000001</v>
+        <v>46.448500000000003</v>
       </c>
       <c r="K27" s="7">
-        <v>44.2239</v>
+        <v>45.9358</v>
       </c>
       <c r="L27" s="7">
-        <v>43.9114</v>
+        <v>46.936799999999998</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O27" s="7">
-        <v>1071.5481</v>
+        <v>1081.7791</v>
       </c>
       <c r="P27" s="7">
-        <v>1090.5035</v>
+        <v>1082.0320999999999</v>
       </c>
       <c r="Q27" s="7">
-        <v>1152.9730999999999</v>
+        <v>1080.5248999999999</v>
       </c>
       <c r="R27" s="7">
-        <v>1079.67</v>
+        <v>1080.0183</v>
       </c>
       <c r="S27" s="7">
-        <v>1071.8521000000001</v>
+        <v>1080.096</v>
       </c>
       <c r="T27" s="7">
-        <v>1076.0916999999999</v>
+        <v>1083.9747</v>
       </c>
       <c r="U27" s="7">
-        <v>1070.2357</v>
+        <v>1078.3568</v>
       </c>
       <c r="V27" s="7">
-        <v>1070.7905000000001</v>
+        <v>1077.8314</v>
       </c>
       <c r="W27" s="7">
-        <v>1074.7999</v>
+        <v>1079.1531</v>
       </c>
       <c r="X27" s="7">
-        <v>1071.2733000000001</v>
+        <v>1083.7098000000001</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
@@ -29553,67 +29499,67 @@
         <v>18</v>
       </c>
       <c r="C28" s="7">
-        <v>79.555599999999998</v>
+        <v>85.962199999999996</v>
       </c>
       <c r="D28" s="7">
-        <v>82.736500000000007</v>
+        <v>84.285899999999998</v>
       </c>
       <c r="E28" s="7">
-        <v>81.874399999999994</v>
+        <v>82.863500000000002</v>
       </c>
       <c r="F28" s="7">
-        <v>84.866299999999995</v>
+        <v>86.194500000000005</v>
       </c>
       <c r="G28" s="7">
-        <v>83.398899999999998</v>
+        <v>84.076899999999995</v>
       </c>
       <c r="H28" s="7">
-        <v>83.856399999999994</v>
+        <v>85.337100000000007</v>
       </c>
       <c r="I28" s="7">
-        <v>83.703199999999995</v>
+        <v>85.918700000000001</v>
       </c>
       <c r="J28" s="7">
-        <v>83.741500000000002</v>
+        <v>85.579499999999996</v>
       </c>
       <c r="K28" s="7">
-        <v>83.297600000000003</v>
+        <v>84.610100000000003</v>
       </c>
       <c r="L28" s="7">
-        <v>83.440100000000001</v>
+        <v>84.556799999999996</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O28" s="7">
-        <v>1992.8765000000001</v>
+        <v>2001.1396999999999</v>
       </c>
       <c r="P28" s="7">
-        <v>1989.4703</v>
+        <v>2007.7188000000001</v>
       </c>
       <c r="Q28" s="7">
-        <v>1993.2145</v>
+        <v>1998.1309000000001</v>
       </c>
       <c r="R28" s="7">
-        <v>1985.0156999999999</v>
+        <v>1997.8281999999999</v>
       </c>
       <c r="S28" s="7">
-        <v>2013.2155</v>
+        <v>1997.511</v>
       </c>
       <c r="T28" s="7">
-        <v>1981.0583999999999</v>
+        <v>1996.4679000000001</v>
       </c>
       <c r="U28" s="7">
-        <v>1991.2945</v>
+        <v>2013.5752</v>
       </c>
       <c r="V28" s="7">
-        <v>1982.3389</v>
+        <v>1996.3225</v>
       </c>
       <c r="W28" s="7">
-        <v>1990.1155000000001</v>
+        <v>2005.316</v>
       </c>
       <c r="X28" s="7">
-        <v>1983.6434999999999</v>
+        <v>1994.0840000000001</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.25">
@@ -29621,67 +29567,67 @@
         <v>19</v>
       </c>
       <c r="C29" s="7">
-        <v>0.87250000000000005</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="D29" s="7">
-        <v>0.80549999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="E29" s="7">
-        <v>0.80269999999999997</v>
+        <v>0.79469999999999996</v>
       </c>
       <c r="F29" s="7">
-        <v>0.79690000000000005</v>
+        <v>0.8044</v>
       </c>
       <c r="G29" s="7">
-        <v>0.80130000000000001</v>
+        <v>0.79610000000000003</v>
       </c>
       <c r="H29" s="7">
-        <v>0.79749999999999999</v>
+        <v>0.78969999999999996</v>
       </c>
       <c r="I29" s="7">
-        <v>0.84009999999999996</v>
+        <v>0.78149999999999997</v>
       </c>
       <c r="J29" s="7">
-        <v>0.81840000000000002</v>
+        <v>0.79039999999999999</v>
       </c>
       <c r="K29" s="7">
-        <v>0.81240000000000001</v>
+        <v>0.79169999999999996</v>
       </c>
       <c r="L29" s="7">
-        <v>0.82220000000000004</v>
+        <v>0.79459999999999997</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O29" s="7">
-        <v>4.6365999999999996</v>
+        <v>4.6653000000000002</v>
       </c>
       <c r="P29" s="7">
-        <v>4.5749000000000004</v>
+        <v>4.5583</v>
       </c>
       <c r="Q29" s="7">
-        <v>4.5422000000000002</v>
+        <v>4.5913000000000004</v>
       </c>
       <c r="R29" s="7">
-        <v>4.5556999999999999</v>
+        <v>4.5765000000000002</v>
       </c>
       <c r="S29" s="7">
-        <v>4.6478000000000002</v>
+        <v>4.5471000000000004</v>
       </c>
       <c r="T29" s="7">
-        <v>4.5381</v>
+        <v>4.6257999999999999</v>
       </c>
       <c r="U29" s="7">
-        <v>4.5664999999999996</v>
+        <v>4.5568</v>
       </c>
       <c r="V29" s="7">
-        <v>4.8815999999999997</v>
+        <v>4.5750999999999999</v>
       </c>
       <c r="W29" s="7">
-        <v>4.4542000000000002</v>
+        <v>4.6075999999999997</v>
       </c>
       <c r="X29" s="7">
-        <v>4.4679000000000002</v>
+        <v>4.6936999999999998</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.25">
@@ -29689,67 +29635,67 @@
         <v>20</v>
       </c>
       <c r="C30" s="7">
-        <v>0.5514</v>
+        <v>0.55069999999999997</v>
       </c>
       <c r="D30" s="7">
-        <v>0.54400000000000004</v>
+        <v>0.54220000000000002</v>
       </c>
       <c r="E30" s="7">
-        <v>0.54100000000000004</v>
+        <v>0.53939999999999999</v>
       </c>
       <c r="F30" s="7">
-        <v>0.53310000000000002</v>
+        <v>0.53539999999999999</v>
       </c>
       <c r="G30" s="7">
-        <v>0.53280000000000005</v>
+        <v>0.53779999999999994</v>
       </c>
       <c r="H30" s="7">
-        <v>0.53800000000000003</v>
+        <v>0.53110000000000002</v>
       </c>
       <c r="I30" s="7">
-        <v>0.54359999999999997</v>
+        <v>0.52980000000000005</v>
       </c>
       <c r="J30" s="7">
-        <v>0.53590000000000004</v>
+        <v>0.53210000000000002</v>
       </c>
       <c r="K30" s="7">
-        <v>0.69499999999999995</v>
+        <v>0.56279999999999997</v>
       </c>
       <c r="L30" s="7">
-        <v>0.53900000000000003</v>
+        <v>0.53449999999999998</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O30" s="7">
-        <v>3.0779000000000001</v>
+        <v>3.1572</v>
       </c>
       <c r="P30" s="7">
-        <v>3.5038</v>
+        <v>3.1311</v>
       </c>
       <c r="Q30" s="7">
-        <v>3.0491000000000001</v>
+        <v>3.1396000000000002</v>
       </c>
       <c r="R30" s="7">
-        <v>3.0448</v>
+        <v>3.1873999999999998</v>
       </c>
       <c r="S30" s="7">
-        <v>3.0613999999999999</v>
+        <v>3.1560000000000001</v>
       </c>
       <c r="T30" s="7">
-        <v>3.0707</v>
+        <v>3.1383999999999999</v>
       </c>
       <c r="U30" s="7">
-        <v>3.1352000000000002</v>
+        <v>3.1349999999999998</v>
       </c>
       <c r="V30" s="7">
-        <v>3.0949</v>
+        <v>3.1322999999999999</v>
       </c>
       <c r="W30" s="7">
-        <v>3.1633</v>
+        <v>3.4416000000000002</v>
       </c>
       <c r="X30" s="7">
-        <v>3.1067</v>
+        <v>3.0897999999999999</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
@@ -29757,81 +29703,81 @@
         <v>21</v>
       </c>
       <c r="C31" s="8">
-        <v>0.70840000000000003</v>
+        <v>0.71789999999999998</v>
       </c>
       <c r="D31" s="7">
-        <v>0.70630000000000004</v>
+        <v>0.71660000000000001</v>
       </c>
       <c r="E31" s="7">
-        <v>0.69440000000000002</v>
+        <v>0.70530000000000004</v>
       </c>
       <c r="F31" s="7">
-        <v>0.69259999999999999</v>
+        <v>0.69779999999999998</v>
       </c>
       <c r="G31" s="7">
-        <v>0.69130000000000003</v>
+        <v>0.69230000000000003</v>
       </c>
       <c r="H31" s="7">
-        <v>0.69830000000000003</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="I31" s="7">
-        <v>0.68640000000000001</v>
+        <v>0.69540000000000002</v>
       </c>
       <c r="J31" s="7">
-        <v>0.68559999999999999</v>
+        <v>0.68469999999999998</v>
       </c>
       <c r="K31" s="7">
-        <v>0.68230000000000002</v>
+        <v>0.68569999999999998</v>
       </c>
       <c r="L31" s="7">
-        <v>0.68420000000000003</v>
+        <v>0.69120000000000004</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O31" s="8">
-        <v>3.8971</v>
+        <v>3.7201</v>
       </c>
       <c r="P31" s="7">
-        <v>3.9605999999999999</v>
+        <v>3.7606000000000002</v>
       </c>
       <c r="Q31" s="7">
-        <v>3.9091999999999998</v>
+        <v>3.9746000000000001</v>
       </c>
       <c r="R31" s="7">
-        <v>3.9257</v>
+        <v>3.9140000000000001</v>
       </c>
       <c r="S31" s="7">
-        <v>3.9053</v>
+        <v>3.6999</v>
       </c>
       <c r="T31" s="7">
-        <v>4.2199</v>
+        <v>3.7429000000000001</v>
       </c>
       <c r="U31" s="7">
-        <v>3.7858000000000001</v>
+        <v>3.8731</v>
       </c>
       <c r="V31" s="7">
-        <v>3.8134000000000001</v>
+        <v>4.2115999999999998</v>
       </c>
       <c r="W31" s="7">
-        <v>3.8363999999999998</v>
+        <v>3.7288000000000001</v>
       </c>
       <c r="X31" s="7">
-        <v>3.9007000000000001</v>
+        <v>3.8300999999999998</v>
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="26"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="17"/>
       <c r="K34" s="1" t="s">
         <v>25</v>
       </c>
@@ -29861,7 +29807,7 @@
       </c>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="23"/>
+      <c r="B35" s="14"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -29914,27 +29860,27 @@
       </c>
       <c r="C36" s="7">
         <f t="shared" ref="C36:C41" si="0">IF(COUNTBLANK(C6:L6)&gt;0,"undone",TRIMMEAN(C6:L6,2/COUNT(C6:L6)))</f>
-        <v>3.2374999999999991E-3</v>
+        <v>4.8124999999999991E-3</v>
       </c>
       <c r="D36" s="7">
         <f t="shared" ref="D36:D41" si="1">IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
-        <v>9.2087499999999989E-2</v>
+        <v>0.13966250000000002</v>
       </c>
       <c r="E36" s="7">
         <f t="shared" ref="E36:E41" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
-        <v>0.32903749999999998</v>
+        <v>0.38126250000000006</v>
       </c>
       <c r="F36" s="7">
         <f t="shared" ref="F36:F41" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
-        <v>8.5749499999999994</v>
+        <v>9.1625374999999991</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" ref="G36:G41" si="4">IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
-        <v>34.517949999999999</v>
+        <v>36.635325000000002</v>
       </c>
       <c r="H36" s="7">
         <f t="shared" ref="H36:H41" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
-        <v>848.96680000000015</v>
+        <v>868.77935000000002</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>26</v>
@@ -29970,27 +29916,27 @@
       </c>
       <c r="C37" s="7">
         <f t="shared" si="0"/>
-        <v>4.725E-3</v>
+        <v>7.4500000000000009E-3</v>
       </c>
       <c r="D37" s="7">
         <f t="shared" si="1"/>
-        <v>0.11115</v>
+        <v>0.1338625</v>
       </c>
       <c r="E37" s="7">
         <f t="shared" si="2"/>
-        <v>0.45730000000000004</v>
+        <v>0.67284999999999995</v>
       </c>
       <c r="F37" s="7">
         <f t="shared" si="3"/>
-        <v>10.927024999999999</v>
+        <v>11.793262499999999</v>
       </c>
       <c r="G37" s="7">
         <f t="shared" si="4"/>
-        <v>45.488837500000002</v>
+        <v>46.627675000000004</v>
       </c>
       <c r="H37" s="7">
         <f t="shared" si="5"/>
-        <v>1075.8161375</v>
+        <v>1080.7087624999999</v>
       </c>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
@@ -29999,27 +29945,27 @@
       </c>
       <c r="C38" s="7">
         <f t="shared" si="0"/>
-        <v>7.9500000000000005E-3</v>
+        <v>1.2637499999999998E-2</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="1"/>
-        <v>0.20223750000000001</v>
+        <v>0.22673750000000004</v>
       </c>
       <c r="E38" s="7">
         <f t="shared" si="2"/>
-        <v>0.8023125000000001</v>
+        <v>0.97297500000000003</v>
       </c>
       <c r="F38" s="7">
         <f t="shared" si="3"/>
-        <v>19.875374999999998</v>
+        <v>21.582700000000003</v>
       </c>
       <c r="G38" s="7">
         <f t="shared" si="4"/>
-        <v>83.256074999999996</v>
+        <v>85.040899999999993</v>
       </c>
       <c r="H38" s="7">
         <f t="shared" si="5"/>
-        <v>1988.4961750000002</v>
+        <v>2000.0543750000002</v>
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
@@ -30028,27 +29974,27 @@
       </c>
       <c r="C39" s="7">
         <f t="shared" si="0"/>
-        <v>2.8250000000000003E-3</v>
+        <v>4.4374999999999996E-3</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="1"/>
-        <v>1.7975000000000001E-2</v>
+        <v>2.1587499999999999E-2</v>
       </c>
       <c r="E39" s="7">
         <f t="shared" si="2"/>
-        <v>3.8687499999999993E-2</v>
+        <v>4.1737500000000004E-2</v>
       </c>
       <c r="F39" s="7">
         <f t="shared" si="3"/>
-        <v>0.36593750000000003</v>
+        <v>0.35088750000000002</v>
       </c>
       <c r="G39" s="7">
         <f t="shared" si="4"/>
-        <v>0.81251249999999997</v>
+        <v>0.79519999999999991</v>
       </c>
       <c r="H39" s="7">
         <f t="shared" si="5"/>
-        <v>4.5662125000000007</v>
+        <v>4.5945875000000003</v>
       </c>
       <c r="J39" s="9"/>
     </row>
@@ -30058,27 +30004,27 @@
       </c>
       <c r="C40" s="7">
         <f t="shared" si="0"/>
-        <v>1.5999999999999999E-3</v>
+        <v>2.3625E-3</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="1"/>
-        <v>9.1750000000000009E-3</v>
+        <v>1.2125E-2</v>
       </c>
       <c r="E40" s="7">
         <f t="shared" si="2"/>
-        <v>2.0137499999999999E-2</v>
+        <v>2.2712500000000004E-2</v>
       </c>
       <c r="F40" s="7">
         <f t="shared" si="3"/>
-        <v>0.21444999999999997</v>
+        <v>0.273725</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="4"/>
-        <v>0.54075000000000006</v>
+        <v>0.53790000000000004</v>
       </c>
       <c r="H40" s="7">
         <f t="shared" si="5"/>
-        <v>3.0949</v>
+        <v>3.147125</v>
       </c>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
@@ -30087,27 +30033,27 @@
       </c>
       <c r="C41" s="7">
         <f t="shared" si="0"/>
-        <v>3.0625000000000001E-3</v>
+        <v>4.5374999999999999E-3</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="1"/>
-        <v>1.7774999999999999E-2</v>
+        <v>2.4125000000000001E-2</v>
       </c>
       <c r="E41" s="7">
         <f t="shared" si="2"/>
-        <v>3.9275000000000004E-2</v>
+        <v>4.4487499999999999E-2</v>
       </c>
       <c r="F41" s="7">
         <f t="shared" si="3"/>
-        <v>0.29073749999999998</v>
+        <v>0.31668750000000001</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="4"/>
-        <v>0.69238750000000004</v>
+        <v>0.69691249999999993</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="5"/>
-        <v>3.8935500000000003</v>
+        <v>3.8180250000000004</v>
       </c>
     </row>
     <row r="44" spans="2:17" ht="27.6" x14ac:dyDescent="0.25">
@@ -30159,10 +30105,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="12"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -30181,39 +30127,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="21"/>
-      <c r="N4" s="22" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="17"/>
+      <c r="N4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="19" t="s">
+      <c r="O4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20"/>
-      <c r="X4" s="21"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="17"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="23"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -30244,7 +30190,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="23"/>
+      <c r="N5" s="14"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -30287,7 +30233,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="E6" s="7">
-        <v>2.0000000000000001E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="F6" s="7">
         <v>2.0000000000000001E-4</v>
@@ -30296,19 +30242,19 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="H6" s="7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="I6" s="7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="J6" s="7">
         <v>1E-4</v>
       </c>
-      <c r="I6" s="7">
+      <c r="K6" s="7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="L6" s="7">
         <v>1E-4</v>
-      </c>
-      <c r="J6" s="7">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="K6" s="7">
-        <v>1E-4</v>
-      </c>
-      <c r="L6" s="7">
-        <v>2.0000000000000001E-4</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>16</v>
@@ -30323,10 +30269,10 @@
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="R6" s="7">
-        <v>8.0000000000000004E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="S6" s="7">
-        <v>8.0000000000000004E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="T6" s="7">
         <v>8.0000000000000004E-4</v>
@@ -30335,10 +30281,10 @@
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="V6" s="7">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="W6" s="7">
         <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="W6" s="7">
-        <v>8.0000000000000004E-4</v>
       </c>
       <c r="X6" s="7">
         <v>8.0000000000000004E-4</v>
@@ -30349,31 +30295,31 @@
         <v>17</v>
       </c>
       <c r="C7" s="7">
-        <v>5.3E-3</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="D7" s="7">
         <v>4.8999999999999998E-3</v>
       </c>
       <c r="E7" s="7">
-        <v>4.4000000000000003E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="F7" s="7">
         <v>4.4000000000000003E-3</v>
       </c>
       <c r="G7" s="7">
-        <v>4.3E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="H7" s="7">
         <v>4.3E-3</v>
       </c>
       <c r="I7" s="7">
-        <v>4.3E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="J7" s="7">
-        <v>4.3E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="K7" s="7">
-        <v>4.3E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="L7" s="7">
         <v>4.4000000000000003E-3</v>
@@ -30382,34 +30328,34 @@
         <v>17</v>
       </c>
       <c r="O7" s="7">
-        <v>0.11260000000000001</v>
+        <v>0.1105</v>
       </c>
       <c r="P7" s="7">
-        <v>0.1056</v>
+        <v>0.1074</v>
       </c>
       <c r="Q7" s="7">
-        <v>0.1057</v>
+        <v>0.1075</v>
       </c>
       <c r="R7" s="7">
-        <v>0.1056</v>
+        <v>0.1074</v>
       </c>
       <c r="S7" s="7">
-        <v>0.1057</v>
+        <v>0.1075</v>
       </c>
       <c r="T7" s="7">
-        <v>0.1057</v>
+        <v>0.1152</v>
       </c>
       <c r="U7" s="7">
-        <v>0.1057</v>
+        <v>0.1074</v>
       </c>
       <c r="V7" s="7">
-        <v>0.1056</v>
+        <v>0.1074</v>
       </c>
       <c r="W7" s="7">
-        <v>0.1057</v>
+        <v>0.1074</v>
       </c>
       <c r="X7" s="7">
-        <v>0.1057</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -30420,10 +30366,10 @@
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="D8" s="7">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="E8" s="7">
         <v>5.1999999999999998E-3</v>
-      </c>
-      <c r="E8" s="7">
-        <v>5.1000000000000004E-3</v>
       </c>
       <c r="F8" s="7">
         <v>5.1000000000000004E-3</v>
@@ -30444,40 +30390,40 @@
         <v>5.1000000000000004E-3</v>
       </c>
       <c r="L8" s="7">
-        <v>5.0000000000000001E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O8" s="7">
-        <v>0.1242</v>
+        <v>0.12620000000000001</v>
       </c>
       <c r="P8" s="7">
-        <v>0.1242</v>
+        <v>0.12620000000000001</v>
       </c>
       <c r="Q8" s="7">
-        <v>0.1242</v>
+        <v>0.12620000000000001</v>
       </c>
       <c r="R8" s="7">
-        <v>0.1242</v>
+        <v>0.12609999999999999</v>
       </c>
       <c r="S8" s="7">
-        <v>0.1283</v>
+        <v>0.13070000000000001</v>
       </c>
       <c r="T8" s="7">
-        <v>0.1249</v>
+        <v>0.1313</v>
       </c>
       <c r="U8" s="7">
-        <v>0.12479999999999999</v>
+        <v>0.1275</v>
       </c>
       <c r="V8" s="7">
-        <v>0.12770000000000001</v>
+        <v>0.1275</v>
       </c>
       <c r="W8" s="7">
-        <v>0.1249</v>
+        <v>0.12740000000000001</v>
       </c>
       <c r="X8" s="7">
-        <v>0.12479999999999999</v>
+        <v>0.1275</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -30485,67 +30431,67 @@
         <v>19</v>
       </c>
       <c r="C9" s="7">
-        <v>3.3999999999999998E-3</v>
+        <v>3.3E-3</v>
       </c>
       <c r="D9" s="7">
         <v>2.7000000000000001E-3</v>
       </c>
       <c r="E9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="F9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="G9" s="7">
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="H9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="I9" s="7">
         <v>2.7000000000000001E-3</v>
       </c>
       <c r="J9" s="7">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="K9" s="7">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="L9" s="7">
         <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="K9" s="7">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="L9" s="7">
-        <v>2.7000000000000001E-3</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O9" s="7">
+        <v>1.67E-2</v>
+      </c>
+      <c r="P9" s="7">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="R9" s="7">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="S9" s="7">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="T9" s="7">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="U9" s="7">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="V9" s="7">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="W9" s="7">
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="P9" s="7">
-        <v>1.61E-2</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>1.6E-2</v>
-      </c>
-      <c r="R9" s="7">
-        <v>1.6E-2</v>
-      </c>
-      <c r="S9" s="7">
-        <v>1.6E-2</v>
-      </c>
-      <c r="T9" s="7">
-        <v>1.61E-2</v>
-      </c>
-      <c r="U9" s="7">
-        <v>1.5900000000000001E-2</v>
-      </c>
-      <c r="V9" s="7">
-        <v>1.61E-2</v>
-      </c>
-      <c r="W9" s="7">
-        <v>1.5900000000000001E-2</v>
-      </c>
       <c r="X9" s="7">
-        <v>1.61E-2</v>
+        <v>1.6199999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -30553,67 +30499,67 @@
         <v>20</v>
       </c>
       <c r="C10" s="7">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D10" s="7">
         <v>4.7999999999999996E-3</v>
-      </c>
-      <c r="D10" s="7">
-        <v>4.7000000000000002E-3</v>
       </c>
       <c r="E10" s="7">
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="F10" s="7">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="G10" s="7">
         <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="G10" s="7">
-        <v>4.3E-3</v>
       </c>
       <c r="H10" s="7">
         <v>4.3E-3</v>
       </c>
       <c r="I10" s="7">
-        <v>4.3E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="J10" s="7">
         <v>4.4000000000000003E-3</v>
       </c>
       <c r="K10" s="7">
-        <v>4.3E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="L10" s="7">
-        <v>4.3E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O10" s="7">
-        <v>9.9199999999999997E-2</v>
+        <v>9.8100000000000007E-2</v>
       </c>
       <c r="P10" s="7">
-        <v>9.9099999999999994E-2</v>
+        <v>0.1016</v>
       </c>
       <c r="Q10" s="7">
-        <v>9.9299999999999999E-2</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="R10" s="7">
-        <v>9.9400000000000002E-2</v>
+        <v>0.1011</v>
       </c>
       <c r="S10" s="7">
-        <v>9.9199999999999997E-2</v>
+        <v>0.1016</v>
       </c>
       <c r="T10" s="7">
-        <v>0.1113</v>
+        <v>0.1014</v>
       </c>
       <c r="U10" s="7">
-        <v>8.3599999999999994E-2</v>
+        <v>0.10150000000000001</v>
       </c>
       <c r="V10" s="7">
-        <v>8.3400000000000002E-2</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="W10" s="7">
-        <v>8.3199999999999996E-2</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="X10" s="7">
-        <v>8.3599999999999994E-2</v>
+        <v>0.1007</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -30621,67 +30567,67 @@
         <v>21</v>
       </c>
       <c r="C11" s="8">
-        <v>3.0999999999999999E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="D11" s="7">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="E11" s="7">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="F11" s="7">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="G11" s="7">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="H11" s="7">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="F11" s="7">
-        <v>2.3999999999999998E-3</v>
-      </c>
-      <c r="G11" s="7">
-        <v>2.3E-3</v>
-      </c>
-      <c r="H11" s="7">
-        <v>2.5000000000000001E-3</v>
-      </c>
       <c r="I11" s="7">
-        <v>2.3999999999999998E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="J11" s="7">
-        <v>2.3999999999999998E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="K11" s="7">
-        <v>2.3999999999999998E-3</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="L11" s="7">
-        <v>2.3E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O11" s="8">
-        <v>1.34E-2</v>
+        <v>1.77E-2</v>
       </c>
       <c r="P11" s="7">
-        <v>1.34E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="Q11" s="7">
-        <v>1.24E-2</v>
+        <v>8.8700000000000001E-2</v>
       </c>
       <c r="R11" s="7">
-        <v>1.2200000000000001E-2</v>
+        <v>2.8400000000000002E-2</v>
       </c>
       <c r="S11" s="7">
-        <v>1.2200000000000001E-2</v>
+        <v>2.6200000000000001E-2</v>
       </c>
       <c r="T11" s="7">
-        <v>1.23E-2</v>
+        <v>2.6499999999999999E-2</v>
       </c>
       <c r="U11" s="7">
-        <v>1.23E-2</v>
+        <v>2.1299999999999999E-2</v>
       </c>
       <c r="V11" s="7">
-        <v>1.21E-2</v>
+        <v>2.0400000000000001E-2</v>
       </c>
       <c r="W11" s="7">
-        <v>1.23E-2</v>
+        <v>2.01E-2</v>
       </c>
       <c r="X11" s="7">
-        <v>1.2200000000000001E-2</v>
+        <v>1.9699999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -30701,39 +30647,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="21"/>
-      <c r="N14" s="22" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="17"/>
+      <c r="N14" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="19" t="s">
+      <c r="O14" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="20"/>
-      <c r="U14" s="20"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="20"/>
-      <c r="X14" s="21"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="17"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="23"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -30764,7 +30710,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="23"/>
+      <c r="N15" s="14"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -30801,34 +30747,34 @@
         <v>16</v>
       </c>
       <c r="C16" s="7">
-        <v>1.6999999999999999E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="D16" s="7">
-        <v>1.6000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="E16" s="7">
-        <v>1.6999999999999999E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="F16" s="7">
-        <v>1.6000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G16" s="7">
-        <v>1.6000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="H16" s="7">
-        <v>1.6000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="I16" s="7">
-        <v>1.6000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="J16" s="7">
-        <v>1.6000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="K16" s="7">
-        <v>1.6000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="L16" s="7">
-        <v>1.6000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>16</v>
@@ -30843,10 +30789,10 @@
         <v>7.3000000000000001E-3</v>
       </c>
       <c r="R16" s="7">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="S16" s="7">
         <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="S16" s="7">
-        <v>7.3000000000000001E-3</v>
       </c>
       <c r="T16" s="7">
         <v>7.4000000000000003E-3</v>
@@ -30858,7 +30804,7 @@
         <v>7.4000000000000003E-3</v>
       </c>
       <c r="W16" s="7">
-        <v>7.4000000000000003E-3</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="X16" s="7">
         <v>7.4000000000000003E-3</v>
@@ -30869,67 +30815,67 @@
         <v>17</v>
       </c>
       <c r="C17" s="7">
-        <v>0.43509999999999999</v>
+        <v>0.4728</v>
       </c>
       <c r="D17" s="7">
-        <v>0.42149999999999999</v>
+        <v>0.42830000000000001</v>
       </c>
       <c r="E17" s="7">
-        <v>0.42149999999999999</v>
+        <v>0.42130000000000001</v>
       </c>
       <c r="F17" s="7">
-        <v>0.4214</v>
+        <v>0.42559999999999998</v>
       </c>
       <c r="G17" s="7">
-        <v>0.42430000000000001</v>
+        <v>0.41320000000000001</v>
       </c>
       <c r="H17" s="7">
-        <v>0.42220000000000002</v>
+        <v>0.41310000000000002</v>
       </c>
       <c r="I17" s="7">
-        <v>0.42730000000000001</v>
+        <v>0.41310000000000002</v>
       </c>
       <c r="J17" s="7">
-        <v>0.42449999999999999</v>
+        <v>0.41310000000000002</v>
       </c>
       <c r="K17" s="7">
-        <v>0.42749999999999999</v>
+        <v>0.42249999999999999</v>
       </c>
       <c r="L17" s="7">
-        <v>0.42880000000000001</v>
+        <v>0.41570000000000001</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O17" s="7">
-        <v>10.6355</v>
+        <v>10.7676</v>
       </c>
       <c r="P17" s="7">
-        <v>12.818099999999999</v>
+        <v>10.875</v>
       </c>
       <c r="Q17" s="7">
-        <v>10.764799999999999</v>
+        <v>10.694900000000001</v>
       </c>
       <c r="R17" s="7">
-        <v>10.975899999999999</v>
+        <v>10.8988</v>
       </c>
       <c r="S17" s="7">
-        <v>10.452</v>
+        <v>10.5893</v>
       </c>
       <c r="T17" s="7">
-        <v>10.635199999999999</v>
+        <v>10.6539</v>
       </c>
       <c r="U17" s="7">
-        <v>10.6526</v>
+        <v>10.716799999999999</v>
       </c>
       <c r="V17" s="7">
-        <v>10.620699999999999</v>
+        <v>11.0623</v>
       </c>
       <c r="W17" s="7">
-        <v>10.8705</v>
+        <v>10.667999999999999</v>
       </c>
       <c r="X17" s="7">
-        <v>10.756399999999999</v>
+        <v>10.880599999999999</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
@@ -30937,67 +30883,67 @@
         <v>18</v>
       </c>
       <c r="C18" s="7">
-        <v>0.50090000000000001</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="D18" s="7">
-        <v>0.50090000000000001</v>
+        <v>0.49430000000000002</v>
       </c>
       <c r="E18" s="7">
-        <v>0.501</v>
+        <v>0.49430000000000002</v>
       </c>
       <c r="F18" s="7">
-        <v>0.50380000000000003</v>
+        <v>0.49569999999999997</v>
       </c>
       <c r="G18" s="7">
-        <v>0.50170000000000003</v>
+        <v>0.49390000000000001</v>
       </c>
       <c r="H18" s="7">
-        <v>0.49590000000000001</v>
+        <v>0.49680000000000002</v>
       </c>
       <c r="I18" s="7">
-        <v>0.49590000000000001</v>
+        <v>0.49359999999999998</v>
       </c>
       <c r="J18" s="7">
-        <v>0.49869999999999998</v>
+        <v>0.49370000000000003</v>
       </c>
       <c r="K18" s="7">
-        <v>0.49580000000000002</v>
+        <v>0.49370000000000003</v>
       </c>
       <c r="L18" s="7">
-        <v>0.49569999999999997</v>
+        <v>0.49630000000000002</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O18" s="7">
-        <v>12.281499999999999</v>
+        <v>12.4415</v>
       </c>
       <c r="P18" s="7">
-        <v>12.3811</v>
+        <v>12.48</v>
       </c>
       <c r="Q18" s="7">
-        <v>12.477499999999999</v>
+        <v>12.531000000000001</v>
       </c>
       <c r="R18" s="7">
-        <v>12.4749</v>
+        <v>12.525499999999999</v>
       </c>
       <c r="S18" s="7">
-        <v>12.6495</v>
+        <v>12.5306</v>
       </c>
       <c r="T18" s="7">
-        <v>12.4552</v>
+        <v>12.663399999999999</v>
       </c>
       <c r="U18" s="7">
-        <v>12.4793</v>
+        <v>12.2395</v>
       </c>
       <c r="V18" s="7">
-        <v>12.6523</v>
+        <v>12.3895</v>
       </c>
       <c r="W18" s="7">
-        <v>12.405900000000001</v>
+        <v>12.596</v>
       </c>
       <c r="X18" s="7">
-        <v>12.3338</v>
+        <v>12.5985</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
@@ -31005,67 +30951,67 @@
         <v>19</v>
       </c>
       <c r="C19" s="7">
-        <v>3.4700000000000002E-2</v>
+        <v>3.5099999999999999E-2</v>
       </c>
       <c r="D19" s="7">
-        <v>3.4500000000000003E-2</v>
+        <v>3.44E-2</v>
       </c>
       <c r="E19" s="7">
         <v>3.4500000000000003E-2</v>
       </c>
       <c r="F19" s="7">
-        <v>3.44E-2</v>
+        <v>3.4299999999999997E-2</v>
       </c>
       <c r="G19" s="7">
         <v>3.4500000000000003E-2</v>
       </c>
       <c r="H19" s="7">
-        <v>3.4700000000000002E-2</v>
+        <v>3.4299999999999997E-2</v>
       </c>
       <c r="I19" s="7">
-        <v>4.7699999999999999E-2</v>
+        <v>3.44E-2</v>
       </c>
       <c r="J19" s="7">
-        <v>4.8500000000000001E-2</v>
+        <v>3.44E-2</v>
       </c>
       <c r="K19" s="7">
-        <v>4.0300000000000002E-2</v>
+        <v>3.4299999999999997E-2</v>
       </c>
       <c r="L19" s="7">
-        <v>3.4500000000000003E-2</v>
+        <v>3.44E-2</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O19" s="7">
-        <v>0.20760000000000001</v>
+        <v>0.2122</v>
       </c>
       <c r="P19" s="7">
-        <v>0.20949999999999999</v>
+        <v>0.2114</v>
       </c>
       <c r="Q19" s="7">
-        <v>0.2041</v>
+        <v>0.21060000000000001</v>
       </c>
       <c r="R19" s="7">
-        <v>0.20399999999999999</v>
+        <v>0.20610000000000001</v>
       </c>
       <c r="S19" s="7">
-        <v>0.20430000000000001</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="T19" s="7">
-        <v>0.2041</v>
+        <v>0.2064</v>
       </c>
       <c r="U19" s="7">
-        <v>0.2041</v>
+        <v>0.21190000000000001</v>
       </c>
       <c r="V19" s="7">
-        <v>0.2044</v>
+        <v>0.20630000000000001</v>
       </c>
       <c r="W19" s="7">
-        <v>0.20380000000000001</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="X19" s="7">
-        <v>0.20399999999999999</v>
+        <v>0.20810000000000001</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.25">
@@ -31073,67 +31019,67 @@
         <v>20</v>
       </c>
       <c r="C20" s="7">
-        <v>0.38779999999999998</v>
+        <v>0.38600000000000001</v>
       </c>
       <c r="D20" s="7">
-        <v>0.3911</v>
+        <v>0.38600000000000001</v>
       </c>
       <c r="E20" s="7">
-        <v>0.38790000000000002</v>
+        <v>0.38569999999999999</v>
       </c>
       <c r="F20" s="7">
-        <v>0.3876</v>
+        <v>0.38550000000000001</v>
       </c>
       <c r="G20" s="7">
-        <v>0.39029999999999998</v>
+        <v>0.38850000000000001</v>
       </c>
       <c r="H20" s="7">
-        <v>0.38679999999999998</v>
+        <v>0.38529999999999998</v>
       </c>
       <c r="I20" s="7">
-        <v>0.3871</v>
+        <v>0.3856</v>
       </c>
       <c r="J20" s="7">
-        <v>0.38719999999999999</v>
+        <v>0.38540000000000002</v>
       </c>
       <c r="K20" s="7">
-        <v>0.38700000000000001</v>
+        <v>0.3886</v>
       </c>
       <c r="L20" s="7">
-        <v>0.38969999999999999</v>
+        <v>0.3856</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O20" s="7">
-        <v>9.5584000000000007</v>
+        <v>9.6997999999999998</v>
       </c>
       <c r="P20" s="7">
-        <v>9.5318000000000005</v>
+        <v>9.5576000000000008</v>
       </c>
       <c r="Q20" s="7">
-        <v>9.4718999999999998</v>
+        <v>9.6310000000000002</v>
       </c>
       <c r="R20" s="7">
-        <v>9.5315999999999992</v>
+        <v>9.6272000000000002</v>
       </c>
       <c r="S20" s="7">
-        <v>9.5273000000000003</v>
+        <v>9.5707000000000004</v>
       </c>
       <c r="T20" s="7">
-        <v>9.5197000000000003</v>
+        <v>9.6526999999999994</v>
       </c>
       <c r="U20" s="7">
-        <v>9.5466999999999995</v>
+        <v>9.5907999999999998</v>
       </c>
       <c r="V20" s="7">
-        <v>9.5459999999999994</v>
+        <v>9.6067999999999998</v>
       </c>
       <c r="W20" s="7">
-        <v>9.5281000000000002</v>
+        <v>9.8727999999999998</v>
       </c>
       <c r="X20" s="7">
-        <v>9.766</v>
+        <v>9.3752999999999993</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
@@ -31141,67 +31087,67 @@
         <v>21</v>
       </c>
       <c r="C21" s="8">
-        <v>3.15E-2</v>
+        <v>3.5099999999999999E-2</v>
       </c>
       <c r="D21" s="7">
-        <v>2.9700000000000001E-2</v>
+        <v>3.3399999999999999E-2</v>
       </c>
       <c r="E21" s="7">
-        <v>3.0499999999999999E-2</v>
+        <v>3.3500000000000002E-2</v>
       </c>
       <c r="F21" s="7">
-        <v>2.9499999999999998E-2</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="G21" s="7">
-        <v>2.86E-2</v>
+        <v>3.3300000000000003E-2</v>
       </c>
       <c r="H21" s="7">
-        <v>2.8500000000000001E-2</v>
+        <v>3.27E-2</v>
       </c>
       <c r="I21" s="7">
-        <v>2.8500000000000001E-2</v>
+        <v>3.2599999999999997E-2</v>
       </c>
       <c r="J21" s="7">
-        <v>2.8299999999999999E-2</v>
+        <v>3.2500000000000001E-2</v>
       </c>
       <c r="K21" s="7">
-        <v>2.8400000000000002E-2</v>
+        <v>3.2800000000000003E-2</v>
       </c>
       <c r="L21" s="7">
-        <v>2.8500000000000001E-2</v>
+        <v>3.2599999999999997E-2</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O21" s="8">
-        <v>0.1681</v>
+        <v>0.17749999999999999</v>
       </c>
       <c r="P21" s="7">
-        <v>0.15740000000000001</v>
+        <v>0.17610000000000001</v>
       </c>
       <c r="Q21" s="7">
-        <v>0.1573</v>
+        <v>0.17649999999999999</v>
       </c>
       <c r="R21" s="7">
-        <v>0.15759999999999999</v>
+        <v>0.17430000000000001</v>
       </c>
       <c r="S21" s="7">
-        <v>0.1585</v>
+        <v>0.17330000000000001</v>
       </c>
       <c r="T21" s="7">
-        <v>0.15859999999999999</v>
+        <v>0.17150000000000001</v>
       </c>
       <c r="U21" s="7">
-        <v>0.1575</v>
+        <v>0.17050000000000001</v>
       </c>
       <c r="V21" s="7">
-        <v>0.15559999999999999</v>
+        <v>0.17069999999999999</v>
       </c>
       <c r="W21" s="7">
-        <v>0.156</v>
+        <v>0.17069999999999999</v>
       </c>
       <c r="X21" s="7">
-        <v>0.15579999999999999</v>
+        <v>0.17019999999999999</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
@@ -31221,39 +31167,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="21"/>
-      <c r="N24" s="22" t="s">
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="17"/>
+      <c r="N24" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="19" t="s">
+      <c r="O24" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20"/>
-      <c r="X24" s="21"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="17"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="23"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -31284,7 +31230,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="23"/>
+      <c r="N25" s="14"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -31321,67 +31267,67 @@
         <v>16</v>
       </c>
       <c r="C26" s="7">
-        <v>1.4500000000000001E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="D26" s="7">
-        <v>1.4500000000000001E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="E26" s="7">
-        <v>1.4500000000000001E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="F26" s="7">
-        <v>1.44E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="G26" s="7">
-        <v>1.44E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="H26" s="7">
-        <v>1.4500000000000001E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="I26" s="7">
-        <v>1.44E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="J26" s="7">
-        <v>1.44E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="K26" s="7">
-        <v>1.44E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="L26" s="7">
-        <v>1.4500000000000001E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O26" s="7">
-        <v>7.5300000000000006E-2</v>
+        <v>7.4800000000000005E-2</v>
       </c>
       <c r="P26" s="7">
-        <v>8.2000000000000003E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="Q26" s="7">
-        <v>8.2000000000000003E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="R26" s="7">
-        <v>8.2000000000000003E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="S26" s="7">
-        <v>8.1900000000000001E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="T26" s="7">
-        <v>8.2000000000000003E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="U26" s="7">
-        <v>8.1900000000000001E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="V26" s="7">
-        <v>8.7300000000000003E-2</v>
+        <v>8.14E-2</v>
       </c>
       <c r="W26" s="7">
-        <v>8.3599999999999994E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="X26" s="7">
-        <v>8.2000000000000003E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
@@ -31389,67 +31335,67 @@
         <v>17</v>
       </c>
       <c r="C27" s="7">
-        <v>42.495199999999997</v>
+        <v>42.798400000000001</v>
       </c>
       <c r="D27" s="7">
-        <v>42.446399999999997</v>
+        <v>43.040799999999997</v>
       </c>
       <c r="E27" s="7">
-        <v>43.199399999999997</v>
+        <v>42.493600000000001</v>
       </c>
       <c r="F27" s="7">
-        <v>43.211100000000002</v>
+        <v>42.705199999999998</v>
       </c>
       <c r="G27" s="7">
-        <v>42.449199999999998</v>
+        <v>43.103900000000003</v>
       </c>
       <c r="H27" s="7">
-        <v>42.714500000000001</v>
+        <v>42.894599999999997</v>
       </c>
       <c r="I27" s="7">
-        <v>42.832799999999999</v>
+        <v>42.5122</v>
       </c>
       <c r="J27" s="7">
-        <v>43.162599999999998</v>
+        <v>43.038699999999999</v>
       </c>
       <c r="K27" s="7">
-        <v>42.555399999999999</v>
+        <v>42.733400000000003</v>
       </c>
       <c r="L27" s="7">
-        <v>42.995100000000001</v>
+        <v>43.223300000000002</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O27" s="7">
-        <v>1067.8127999999999</v>
+        <v>1073.5264</v>
       </c>
       <c r="P27" s="7">
-        <v>1068.742</v>
+        <v>1069.1261</v>
       </c>
       <c r="Q27" s="7">
-        <v>1068.3106</v>
+        <v>1069.9347</v>
       </c>
       <c r="R27" s="7">
-        <v>1073.9188999999999</v>
+        <v>1076.0891999999999</v>
       </c>
       <c r="S27" s="7">
-        <v>1069.395</v>
+        <v>1073.9666999999999</v>
       </c>
       <c r="T27" s="7">
-        <v>1070.9504999999999</v>
+        <v>1071.7</v>
       </c>
       <c r="U27" s="7">
-        <v>1069.8886</v>
+        <v>1074.7550000000001</v>
       </c>
       <c r="V27" s="7">
-        <v>1077.56</v>
+        <v>1088.5278000000001</v>
       </c>
       <c r="W27" s="7">
-        <v>1072.7401</v>
+        <v>1075.3561</v>
       </c>
       <c r="X27" s="7">
-        <v>1069.9748999999999</v>
+        <v>1089.2002</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
@@ -31457,67 +31403,67 @@
         <v>18</v>
       </c>
       <c r="C28" s="7">
-        <v>50.0229</v>
+        <v>50.285299999999999</v>
       </c>
       <c r="D28" s="7">
-        <v>49.666800000000002</v>
+        <v>50.071100000000001</v>
       </c>
       <c r="E28" s="7">
-        <v>49.838700000000003</v>
+        <v>49.988700000000001</v>
       </c>
       <c r="F28" s="7">
-        <v>49.8506</v>
+        <v>50.392499999999998</v>
       </c>
       <c r="G28" s="7">
-        <v>50.689700000000002</v>
+        <v>50.91</v>
       </c>
       <c r="H28" s="7">
-        <v>50.465499999999999</v>
+        <v>50.155000000000001</v>
       </c>
       <c r="I28" s="7">
-        <v>51.234900000000003</v>
+        <v>50.233600000000003</v>
       </c>
       <c r="J28" s="7">
-        <v>49.853900000000003</v>
+        <v>50.6706</v>
       </c>
       <c r="K28" s="7">
-        <v>49.991900000000001</v>
+        <v>50.142000000000003</v>
       </c>
       <c r="L28" s="7">
-        <v>49.697899999999997</v>
+        <v>49.941499999999998</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O28" s="7">
-        <v>1249.0036</v>
+        <v>1298.9223</v>
       </c>
       <c r="P28" s="7">
-        <v>1257.0833</v>
+        <v>1272.8871999999999</v>
       </c>
       <c r="Q28" s="7">
-        <v>1251.0545</v>
+        <v>1252.0021999999999</v>
       </c>
       <c r="R28" s="7">
-        <v>1246.2598</v>
+        <v>1267.1133</v>
       </c>
       <c r="S28" s="7">
-        <v>1252.7464</v>
+        <v>1256.5279</v>
       </c>
       <c r="T28" s="7">
-        <v>1246.9866</v>
+        <v>1256.3224</v>
       </c>
       <c r="U28" s="7">
-        <v>1246.7275999999999</v>
+        <v>1255.9218000000001</v>
       </c>
       <c r="V28" s="7">
-        <v>1248.1189999999999</v>
+        <v>1252.8581999999999</v>
       </c>
       <c r="W28" s="7">
-        <v>1247.336</v>
+        <v>1263.2637</v>
       </c>
       <c r="X28" s="7">
-        <v>1246.6805999999999</v>
+        <v>1258.2191</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.25">
@@ -31525,67 +31471,67 @@
         <v>19</v>
       </c>
       <c r="C29" s="7">
-        <v>0.4415</v>
+        <v>0.43859999999999999</v>
       </c>
       <c r="D29" s="7">
-        <v>0.44119999999999998</v>
+        <v>0.43359999999999999</v>
       </c>
       <c r="E29" s="7">
-        <v>0.44030000000000002</v>
+        <v>0.43280000000000002</v>
       </c>
       <c r="F29" s="7">
-        <v>0.43559999999999999</v>
+        <v>0.43340000000000001</v>
       </c>
       <c r="G29" s="7">
-        <v>0.43880000000000002</v>
+        <v>0.4345</v>
       </c>
       <c r="H29" s="7">
-        <v>0.43369999999999997</v>
+        <v>0.4325</v>
       </c>
       <c r="I29" s="7">
-        <v>0.43680000000000002</v>
+        <v>0.43990000000000001</v>
       </c>
       <c r="J29" s="7">
-        <v>0.43280000000000002</v>
+        <v>0.43909999999999999</v>
       </c>
       <c r="K29" s="7">
-        <v>0.43369999999999997</v>
+        <v>0.43869999999999998</v>
       </c>
       <c r="L29" s="7">
-        <v>0.43359999999999999</v>
+        <v>0.434</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O29" s="7">
-        <v>2.5145</v>
+        <v>2.5009000000000001</v>
       </c>
       <c r="P29" s="7">
-        <v>2.4899</v>
+        <v>2.4756999999999998</v>
       </c>
       <c r="Q29" s="7">
-        <v>2.4817999999999998</v>
+        <v>2.4910999999999999</v>
       </c>
       <c r="R29" s="7">
-        <v>2.5047999999999999</v>
+        <v>2.4805000000000001</v>
       </c>
       <c r="S29" s="7">
-        <v>2.4796999999999998</v>
+        <v>2.5541999999999998</v>
       </c>
       <c r="T29" s="7">
-        <v>2.5041000000000002</v>
+        <v>2.6444000000000001</v>
       </c>
       <c r="U29" s="7">
-        <v>2.4923999999999999</v>
+        <v>2.4403999999999999</v>
       </c>
       <c r="V29" s="7">
-        <v>2.9016000000000002</v>
+        <v>2.4607000000000001</v>
       </c>
       <c r="W29" s="7">
-        <v>2.4239000000000002</v>
+        <v>2.4626999999999999</v>
       </c>
       <c r="X29" s="7">
-        <v>2.4293999999999998</v>
+        <v>2.5531000000000001</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.25">
@@ -31593,67 +31539,67 @@
         <v>20</v>
       </c>
       <c r="C30" s="7">
-        <v>37.9071</v>
+        <v>38.289200000000001</v>
       </c>
       <c r="D30" s="7">
-        <v>37.999299999999998</v>
+        <v>37.979399999999998</v>
       </c>
       <c r="E30" s="7">
-        <v>37.873399999999997</v>
+        <v>38.9358</v>
       </c>
       <c r="F30" s="7">
-        <v>38.021299999999997</v>
+        <v>37.8108</v>
       </c>
       <c r="G30" s="7">
-        <v>38.034500000000001</v>
+        <v>38.116999999999997</v>
       </c>
       <c r="H30" s="7">
-        <v>37.784300000000002</v>
+        <v>38.197099999999999</v>
       </c>
       <c r="I30" s="7">
-        <v>38.297800000000002</v>
+        <v>37.896900000000002</v>
       </c>
       <c r="J30" s="7">
-        <v>38.147300000000001</v>
+        <v>38.2087</v>
       </c>
       <c r="K30" s="7">
-        <v>38.0456</v>
+        <v>38.067900000000002</v>
       </c>
       <c r="L30" s="7">
-        <v>38.0642</v>
+        <v>38.331200000000003</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O30" s="7">
-        <v>946.50329999999997</v>
+        <v>948.82309999999995</v>
       </c>
       <c r="P30" s="7">
-        <v>945.11410000000001</v>
+        <v>951.61369999999999</v>
       </c>
       <c r="Q30" s="7">
-        <v>948.30470000000003</v>
+        <v>950.03269999999998</v>
       </c>
       <c r="R30" s="7">
-        <v>944.83420000000001</v>
+        <v>949.83169999999996</v>
       </c>
       <c r="S30" s="7">
-        <v>944.54679999999996</v>
+        <v>948.57219999999995</v>
       </c>
       <c r="T30" s="7">
-        <v>944.74469999999997</v>
+        <v>947.44970000000001</v>
       </c>
       <c r="U30" s="7">
-        <v>947.21109999999999</v>
+        <v>951.57069999999999</v>
       </c>
       <c r="V30" s="7">
-        <v>945.00059999999996</v>
+        <v>950.87750000000005</v>
       </c>
       <c r="W30" s="7">
-        <v>946.19650000000001</v>
+        <v>947.33680000000004</v>
       </c>
       <c r="X30" s="7">
-        <v>945.83730000000003</v>
+        <v>948.62940000000003</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
@@ -31661,81 +31607,81 @@
         <v>21</v>
       </c>
       <c r="C31" s="8">
-        <v>0.38479999999999998</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="D31" s="7">
-        <v>0.36549999999999999</v>
+        <v>0.33460000000000001</v>
       </c>
       <c r="E31" s="7">
-        <v>0.36670000000000003</v>
+        <v>0.33229999999999998</v>
       </c>
       <c r="F31" s="7">
-        <v>0.37419999999999998</v>
+        <v>0.33090000000000003</v>
       </c>
       <c r="G31" s="7">
-        <v>0.36720000000000003</v>
+        <v>0.32550000000000001</v>
       </c>
       <c r="H31" s="7">
-        <v>0.38080000000000003</v>
+        <v>0.3256</v>
       </c>
       <c r="I31" s="7">
-        <v>0.36230000000000001</v>
+        <v>0.3881</v>
       </c>
       <c r="J31" s="7">
-        <v>0.3594</v>
+        <v>0.35239999999999999</v>
       </c>
       <c r="K31" s="7">
-        <v>0.37490000000000001</v>
+        <v>0.33250000000000002</v>
       </c>
       <c r="L31" s="7">
-        <v>0.37719999999999998</v>
+        <v>0.33179999999999998</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O31" s="8">
-        <v>2.6922000000000001</v>
+        <v>2.1179000000000001</v>
       </c>
       <c r="P31" s="7">
-        <v>2.7564000000000002</v>
+        <v>2.0769000000000002</v>
       </c>
       <c r="Q31" s="7">
-        <v>2.7909999999999999</v>
+        <v>2.0644999999999998</v>
       </c>
       <c r="R31" s="7">
-        <v>2.7925</v>
+        <v>2.0682999999999998</v>
       </c>
       <c r="S31" s="7">
-        <v>2.7885</v>
+        <v>2.0952000000000002</v>
       </c>
       <c r="T31" s="7">
-        <v>2.8820999999999999</v>
+        <v>2.0419999999999998</v>
       </c>
       <c r="U31" s="7">
-        <v>2.8068</v>
+        <v>2.1225999999999998</v>
       </c>
       <c r="V31" s="7">
-        <v>2.7907999999999999</v>
+        <v>2.0956000000000001</v>
       </c>
       <c r="W31" s="7">
-        <v>2.8008999999999999</v>
+        <v>2.1436000000000002</v>
       </c>
       <c r="X31" s="7">
-        <v>2.7896999999999998</v>
+        <v>2.1164999999999998</v>
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="26"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="17"/>
       <c r="K34" s="1" t="s">
         <v>25</v>
       </c>
@@ -31765,7 +31711,7 @@
       </c>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="23"/>
+      <c r="B35" s="14"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -31822,23 +31768,23 @@
       </c>
       <c r="D36" s="7">
         <f t="shared" ref="D36:D41" si="1">IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
-        <v>8.0000000000000015E-4</v>
+        <v>8.25E-4</v>
       </c>
       <c r="E36" s="7">
         <f t="shared" ref="E36:E41" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
-        <v>1.6125000000000002E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="F36" s="7">
         <f t="shared" ref="F36:F41" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
-        <v>7.3875000000000017E-3</v>
+        <v>7.3750000000000013E-3</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" ref="G36:G41" si="4">IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
-        <v>1.4450000000000003E-2</v>
+        <v>1.4599999999999998E-2</v>
       </c>
       <c r="H36" s="7">
         <f t="shared" ref="H36:H41" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
-        <v>8.2174999999999998E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>26</v>
@@ -31874,27 +31820,27 @@
       </c>
       <c r="C37" s="7">
         <f t="shared" si="0"/>
-        <v>4.4124999999999998E-3</v>
+        <v>4.4875000000000002E-3</v>
       </c>
       <c r="D37" s="7">
         <f t="shared" si="1"/>
-        <v>0.10567500000000001</v>
+        <v>0.10781249999999998</v>
       </c>
       <c r="E37" s="7">
         <f t="shared" si="2"/>
-        <v>0.42470000000000008</v>
+        <v>0.41909999999999997</v>
       </c>
       <c r="F37" s="7">
         <f t="shared" si="3"/>
-        <v>10.738949999999997</v>
+        <v>10.769450000000001</v>
       </c>
       <c r="G37" s="7">
         <f t="shared" si="4"/>
-        <v>42.800525</v>
+        <v>42.853400000000001</v>
       </c>
       <c r="H37" s="7">
         <f t="shared" si="5"/>
-        <v>1070.4900749999999</v>
+        <v>1075.4819874999998</v>
       </c>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
@@ -31903,27 +31849,27 @@
       </c>
       <c r="C38" s="7">
         <f t="shared" si="0"/>
-        <v>5.1124999999999999E-3</v>
+        <v>5.1624999999999996E-3</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="1"/>
-        <v>0.12496250000000002</v>
+        <v>0.12739999999999999</v>
       </c>
       <c r="E38" s="7">
         <f t="shared" si="2"/>
-        <v>0.49884999999999996</v>
+        <v>0.49443750000000003</v>
       </c>
       <c r="F38" s="7">
         <f t="shared" si="3"/>
-        <v>12.45715</v>
+        <v>12.511575000000001</v>
       </c>
       <c r="G38" s="7">
         <f t="shared" si="4"/>
-        <v>50.051387499999997</v>
+        <v>50.242349999999995</v>
       </c>
       <c r="H38" s="7">
         <f t="shared" si="5"/>
-        <v>1248.5817875</v>
+        <v>1260.3892000000001</v>
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
@@ -31932,27 +31878,27 @@
       </c>
       <c r="C39" s="7">
         <f t="shared" si="0"/>
-        <v>2.6750000000000003E-3</v>
+        <v>2.6500000000000004E-3</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="1"/>
-        <v>1.6037500000000003E-2</v>
+        <v>1.6387499999999999E-2</v>
       </c>
       <c r="E39" s="7">
         <f t="shared" si="2"/>
-        <v>3.6924999999999999E-2</v>
+        <v>3.4399999999999993E-2</v>
       </c>
       <c r="F39" s="7">
         <f t="shared" si="3"/>
-        <v>0.20457499999999998</v>
+        <v>0.20878750000000001</v>
       </c>
       <c r="G39" s="7">
         <f t="shared" si="4"/>
-        <v>0.43671249999999995</v>
+        <v>0.43558749999999996</v>
       </c>
       <c r="H39" s="7">
         <f t="shared" si="5"/>
-        <v>2.4870749999999999</v>
+        <v>2.4973625000000004</v>
       </c>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
@@ -31961,27 +31907,27 @@
       </c>
       <c r="C40" s="7">
         <f t="shared" si="0"/>
-        <v>4.3999999999999994E-3</v>
+        <v>4.4750000000000007E-3</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="1"/>
-        <v>9.3350000000000002E-2</v>
+        <v>0.1011625</v>
       </c>
       <c r="E40" s="7">
         <f t="shared" si="2"/>
-        <v>0.38807499999999995</v>
+        <v>0.38603750000000003</v>
       </c>
       <c r="F40" s="7">
         <f t="shared" si="3"/>
-        <v>9.5362000000000009</v>
+        <v>9.6170749999999998</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="4"/>
-        <v>38.011587500000005</v>
+        <v>38.135925</v>
       </c>
       <c r="H40" s="7">
         <f t="shared" si="5"/>
-        <v>945.68022500000006</v>
+        <v>949.47337500000003</v>
       </c>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
@@ -31990,27 +31936,27 @@
       </c>
       <c r="C41" s="7">
         <f t="shared" si="0"/>
-        <v>2.5374999999999998E-3</v>
+        <v>3.0249999999999999E-3</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="1"/>
-        <v>1.2412500000000003E-2</v>
+        <v>2.3074999999999998E-2</v>
       </c>
       <c r="E41" s="7">
         <f t="shared" si="2"/>
-        <v>2.9025000000000002E-2</v>
+        <v>3.3175000000000003E-2</v>
       </c>
       <c r="F41" s="7">
         <f t="shared" si="3"/>
-        <v>0.15733749999999996</v>
+        <v>0.17295000000000002</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="4"/>
-        <v>0.37109999999999999</v>
+        <v>0.33651249999999994</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="5"/>
-        <v>2.7895749999999997</v>
+        <v>2.0946875</v>
       </c>
     </row>
     <row r="44" spans="2:17" ht="27.6" x14ac:dyDescent="0.25">
@@ -32023,11 +31969,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -32038,6 +31979,11 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -32060,10 +32006,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="12"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -32082,39 +32028,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="15"/>
-      <c r="N4" s="11" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="17"/>
+      <c r="N4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="15"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="17"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="12"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -32145,7 +32091,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="12"/>
+      <c r="N5" s="14"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -32182,61 +32128,61 @@
         <v>16</v>
       </c>
       <c r="C6" s="7">
-        <v>7.4999999999999997E-3</v>
+        <v>7.6E-3</v>
       </c>
       <c r="D6" s="7">
-        <v>7.1999999999999998E-3</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="E6" s="7">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="F6" s="7">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F6" s="7">
-        <v>6.8999999999999999E-3</v>
-      </c>
       <c r="G6" s="7">
-        <v>6.8999999999999999E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="H6" s="7">
-        <v>7.0000000000000001E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="I6" s="7">
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="J6" s="7">
-        <v>6.8999999999999999E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="K6" s="7">
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="L6" s="7">
-        <v>6.8999999999999999E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O6" s="7">
-        <v>0.17480000000000001</v>
+        <v>0.17630000000000001</v>
       </c>
       <c r="P6" s="7">
-        <v>0.17699999999999999</v>
+        <v>0.1714</v>
       </c>
       <c r="Q6" s="7">
-        <v>0.17130000000000001</v>
+        <v>0.1714</v>
       </c>
       <c r="R6" s="7">
-        <v>0.17130000000000001</v>
+        <v>0.17510000000000001</v>
       </c>
       <c r="S6" s="7">
-        <v>0.1714</v>
+        <v>0.1716</v>
       </c>
       <c r="T6" s="7">
-        <v>0.17130000000000001</v>
+        <v>0.17150000000000001</v>
       </c>
       <c r="U6" s="7">
-        <v>0.1714</v>
+        <v>0.17150000000000001</v>
       </c>
       <c r="V6" s="7">
-        <v>0.1769</v>
+        <v>0.1716</v>
       </c>
       <c r="W6" s="7">
         <v>0.17150000000000001</v>
@@ -32250,7 +32196,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="7">
-        <v>6.0000000000000001E-3</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="D7" s="7">
         <v>5.3E-3</v>
@@ -32262,55 +32208,55 @@
         <v>5.1999999999999998E-3</v>
       </c>
       <c r="G7" s="7">
-        <v>5.0000000000000001E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="H7" s="7">
         <v>5.1000000000000004E-3</v>
       </c>
       <c r="I7" s="7">
-        <v>5.0000000000000001E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="J7" s="7">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="K7" s="7">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="L7" s="7">
         <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="L7" s="7">
-        <v>5.0000000000000001E-3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O7" s="7">
-        <v>0.13009999999999999</v>
+        <v>0.12989999999999999</v>
       </c>
       <c r="P7" s="7">
-        <v>0.13009999999999999</v>
+        <v>0.1298</v>
       </c>
       <c r="Q7" s="7">
-        <v>0.1343</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="R7" s="7">
-        <v>0.12920000000000001</v>
+        <v>0.1293</v>
       </c>
       <c r="S7" s="7">
-        <v>0.17019999999999999</v>
+        <v>0.12590000000000001</v>
       </c>
       <c r="T7" s="7">
-        <v>0.13020000000000001</v>
+        <v>0.1133</v>
       </c>
       <c r="U7" s="7">
-        <v>0.1138</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="V7" s="7">
-        <v>0.1133</v>
+        <v>0.1125</v>
       </c>
       <c r="W7" s="7">
-        <v>0.1132</v>
+        <v>0.11260000000000001</v>
       </c>
       <c r="X7" s="7">
-        <v>0.1133</v>
+        <v>0.11269999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -32321,64 +32267,64 @@
         <v>1.0699999999999999E-2</v>
       </c>
       <c r="D8" s="7">
-        <v>1.0800000000000001E-2</v>
+        <v>1.14E-2</v>
       </c>
       <c r="E8" s="7">
-        <v>1.0699999999999999E-2</v>
+        <v>1.14E-2</v>
       </c>
       <c r="F8" s="7">
-        <v>1.0800000000000001E-2</v>
+        <v>1.14E-2</v>
       </c>
       <c r="G8" s="7">
-        <v>1.09E-2</v>
+        <v>1.14E-2</v>
       </c>
       <c r="H8" s="7">
-        <v>1.0999999999999999E-2</v>
+        <v>1.1299999999999999E-2</v>
       </c>
       <c r="I8" s="7">
-        <v>1.0999999999999999E-2</v>
+        <v>1.14E-2</v>
       </c>
       <c r="J8" s="7">
-        <v>1.09E-2</v>
+        <v>1.14E-2</v>
       </c>
       <c r="K8" s="7">
-        <v>1.0999999999999999E-2</v>
+        <v>1.1299999999999999E-2</v>
       </c>
       <c r="L8" s="7">
-        <v>1.09E-2</v>
+        <v>1.14E-2</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O8" s="7">
-        <v>0.25890000000000002</v>
+        <v>0.254</v>
       </c>
       <c r="P8" s="7">
-        <v>0.2656</v>
+        <v>0.26690000000000003</v>
       </c>
       <c r="Q8" s="7">
-        <v>0.25829999999999997</v>
+        <v>0.26679999999999998</v>
       </c>
       <c r="R8" s="7">
-        <v>0.25369999999999998</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="S8" s="7">
-        <v>0.25729999999999997</v>
+        <v>0.25750000000000001</v>
       </c>
       <c r="T8" s="7">
-        <v>0.27939999999999998</v>
+        <v>0.25390000000000001</v>
       </c>
       <c r="U8" s="7">
-        <v>0.25519999999999998</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="V8" s="7">
-        <v>0.25509999999999999</v>
+        <v>0.27210000000000001</v>
       </c>
       <c r="W8" s="7">
-        <v>0.2646</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="X8" s="7">
-        <v>0.25950000000000001</v>
+        <v>0.2712</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -32386,7 +32332,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="7">
-        <v>3.7000000000000002E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="D9" s="7">
         <v>2.8E-3</v>
@@ -32395,22 +32341,22 @@
         <v>2.8E-3</v>
       </c>
       <c r="F9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="G9" s="7">
         <v>2.7000000000000001E-3</v>
       </c>
       <c r="H9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="I9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="J9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="K9" s="7">
-        <v>2.7000000000000001E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="L9" s="7">
         <v>2.7000000000000001E-3</v>
@@ -32419,10 +32365,10 @@
         <v>19</v>
       </c>
       <c r="O9" s="7">
-        <v>1.7500000000000002E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="P9" s="7">
-        <v>1.67E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="Q9" s="7">
         <v>1.6799999999999999E-2</v>
@@ -32434,19 +32380,19 @@
         <v>1.6799999999999999E-2</v>
       </c>
       <c r="T9" s="7">
-        <v>1.67E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="U9" s="7">
-        <v>1.67E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="V9" s="7">
         <v>1.6799999999999999E-2</v>
       </c>
       <c r="W9" s="7">
-        <v>6.6600000000000006E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="X9" s="7">
-        <v>1.67E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -32454,67 +32400,67 @@
         <v>20</v>
       </c>
       <c r="C10" s="7">
-        <v>4.7999999999999996E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="D10" s="7">
-        <v>4.4000000000000003E-3</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="E10" s="7">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="F10" s="7">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="F10" s="7">
+      <c r="G10" s="7">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="H10" s="7">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="I10" s="7">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G10" s="7">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H10" s="7">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="I10" s="7">
+      <c r="J10" s="7">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="J10" s="7">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="K10" s="7">
-        <v>4.0000000000000001E-3</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="L10" s="7">
-        <v>4.0000000000000001E-3</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O10" s="7">
-        <v>0.1017</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="P10" s="7">
-        <v>0.1019</v>
+        <v>9.3100000000000002E-2</v>
       </c>
       <c r="Q10" s="7">
-        <v>0.1011</v>
+        <v>9.3100000000000002E-2</v>
       </c>
       <c r="R10" s="7">
-        <v>0.1012</v>
+        <v>9.7100000000000006E-2</v>
       </c>
       <c r="S10" s="7">
-        <v>0.10390000000000001</v>
+        <v>9.2700000000000005E-2</v>
       </c>
       <c r="T10" s="7">
-        <v>0.1013</v>
+        <v>9.2799999999999994E-2</v>
       </c>
       <c r="U10" s="7">
-        <v>0.1012</v>
+        <v>9.2799999999999994E-2</v>
       </c>
       <c r="V10" s="7">
-        <v>0.1012</v>
+        <v>9.2700000000000005E-2</v>
       </c>
       <c r="W10" s="7">
-        <v>0.1012</v>
+        <v>9.2600000000000002E-2</v>
       </c>
       <c r="X10" s="7">
-        <v>0.1051</v>
+        <v>9.2700000000000005E-2</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -32522,67 +32468,67 @@
         <v>21</v>
       </c>
       <c r="C11" s="8">
-        <v>3.5000000000000001E-3</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="D11" s="7">
-        <v>3.0000000000000001E-3</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="E11" s="7">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="F11" s="7">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="F11" s="7">
+      <c r="G11" s="7">
+        <v>2.8E-3</v>
+      </c>
+      <c r="H11" s="7">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="I11" s="7">
         <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="G11" s="7">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="H11" s="7">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="I11" s="7">
-        <v>2.7000000000000001E-3</v>
       </c>
       <c r="J11" s="7">
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="K11" s="7">
-        <v>2.5999999999999999E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="L11" s="7">
-        <v>2.5999999999999999E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O11" s="8">
-        <v>1.5599999999999999E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="P11" s="7">
-        <v>1.46E-2</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="Q11" s="7">
-        <v>1.49E-2</v>
+        <v>1.52E-2</v>
       </c>
       <c r="R11" s="7">
-        <v>1.3899999999999999E-2</v>
+        <v>1.52E-2</v>
       </c>
       <c r="S11" s="7">
-        <v>1.3299999999999999E-2</v>
+        <v>1.52E-2</v>
       </c>
       <c r="T11" s="7">
-        <v>1.29E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="U11" s="7">
-        <v>1.32E-2</v>
+        <v>1.5100000000000001E-2</v>
       </c>
       <c r="V11" s="7">
-        <v>1.29E-2</v>
+        <v>1.52E-2</v>
       </c>
       <c r="W11" s="7">
-        <v>1.29E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="X11" s="7">
-        <v>1.3100000000000001E-2</v>
+        <v>1.5100000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -32602,39 +32548,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="15"/>
-      <c r="N14" s="11" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="17"/>
+      <c r="N14" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="O14" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="15"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="17"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="12"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -32665,7 +32611,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="12"/>
+      <c r="N15" s="14"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -32702,67 +32648,67 @@
         <v>16</v>
       </c>
       <c r="C16" s="7">
-        <v>0.68989999999999996</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="D16" s="7">
-        <v>0.68389999999999995</v>
+        <v>0.69350000000000001</v>
       </c>
       <c r="E16" s="7">
-        <v>0.66700000000000004</v>
+        <v>0.67989999999999995</v>
       </c>
       <c r="F16" s="7">
-        <v>0.6845</v>
+        <v>0.67849999999999999</v>
       </c>
       <c r="G16" s="7">
-        <v>0.68820000000000003</v>
+        <v>0.68240000000000001</v>
       </c>
       <c r="H16" s="7">
-        <v>0.68110000000000004</v>
+        <v>0.67879999999999996</v>
       </c>
       <c r="I16" s="7">
-        <v>0.69020000000000004</v>
+        <v>0.68159999999999998</v>
       </c>
       <c r="J16" s="7">
-        <v>0.68640000000000001</v>
+        <v>0.70079999999999998</v>
       </c>
       <c r="K16" s="7">
-        <v>0.68100000000000005</v>
+        <v>0.67720000000000002</v>
       </c>
       <c r="L16" s="7">
-        <v>0.68920000000000003</v>
+        <v>0.68359999999999999</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O16" s="7">
-        <v>16.920300000000001</v>
+        <v>16.631599999999999</v>
       </c>
       <c r="P16" s="7">
-        <v>17.025300000000001</v>
+        <v>16.895800000000001</v>
       </c>
       <c r="Q16" s="7">
-        <v>16.694500000000001</v>
+        <v>17.054500000000001</v>
       </c>
       <c r="R16" s="7">
-        <v>17.04</v>
+        <v>17.028199999999998</v>
       </c>
       <c r="S16" s="7">
-        <v>16.639399999999998</v>
+        <v>16.7546</v>
       </c>
       <c r="T16" s="7">
-        <v>16.909400000000002</v>
+        <v>16.9377</v>
       </c>
       <c r="U16" s="7">
-        <v>16.9025</v>
+        <v>17.054500000000001</v>
       </c>
       <c r="V16" s="7">
-        <v>17.027799999999999</v>
+        <v>16.916</v>
       </c>
       <c r="W16" s="7">
-        <v>16.7257</v>
+        <v>16.843699999999998</v>
       </c>
       <c r="X16" s="7">
-        <v>17.191099999999999</v>
+        <v>17.021699999999999</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
@@ -32770,67 +32716,67 @@
         <v>17</v>
       </c>
       <c r="C17" s="7">
-        <v>0.51280000000000003</v>
+        <v>0.50470000000000004</v>
       </c>
       <c r="D17" s="7">
-        <v>0.44080000000000003</v>
+        <v>0.50480000000000003</v>
       </c>
       <c r="E17" s="7">
-        <v>0.45329999999999998</v>
+        <v>0.50529999999999997</v>
       </c>
       <c r="F17" s="7">
-        <v>0.50149999999999995</v>
+        <v>0.50829999999999997</v>
       </c>
       <c r="G17" s="7">
-        <v>0.50480000000000003</v>
+        <v>0.50539999999999996</v>
       </c>
       <c r="H17" s="7">
-        <v>0.44629999999999997</v>
+        <v>0.50529999999999997</v>
       </c>
       <c r="I17" s="7">
-        <v>0.51200000000000001</v>
+        <v>0.51180000000000003</v>
       </c>
       <c r="J17" s="7">
-        <v>0.44579999999999997</v>
+        <v>0.51129999999999998</v>
       </c>
       <c r="K17" s="7">
-        <v>0.44740000000000002</v>
+        <v>0.50819999999999999</v>
       </c>
       <c r="L17" s="7">
-        <v>0.68979999999999997</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O17" s="7">
-        <v>11.850199999999999</v>
+        <v>11.842000000000001</v>
       </c>
       <c r="P17" s="7">
-        <v>12.0915</v>
+        <v>12.422800000000001</v>
       </c>
       <c r="Q17" s="7">
-        <v>12.497400000000001</v>
+        <v>12.0562</v>
       </c>
       <c r="R17" s="7">
-        <v>12.0062</v>
+        <v>11.983499999999999</v>
       </c>
       <c r="S17" s="7">
-        <v>11.7148</v>
+        <v>12.0177</v>
       </c>
       <c r="T17" s="7">
-        <v>11.9001</v>
+        <v>11.9557</v>
       </c>
       <c r="U17" s="7">
-        <v>11.708299999999999</v>
+        <v>12.2088</v>
       </c>
       <c r="V17" s="7">
-        <v>11.889099999999999</v>
+        <v>12.6119</v>
       </c>
       <c r="W17" s="7">
-        <v>11.9368</v>
+        <v>12.0261</v>
       </c>
       <c r="X17" s="7">
-        <v>12.292899999999999</v>
+        <v>12.4359</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
@@ -32838,67 +32784,67 @@
         <v>18</v>
       </c>
       <c r="C18" s="7">
-        <v>1.2501</v>
+        <v>1.0188999999999999</v>
       </c>
       <c r="D18" s="7">
-        <v>1.0087999999999999</v>
+        <v>1.0149999999999999</v>
       </c>
       <c r="E18" s="7">
-        <v>0.9899</v>
+        <v>1.0226999999999999</v>
       </c>
       <c r="F18" s="7">
-        <v>0.98770000000000002</v>
+        <v>1.0337000000000001</v>
       </c>
       <c r="G18" s="7">
-        <v>0.98450000000000004</v>
+        <v>1.0282</v>
       </c>
       <c r="H18" s="7">
-        <v>1.0074000000000001</v>
+        <v>1.0222</v>
       </c>
       <c r="I18" s="7">
-        <v>1.0205</v>
+        <v>1.0150999999999999</v>
       </c>
       <c r="J18" s="7">
-        <v>0.99329999999999996</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="K18" s="7">
-        <v>0.998</v>
+        <v>1.1144000000000001</v>
       </c>
       <c r="L18" s="7">
-        <v>0.99639999999999995</v>
+        <v>1.3367</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O18" s="7">
-        <v>25.4651</v>
+        <v>25.665500000000002</v>
       </c>
       <c r="P18" s="7">
-        <v>25.5458</v>
+        <v>25.500299999999999</v>
       </c>
       <c r="Q18" s="7">
-        <v>25.408899999999999</v>
+        <v>25.6953</v>
       </c>
       <c r="R18" s="7">
-        <v>25.216699999999999</v>
+        <v>25.7408</v>
       </c>
       <c r="S18" s="7">
-        <v>25.8779</v>
+        <v>25.3308</v>
       </c>
       <c r="T18" s="7">
-        <v>25.418399999999998</v>
+        <v>25.752500000000001</v>
       </c>
       <c r="U18" s="7">
-        <v>25.435600000000001</v>
+        <v>25.857199999999999</v>
       </c>
       <c r="V18" s="7">
-        <v>25.497800000000002</v>
+        <v>26.359000000000002</v>
       </c>
       <c r="W18" s="7">
-        <v>25.334399999999999</v>
+        <v>26.685199999999998</v>
       </c>
       <c r="X18" s="7">
-        <v>25.971399999999999</v>
+        <v>26.0779</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
@@ -32906,67 +32852,67 @@
         <v>19</v>
       </c>
       <c r="C19" s="7">
-        <v>3.5999999999999997E-2</v>
+        <v>4.2099999999999999E-2</v>
       </c>
       <c r="D19" s="7">
-        <v>3.5099999999999999E-2</v>
+        <v>4.07E-2</v>
       </c>
       <c r="E19" s="7">
-        <v>3.5200000000000002E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="F19" s="7">
-        <v>3.5000000000000003E-2</v>
+        <v>4.07E-2</v>
       </c>
       <c r="G19" s="7">
-        <v>3.5200000000000002E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="H19" s="7">
-        <v>3.5000000000000003E-2</v>
+        <v>4.0899999999999999E-2</v>
       </c>
       <c r="I19" s="7">
-        <v>3.5099999999999999E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="J19" s="7">
-        <v>3.5200000000000002E-2</v>
+        <v>4.07E-2</v>
       </c>
       <c r="K19" s="7">
-        <v>3.5099999999999999E-2</v>
+        <v>4.36E-2</v>
       </c>
       <c r="L19" s="7">
-        <v>3.5099999999999999E-2</v>
+        <v>4.36E-2</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O19" s="7">
-        <v>0.214</v>
+        <v>0.2142</v>
       </c>
       <c r="P19" s="7">
-        <v>0.2112</v>
+        <v>0.21310000000000001</v>
       </c>
       <c r="Q19" s="7">
-        <v>0.21329999999999999</v>
+        <v>0.21249999999999999</v>
       </c>
       <c r="R19" s="7">
-        <v>0.21160000000000001</v>
+        <v>0.21049999999999999</v>
       </c>
       <c r="S19" s="7">
-        <v>0.21540000000000001</v>
+        <v>0.2051</v>
       </c>
       <c r="T19" s="7">
-        <v>0.21029999999999999</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="U19" s="7">
-        <v>0.2102</v>
+        <v>0.20960000000000001</v>
       </c>
       <c r="V19" s="7">
-        <v>0.22789999999999999</v>
+        <v>0.20519999999999999</v>
       </c>
       <c r="W19" s="7">
-        <v>0.2102</v>
+        <v>0.2054</v>
       </c>
       <c r="X19" s="7">
-        <v>0.21029999999999999</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.25">
@@ -32974,67 +32920,67 @@
         <v>20</v>
       </c>
       <c r="C20" s="7">
-        <v>0.38969999999999999</v>
+        <v>0.40749999999999997</v>
       </c>
       <c r="D20" s="7">
-        <v>0.38840000000000002</v>
+        <v>0.34620000000000001</v>
       </c>
       <c r="E20" s="7">
-        <v>0.38450000000000001</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="F20" s="7">
-        <v>0.3876</v>
+        <v>0.37919999999999998</v>
       </c>
       <c r="G20" s="7">
-        <v>0.38369999999999999</v>
+        <v>0.3805</v>
       </c>
       <c r="H20" s="7">
-        <v>0.38540000000000002</v>
+        <v>0.38290000000000002</v>
       </c>
       <c r="I20" s="7">
-        <v>0.38390000000000002</v>
+        <v>0.38290000000000002</v>
       </c>
       <c r="J20" s="7">
-        <v>0.38400000000000001</v>
+        <v>0.3831</v>
       </c>
       <c r="K20" s="7">
-        <v>0.38379999999999997</v>
+        <v>0.38059999999999999</v>
       </c>
       <c r="L20" s="7">
-        <v>0.38879999999999998</v>
+        <v>0.3805</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O20" s="7">
-        <v>9.5238999999999994</v>
+        <v>9.3422999999999998</v>
       </c>
       <c r="P20" s="7">
-        <v>9.5929000000000002</v>
+        <v>9.5853999999999999</v>
       </c>
       <c r="Q20" s="7">
-        <v>9.6265000000000001</v>
+        <v>9.7826000000000004</v>
       </c>
       <c r="R20" s="7">
-        <v>9.5663</v>
+        <v>9.8247999999999998</v>
       </c>
       <c r="S20" s="7">
-        <v>9.6060999999999996</v>
+        <v>9.4528999999999996</v>
       </c>
       <c r="T20" s="7">
-        <v>9.9222000000000001</v>
+        <v>9.5140999999999991</v>
       </c>
       <c r="U20" s="7">
-        <v>9.5063999999999993</v>
+        <v>9.6502999999999997</v>
       </c>
       <c r="V20" s="7">
-        <v>9.7729999999999997</v>
+        <v>9.5998999999999999</v>
       </c>
       <c r="W20" s="7">
-        <v>9.3637999999999995</v>
+        <v>9.5877999999999997</v>
       </c>
       <c r="X20" s="7">
-        <v>9.4422999999999995</v>
+        <v>9.8443000000000005</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
@@ -33042,67 +32988,67 @@
         <v>21</v>
       </c>
       <c r="C21" s="8">
-        <v>3.2399999999999998E-2</v>
+        <v>3.3700000000000001E-2</v>
       </c>
       <c r="D21" s="7">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="F21" s="7">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G21" s="7">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="H21" s="7">
+        <v>2.87E-2</v>
+      </c>
+      <c r="I21" s="7">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="J21" s="7">
+        <v>2.86E-2</v>
+      </c>
+      <c r="K21" s="7">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="L21" s="7">
         <v>2.8899999999999999E-2</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2.7400000000000001E-2</v>
-      </c>
-      <c r="F21" s="7">
-        <v>3.1800000000000002E-2</v>
-      </c>
-      <c r="G21" s="7">
-        <v>2.9600000000000001E-2</v>
-      </c>
-      <c r="H21" s="7">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="I21" s="7">
-        <v>2.7799999999999998E-2</v>
-      </c>
-      <c r="J21" s="7">
-        <v>2.76E-2</v>
-      </c>
-      <c r="K21" s="7">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="L21" s="7">
-        <v>2.8000000000000001E-2</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O21" s="8">
-        <v>2.1086999999999998</v>
+        <v>0.16109999999999999</v>
       </c>
       <c r="P21" s="7">
-        <v>2.2776000000000001</v>
+        <v>0.1492</v>
       </c>
       <c r="Q21" s="7">
-        <v>2.1141999999999999</v>
+        <v>0.14779999999999999</v>
       </c>
       <c r="R21" s="7">
-        <v>2.1067</v>
+        <v>0.15279999999999999</v>
       </c>
       <c r="S21" s="7">
-        <v>2.0512999999999999</v>
+        <v>0.14979999999999999</v>
       </c>
       <c r="T21" s="7">
-        <v>2.0969000000000002</v>
+        <v>0.15010000000000001</v>
       </c>
       <c r="U21" s="7">
-        <v>2.1240000000000001</v>
+        <v>0.1537</v>
       </c>
       <c r="V21" s="7">
-        <v>2.1334</v>
+        <v>0.15459999999999999</v>
       </c>
       <c r="W21" s="7">
-        <v>2.1204999999999998</v>
+        <v>0.1555</v>
       </c>
       <c r="X21" s="7">
-        <v>2.1145999999999998</v>
+        <v>0.15040000000000001</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
@@ -33122,39 +33068,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="15"/>
-      <c r="N24" s="11" t="s">
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="17"/>
+      <c r="N24" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="13" t="s">
+      <c r="O24" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="15"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="17"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="12"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -33185,7 +33131,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="12"/>
+      <c r="N25" s="14"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -33222,67 +33168,67 @@
         <v>16</v>
       </c>
       <c r="C26" s="7">
-        <v>67.531700000000001</v>
+        <v>67.933700000000002</v>
       </c>
       <c r="D26" s="7">
-        <v>68.365600000000001</v>
+        <v>68.429599999999994</v>
       </c>
       <c r="E26" s="7">
-        <v>68.717500000000001</v>
+        <v>67.293499999999995</v>
       </c>
       <c r="F26" s="7">
-        <v>68.486199999999997</v>
+        <v>68.242000000000004</v>
       </c>
       <c r="G26" s="7">
-        <v>67.471100000000007</v>
+        <v>67.575699999999998</v>
       </c>
       <c r="H26" s="7">
-        <v>67.694800000000001</v>
+        <v>68.739000000000004</v>
       </c>
       <c r="I26" s="7">
-        <v>68.088999999999999</v>
+        <v>67.739099999999993</v>
       </c>
       <c r="J26" s="7">
-        <v>67.8489</v>
+        <v>67.619500000000002</v>
       </c>
       <c r="K26" s="7">
-        <v>67.704300000000003</v>
+        <v>67.644099999999995</v>
       </c>
       <c r="L26" s="7">
-        <v>67.257900000000006</v>
+        <v>67.5976</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O26" s="7">
-        <v>1704.355</v>
+        <v>1703.6822999999999</v>
       </c>
       <c r="P26" s="7">
-        <v>1706.5268000000001</v>
+        <v>1700.4722999999999</v>
       </c>
       <c r="Q26" s="7">
-        <v>1697.0744</v>
+        <v>1702.8570999999999</v>
       </c>
       <c r="R26" s="7">
-        <v>1696.6005</v>
+        <v>1703.1754000000001</v>
       </c>
       <c r="S26" s="7">
-        <v>1698.7782999999999</v>
+        <v>1701.4158</v>
       </c>
       <c r="T26" s="7">
-        <v>1697.3117999999999</v>
+        <v>1704.203</v>
       </c>
       <c r="U26" s="7">
-        <v>1705.2108000000001</v>
+        <v>1699.6523</v>
       </c>
       <c r="V26" s="7">
-        <v>1694.2313999999999</v>
+        <v>1698.0775000000001</v>
       </c>
       <c r="W26" s="7">
-        <v>1702.827</v>
+        <v>1708.38</v>
       </c>
       <c r="X26" s="7">
-        <v>1692.5108</v>
+        <v>1708.3657000000001</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
@@ -33290,67 +33236,67 @@
         <v>17</v>
       </c>
       <c r="C27" s="7">
-        <v>46.318600000000004</v>
+        <v>48.371899999999997</v>
       </c>
       <c r="D27" s="7">
-        <v>49.363599999999998</v>
+        <v>48.268099999999997</v>
       </c>
       <c r="E27" s="7">
-        <v>49.122199999999999</v>
+        <v>47.000900000000001</v>
       </c>
       <c r="F27" s="7">
-        <v>48.263599999999997</v>
+        <v>48.863999999999997</v>
       </c>
       <c r="G27" s="7">
-        <v>46.6447</v>
+        <v>48.365499999999997</v>
       </c>
       <c r="H27" s="7">
-        <v>47.982199999999999</v>
+        <v>48.226799999999997</v>
       </c>
       <c r="I27" s="7">
-        <v>49.3</v>
+        <v>48.732500000000002</v>
       </c>
       <c r="J27" s="7">
-        <v>48.601500000000001</v>
+        <v>48.401000000000003</v>
       </c>
       <c r="K27" s="7">
-        <v>48.712000000000003</v>
+        <v>48.909300000000002</v>
       </c>
       <c r="L27" s="7">
-        <v>48.437600000000003</v>
+        <v>49.071800000000003</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="O27" s="7">
-        <v>1212.8842</v>
+        <v>1214.5501999999999</v>
       </c>
       <c r="P27" s="7">
-        <v>1220.2150999999999</v>
+        <v>1224.7465999999999</v>
       </c>
       <c r="Q27" s="7">
-        <v>1207.1577</v>
+        <v>1215.5352</v>
       </c>
       <c r="R27" s="7">
-        <v>1206.5849000000001</v>
+        <v>1215.7969000000001</v>
       </c>
       <c r="S27" s="7">
-        <v>1205.1511</v>
+        <v>1210.4492</v>
       </c>
       <c r="T27" s="7">
-        <v>1210.357</v>
+        <v>1214.7157999999999</v>
       </c>
       <c r="U27" s="7">
-        <v>1216.5509</v>
+        <v>1209.5414000000001</v>
       </c>
       <c r="V27" s="7">
-        <v>1214.7883999999999</v>
+        <v>1211.8927000000001</v>
       </c>
       <c r="W27" s="7">
-        <v>1211.2609</v>
+        <v>1216.9775</v>
       </c>
       <c r="X27" s="7">
-        <v>1211.2910999999999</v>
+        <v>1211.4746</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
@@ -33358,67 +33304,67 @@
         <v>18</v>
       </c>
       <c r="C28" s="7">
-        <v>101.9512</v>
+        <v>102.3861</v>
       </c>
       <c r="D28" s="7">
-        <v>101.96720000000001</v>
+        <v>102.0432</v>
       </c>
       <c r="E28" s="7">
-        <v>102.4148</v>
+        <v>102.0585</v>
       </c>
       <c r="F28" s="7">
-        <v>102.0264</v>
+        <v>102.0401</v>
       </c>
       <c r="G28" s="7">
-        <v>101.7398</v>
+        <v>102.10680000000001</v>
       </c>
       <c r="H28" s="7">
-        <v>102.89409999999999</v>
+        <v>102.4975</v>
       </c>
       <c r="I28" s="7">
-        <v>101.6403</v>
+        <v>102.7627</v>
       </c>
       <c r="J28" s="7">
-        <v>101.6966</v>
+        <v>102.17100000000001</v>
       </c>
       <c r="K28" s="7">
-        <v>102.2206</v>
+        <v>103.20529999999999</v>
       </c>
       <c r="L28" s="7">
-        <v>101.6915</v>
+        <v>102.02290000000001</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O28" s="7">
-        <v>2568.9774000000002</v>
+        <v>2566.2633999999998</v>
       </c>
       <c r="P28" s="7">
-        <v>2557.8825000000002</v>
+        <v>2564.9863999999998</v>
       </c>
       <c r="Q28" s="7">
-        <v>2558.6363999999999</v>
+        <v>2566.6405</v>
       </c>
       <c r="R28" s="7">
-        <v>2552.7147</v>
+        <v>2561.5810999999999</v>
       </c>
       <c r="S28" s="7">
-        <v>2563.7993999999999</v>
+        <v>2576.7689999999998</v>
       </c>
       <c r="T28" s="7">
-        <v>2558.0715</v>
+        <v>2563.0985000000001</v>
       </c>
       <c r="U28" s="7">
-        <v>2558.2168000000001</v>
+        <v>2565.9958000000001</v>
       </c>
       <c r="V28" s="7">
-        <v>2562.7926000000002</v>
+        <v>2579.1403</v>
       </c>
       <c r="W28" s="7">
-        <v>2557.5095000000001</v>
+        <v>2564.8946999999998</v>
       </c>
       <c r="X28" s="7">
-        <v>2554.0119</v>
+        <v>2566.3651</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.25">
@@ -33426,67 +33372,67 @@
         <v>19</v>
       </c>
       <c r="C29" s="7">
+        <v>0.45340000000000003</v>
+      </c>
+      <c r="D29" s="7">
+        <v>0.45190000000000002</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.44950000000000001</v>
+      </c>
+      <c r="F29" s="7">
+        <v>0.4531</v>
+      </c>
+      <c r="G29" s="7">
+        <v>0.45290000000000002</v>
+      </c>
+      <c r="H29" s="7">
+        <v>0.46429999999999999</v>
+      </c>
+      <c r="I29" s="7">
         <v>0.4456</v>
       </c>
-      <c r="D29" s="7">
-        <v>0.44919999999999999</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.43980000000000002</v>
-      </c>
-      <c r="F29" s="7">
-        <v>0.47370000000000001</v>
-      </c>
-      <c r="G29" s="7">
-        <v>0.43969999999999998</v>
-      </c>
-      <c r="H29" s="7">
-        <v>0.44790000000000002</v>
-      </c>
-      <c r="I29" s="7">
-        <v>0.44019999999999998</v>
-      </c>
       <c r="J29" s="7">
-        <v>0.44450000000000001</v>
+        <v>0.44819999999999999</v>
       </c>
       <c r="K29" s="7">
-        <v>0.43969999999999998</v>
+        <v>0.44640000000000002</v>
       </c>
       <c r="L29" s="7">
-        <v>0.443</v>
+        <v>0.44769999999999999</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="O29" s="7">
-        <v>2.6747999999999998</v>
+        <v>2.5148999999999999</v>
       </c>
       <c r="P29" s="7">
-        <v>2.5108999999999999</v>
+        <v>2.5270999999999999</v>
       </c>
       <c r="Q29" s="7">
-        <v>2.4885000000000002</v>
+        <v>2.5731000000000002</v>
       </c>
       <c r="R29" s="7">
-        <v>2.4946000000000002</v>
+        <v>2.5417999999999998</v>
       </c>
       <c r="S29" s="7">
-        <v>2.4944000000000002</v>
+        <v>2.8527999999999998</v>
       </c>
       <c r="T29" s="7">
-        <v>2.5190000000000001</v>
+        <v>2.5996000000000001</v>
       </c>
       <c r="U29" s="7">
-        <v>2.5017</v>
+        <v>2.4969999999999999</v>
       </c>
       <c r="V29" s="7">
-        <v>2.5183</v>
+        <v>2.5337999999999998</v>
       </c>
       <c r="W29" s="7">
-        <v>2.5156999999999998</v>
+        <v>2.5266999999999999</v>
       </c>
       <c r="X29" s="7">
-        <v>2.5139</v>
+        <v>2.5442</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.25">
@@ -33494,67 +33440,67 @@
         <v>20</v>
       </c>
       <c r="C30" s="7">
-        <v>37.799500000000002</v>
+        <v>38.004300000000001</v>
       </c>
       <c r="D30" s="7">
-        <v>38.145299999999999</v>
+        <v>38.103999999999999</v>
       </c>
       <c r="E30" s="7">
-        <v>37.7181</v>
+        <v>38.091799999999999</v>
       </c>
       <c r="F30" s="7">
-        <v>38.5563</v>
+        <v>37.987900000000003</v>
       </c>
       <c r="G30" s="7">
-        <v>37.9253</v>
+        <v>37.7117</v>
       </c>
       <c r="H30" s="7">
-        <v>37.891500000000001</v>
+        <v>37.970500000000001</v>
       </c>
       <c r="I30" s="7">
-        <v>38.280500000000004</v>
+        <v>37.252099999999999</v>
       </c>
       <c r="J30" s="7">
-        <v>37.790300000000002</v>
+        <v>37.818800000000003</v>
       </c>
       <c r="K30" s="7">
-        <v>37.927599999999998</v>
+        <v>38.015799999999999</v>
       </c>
       <c r="L30" s="7">
-        <v>38.103999999999999</v>
+        <v>37.974200000000003</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O30" s="7">
-        <v>943.43960000000004</v>
+        <v>941.83159999999998</v>
       </c>
       <c r="P30" s="7">
-        <v>939.11509999999998</v>
+        <v>941.24249999999995</v>
       </c>
       <c r="Q30" s="7">
-        <v>942.70849999999996</v>
+        <v>949.31079999999997</v>
       </c>
       <c r="R30" s="7">
-        <v>938.6848</v>
+        <v>942.15750000000003</v>
       </c>
       <c r="S30" s="7">
-        <v>939.2251</v>
+        <v>941.63829999999996</v>
       </c>
       <c r="T30" s="7">
-        <v>940.30679999999995</v>
+        <v>945.69349999999997</v>
       </c>
       <c r="U30" s="7">
-        <v>941.39530000000002</v>
+        <v>943.63009999999997</v>
       </c>
       <c r="V30" s="7">
-        <v>943.50930000000005</v>
+        <v>943.80250000000001</v>
       </c>
       <c r="W30" s="7">
-        <v>947.02620000000002</v>
+        <v>943.05520000000001</v>
       </c>
       <c r="X30" s="7">
-        <v>940.02210000000002</v>
+        <v>941.34540000000004</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
@@ -33562,81 +33508,81 @@
         <v>21</v>
       </c>
       <c r="C31" s="8">
-        <v>18.523099999999999</v>
+        <v>0.37480000000000002</v>
       </c>
       <c r="D31" s="7">
-        <v>18.729099999999999</v>
+        <v>0.36249999999999999</v>
       </c>
       <c r="E31" s="7">
-        <v>19.262899999999998</v>
+        <v>0.3629</v>
       </c>
       <c r="F31" s="7">
-        <v>19.386299999999999</v>
+        <v>0.36120000000000002</v>
       </c>
       <c r="G31" s="7">
-        <v>19.2669</v>
+        <v>0.3579</v>
       </c>
       <c r="H31" s="7">
-        <v>18.703700000000001</v>
+        <v>0.35709999999999997</v>
       </c>
       <c r="I31" s="7">
-        <v>18.654499999999999</v>
+        <v>0.36330000000000001</v>
       </c>
       <c r="J31" s="7">
-        <v>18.894100000000002</v>
+        <v>0.36549999999999999</v>
       </c>
       <c r="K31" s="7">
-        <v>19.3001</v>
+        <v>0.36159999999999998</v>
       </c>
       <c r="L31" s="7">
-        <v>19.180599999999998</v>
+        <v>0.36059999999999998</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>21</v>
       </c>
       <c r="O31" s="8">
-        <v>714.22910000000002</v>
+        <v>2.0165999999999999</v>
       </c>
       <c r="P31" s="7">
-        <v>714.57740000000001</v>
+        <v>2.0133999999999999</v>
       </c>
       <c r="Q31" s="7">
-        <v>670.0172</v>
+        <v>2.0234000000000001</v>
       </c>
       <c r="R31" s="7">
-        <v>722.71590000000003</v>
+        <v>1.9847999999999999</v>
       </c>
       <c r="S31" s="7">
-        <v>715.40890000000002</v>
+        <v>2.3378999999999999</v>
       </c>
       <c r="T31" s="7">
-        <v>662.06359999999995</v>
+        <v>1.9461999999999999</v>
       </c>
       <c r="U31" s="7">
-        <v>697.14430000000004</v>
+        <v>1.9322999999999999</v>
       </c>
       <c r="V31" s="7">
-        <v>714.52409999999998</v>
+        <v>1.9685999999999999</v>
       </c>
       <c r="W31" s="7">
-        <v>713.06240000000003</v>
+        <v>1.9550000000000001</v>
       </c>
       <c r="X31" s="7">
-        <v>715.01620000000003</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="15"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="17"/>
       <c r="K34" s="1" t="s">
         <v>25</v>
       </c>
@@ -33666,7 +33612,7 @@
       </c>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="12"/>
+      <c r="B35" s="14"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -33719,27 +33665,27 @@
       </c>
       <c r="C36" s="7">
         <f t="shared" ref="C36:C41" si="0">IF(COUNTBLANK(C6:L6)&gt;0,"undone",TRIMMEAN(C6:L6,2/COUNT(C6:L6)))</f>
-        <v>6.9874999999999989E-3</v>
+        <v>7.0875000000000009E-3</v>
       </c>
       <c r="D36" s="7">
         <f t="shared" ref="D36:D41" si="1">IF(COUNTBLANK(O6:X6)&gt;0,"undone",TRIMMEAN(O6:X6,2/COUNT(O6:X6)))</f>
-        <v>0.17252500000000001</v>
+        <v>0.17197499999999999</v>
       </c>
       <c r="E36" s="7">
         <f t="shared" ref="E36:E41" si="2">IF(COUNTBLANK(C16:L16)&gt;0,"undone",TRIMMEAN(C16:L16,2/COUNT(C16:L16)))</f>
-        <v>0.68552499999999994</v>
+        <v>0.68328750000000005</v>
       </c>
       <c r="F36" s="7">
         <f t="shared" ref="F36:F41" si="3">IF(COUNTBLANK(O16:X16)&gt;0,"undone",TRIMMEAN(O16:X16,2/COUNT(O16:X16)))</f>
-        <v>16.905687500000003</v>
+        <v>16.931525000000001</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" ref="G36:G41" si="4">IF(COUNTBLANK(C26:L26)&gt;0,"undone",TRIMMEAN(C26:L26,2/COUNT(C26:L26)))</f>
-        <v>67.898949999999999</v>
+        <v>67.847662499999998</v>
       </c>
       <c r="H36" s="7">
         <f t="shared" ref="H36:H41" si="5">IF(COUNTBLANK(O26:X26)&gt;0,"undone",TRIMMEAN(O26:X26,2/COUNT(O26:X26)))</f>
-        <v>1699.54865</v>
+        <v>1702.9779874999999</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>26</v>
@@ -33779,23 +33725,23 @@
       </c>
       <c r="D37" s="7">
         <f t="shared" si="1"/>
-        <v>0.12428749999999998</v>
+        <v>0.12125</v>
       </c>
       <c r="E37" s="7">
         <f t="shared" si="2"/>
-        <v>0.47798750000000001</v>
+        <v>0.50707499999999994</v>
       </c>
       <c r="F37" s="7">
         <f t="shared" si="3"/>
-        <v>11.9602</v>
+        <v>12.1383375</v>
       </c>
       <c r="G37" s="7">
         <f t="shared" si="4"/>
-        <v>48.382975000000002</v>
+        <v>48.517387499999998</v>
       </c>
       <c r="H37" s="7">
         <f t="shared" si="5"/>
-        <v>1211.3593874999999</v>
+        <v>1213.9240124999999</v>
       </c>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
@@ -33804,27 +33750,27 @@
       </c>
       <c r="C38" s="7">
         <f t="shared" si="0"/>
-        <v>1.0874999999999999E-2</v>
+        <v>1.1375E-2</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="1"/>
-        <v>0.25931249999999995</v>
+        <v>0.26517499999999999</v>
       </c>
       <c r="E38" s="7">
         <f t="shared" si="2"/>
-        <v>1.0002499999999999</v>
+        <v>1.0350250000000001</v>
       </c>
       <c r="F38" s="7">
         <f t="shared" si="3"/>
-        <v>25.497987499999997</v>
+        <v>25.831062500000002</v>
       </c>
       <c r="G38" s="7">
         <f t="shared" si="4"/>
-        <v>101.96351250000001</v>
+        <v>102.25823750000001</v>
       </c>
       <c r="H38" s="7">
         <f t="shared" si="5"/>
-        <v>2558.8650750000002</v>
+        <v>2566.876675</v>
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
@@ -33833,27 +33779,27 @@
       </c>
       <c r="C39" s="7">
         <f t="shared" si="0"/>
-        <v>2.7250000000000004E-3</v>
+        <v>2.7875E-3</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="1"/>
-        <v>1.685E-2</v>
+        <v>1.6812499999999998E-2</v>
       </c>
       <c r="E39" s="7">
         <f t="shared" si="2"/>
-        <v>3.5125000000000003E-2</v>
+        <v>4.1299999999999989E-2</v>
       </c>
       <c r="F39" s="7">
         <f t="shared" si="3"/>
-        <v>0.21203749999999999</v>
+        <v>0.20830000000000001</v>
       </c>
       <c r="G39" s="7">
         <f t="shared" si="4"/>
-        <v>0.44373750000000001</v>
+        <v>0.45038750000000005</v>
       </c>
       <c r="H39" s="7">
         <f t="shared" si="5"/>
-        <v>2.5085625</v>
+        <v>2.54515</v>
       </c>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
@@ -33862,27 +33808,27 @@
       </c>
       <c r="C40" s="7">
         <f t="shared" si="0"/>
-        <v>4.0750000000000005E-3</v>
+        <v>4.1749999999999999E-3</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="1"/>
-        <v>0.10169999999999998</v>
+        <v>9.3112500000000001E-2</v>
       </c>
       <c r="E40" s="7">
         <f t="shared" si="2"/>
-        <v>0.38579999999999998</v>
+        <v>0.37921249999999995</v>
       </c>
       <c r="F40" s="7">
         <f t="shared" si="3"/>
-        <v>9.5796749999999999</v>
+        <v>9.6247250000000015</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="4"/>
-        <v>37.982999999999997</v>
+        <v>37.946875000000006</v>
       </c>
       <c r="H40" s="7">
         <f t="shared" si="5"/>
-        <v>941.21522500000003</v>
+        <v>942.89426249999997</v>
       </c>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
@@ -33891,27 +33837,27 @@
       </c>
       <c r="C41" s="7">
         <f t="shared" si="0"/>
-        <v>2.6749999999999994E-3</v>
+        <v>2.7125000000000005E-3</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="1"/>
-        <v>1.3599999999999999E-2</v>
+        <v>1.5162500000000001E-2</v>
       </c>
       <c r="E41" s="7">
         <f t="shared" si="2"/>
-        <v>2.8712500000000002E-2</v>
+        <v>3.0974999999999999E-2</v>
       </c>
       <c r="F41" s="7">
         <f t="shared" si="3"/>
-        <v>2.1148750000000001</v>
+        <v>0.15201250000000002</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="4"/>
-        <v>18.998987500000002</v>
+        <v>0.36193750000000002</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="5"/>
-        <v>706.74744999999996</v>
+        <v>1.9822499999999998</v>
       </c>
     </row>
     <row r="44" spans="2:17" ht="27.6" x14ac:dyDescent="0.25">
@@ -33924,11 +33870,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -33939,6 +33880,11 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data collecting.xlsx
+++ b/data collecting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phure\เอกสาร\GitHub\c-sorting-algorithm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BD2835-3152-4496-8075-BE1779657C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280E8795-C449-4911-9272-6FED896CBA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
   </bookViews>
@@ -20,9 +20,6 @@
     <sheet name="Rev-Sorted" sheetId="3" r:id="rId5"/>
     <sheet name="rev_sorted_grpah " sheetId="13" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -304,22 +301,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -27823,50 +27820,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Random"/>
-      <sheetName val="random_grpah"/>
-      <sheetName val="Sorted"/>
-      <sheetName val="sorted_grpah "/>
-      <sheetName val="Rev-Sorted"/>
-      <sheetName val="rev_sorted_grpah "/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1">
-        <row r="35">
-          <cell r="C35">
-            <v>100</v>
-          </cell>
-          <cell r="D35">
-            <v>500</v>
-          </cell>
-          <cell r="E35">
-            <v>1000</v>
-          </cell>
-          <cell r="F35">
-            <v>5000</v>
-          </cell>
-          <cell r="G35">
-            <v>10000</v>
-          </cell>
-          <cell r="H35">
-            <v>50000</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีมของ Office">
   <a:themeElements>
@@ -28188,11 +28141,11 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="1"/>
-    <col min="2" max="2" width="20.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="7" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="13" width="8.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.5" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.5" style="1" bestFit="1" customWidth="1"/>
@@ -28201,10 +28154,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
+      <c r="B1" s="17"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -28223,39 +28176,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="17"/>
-      <c r="N4" s="13" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="15"/>
+      <c r="N4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="17"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="15"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="14"/>
+      <c r="B5" s="12"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -28286,7 +28239,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="14"/>
+      <c r="N5" s="12"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -28743,39 +28696,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="17"/>
-      <c r="N14" s="13" t="s">
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="15"/>
+      <c r="N14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="18" t="s">
+      <c r="O14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="17"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="15"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="14"/>
+      <c r="B15" s="12"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -28806,7 +28759,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="14"/>
+      <c r="N15" s="12"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -29263,39 +29216,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="17"/>
-      <c r="N24" s="13" t="s">
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="15"/>
+      <c r="N24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="18" t="s">
+      <c r="O24" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="17"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="15"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="14"/>
+      <c r="B25" s="12"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -29326,7 +29279,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="14"/>
+      <c r="N25" s="12"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -29767,47 +29720,41 @@
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="17"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="15"/>
       <c r="K34" s="1" t="s">
         <v>25</v>
       </c>
       <c r="L34" s="1">
-        <f>[1]Sorted!C35</f>
         <v>100</v>
       </c>
       <c r="M34" s="1">
-        <f>[1]Sorted!D35</f>
         <v>500</v>
       </c>
       <c r="N34" s="1">
-        <f>[1]Sorted!E35</f>
         <v>1000</v>
       </c>
       <c r="O34" s="1">
-        <f>[1]Sorted!F35</f>
         <v>5000</v>
       </c>
       <c r="P34" s="1">
-        <f>[1]Sorted!G35</f>
         <v>10000</v>
       </c>
       <c r="Q34" s="1">
-        <f>[1]Sorted!H35</f>
         <v>50000</v>
       </c>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="14"/>
+      <c r="B35" s="12"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -29830,27 +29777,21 @@
         <v>27</v>
       </c>
       <c r="L35" s="1">
-        <f>[1]Sorted!C35^2</f>
         <v>10000</v>
       </c>
       <c r="M35" s="1">
-        <f>[1]Sorted!D35^2</f>
         <v>250000</v>
       </c>
       <c r="N35" s="1">
-        <f>[1]Sorted!E35^2</f>
         <v>1000000</v>
       </c>
       <c r="O35" s="1">
-        <f>[1]Sorted!F35^2</f>
         <v>25000000</v>
       </c>
       <c r="P35" s="1">
-        <f>[1]Sorted!G35^2</f>
         <v>100000000</v>
       </c>
       <c r="Q35" s="1">
-        <f>[1]Sorted!H35^2</f>
         <v>2500000000</v>
       </c>
     </row>
@@ -29886,27 +29827,21 @@
         <v>26</v>
       </c>
       <c r="L36" s="1">
-        <f>[1]Sorted!C35*LOG([1]Sorted!C35)</f>
         <v>200</v>
       </c>
       <c r="M36" s="1">
-        <f>[1]Sorted!D35*LOG([1]Sorted!D35)</f>
         <v>1349.4850021680095</v>
       </c>
       <c r="N36" s="1">
-        <f>[1]Sorted!E35*LOG([1]Sorted!E35)</f>
         <v>3000</v>
       </c>
       <c r="O36" s="1">
-        <f>[1]Sorted!F35*LOG([1]Sorted!F35)</f>
         <v>18494.850021680093</v>
       </c>
       <c r="P36" s="1">
-        <f>[1]Sorted!G35*LOG([1]Sorted!G35)</f>
         <v>40000</v>
       </c>
       <c r="Q36" s="1">
-        <f>[1]Sorted!H35*LOG([1]Sorted!H35)</f>
         <v>234948.50021680092</v>
       </c>
     </row>
@@ -30105,10 +30040,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="12"/>
+      <c r="B1" s="17"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -30127,39 +30062,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="17"/>
-      <c r="N4" s="13" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="15"/>
+      <c r="N4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="17"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="15"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="14"/>
+      <c r="B5" s="12"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -30190,7 +30125,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="14"/>
+      <c r="N5" s="12"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -30647,39 +30582,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="17"/>
-      <c r="N14" s="13" t="s">
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="15"/>
+      <c r="N14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="18" t="s">
+      <c r="O14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="17"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="15"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="14"/>
+      <c r="B15" s="12"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -30710,7 +30645,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="14"/>
+      <c r="N15" s="12"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -31167,39 +31102,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="17"/>
-      <c r="N24" s="13" t="s">
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="15"/>
+      <c r="N24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="18" t="s">
+      <c r="O24" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="17"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="15"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="14"/>
+      <c r="B25" s="12"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -31230,7 +31165,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="14"/>
+      <c r="N25" s="12"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -31671,47 +31606,41 @@
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="17"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="15"/>
       <c r="K34" s="1" t="s">
         <v>25</v>
       </c>
       <c r="L34" s="1">
-        <f>[1]Sorted!C35</f>
         <v>100</v>
       </c>
       <c r="M34" s="1">
-        <f>[1]Sorted!D35</f>
         <v>500</v>
       </c>
       <c r="N34" s="1">
-        <f>[1]Sorted!E35</f>
         <v>1000</v>
       </c>
       <c r="O34" s="1">
-        <f>[1]Sorted!F35</f>
         <v>5000</v>
       </c>
       <c r="P34" s="1">
-        <f>[1]Sorted!G35</f>
         <v>10000</v>
       </c>
       <c r="Q34" s="1">
-        <f>[1]Sorted!H35</f>
         <v>50000</v>
       </c>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="14"/>
+      <c r="B35" s="12"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -31734,27 +31663,21 @@
         <v>27</v>
       </c>
       <c r="L35" s="1">
-        <f>[1]Sorted!C35^2</f>
         <v>10000</v>
       </c>
       <c r="M35" s="1">
-        <f>[1]Sorted!D35^2</f>
         <v>250000</v>
       </c>
       <c r="N35" s="1">
-        <f>[1]Sorted!E35^2</f>
         <v>1000000</v>
       </c>
       <c r="O35" s="1">
-        <f>[1]Sorted!F35^2</f>
         <v>25000000</v>
       </c>
       <c r="P35" s="1">
-        <f>[1]Sorted!G35^2</f>
         <v>100000000</v>
       </c>
       <c r="Q35" s="1">
-        <f>[1]Sorted!H35^2</f>
         <v>2500000000</v>
       </c>
     </row>
@@ -31790,27 +31713,21 @@
         <v>26</v>
       </c>
       <c r="L36" s="1">
-        <f>[1]Sorted!C35*LOG([1]Sorted!C35)</f>
         <v>200</v>
       </c>
       <c r="M36" s="1">
-        <f>[1]Sorted!D35*LOG([1]Sorted!D35)</f>
         <v>1349.4850021680095</v>
       </c>
       <c r="N36" s="1">
-        <f>[1]Sorted!E35*LOG([1]Sorted!E35)</f>
         <v>3000</v>
       </c>
       <c r="O36" s="1">
-        <f>[1]Sorted!F35*LOG([1]Sorted!F35)</f>
         <v>18494.850021680093</v>
       </c>
       <c r="P36" s="1">
-        <f>[1]Sorted!G35*LOG([1]Sorted!G35)</f>
         <v>40000</v>
       </c>
       <c r="Q36" s="1">
-        <f>[1]Sorted!H35*LOG([1]Sorted!H35)</f>
         <v>234948.50021680092</v>
       </c>
     </row>
@@ -31969,6 +31886,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -31979,11 +31901,6 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -32006,10 +31923,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="12"/>
+      <c r="B1" s="17"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -32028,39 +31945,39 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="17"/>
-      <c r="N4" s="13" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="15"/>
+      <c r="N4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="17"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="15"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="14"/>
+      <c r="B5" s="12"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -32091,7 +32008,7 @@
       <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="14"/>
+      <c r="N5" s="12"/>
       <c r="O5" s="5" t="s">
         <v>2</v>
       </c>
@@ -32548,39 +32465,39 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="17"/>
-      <c r="N14" s="13" t="s">
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="15"/>
+      <c r="N14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="18" t="s">
+      <c r="O14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="17"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="15"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" s="14"/>
+      <c r="B15" s="12"/>
       <c r="C15" s="5" t="s">
         <v>2</v>
       </c>
@@ -32611,7 +32528,7 @@
       <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="14"/>
+      <c r="N15" s="12"/>
       <c r="O15" s="5" t="s">
         <v>2</v>
       </c>
@@ -33068,39 +32985,39 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="17"/>
-      <c r="N24" s="13" t="s">
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="15"/>
+      <c r="N24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="18" t="s">
+      <c r="O24" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="17"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="15"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" s="14"/>
+      <c r="B25" s="12"/>
       <c r="C25" s="5" t="s">
         <v>2</v>
       </c>
@@ -33131,7 +33048,7 @@
       <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N25" s="14"/>
+      <c r="N25" s="12"/>
       <c r="O25" s="5" t="s">
         <v>2</v>
       </c>
@@ -33572,47 +33489,41 @@
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="17"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="15"/>
       <c r="K34" s="1" t="s">
         <v>25</v>
       </c>
       <c r="L34" s="1">
-        <f>[1]Sorted!C35</f>
         <v>100</v>
       </c>
       <c r="M34" s="1">
-        <f>[1]Sorted!D35</f>
         <v>500</v>
       </c>
       <c r="N34" s="1">
-        <f>[1]Sorted!E35</f>
         <v>1000</v>
       </c>
       <c r="O34" s="1">
-        <f>[1]Sorted!F35</f>
         <v>5000</v>
       </c>
       <c r="P34" s="1">
-        <f>[1]Sorted!G35</f>
         <v>10000</v>
       </c>
       <c r="Q34" s="1">
-        <f>[1]Sorted!H35</f>
         <v>50000</v>
       </c>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="14"/>
+      <c r="B35" s="12"/>
       <c r="C35" s="2">
         <v>100</v>
       </c>
@@ -33635,27 +33546,21 @@
         <v>27</v>
       </c>
       <c r="L35" s="1">
-        <f>[1]Sorted!C35^2</f>
         <v>10000</v>
       </c>
       <c r="M35" s="1">
-        <f>[1]Sorted!D35^2</f>
         <v>250000</v>
       </c>
       <c r="N35" s="1">
-        <f>[1]Sorted!E35^2</f>
         <v>1000000</v>
       </c>
       <c r="O35" s="1">
-        <f>[1]Sorted!F35^2</f>
         <v>25000000</v>
       </c>
       <c r="P35" s="1">
-        <f>[1]Sorted!G35^2</f>
         <v>100000000</v>
       </c>
       <c r="Q35" s="1">
-        <f>[1]Sorted!H35^2</f>
         <v>2500000000</v>
       </c>
     </row>
@@ -33691,27 +33596,21 @@
         <v>26</v>
       </c>
       <c r="L36" s="1">
-        <f>[1]Sorted!C35*LOG([1]Sorted!C35)</f>
         <v>200</v>
       </c>
       <c r="M36" s="1">
-        <f>[1]Sorted!D35*LOG([1]Sorted!D35)</f>
         <v>1349.4850021680095</v>
       </c>
       <c r="N36" s="1">
-        <f>[1]Sorted!E35*LOG([1]Sorted!E35)</f>
         <v>3000</v>
       </c>
       <c r="O36" s="1">
-        <f>[1]Sorted!F35*LOG([1]Sorted!F35)</f>
         <v>18494.850021680093</v>
       </c>
       <c r="P36" s="1">
-        <f>[1]Sorted!G35*LOG([1]Sorted!G35)</f>
         <v>40000</v>
       </c>
       <c r="Q36" s="1">
-        <f>[1]Sorted!H35*LOG([1]Sorted!H35)</f>
         <v>234948.50021680092</v>
       </c>
     </row>
@@ -33870,6 +33769,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -33880,11 +33784,6 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data collecting.xlsx
+++ b/data collecting.xlsx
@@ -31886,11 +31886,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -31901,6 +31896,11 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -33769,11 +33769,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -33784,6 +33779,11 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data collecting.xlsx
+++ b/data collecting.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280E8795-C449-4911-9272-6FED896CBA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
   </bookViews>
   <sheets>
     <sheet name="Random" sheetId="1" r:id="rId1"/>
@@ -31886,6 +31886,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -31896,11 +31901,6 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -33769,6 +33769,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -33779,11 +33784,6 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data collecting.xlsx
+++ b/data collecting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phure\เอกสาร\GitHub\c-sorting-algorithm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280E8795-C449-4911-9272-6FED896CBA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2BEA8A-73BA-4406-858C-BC6468555658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
   </bookViews>
   <sheets>
     <sheet name="Random" sheetId="1" r:id="rId1"/>
@@ -305,18 +305,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -467,22 +467,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -580,22 +580,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1130,22 +1130,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1243,22 +1243,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1793,22 +1793,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1906,22 +1906,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2456,22 +2456,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2569,22 +2569,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3119,22 +3119,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3232,22 +3232,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3822,22 +3822,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3913,22 +3913,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4008,22 +4008,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4099,22 +4099,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4192,22 +4192,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4282,22 +4282,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4351,7 +4351,7 @@
         <c:axId val="684990623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="50000"/>
+          <c:max val="200000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -4463,7 +4463,6 @@
         <c:crossAx val="685575535"/>
         <c:crossesAt val="1.0000000000000002E-3"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="5000"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="685575535"/>
@@ -4560,7 +4559,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -4801,22 +4800,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4914,22 +4913,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5464,22 +5463,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5577,22 +5576,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6127,22 +6126,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6240,22 +6239,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6790,22 +6789,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6903,22 +6902,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7453,22 +7452,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7566,22 +7565,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8116,22 +8115,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8229,22 +8228,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8771,22 +8770,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8884,22 +8883,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9461,22 +9460,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9552,22 +9551,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9647,22 +9646,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9738,22 +9737,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9831,22 +9830,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9921,22 +9920,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9990,7 +9989,7 @@
         <c:axId val="684990623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="50000"/>
+          <c:max val="200000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -10102,7 +10101,6 @@
         <c:crossAx val="685575535"/>
         <c:crossesAt val="1.0000000000000002E-3"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="5000"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="685575535"/>
@@ -10199,7 +10197,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -10440,22 +10438,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10553,22 +10551,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11103,22 +11101,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11216,22 +11214,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11766,22 +11764,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11879,22 +11877,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12429,22 +12427,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12542,22 +12540,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13148,22 +13146,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13239,22 +13237,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13334,22 +13332,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13425,22 +13423,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13518,22 +13516,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13608,22 +13606,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13677,7 +13675,7 @@
         <c:axId val="684990623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="50000"/>
+          <c:max val="200000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -13797,7 +13795,6 @@
         <c:crossAx val="685575535"/>
         <c:crossesAt val="1.0000000000000002E-3"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="5000"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="685575535"/>
@@ -13894,7 +13891,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
@@ -14135,22 +14132,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14248,22 +14245,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14790,22 +14787,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14903,22 +14900,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50000</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -28154,10 +28151,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -28165,21 +28162,21 @@
       </c>
       <c r="C3" s="1">
         <f>C35</f>
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="O3" s="1">
         <f>D35</f>
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="14"/>
@@ -28194,7 +28191,7 @@
       <c r="N4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="16" t="s">
         <v>15</v>
       </c>
       <c r="P4" s="14"/>
@@ -28685,21 +28682,21 @@
       </c>
       <c r="C13" s="1">
         <f>E35</f>
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="N13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="O13" s="1">
         <f>F35</f>
-        <v>5000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="14"/>
@@ -28714,7 +28711,7 @@
       <c r="N14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="O14" s="16" t="s">
         <v>15</v>
       </c>
       <c r="P14" s="14"/>
@@ -29205,21 +29202,21 @@
       </c>
       <c r="C23" s="1">
         <f>G35</f>
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="N23" s="4" t="s">
         <v>12</v>
       </c>
       <c r="O23" s="1">
         <f>H35</f>
-        <v>50000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="14"/>
@@ -29234,7 +29231,7 @@
       <c r="N24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="13" t="s">
+      <c r="O24" s="16" t="s">
         <v>15</v>
       </c>
       <c r="P24" s="14"/>
@@ -29723,7 +29720,7 @@
       <c r="B34" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="13" t="s">
         <v>22</v>
       </c>
       <c r="D34" s="14"/>
@@ -29756,22 +29753,22 @@
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="12"/>
       <c r="C35" s="2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D35" s="2">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="E35" s="2">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="F35" s="2">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="G35" s="2">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="H35" s="2">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>27</v>
@@ -30040,10 +30037,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -30051,21 +30048,21 @@
       </c>
       <c r="C3" s="1">
         <f>C35</f>
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="O3" s="1">
         <f>D35</f>
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="14"/>
@@ -30080,7 +30077,7 @@
       <c r="N4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="16" t="s">
         <v>15</v>
       </c>
       <c r="P4" s="14"/>
@@ -30571,21 +30568,21 @@
       </c>
       <c r="C13" s="1">
         <f>E35</f>
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="N13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="O13" s="1">
         <f>F35</f>
-        <v>5000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="14"/>
@@ -30600,7 +30597,7 @@
       <c r="N14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="O14" s="16" t="s">
         <v>15</v>
       </c>
       <c r="P14" s="14"/>
@@ -31091,21 +31088,21 @@
       </c>
       <c r="C23" s="1">
         <f>G35</f>
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="N23" s="4" t="s">
         <v>12</v>
       </c>
       <c r="O23" s="1">
         <f>H35</f>
-        <v>50000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="14"/>
@@ -31120,7 +31117,7 @@
       <c r="N24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="13" t="s">
+      <c r="O24" s="16" t="s">
         <v>15</v>
       </c>
       <c r="P24" s="14"/>
@@ -31609,7 +31606,7 @@
       <c r="B34" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="13" t="s">
         <v>22</v>
       </c>
       <c r="D34" s="14"/>
@@ -31642,22 +31639,22 @@
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="12"/>
       <c r="C35" s="2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D35" s="2">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="E35" s="2">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="F35" s="2">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="G35" s="2">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="H35" s="2">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>27</v>
@@ -31886,11 +31883,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -31901,6 +31893,11 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -31923,10 +31920,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -31934,21 +31931,21 @@
       </c>
       <c r="C3" s="1">
         <f>C35</f>
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="O3" s="1">
         <f>D35</f>
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="14"/>
@@ -31963,7 +31960,7 @@
       <c r="N4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="16" t="s">
         <v>15</v>
       </c>
       <c r="P4" s="14"/>
@@ -32454,21 +32451,21 @@
       </c>
       <c r="C13" s="1">
         <f>E35</f>
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="N13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="O13" s="1">
         <f>F35</f>
-        <v>5000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="14"/>
@@ -32483,7 +32480,7 @@
       <c r="N14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="O14" s="16" t="s">
         <v>15</v>
       </c>
       <c r="P14" s="14"/>
@@ -32974,21 +32971,21 @@
       </c>
       <c r="C23" s="1">
         <f>G35</f>
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="N23" s="4" t="s">
         <v>12</v>
       </c>
       <c r="O23" s="1">
         <f>H35</f>
-        <v>50000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="14"/>
@@ -33003,7 +33000,7 @@
       <c r="N24" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="13" t="s">
+      <c r="O24" s="16" t="s">
         <v>15</v>
       </c>
       <c r="P24" s="14"/>
@@ -33492,7 +33489,7 @@
       <c r="B34" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="13" t="s">
         <v>22</v>
       </c>
       <c r="D34" s="14"/>
@@ -33525,22 +33522,22 @@
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="12"/>
       <c r="C35" s="2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D35" s="2">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="E35" s="2">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="F35" s="2">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="G35" s="2">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="H35" s="2">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>27</v>
@@ -33769,11 +33766,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="N24:N25"/>
     <mergeCell ref="O24:X24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B4:B5"/>
@@ -33784,6 +33776,11 @@
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:X14"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="N24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data collecting.xlsx
+++ b/data collecting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phure\เอกสาร\GitHub\c-sorting-algorithm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782A1B63-05B9-42D3-9BD3-1852764ACD01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD50C0CB-11DA-4DE5-A097-A79AE8B5994A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{D32EC7AF-07E4-482F-A8FA-A097486C4469}"/>
   </bookViews>
   <sheets>
     <sheet name="Random" sheetId="1" r:id="rId1"/>
@@ -27141,13 +27141,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>605702</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>174472</xdr:rowOff>
+      <xdr:rowOff>174471</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>248202</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>107401</xdr:rowOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>58271</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -27159,7 +27159,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks noChangeAspect="1"/>
+          <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -27445,13 +27445,13 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>174028</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>131203</xdr:rowOff>
+      <xdr:rowOff>131202</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>784096</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>149647</xdr:rowOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>108423</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -27463,7 +27463,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks noChangeAspect="1"/>
+          <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
